--- a/RSI_2026_Schedule.xlsx
+++ b/RSI_2026_Schedule.xlsx
@@ -794,7 +794,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Characterizing Myo15-Cre Recombination in Cochlear Hair Cells to Validate Disease Models for Usher Syndrome Type 1F Gene Therapy​</t>
+          <t>Characterizing Myo15-Cre Recombination in Cochlear Hair Cells to Validate Disease Models for Usher Syndrome Type 1F Gene Therapy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>(Title TBD)</t>
+          <t>Interactions of lipid droplets and Them1-containing condensates to regulate metabolism</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>(Title TBD)</t>
+          <t>Hybrid controls strategy for Automatic Laser Beam Alignment</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>(Title TBD)</t>
+          <t>Critical Groups of Signed Subdivided Wheels</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">

--- a/RSI_2026_Schedule.xlsx
+++ b/RSI_2026_Schedule.xlsx
@@ -4914,7 +4914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4956,7 +4956,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Morning Session</t>
+          <t>Block T1 (9:00 AM – 10:30 AM)</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Anushka Tonapi</t>
+          <t>Mira Cakmak</t>
         </is>
       </c>
       <c r="C9" s="11">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>Riya Mehrotra</t>
+          <t>Mahi Kohli</t>
         </is>
       </c>
       <c r="G9" s="11">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="J9" s="10" t="inlineStr">
         <is>
-          <t>Yernar Doskhan</t>
+          <t>Michael Luo</t>
         </is>
       </c>
       <c r="K9" s="11">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Grisham Paimagam</t>
+          <t>Zephyr Larson</t>
         </is>
       </c>
       <c r="C10" s="11">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>Tara Saini</t>
+          <t>Alejandra Stephanie Perry</t>
         </is>
       </c>
       <c r="G10" s="11">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="J10" s="10" t="inlineStr">
         <is>
-          <t>Cooper Ho</t>
+          <t>Sirius Sun</t>
         </is>
       </c>
       <c r="K10" s="11">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Katrina Liu</t>
+          <t>Riya Mehrotra</t>
         </is>
       </c>
       <c r="C11" s="11">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>Xindi Luo</t>
+          <t>Ferris Li</t>
         </is>
       </c>
       <c r="G11" s="11">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
-          <t>Lillie Lin Li</t>
+          <t>Anushka Tonapi</t>
         </is>
       </c>
       <c r="K11" s="11">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Lincoln Liu</t>
+          <t>Tara Saini</t>
         </is>
       </c>
       <c r="C12" s="11">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>Asher Wang</t>
+          <t>Lincoln Liu</t>
         </is>
       </c>
       <c r="G12" s="11">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="J12" s="10" t="inlineStr">
         <is>
-          <t>Eason Turner</t>
+          <t>Grisham Paimagam</t>
         </is>
       </c>
       <c r="K12" s="11">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Tony Lu</t>
+          <t>Xindi Luo</t>
         </is>
       </c>
       <c r="C13" s="11">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>Azaria Tsegaye</t>
+          <t>Tony Lu</t>
         </is>
       </c>
       <c r="G13" s="11">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>Kai Xuen Toh</t>
+          <t>Benson Hsueh</t>
         </is>
       </c>
       <c r="K13" s="11">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Michael Luo</t>
+          <t>Kai Xuen Toh</t>
         </is>
       </c>
       <c r="C14" s="11">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>Dhruv Jain</t>
+          <t>Siddhi Kochar</t>
         </is>
       </c>
       <c r="G14" s="11">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="J14" s="10" t="inlineStr">
         <is>
-          <t>Siddhi Kochar</t>
+          <t>Matey Minev</t>
         </is>
       </c>
       <c r="K14" s="11">
@@ -5393,324 +5393,344 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>10:36 AM – 10:52 AM</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>Sirius Sun</t>
-        </is>
-      </c>
-      <c r="C15" s="11">
-        <f>IFERROR(VLOOKUP($B15,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="D15" s="11">
-        <f>IFERROR(VLOOKUP($B15,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="E15" s="11">
-        <f>IFERROR(VLOOKUP($B15,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Break (10:30 AM – 11:00 AM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Block T2 (11:00 AM – 12:30 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Room 32-124</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Room 32-141</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Room 32-155</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Mentor</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>Mentor</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t>Mentor</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>11:00 AM – 11:16 AM</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Katrina Liu</t>
+        </is>
+      </c>
+      <c r="C19" s="11">
+        <f>IFERROR(VLOOKUP($B19,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="D19" s="11">
+        <f>IFERROR(VLOOKUP($B19,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="E19" s="11">
+        <f>IFERROR(VLOOKUP($B19,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>Nikola Veselinov</t>
+        </is>
+      </c>
+      <c r="G19" s="11">
+        <f>IFERROR(VLOOKUP($F19,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="11">
+        <f>IFERROR(VLOOKUP($F19,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I19" s="11">
+        <f>IFERROR(VLOOKUP($F19,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J19" s="10" t="inlineStr">
+        <is>
+          <t>Eason Turner</t>
+        </is>
+      </c>
+      <c r="K19" s="11">
+        <f>IFERROR(VLOOKUP($J19,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="L19" s="11">
+        <f>IFERROR(VLOOKUP($J19,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="M19" s="11">
+        <f>IFERROR(VLOOKUP($J19,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>11:16 AM – 11:32 AM</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Miguel Shim</t>
+        </is>
+      </c>
+      <c r="C20" s="11">
+        <f>IFERROR(VLOOKUP($B20,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="D20" s="11">
+        <f>IFERROR(VLOOKUP($B20,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="E20" s="11">
+        <f>IFERROR(VLOOKUP($B20,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>Timothy Chen</t>
+        </is>
+      </c>
+      <c r="G20" s="11">
+        <f>IFERROR(VLOOKUP($F20,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="11">
+        <f>IFERROR(VLOOKUP($F20,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I20" s="11">
+        <f>IFERROR(VLOOKUP($F20,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
         <is>
           <t>Lluc Simon</t>
         </is>
       </c>
-      <c r="G15" s="11">
-        <f>IFERROR(VLOOKUP($F15,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="11">
-        <f>IFERROR(VLOOKUP($F15,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="I15" s="11">
-        <f>IFERROR(VLOOKUP($F15,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="J15" s="10" t="inlineStr"/>
-      <c r="K15" s="11">
-        <f>IFERROR(VLOOKUP($J15,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="L15" s="11">
-        <f>IFERROR(VLOOKUP($J15,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="M15" s="11">
-        <f>IFERROR(VLOOKUP($J15,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>10:52 AM – 11:08 AM</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>Nikola Veselinov</t>
-        </is>
-      </c>
-      <c r="C16" s="11">
-        <f>IFERROR(VLOOKUP($B16,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="D16" s="11">
-        <f>IFERROR(VLOOKUP($B16,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="E16" s="11">
-        <f>IFERROR(VLOOKUP($B16,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="K20" s="11">
+        <f>IFERROR(VLOOKUP($J20,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="L20" s="11">
+        <f>IFERROR(VLOOKUP($J20,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="M20" s="11">
+        <f>IFERROR(VLOOKUP($J20,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>11:32 AM – 11:48 AM</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Sylvia Lee</t>
+        </is>
+      </c>
+      <c r="C21" s="11">
+        <f>IFERROR(VLOOKUP($B21,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="D21" s="11">
+        <f>IFERROR(VLOOKUP($B21,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="E21" s="11">
+        <f>IFERROR(VLOOKUP($B21,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>Mustafa Bakhodirov</t>
+        </is>
+      </c>
+      <c r="G21" s="11">
+        <f>IFERROR(VLOOKUP($F21,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="11">
+        <f>IFERROR(VLOOKUP($F21,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I21" s="11">
+        <f>IFERROR(VLOOKUP($F21,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
         <is>
           <t>Mikołaj Stefaniak</t>
         </is>
       </c>
-      <c r="G16" s="11">
-        <f>IFERROR(VLOOKUP($F16,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="11">
-        <f>IFERROR(VLOOKUP($F16,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="I16" s="11">
-        <f>IFERROR(VLOOKUP($F16,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="J16" s="10" t="inlineStr"/>
-      <c r="K16" s="11">
-        <f>IFERROR(VLOOKUP($J16,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="L16" s="11">
-        <f>IFERROR(VLOOKUP($J16,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="M16" s="11">
-        <f>IFERROR(VLOOKUP($J16,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>11:08 AM – 11:24 AM</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>Timothy Chen</t>
-        </is>
-      </c>
-      <c r="C17" s="11">
-        <f>IFERROR(VLOOKUP($B17,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="D17" s="11">
-        <f>IFERROR(VLOOKUP($B17,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="E17" s="11">
-        <f>IFERROR(VLOOKUP($B17,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>Miguel Shim</t>
-        </is>
-      </c>
-      <c r="G17" s="11">
-        <f>IFERROR(VLOOKUP($F17,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="11">
-        <f>IFERROR(VLOOKUP($F17,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="I17" s="11">
-        <f>IFERROR(VLOOKUP($F17,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="J17" s="10" t="inlineStr"/>
-      <c r="K17" s="11">
-        <f>IFERROR(VLOOKUP($J17,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="L17" s="11">
-        <f>IFERROR(VLOOKUP($J17,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="M17" s="11">
-        <f>IFERROR(VLOOKUP($J17,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>11:24 AM – 11:40 AM</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr"/>
-      <c r="C18" s="11">
-        <f>IFERROR(VLOOKUP($B18,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="D18" s="11">
-        <f>IFERROR(VLOOKUP($B18,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="E18" s="11">
-        <f>IFERROR(VLOOKUP($B18,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>Sylvia Lee</t>
-        </is>
-      </c>
-      <c r="G18" s="11">
-        <f>IFERROR(VLOOKUP($F18,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="H18" s="11">
-        <f>IFERROR(VLOOKUP($F18,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="I18" s="11">
-        <f>IFERROR(VLOOKUP($F18,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="J18" s="10" t="inlineStr"/>
-      <c r="K18" s="11">
-        <f>IFERROR(VLOOKUP($J18,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="L18" s="11">
-        <f>IFERROR(VLOOKUP($J18,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="M18" s="11">
-        <f>IFERROR(VLOOKUP($J18,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>Lunch Break (12:00 PM – 1:00 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Afternoon Session</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Room 32-124</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>Room 32-141</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>Room 32-155</t>
-        </is>
+      <c r="K21" s="11">
+        <f>IFERROR(VLOOKUP($J21,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="L21" s="11">
+        <f>IFERROR(VLOOKUP($J21,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="M21" s="11">
+        <f>IFERROR(VLOOKUP($J21,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>Mentor</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>Mentor</t>
-        </is>
-      </c>
-      <c r="J22" s="8" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="K22" s="8" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="L22" s="8" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="M22" s="8" t="inlineStr">
-        <is>
-          <t>Mentor</t>
-        </is>
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>11:48 AM – 12:04 PM</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Pavan Subramani</t>
+        </is>
+      </c>
+      <c r="C22" s="11">
+        <f>IFERROR(VLOOKUP($B22,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="D22" s="11">
+        <f>IFERROR(VLOOKUP($B22,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="E22" s="11">
+        <f>IFERROR(VLOOKUP($B22,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>Asher Wang</t>
+        </is>
+      </c>
+      <c r="G22" s="11">
+        <f>IFERROR(VLOOKUP($F22,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="11">
+        <f>IFERROR(VLOOKUP($F22,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I22" s="11">
+        <f>IFERROR(VLOOKUP($F22,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>Alejandro Mayorga</t>
+        </is>
+      </c>
+      <c r="K22" s="11">
+        <f>IFERROR(VLOOKUP($J22,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="L22" s="11">
+        <f>IFERROR(VLOOKUP($J22,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="M22" s="11">
+        <f>IFERROR(VLOOKUP($J22,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>1:00 PM – 1:16 PM</t>
+          <t>12:04 PM – 12:20 PM</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Aaryan Patel</t>
+          <t>Cassidy Stocker</t>
         </is>
       </c>
       <c r="C23" s="11">
@@ -5744,7 +5764,7 @@
       </c>
       <c r="J23" s="10" t="inlineStr">
         <is>
-          <t>Annika Chadha</t>
+          <t>Eric Buehler</t>
         </is>
       </c>
       <c r="K23" s="11">
@@ -5763,12 +5783,12 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>1:16 PM – 1:32 PM</t>
+          <t>12:20 PM – 12:36 PM</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Andy Jo</t>
+          <t>Sara Mitchell</t>
         </is>
       </c>
       <c r="C24" s="11">
@@ -5802,7 +5822,7 @@
       </c>
       <c r="J24" s="10" t="inlineStr">
         <is>
-          <t>Dex Theisen</t>
+          <t>Layth Alzahrani</t>
         </is>
       </c>
       <c r="K24" s="11">
@@ -5819,242 +5839,112 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>1:32 PM – 1:48 PM</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>Jay Desai</t>
-        </is>
-      </c>
-      <c r="C25" s="11">
-        <f>IFERROR(VLOOKUP($B25,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="D25" s="11">
-        <f>IFERROR(VLOOKUP($B25,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="E25" s="11">
-        <f>IFERROR(VLOOKUP($B25,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>Sowmya Sankaran</t>
-        </is>
-      </c>
-      <c r="G25" s="11">
-        <f>IFERROR(VLOOKUP($F25,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="11">
-        <f>IFERROR(VLOOKUP($F25,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="I25" s="11">
-        <f>IFERROR(VLOOKUP($F25,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="J25" s="10" t="inlineStr">
-        <is>
-          <t>David Shi</t>
-        </is>
-      </c>
-      <c r="K25" s="11">
-        <f>IFERROR(VLOOKUP($J25,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="L25" s="11">
-        <f>IFERROR(VLOOKUP($J25,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="M25" s="11">
-        <f>IFERROR(VLOOKUP($J25,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Lunch Break (12:30 PM – 1:15 PM)</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>1:48 PM – 2:04 PM</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>Alejandro Mayorga</t>
-        </is>
-      </c>
-      <c r="C26" s="11">
-        <f>IFERROR(VLOOKUP($B26,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="D26" s="11">
-        <f>IFERROR(VLOOKUP($B26,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="E26" s="11">
-        <f>IFERROR(VLOOKUP($B26,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>Tanay Arora</t>
-        </is>
-      </c>
-      <c r="G26" s="11">
-        <f>IFERROR(VLOOKUP($F26,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="11">
-        <f>IFERROR(VLOOKUP($F26,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="I26" s="11">
-        <f>IFERROR(VLOOKUP($F26,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="J26" s="10" t="inlineStr">
-        <is>
-          <t>David Wang</t>
-        </is>
-      </c>
-      <c r="K26" s="11">
-        <f>IFERROR(VLOOKUP($J26,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="L26" s="11">
-        <f>IFERROR(VLOOKUP($J26,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="M26" s="11">
-        <f>IFERROR(VLOOKUP($J26,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Block T3 (1:15 PM – 2:45 PM)</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>2:04 PM – 2:20 PM</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>Eric Buehler</t>
-        </is>
-      </c>
-      <c r="C27" s="11">
-        <f>IFERROR(VLOOKUP($B27,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="D27" s="11">
-        <f>IFERROR(VLOOKUP($B27,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="E27" s="11">
-        <f>IFERROR(VLOOKUP($B27,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t>Daniel Guo</t>
-        </is>
-      </c>
-      <c r="G27" s="11">
-        <f>IFERROR(VLOOKUP($F27,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="11">
-        <f>IFERROR(VLOOKUP($F27,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="I27" s="11">
-        <f>IFERROR(VLOOKUP($F27,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="J27" s="10" t="inlineStr">
-        <is>
-          <t>Pavan Subramani</t>
-        </is>
-      </c>
-      <c r="K27" s="11">
-        <f>IFERROR(VLOOKUP($J27,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="L27" s="11">
-        <f>IFERROR(VLOOKUP($J27,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="M27" s="11">
-        <f>IFERROR(VLOOKUP($J27,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Room 32-124</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Room 32-141</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>Room 32-155</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>2:20 PM – 2:36 PM</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>Layth Alzahrani</t>
-        </is>
-      </c>
-      <c r="C28" s="11">
-        <f>IFERROR(VLOOKUP($B28,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="D28" s="11">
-        <f>IFERROR(VLOOKUP($B28,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="E28" s="11">
-        <f>IFERROR(VLOOKUP($B28,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>Jordan Chong</t>
-        </is>
-      </c>
-      <c r="G28" s="11">
-        <f>IFERROR(VLOOKUP($F28,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="11">
-        <f>IFERROR(VLOOKUP($F28,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="I28" s="11">
-        <f>IFERROR(VLOOKUP($F28,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="J28" s="10" t="inlineStr"/>
-      <c r="K28" s="11">
-        <f>IFERROR(VLOOKUP($J28,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="L28" s="11">
-        <f>IFERROR(VLOOKUP($J28,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="M28" s="11">
-        <f>IFERROR(VLOOKUP($J28,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>Mentor</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>Mentor</t>
+        </is>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t>Mentor</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>2:36 PM – 2:52 PM</t>
+          <t>1:15 PM – 1:31 PM</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Benson Hsueh</t>
+          <t>Atharva Tyagi</t>
         </is>
       </c>
       <c r="C29" s="11">
@@ -6071,7 +5961,7 @@
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>Logan Duran</t>
+          <t>Shrivali Gupta</t>
         </is>
       </c>
       <c r="G29" s="11">
@@ -6086,7 +5976,11 @@
         <f>IFERROR(VLOOKUP($F29,Data!$A:$D,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="J29" s="10" t="inlineStr"/>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>Rishi Pampati</t>
+        </is>
+      </c>
       <c r="K29" s="11">
         <f>IFERROR(VLOOKUP($J29,Data!$A:$D,4,FALSE),"")</f>
         <v/>
@@ -6103,12 +5997,12 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>2:52 PM – 3:08 PM</t>
+          <t>1:31 PM – 1:47 PM</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Matey Minev</t>
+          <t>Ayush Vispute</t>
         </is>
       </c>
       <c r="C30" s="11">
@@ -6125,7 +6019,7 @@
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>Mustafa Bakhodirov</t>
+          <t>Danu Kim</t>
         </is>
       </c>
       <c r="G30" s="11">
@@ -6140,7 +6034,11 @@
         <f>IFERROR(VLOOKUP($F30,Data!$A:$D,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="J30" s="10" t="inlineStr"/>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>Shaden Alharbi</t>
+        </is>
+      </c>
       <c r="K30" s="11">
         <f>IFERROR(VLOOKUP($J30,Data!$A:$D,4,FALSE),"")</f>
         <v/>
@@ -6157,12 +6055,12 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>3:08 PM – 3:24 PM</t>
+          <t>1:47 PM – 2:03 PM</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Can Nalbantoglu</t>
+          <t>Bryan Cho</t>
         </is>
       </c>
       <c r="C31" s="11">
@@ -6177,7 +6075,11 @@
         <f>IFERROR(VLOOKUP($B31,Data!$A:$D,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F31" s="10" t="inlineStr"/>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>Leonardo Bartoccini</t>
+        </is>
+      </c>
       <c r="G31" s="11">
         <f>IFERROR(VLOOKUP($F31,Data!$A:$D,4,FALSE),"")</f>
         <v/>
@@ -6190,7 +6092,11 @@
         <f>IFERROR(VLOOKUP($F31,Data!$A:$D,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="J31" s="10" t="inlineStr"/>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>Greeshma Vinoy</t>
+        </is>
+      </c>
       <c r="K31" s="11">
         <f>IFERROR(VLOOKUP($J31,Data!$A:$D,4,FALSE),"")</f>
         <v/>
@@ -6207,12 +6113,12 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>3:24 PM – 3:40 PM</t>
+          <t>2:03 PM – 2:19 PM</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Danu Kim</t>
+          <t>Claire Zhan</t>
         </is>
       </c>
       <c r="C32" s="11">
@@ -6227,7 +6133,11 @@
         <f>IFERROR(VLOOKUP($B32,Data!$A:$D,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F32" s="10" t="inlineStr"/>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>Namie Djaja</t>
+        </is>
+      </c>
       <c r="G32" s="11">
         <f>IFERROR(VLOOKUP($F32,Data!$A:$D,4,FALSE),"")</f>
         <v/>
@@ -6240,7 +6150,11 @@
         <f>IFERROR(VLOOKUP($F32,Data!$A:$D,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="J32" s="10" t="inlineStr"/>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>Sofia Passos</t>
+        </is>
+      </c>
       <c r="K32" s="11">
         <f>IFERROR(VLOOKUP($J32,Data!$A:$D,4,FALSE),"")</f>
         <v/>
@@ -6257,12 +6171,12 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>3:40 PM – 3:56 PM</t>
+          <t>2:19 PM – 2:35 PM</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Leonardo Bartoccini</t>
+          <t>Malin Janna Vega</t>
         </is>
       </c>
       <c r="C33" s="11">
@@ -6277,7 +6191,11 @@
         <f>IFERROR(VLOOKUP($B33,Data!$A:$D,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F33" s="10" t="inlineStr"/>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>Rohan Peddamallu</t>
+        </is>
+      </c>
       <c r="G33" s="11">
         <f>IFERROR(VLOOKUP($F33,Data!$A:$D,4,FALSE),"")</f>
         <v/>
@@ -6290,7 +6208,11 @@
         <f>IFERROR(VLOOKUP($F33,Data!$A:$D,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="J33" s="10" t="inlineStr"/>
+      <c r="J33" s="10" t="inlineStr">
+        <is>
+          <t>Can Nalbantoglu</t>
+        </is>
+      </c>
       <c r="K33" s="11">
         <f>IFERROR(VLOOKUP($J33,Data!$A:$D,4,FALSE),"")</f>
         <v/>
@@ -6307,12 +6229,12 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>3:56 PM – 4:12 PM</t>
+          <t>2:35 PM – 2:51 PM</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Namie Djaja</t>
+          <t>Sarah Dingli</t>
         </is>
       </c>
       <c r="C34" s="11">
@@ -6327,7 +6249,11 @@
         <f>IFERROR(VLOOKUP($B34,Data!$A:$D,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F34" s="10" t="inlineStr"/>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>Nabet El Hajjar</t>
+        </is>
+      </c>
       <c r="G34" s="11">
         <f>IFERROR(VLOOKUP($F34,Data!$A:$D,4,FALSE),"")</f>
         <v/>
@@ -6340,7 +6266,11 @@
         <f>IFERROR(VLOOKUP($F34,Data!$A:$D,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="J34" s="10" t="inlineStr"/>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>Daniel Guo</t>
+        </is>
+      </c>
       <c r="K34" s="11">
         <f>IFERROR(VLOOKUP($J34,Data!$A:$D,4,FALSE),"")</f>
         <v/>
@@ -6355,162 +6285,286 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>4:12 PM – 4:28 PM</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>Rohan Peddamallu</t>
-        </is>
-      </c>
-      <c r="C35" s="11">
-        <f>IFERROR(VLOOKUP($B35,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="D35" s="11">
-        <f>IFERROR(VLOOKUP($B35,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="E35" s="11">
-        <f>IFERROR(VLOOKUP($B35,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F35" s="10" t="inlineStr"/>
-      <c r="G35" s="11">
-        <f>IFERROR(VLOOKUP($F35,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="11">
-        <f>IFERROR(VLOOKUP($F35,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="I35" s="11">
-        <f>IFERROR(VLOOKUP($F35,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="J35" s="10" t="inlineStr"/>
-      <c r="K35" s="11">
-        <f>IFERROR(VLOOKUP($J35,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="L35" s="11">
-        <f>IFERROR(VLOOKUP($J35,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="M35" s="11">
-        <f>IFERROR(VLOOKUP($J35,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Break (2:45 PM – 3:15 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Block T4 (3:15 PM – 4:45 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Room 32-124</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>Room 32-141</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>Room 32-155</t>
+        </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>Friday, August 7, 2026</t>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>Mentor</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>Mentor</t>
+        </is>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="L38" s="8" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="M38" s="8" t="inlineStr">
+        <is>
+          <t>Mentor</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Morning Session</t>
-        </is>
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>3:15 PM – 3:31 PM</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Sophia Zhao</t>
+        </is>
+      </c>
+      <c r="C39" s="11">
+        <f>IFERROR(VLOOKUP($B39,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="D39" s="11">
+        <f>IFERROR(VLOOKUP($B39,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="11">
+        <f>IFERROR(VLOOKUP($B39,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>Mahima Lele</t>
+        </is>
+      </c>
+      <c r="G39" s="11">
+        <f>IFERROR(VLOOKUP($F39,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="11">
+        <f>IFERROR(VLOOKUP($F39,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I39" s="11">
+        <f>IFERROR(VLOOKUP($F39,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="10" t="inlineStr">
+        <is>
+          <t>Alex Ren</t>
+        </is>
+      </c>
+      <c r="K39" s="11">
+        <f>IFERROR(VLOOKUP($J39,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="L39" s="11">
+        <f>IFERROR(VLOOKUP($J39,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="M39" s="11">
+        <f>IFERROR(VLOOKUP($J39,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Room 32-124</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>Room 32-141</t>
-        </is>
-      </c>
-      <c r="J40" s="7" t="inlineStr">
-        <is>
-          <t>Room 32-155</t>
-        </is>
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>3:31 PM – 3:47 PM</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Yong Ding</t>
+        </is>
+      </c>
+      <c r="C40" s="11">
+        <f>IFERROR(VLOOKUP($B40,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="D40" s="11">
+        <f>IFERROR(VLOOKUP($B40,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="11">
+        <f>IFERROR(VLOOKUP($B40,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>Cooper Ho</t>
+        </is>
+      </c>
+      <c r="G40" s="11">
+        <f>IFERROR(VLOOKUP($F40,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="11">
+        <f>IFERROR(VLOOKUP($F40,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I40" s="11">
+        <f>IFERROR(VLOOKUP($F40,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>Amogh Dattatri</t>
+        </is>
+      </c>
+      <c r="K40" s="11">
+        <f>IFERROR(VLOOKUP($J40,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="L40" s="11">
+        <f>IFERROR(VLOOKUP($J40,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="M40" s="11">
+        <f>IFERROR(VLOOKUP($J40,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>Mentor</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="I41" s="8" t="inlineStr">
-        <is>
-          <t>Mentor</t>
-        </is>
-      </c>
-      <c r="J41" s="8" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="K41" s="8" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="L41" s="8" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="M41" s="8" t="inlineStr">
-        <is>
-          <t>Mentor</t>
-        </is>
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>3:47 PM – 4:03 PM</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>Dhruv Jain</t>
+        </is>
+      </c>
+      <c r="C41" s="11">
+        <f>IFERROR(VLOOKUP($B41,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="D41" s="11">
+        <f>IFERROR(VLOOKUP($B41,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="11">
+        <f>IFERROR(VLOOKUP($B41,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>Lillie Lin Li</t>
+        </is>
+      </c>
+      <c r="G41" s="11">
+        <f>IFERROR(VLOOKUP($F41,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="11">
+        <f>IFERROR(VLOOKUP($F41,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I41" s="11">
+        <f>IFERROR(VLOOKUP($F41,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J41" s="10" t="inlineStr">
+        <is>
+          <t>Chloe Giglio</t>
+        </is>
+      </c>
+      <c r="K41" s="11">
+        <f>IFERROR(VLOOKUP($J41,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="L41" s="11">
+        <f>IFERROR(VLOOKUP($J41,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="M41" s="11">
+        <f>IFERROR(VLOOKUP($J41,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>9:00 AM – 9:16 AM</t>
+          <t>4:03 PM – 4:19 PM</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Abigail Qi</t>
+          <t>Aaryan Patel</t>
         </is>
       </c>
       <c r="C42" s="11">
@@ -6527,7 +6581,7 @@
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>Alex Ren</t>
+          <t>Lara Otico</t>
         </is>
       </c>
       <c r="G42" s="11">
@@ -6544,7 +6598,7 @@
       </c>
       <c r="J42" s="10" t="inlineStr">
         <is>
-          <t>Cassidy Stocker</t>
+          <t>Ipek Zeynioğlu</t>
         </is>
       </c>
       <c r="K42" s="11">
@@ -6563,12 +6617,12 @@
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>9:16 AM – 9:32 AM</t>
+          <t>4:19 PM – 4:35 PM</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Luke Itomura</t>
+          <t>Andy Jo</t>
         </is>
       </c>
       <c r="C43" s="11">
@@ -6585,7 +6639,7 @@
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>Amogh Dattatri</t>
+          <t>Jordan Chong</t>
         </is>
       </c>
       <c r="G43" s="11">
@@ -6602,7 +6656,7 @@
       </c>
       <c r="J43" s="10" t="inlineStr">
         <is>
-          <t>Sara Mitchell</t>
+          <t>Tristan Sun</t>
         </is>
       </c>
       <c r="K43" s="11">
@@ -6621,12 +6675,12 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>9:32 AM – 9:48 AM</t>
+          <t>4:35 PM – 4:51 PM</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Ahmed Sultan</t>
+          <t>Jay Desai</t>
         </is>
       </c>
       <c r="C44" s="11">
@@ -6643,7 +6697,7 @@
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>Chloe Giglio</t>
+          <t>Amritha Praveen</t>
         </is>
       </c>
       <c r="G44" s="11">
@@ -6660,7 +6714,7 @@
       </c>
       <c r="J44" s="10" t="inlineStr">
         <is>
-          <t>Greeshma Vinoy</t>
+          <t>Álvaro Daniel Villafuerte González</t>
         </is>
       </c>
       <c r="K44" s="11">
@@ -6676,349 +6730,115 @@
         <v/>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="9" t="inlineStr">
-        <is>
-          <t>9:48 AM – 10:04 AM</t>
-        </is>
-      </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>Alejandra Stephanie Perry</t>
-        </is>
-      </c>
-      <c r="C45" s="11">
-        <f>IFERROR(VLOOKUP($B45,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="D45" s="11">
-        <f>IFERROR(VLOOKUP($B45,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="E45" s="11">
-        <f>IFERROR(VLOOKUP($B45,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F45" s="10" t="inlineStr">
-        <is>
-          <t>Ipek Zeynioğlu</t>
-        </is>
-      </c>
-      <c r="G45" s="11">
-        <f>IFERROR(VLOOKUP($F45,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="11">
-        <f>IFERROR(VLOOKUP($F45,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="I45" s="11">
-        <f>IFERROR(VLOOKUP($F45,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="J45" s="10" t="inlineStr">
-        <is>
-          <t>Sofia Passos</t>
-        </is>
-      </c>
-      <c r="K45" s="11">
-        <f>IFERROR(VLOOKUP($J45,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="L45" s="11">
-        <f>IFERROR(VLOOKUP($J45,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="M45" s="11">
-        <f>IFERROR(VLOOKUP($J45,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="9" t="inlineStr">
-        <is>
-          <t>10:04 AM – 10:20 AM</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="inlineStr">
-        <is>
-          <t>Ferris Li</t>
-        </is>
-      </c>
-      <c r="C46" s="11">
-        <f>IFERROR(VLOOKUP($B46,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="D46" s="11">
-        <f>IFERROR(VLOOKUP($B46,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="E46" s="11">
-        <f>IFERROR(VLOOKUP($B46,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F46" s="10" t="inlineStr">
-        <is>
-          <t>Tristan Sun</t>
-        </is>
-      </c>
-      <c r="G46" s="11">
-        <f>IFERROR(VLOOKUP($F46,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="H46" s="11">
-        <f>IFERROR(VLOOKUP($F46,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="I46" s="11">
-        <f>IFERROR(VLOOKUP($F46,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="J46" s="10" t="inlineStr">
-        <is>
-          <t>Haya Mekdash</t>
-        </is>
-      </c>
-      <c r="K46" s="11">
-        <f>IFERROR(VLOOKUP($J46,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="L46" s="11">
-        <f>IFERROR(VLOOKUP($J46,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="M46" s="11">
-        <f>IFERROR(VLOOKUP($J46,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
     <row r="47">
-      <c r="A47" s="9" t="inlineStr">
-        <is>
-          <t>10:20 AM – 10:36 AM</t>
-        </is>
-      </c>
-      <c r="B47" s="10" t="inlineStr">
-        <is>
-          <t>Mahi Kohli</t>
-        </is>
-      </c>
-      <c r="C47" s="11">
-        <f>IFERROR(VLOOKUP($B47,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="D47" s="11">
-        <f>IFERROR(VLOOKUP($B47,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="E47" s="11">
-        <f>IFERROR(VLOOKUP($B47,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F47" s="10" t="inlineStr">
-        <is>
-          <t>Álvaro Daniel Villafuerte González</t>
-        </is>
-      </c>
-      <c r="G47" s="11">
-        <f>IFERROR(VLOOKUP($F47,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="H47" s="11">
-        <f>IFERROR(VLOOKUP($F47,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="I47" s="11">
-        <f>IFERROR(VLOOKUP($F47,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="J47" s="10" t="inlineStr">
-        <is>
-          <t>Izzy Craciun</t>
-        </is>
-      </c>
-      <c r="K47" s="11">
-        <f>IFERROR(VLOOKUP($J47,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="L47" s="11">
-        <f>IFERROR(VLOOKUP($J47,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="M47" s="11">
-        <f>IFERROR(VLOOKUP($J47,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Friday, August 7, 2026</t>
+        </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="inlineStr">
-        <is>
-          <t>10:36 AM – 10:52 AM</t>
-        </is>
-      </c>
-      <c r="B48" s="10" t="inlineStr"/>
-      <c r="C48" s="11">
-        <f>IFERROR(VLOOKUP($B48,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="D48" s="11">
-        <f>IFERROR(VLOOKUP($B48,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="E48" s="11">
-        <f>IFERROR(VLOOKUP($B48,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F48" s="10" t="inlineStr">
-        <is>
-          <t>Alexis Cho</t>
-        </is>
-      </c>
-      <c r="G48" s="11">
-        <f>IFERROR(VLOOKUP($F48,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="H48" s="11">
-        <f>IFERROR(VLOOKUP($F48,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="I48" s="11">
-        <f>IFERROR(VLOOKUP($F48,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="J48" s="10" t="inlineStr">
-        <is>
-          <t>Karim Mrad</t>
-        </is>
-      </c>
-      <c r="K48" s="11">
-        <f>IFERROR(VLOOKUP($J48,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="L48" s="11">
-        <f>IFERROR(VLOOKUP($J48,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="M48" s="11">
-        <f>IFERROR(VLOOKUP($J48,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Block F1 (9:00 AM – 10:30 AM)</t>
+        </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="inlineStr">
-        <is>
-          <t>10:52 AM – 11:08 AM</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="inlineStr"/>
-      <c r="C49" s="11">
-        <f>IFERROR(VLOOKUP($B49,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="D49" s="11">
-        <f>IFERROR(VLOOKUP($B49,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="E49" s="11">
-        <f>IFERROR(VLOOKUP($B49,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F49" s="10" t="inlineStr">
-        <is>
-          <t>Hannah Thomas</t>
-        </is>
-      </c>
-      <c r="G49" s="11">
-        <f>IFERROR(VLOOKUP($F49,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="H49" s="11">
-        <f>IFERROR(VLOOKUP($F49,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="I49" s="11">
-        <f>IFERROR(VLOOKUP($F49,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="J49" s="10" t="inlineStr">
-        <is>
-          <t>Lara Otico</t>
-        </is>
-      </c>
-      <c r="K49" s="11">
-        <f>IFERROR(VLOOKUP($J49,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="L49" s="11">
-        <f>IFERROR(VLOOKUP($J49,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="M49" s="11">
-        <f>IFERROR(VLOOKUP($J49,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Room 32-124</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>Room 32-141</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>Room 32-155</t>
+        </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="inlineStr">
-        <is>
-          <t>11:08 AM – 11:24 AM</t>
-        </is>
-      </c>
-      <c r="B50" s="10" t="inlineStr"/>
-      <c r="C50" s="11">
-        <f>IFERROR(VLOOKUP($B50,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="D50" s="11">
-        <f>IFERROR(VLOOKUP($B50,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="E50" s="11">
-        <f>IFERROR(VLOOKUP($B50,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F50" s="10" t="inlineStr">
-        <is>
-          <t>Amritha Praveen</t>
-        </is>
-      </c>
-      <c r="G50" s="11">
-        <f>IFERROR(VLOOKUP($F50,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="H50" s="11">
-        <f>IFERROR(VLOOKUP($F50,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="I50" s="11">
-        <f>IFERROR(VLOOKUP($F50,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="J50" s="10" t="inlineStr">
-        <is>
-          <t>Lucia Chen</t>
-        </is>
-      </c>
-      <c r="K50" s="11">
-        <f>IFERROR(VLOOKUP($J50,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="L50" s="11">
-        <f>IFERROR(VLOOKUP($J50,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="M50" s="11">
-        <f>IFERROR(VLOOKUP($J50,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>Mentor</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>Mentor</t>
+        </is>
+      </c>
+      <c r="J50" s="8" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="K50" s="8" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="L50" s="8" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="M50" s="8" t="inlineStr">
+        <is>
+          <t>Mentor</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>11:24 AM – 11:40 AM</t>
-        </is>
-      </c>
-      <c r="B51" s="10" t="inlineStr"/>
+          <t>9:00 AM – 9:16 AM</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>Diya Gandhi</t>
+        </is>
+      </c>
       <c r="C51" s="11">
         <f>IFERROR(VLOOKUP($B51,Data!$A:$D,4,FALSE),"")</f>
         <v/>
@@ -7031,7 +6851,11 @@
         <f>IFERROR(VLOOKUP($B51,Data!$A:$D,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F51" s="10" t="inlineStr"/>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>Abigail Qi</t>
+        </is>
+      </c>
       <c r="G51" s="11">
         <f>IFERROR(VLOOKUP($F51,Data!$A:$D,4,FALSE),"")</f>
         <v/>
@@ -7044,7 +6868,11 @@
         <f>IFERROR(VLOOKUP($F51,Data!$A:$D,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="J51" s="10" t="inlineStr"/>
+      <c r="J51" s="10" t="inlineStr">
+        <is>
+          <t>Sowmya Sankaran</t>
+        </is>
+      </c>
       <c r="K51" s="11">
         <f>IFERROR(VLOOKUP($J51,Data!$A:$D,4,FALSE),"")</f>
         <v/>
@@ -7059,112 +6887,246 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="12" t="inlineStr">
-        <is>
-          <t>Lunch Break (12:00 PM – 1:00 PM)</t>
-        </is>
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>9:16 AM – 9:32 AM</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>David Shi</t>
+        </is>
+      </c>
+      <c r="C52" s="11">
+        <f>IFERROR(VLOOKUP($B52,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="D52" s="11">
+        <f>IFERROR(VLOOKUP($B52,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="E52" s="11">
+        <f>IFERROR(VLOOKUP($B52,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="F52" s="10" t="inlineStr">
+        <is>
+          <t>Luke Itomura</t>
+        </is>
+      </c>
+      <c r="G52" s="11">
+        <f>IFERROR(VLOOKUP($F52,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="H52" s="11">
+        <f>IFERROR(VLOOKUP($F52,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I52" s="11">
+        <f>IFERROR(VLOOKUP($F52,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J52" s="10" t="inlineStr">
+        <is>
+          <t>Tanay Arora</t>
+        </is>
+      </c>
+      <c r="K52" s="11">
+        <f>IFERROR(VLOOKUP($J52,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="L52" s="11">
+        <f>IFERROR(VLOOKUP($J52,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="M52" s="11">
+        <f>IFERROR(VLOOKUP($J52,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>Afternoon Session</t>
-        </is>
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>9:32 AM – 9:48 AM</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>David Wang</t>
+        </is>
+      </c>
+      <c r="C53" s="11">
+        <f>IFERROR(VLOOKUP($B53,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="D53" s="11">
+        <f>IFERROR(VLOOKUP($B53,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="E53" s="11">
+        <f>IFERROR(VLOOKUP($B53,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="F53" s="10" t="inlineStr">
+        <is>
+          <t>Alexis Cho</t>
+        </is>
+      </c>
+      <c r="G53" s="11">
+        <f>IFERROR(VLOOKUP($F53,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="H53" s="11">
+        <f>IFERROR(VLOOKUP($F53,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I53" s="11">
+        <f>IFERROR(VLOOKUP($F53,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J53" s="10" t="inlineStr">
+        <is>
+          <t>Izzy Craciun</t>
+        </is>
+      </c>
+      <c r="K53" s="11">
+        <f>IFERROR(VLOOKUP($J53,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="L53" s="11">
+        <f>IFERROR(VLOOKUP($J53,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="M53" s="11">
+        <f>IFERROR(VLOOKUP($J53,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>Room 32-124</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>Room 32-141</t>
-        </is>
-      </c>
-      <c r="J54" s="7" t="inlineStr">
-        <is>
-          <t>Room 32-155</t>
-        </is>
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>9:48 AM – 10:04 AM</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>Azaria Tsegaye</t>
+        </is>
+      </c>
+      <c r="C54" s="11">
+        <f>IFERROR(VLOOKUP($B54,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="D54" s="11">
+        <f>IFERROR(VLOOKUP($B54,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="E54" s="11">
+        <f>IFERROR(VLOOKUP($B54,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="F54" s="10" t="inlineStr">
+        <is>
+          <t>Hannah Thomas</t>
+        </is>
+      </c>
+      <c r="G54" s="11">
+        <f>IFERROR(VLOOKUP($F54,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="H54" s="11">
+        <f>IFERROR(VLOOKUP($F54,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I54" s="11">
+        <f>IFERROR(VLOOKUP($F54,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J54" s="10" t="inlineStr">
+        <is>
+          <t>Karim Mrad</t>
+        </is>
+      </c>
+      <c r="K54" s="11">
+        <f>IFERROR(VLOOKUP($J54,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="L54" s="11">
+        <f>IFERROR(VLOOKUP($J54,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="M54" s="11">
+        <f>IFERROR(VLOOKUP($J54,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C55" s="8" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t>Mentor</t>
-        </is>
-      </c>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="G55" s="8" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="H55" s="8" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="I55" s="8" t="inlineStr">
-        <is>
-          <t>Mentor</t>
-        </is>
-      </c>
-      <c r="J55" s="8" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="K55" s="8" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="L55" s="8" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="M55" s="8" t="inlineStr">
-        <is>
-          <t>Mentor</t>
-        </is>
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>10:04 AM – 10:20 AM</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>Yernar Doskhan</t>
+        </is>
+      </c>
+      <c r="C55" s="11">
+        <f>IFERROR(VLOOKUP($B55,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="D55" s="11">
+        <f>IFERROR(VLOOKUP($B55,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="E55" s="11">
+        <f>IFERROR(VLOOKUP($B55,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>Logan Duran</t>
+        </is>
+      </c>
+      <c r="G55" s="11">
+        <f>IFERROR(VLOOKUP($F55,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="H55" s="11">
+        <f>IFERROR(VLOOKUP($F55,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I55" s="11">
+        <f>IFERROR(VLOOKUP($F55,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J55" s="10" t="inlineStr">
+        <is>
+          <t>Lucia Chen</t>
+        </is>
+      </c>
+      <c r="K55" s="11">
+        <f>IFERROR(VLOOKUP($J55,Data!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="L55" s="11">
+        <f>IFERROR(VLOOKUP($J55,Data!$A:$D,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="M55" s="11">
+        <f>IFERROR(VLOOKUP($J55,Data!$A:$D,3,FALSE),"")</f>
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>1:00 PM – 1:16 PM</t>
+          <t>10:20 AM – 10:36 AM</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>Matthew Lo</t>
+          <t>Haya Mekdash</t>
         </is>
       </c>
       <c r="C56" s="11">
@@ -7181,7 +7143,7 @@
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>Karl Chu</t>
+          <t>Ahmed Sultan</t>
         </is>
       </c>
       <c r="G56" s="11">
@@ -7198,7 +7160,7 @@
       </c>
       <c r="J56" s="10" t="inlineStr">
         <is>
-          <t>Atharva Tyagi</t>
+          <t>Yoon Seo Pyo</t>
         </is>
       </c>
       <c r="K56" s="11">
@@ -7215,246 +7177,112 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="inlineStr">
-        <is>
-          <t>1:16 PM – 1:32 PM</t>
-        </is>
-      </c>
-      <c r="B57" s="10" t="inlineStr">
-        <is>
-          <t>Sarah Park</t>
-        </is>
-      </c>
-      <c r="C57" s="11">
-        <f>IFERROR(VLOOKUP($B57,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="D57" s="11">
-        <f>IFERROR(VLOOKUP($B57,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="E57" s="11">
-        <f>IFERROR(VLOOKUP($B57,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F57" s="10" t="inlineStr">
-        <is>
-          <t>Selene Manzo</t>
-        </is>
-      </c>
-      <c r="G57" s="11">
-        <f>IFERROR(VLOOKUP($F57,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="H57" s="11">
-        <f>IFERROR(VLOOKUP($F57,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="I57" s="11">
-        <f>IFERROR(VLOOKUP($F57,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="J57" s="10" t="inlineStr">
-        <is>
-          <t>Ayush Vispute</t>
-        </is>
-      </c>
-      <c r="K57" s="11">
-        <f>IFERROR(VLOOKUP($J57,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="L57" s="11">
-        <f>IFERROR(VLOOKUP($J57,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="M57" s="11">
-        <f>IFERROR(VLOOKUP($J57,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>Break (10:30 AM – 11:00 AM)</t>
+        </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="9" t="inlineStr">
-        <is>
-          <t>1:32 PM – 1:48 PM</t>
-        </is>
-      </c>
-      <c r="B58" s="10" t="inlineStr">
-        <is>
-          <t>Raquel Gomez Junco Lobo</t>
-        </is>
-      </c>
-      <c r="C58" s="11">
-        <f>IFERROR(VLOOKUP($B58,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="D58" s="11">
-        <f>IFERROR(VLOOKUP($B58,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="E58" s="11">
-        <f>IFERROR(VLOOKUP($B58,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F58" s="10" t="inlineStr">
-        <is>
-          <t>Mira Cakmak</t>
-        </is>
-      </c>
-      <c r="G58" s="11">
-        <f>IFERROR(VLOOKUP($F58,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="H58" s="11">
-        <f>IFERROR(VLOOKUP($F58,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="I58" s="11">
-        <f>IFERROR(VLOOKUP($F58,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="J58" s="10" t="inlineStr">
-        <is>
-          <t>Bryan Cho</t>
-        </is>
-      </c>
-      <c r="K58" s="11">
-        <f>IFERROR(VLOOKUP($J58,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="L58" s="11">
-        <f>IFERROR(VLOOKUP($J58,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="M58" s="11">
-        <f>IFERROR(VLOOKUP($J58,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>Block F2 (11:00 AM – 12:00 PM)</t>
+        </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="9" t="inlineStr">
-        <is>
-          <t>1:48 PM – 2:04 PM</t>
-        </is>
-      </c>
-      <c r="B59" s="10" t="inlineStr">
-        <is>
-          <t>Ruchika Ramachandran</t>
-        </is>
-      </c>
-      <c r="C59" s="11">
-        <f>IFERROR(VLOOKUP($B59,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="D59" s="11">
-        <f>IFERROR(VLOOKUP($B59,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="E59" s="11">
-        <f>IFERROR(VLOOKUP($B59,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F59" s="10" t="inlineStr">
-        <is>
-          <t>Nabet El Hajjar</t>
-        </is>
-      </c>
-      <c r="G59" s="11">
-        <f>IFERROR(VLOOKUP($F59,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="H59" s="11">
-        <f>IFERROR(VLOOKUP($F59,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="I59" s="11">
-        <f>IFERROR(VLOOKUP($F59,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="J59" s="10" t="inlineStr">
-        <is>
-          <t>Claire Zhan</t>
-        </is>
-      </c>
-      <c r="K59" s="11">
-        <f>IFERROR(VLOOKUP($J59,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="L59" s="11">
-        <f>IFERROR(VLOOKUP($J59,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="M59" s="11">
-        <f>IFERROR(VLOOKUP($J59,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Room 32-124</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>Room 32-141</t>
+        </is>
+      </c>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>Room 32-155</t>
+        </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="9" t="inlineStr">
-        <is>
-          <t>2:04 PM – 2:20 PM</t>
-        </is>
-      </c>
-      <c r="B60" s="10" t="inlineStr">
-        <is>
-          <t>Sarah Dingli</t>
-        </is>
-      </c>
-      <c r="C60" s="11">
-        <f>IFERROR(VLOOKUP($B60,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="D60" s="11">
-        <f>IFERROR(VLOOKUP($B60,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="E60" s="11">
-        <f>IFERROR(VLOOKUP($B60,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F60" s="10" t="inlineStr">
-        <is>
-          <t>Rishi Pampati</t>
-        </is>
-      </c>
-      <c r="G60" s="11">
-        <f>IFERROR(VLOOKUP($F60,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="H60" s="11">
-        <f>IFERROR(VLOOKUP($F60,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="I60" s="11">
-        <f>IFERROR(VLOOKUP($F60,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="J60" s="10" t="inlineStr">
-        <is>
-          <t>Malin Janna Vega</t>
-        </is>
-      </c>
-      <c r="K60" s="11">
-        <f>IFERROR(VLOOKUP($J60,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="L60" s="11">
-        <f>IFERROR(VLOOKUP($J60,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="M60" s="11">
-        <f>IFERROR(VLOOKUP($J60,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>Mentor</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>Mentor</t>
+        </is>
+      </c>
+      <c r="J60" s="8" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="K60" s="8" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="L60" s="8" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="M60" s="8" t="inlineStr">
+        <is>
+          <t>Mentor</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>2:20 PM – 2:36 PM</t>
+          <t>11:00 AM – 11:16 AM</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>Shaden Alharbi</t>
+          <t>Raquel Gomez Junco Lobo</t>
         </is>
       </c>
       <c r="C61" s="11">
@@ -7471,7 +7299,7 @@
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>Shrivali Gupta</t>
+          <t>Annika Chadha</t>
         </is>
       </c>
       <c r="G61" s="11">
@@ -7488,7 +7316,7 @@
       </c>
       <c r="J61" s="10" t="inlineStr">
         <is>
-          <t>Sophia Zhao</t>
+          <t>Avery Wang</t>
         </is>
       </c>
       <c r="K61" s="11">
@@ -7507,10 +7335,14 @@
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>2:36 PM – 2:52 PM</t>
-        </is>
-      </c>
-      <c r="B62" s="10" t="inlineStr"/>
+          <t>11:16 AM – 11:32 AM</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>Matthew Lo</t>
+        </is>
+      </c>
       <c r="C62" s="11">
         <f>IFERROR(VLOOKUP($B62,Data!$A:$D,4,FALSE),"")</f>
         <v/>
@@ -7525,7 +7357,7 @@
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>Yoon Seo Pyo</t>
+          <t>Dex Theisen</t>
         </is>
       </c>
       <c r="G62" s="11">
@@ -7542,7 +7374,7 @@
       </c>
       <c r="J62" s="10" t="inlineStr">
         <is>
-          <t>Yong Ding</t>
+          <t>Ngawang Namgyal</t>
         </is>
       </c>
       <c r="K62" s="11">
@@ -7561,10 +7393,14 @@
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>2:52 PM – 3:08 PM</t>
-        </is>
-      </c>
-      <c r="B63" s="10" t="inlineStr"/>
+          <t>11:32 AM – 11:48 AM</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>Sarah Park</t>
+        </is>
+      </c>
       <c r="C63" s="11">
         <f>IFERROR(VLOOKUP($B63,Data!$A:$D,4,FALSE),"")</f>
         <v/>
@@ -7577,7 +7413,11 @@
         <f>IFERROR(VLOOKUP($B63,Data!$A:$D,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F63" s="10" t="inlineStr"/>
+      <c r="F63" s="10" t="inlineStr">
+        <is>
+          <t>Karl Chu</t>
+        </is>
+      </c>
       <c r="G63" s="11">
         <f>IFERROR(VLOOKUP($F63,Data!$A:$D,4,FALSE),"")</f>
         <v/>
@@ -7590,11 +7430,7 @@
         <f>IFERROR(VLOOKUP($F63,Data!$A:$D,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="J63" s="10" t="inlineStr">
-        <is>
-          <t>Avery Wang</t>
-        </is>
-      </c>
+      <c r="J63" s="10" t="inlineStr"/>
       <c r="K63" s="11">
         <f>IFERROR(VLOOKUP($J63,Data!$A:$D,4,FALSE),"")</f>
         <v/>
@@ -7611,10 +7447,14 @@
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>3:08 PM – 3:24 PM</t>
-        </is>
-      </c>
-      <c r="B64" s="10" t="inlineStr"/>
+          <t>11:48 AM – 12:04 PM</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>Ruchika Ramachandran</t>
+        </is>
+      </c>
       <c r="C64" s="11">
         <f>IFERROR(VLOOKUP($B64,Data!$A:$D,4,FALSE),"")</f>
         <v/>
@@ -7627,7 +7467,11 @@
         <f>IFERROR(VLOOKUP($B64,Data!$A:$D,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F64" s="10" t="inlineStr"/>
+      <c r="F64" s="10" t="inlineStr">
+        <is>
+          <t>Selene Manzo</t>
+        </is>
+      </c>
       <c r="G64" s="11">
         <f>IFERROR(VLOOKUP($F64,Data!$A:$D,4,FALSE),"")</f>
         <v/>
@@ -7640,11 +7484,7 @@
         <f>IFERROR(VLOOKUP($F64,Data!$A:$D,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="J64" s="10" t="inlineStr">
-        <is>
-          <t>Ngawang Namgyal</t>
-        </is>
-      </c>
+      <c r="J64" s="10" t="inlineStr"/>
       <c r="K64" s="11">
         <f>IFERROR(VLOOKUP($J64,Data!$A:$D,4,FALSE),"")</f>
         <v/>
@@ -7658,228 +7498,42 @@
         <v/>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="9" t="inlineStr">
-        <is>
-          <t>3:24 PM – 3:40 PM</t>
-        </is>
-      </c>
-      <c r="B65" s="10" t="inlineStr"/>
-      <c r="C65" s="11">
-        <f>IFERROR(VLOOKUP($B65,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="D65" s="11">
-        <f>IFERROR(VLOOKUP($B65,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="E65" s="11">
-        <f>IFERROR(VLOOKUP($B65,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F65" s="10" t="inlineStr"/>
-      <c r="G65" s="11">
-        <f>IFERROR(VLOOKUP($F65,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="H65" s="11">
-        <f>IFERROR(VLOOKUP($F65,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="I65" s="11">
-        <f>IFERROR(VLOOKUP($F65,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="J65" s="10" t="inlineStr">
-        <is>
-          <t>Zephyr Larson</t>
-        </is>
-      </c>
-      <c r="K65" s="11">
-        <f>IFERROR(VLOOKUP($J65,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="L65" s="11">
-        <f>IFERROR(VLOOKUP($J65,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="M65" s="11">
-        <f>IFERROR(VLOOKUP($J65,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="9" t="inlineStr">
-        <is>
-          <t>3:40 PM – 3:56 PM</t>
-        </is>
-      </c>
-      <c r="B66" s="10" t="inlineStr"/>
-      <c r="C66" s="11">
-        <f>IFERROR(VLOOKUP($B66,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="D66" s="11">
-        <f>IFERROR(VLOOKUP($B66,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="E66" s="11">
-        <f>IFERROR(VLOOKUP($B66,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F66" s="10" t="inlineStr"/>
-      <c r="G66" s="11">
-        <f>IFERROR(VLOOKUP($F66,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="H66" s="11">
-        <f>IFERROR(VLOOKUP($F66,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="I66" s="11">
-        <f>IFERROR(VLOOKUP($F66,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="J66" s="10" t="inlineStr">
-        <is>
-          <t>Diya Gandhi</t>
-        </is>
-      </c>
-      <c r="K66" s="11">
-        <f>IFERROR(VLOOKUP($J66,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="L66" s="11">
-        <f>IFERROR(VLOOKUP($J66,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="M66" s="11">
-        <f>IFERROR(VLOOKUP($J66,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="9" t="inlineStr">
-        <is>
-          <t>3:56 PM – 4:12 PM</t>
-        </is>
-      </c>
-      <c r="B67" s="10" t="inlineStr"/>
-      <c r="C67" s="11">
-        <f>IFERROR(VLOOKUP($B67,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="D67" s="11">
-        <f>IFERROR(VLOOKUP($B67,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="E67" s="11">
-        <f>IFERROR(VLOOKUP($B67,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F67" s="10" t="inlineStr"/>
-      <c r="G67" s="11">
-        <f>IFERROR(VLOOKUP($F67,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="H67" s="11">
-        <f>IFERROR(VLOOKUP($F67,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="I67" s="11">
-        <f>IFERROR(VLOOKUP($F67,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="J67" s="10" t="inlineStr">
-        <is>
-          <t>Mahima Lele</t>
-        </is>
-      </c>
-      <c r="K67" s="11">
-        <f>IFERROR(VLOOKUP($J67,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="L67" s="11">
-        <f>IFERROR(VLOOKUP($J67,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="M67" s="11">
-        <f>IFERROR(VLOOKUP($J67,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="9" t="inlineStr">
-        <is>
-          <t>4:12 PM – 4:28 PM</t>
-        </is>
-      </c>
-      <c r="B68" s="10" t="inlineStr"/>
-      <c r="C68" s="11">
-        <f>IFERROR(VLOOKUP($B68,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="D68" s="11">
-        <f>IFERROR(VLOOKUP($B68,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="E68" s="11">
-        <f>IFERROR(VLOOKUP($B68,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F68" s="10" t="inlineStr"/>
-      <c r="G68" s="11">
-        <f>IFERROR(VLOOKUP($F68,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="H68" s="11">
-        <f>IFERROR(VLOOKUP($F68,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="I68" s="11">
-        <f>IFERROR(VLOOKUP($F68,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="J68" s="10" t="inlineStr"/>
-      <c r="K68" s="11">
-        <f>IFERROR(VLOOKUP($J68,Data!$A:$D,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="L68" s="11">
-        <f>IFERROR(VLOOKUP($J68,Data!$A:$D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="M68" s="11">
-        <f>IFERROR(VLOOKUP($J68,Data!$A:$D,3,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="B40:E40"/>
+  <mergeCells count="32">
+    <mergeCell ref="F27:I27"/>
     <mergeCell ref="A5:M5"/>
-    <mergeCell ref="A53:M53"/>
-    <mergeCell ref="J21:M21"/>
-    <mergeCell ref="A20:M20"/>
-    <mergeCell ref="A38:M38"/>
-    <mergeCell ref="A52:M52"/>
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="A35:M35"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="A57:M57"/>
+    <mergeCell ref="F49:I49"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="A58:M58"/>
+    <mergeCell ref="A48:M48"/>
     <mergeCell ref="B7:E7"/>
-    <mergeCell ref="A39:M39"/>
-    <mergeCell ref="F54:I54"/>
-    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="J59:M59"/>
+    <mergeCell ref="A36:M36"/>
+    <mergeCell ref="B27:E27"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="F7:I7"/>
-    <mergeCell ref="J40:M40"/>
     <mergeCell ref="A6:M6"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="J54:M54"/>
+    <mergeCell ref="F59:I59"/>
+    <mergeCell ref="A25:M25"/>
+    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="J49:M49"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="A26:M26"/>
+    <mergeCell ref="B37:E37"/>
     <mergeCell ref="J7:M7"/>
     <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A47:M47"/>
   </mergeCells>
-  <conditionalFormatting sqref="C4:C75">
+  <conditionalFormatting sqref="C4:C71">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Math"</formula>
     </cfRule>
@@ -7914,7 +7568,7 @@
       <formula>"Other"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G75">
+  <conditionalFormatting sqref="G4:G71">
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="0">
       <formula>"Math"</formula>
     </cfRule>
@@ -7949,7 +7603,7 @@
       <formula>"Other"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4:K75">
+  <conditionalFormatting sqref="K4:K71">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
       <formula>"Math"</formula>
     </cfRule>
@@ -7985,7 +7639,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="B9:B18 B23:B35 B42:B51 B56:B68 F9:F18 F23:F35 F42:F51 F56:F68 J9:J18 J23:J35 J42:J51 J56:J68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B9:B14 B19:B24 B29:B34 B39:B44 B51:B56 B61:B64 F9:F14 F19:F24 F29:F34 F39:F44 F51:F56 F61:F64 J9:J14 J19:J24 J29:J34 J39:J44 J51:J56 J61:J64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Data!$A$2:$A$101</formula1>
     </dataValidation>
   </dataValidations>

--- a/RSI_2026_Schedule.xlsx
+++ b/RSI_2026_Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/evanlim/Documents/rsi-symposium/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B2A2C5A-8A17-F945-BD06-9854FF9D0D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92E78BE2-5E89-3F43-898F-6D7AD94E25E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,18 +39,444 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="706">
   <si>
+    <t>RSI 2026 Symposium Schedule</t>
+  </si>
+  <si>
+    <t>Edit a Name cell to reassign a slot -- Field / Title / Mentor update automatically.</t>
+  </si>
+  <si>
+    <t>Thursday, August 6, 2026</t>
+  </si>
+  <si>
+    <t>Block T1 (9:00 AM – 10:30 AM)</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Room 32-124</t>
+  </si>
+  <si>
+    <t>Room 32-141</t>
+  </si>
+  <si>
+    <t>Room 32-155</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Mentor</t>
+  </si>
+  <si>
+    <t>9:00 AM – 9:16 AM</t>
+  </si>
+  <si>
+    <t>Mira Cakmak</t>
+  </si>
+  <si>
+    <t>Mahi Kohli</t>
+  </si>
+  <si>
+    <t>Anushka Tonapi</t>
+  </si>
+  <si>
+    <t>9:16 AM – 9:32 AM</t>
+  </si>
+  <si>
+    <t>Zephyr Larson</t>
+  </si>
+  <si>
+    <t>Alejandra Stephanie Perry</t>
+  </si>
+  <si>
+    <t>Grisham Paimagam</t>
+  </si>
+  <si>
+    <t>9:32 AM – 9:48 AM</t>
+  </si>
+  <si>
+    <t>Alejandro Mayorga</t>
+  </si>
+  <si>
+    <t>Ferris Li</t>
+  </si>
+  <si>
+    <t>Katrina Liu</t>
+  </si>
+  <si>
+    <t>9:48 AM – 10:04 AM</t>
+  </si>
+  <si>
+    <t>Eric Buehler</t>
+  </si>
+  <si>
+    <t>Benson Hsueh</t>
+  </si>
+  <si>
+    <t>Lincoln Liu</t>
+  </si>
+  <si>
+    <t>10:04 AM – 10:20 AM</t>
+  </si>
+  <si>
+    <t>Layth Alzahrani</t>
+  </si>
+  <si>
+    <t>Matey Minev</t>
+  </si>
+  <si>
+    <t>Tony Lu</t>
+  </si>
+  <si>
+    <t>10:20 AM – 10:36 AM</t>
+  </si>
+  <si>
+    <t>Kai Xuen Toh</t>
+  </si>
+  <si>
+    <t>Siddhi Kochar</t>
+  </si>
+  <si>
+    <t>Michael Luo</t>
+  </si>
+  <si>
+    <t>Break (10:30 AM – 11:00 AM)</t>
+  </si>
+  <si>
+    <t>Block T2 (11:00 AM – 12:30 PM)</t>
+  </si>
+  <si>
+    <t>11:00 AM – 11:16 AM</t>
+  </si>
+  <si>
+    <t>Eason Turner</t>
+  </si>
+  <si>
+    <t>Lluc Simon</t>
+  </si>
+  <si>
+    <t>Sirius Sun</t>
+  </si>
+  <si>
+    <t>11:16 AM – 11:32 AM</t>
+  </si>
+  <si>
+    <t>Miguel Shim</t>
+  </si>
+  <si>
+    <t>Mikołaj Stefaniak</t>
+  </si>
+  <si>
+    <t>Nikola Veselinov</t>
+  </si>
+  <si>
+    <t>11:32 AM – 11:48 AM</t>
+  </si>
+  <si>
+    <t>Sylvia Lee</t>
+  </si>
+  <si>
+    <t>Mustafa Bakhodirov</t>
+  </si>
+  <si>
+    <t>Timothy Chen</t>
+  </si>
+  <si>
+    <t>11:48 AM – 12:04 PM</t>
+  </si>
+  <si>
+    <t>Pavan Subramani</t>
+  </si>
+  <si>
+    <t>Asher Wang</t>
+  </si>
+  <si>
+    <t>Jay Athipatla</t>
+  </si>
+  <si>
+    <t>12:04 PM – 12:20 PM</t>
+  </si>
+  <si>
+    <t>Cassidy Stocker</t>
+  </si>
+  <si>
+    <t>Rishi Pampati</t>
+  </si>
+  <si>
+    <t>Leyu Girma</t>
+  </si>
+  <si>
+    <t>12:20 PM – 12:36 PM</t>
+  </si>
+  <si>
+    <t>Sara Mitchell</t>
+  </si>
+  <si>
+    <t>Shaden Alharbi</t>
+  </si>
+  <si>
+    <t>Riya Mehrotra</t>
+  </si>
+  <si>
+    <t>Lunch Break (12:30 PM – 1:15 PM)</t>
+  </si>
+  <si>
+    <t>Block T3 (1:15 PM – 2:45 PM)</t>
+  </si>
+  <si>
+    <t>1:15 PM – 1:31 PM</t>
+  </si>
+  <si>
+    <t>Atharva Tyagi</t>
+  </si>
+  <si>
+    <t>Shrivali Gupta</t>
+  </si>
+  <si>
+    <t>Tara Saini</t>
+  </si>
+  <si>
+    <t>1:31 PM – 1:47 PM</t>
+  </si>
+  <si>
+    <t>Ayush Vispute</t>
+  </si>
+  <si>
+    <t>Danu Kim</t>
+  </si>
+  <si>
+    <t>Xindi Luo</t>
+  </si>
+  <si>
+    <t>1:47 PM – 2:03 PM</t>
+  </si>
+  <si>
+    <t>Bryan Cho</t>
+  </si>
+  <si>
+    <t>Leonardo Bartoccini</t>
+  </si>
+  <si>
+    <t>Greeshma Vinoy</t>
+  </si>
+  <si>
+    <t>2:03 PM – 2:19 PM</t>
+  </si>
+  <si>
+    <t>Claire Zhan</t>
+  </si>
+  <si>
+    <t>Namie Djaja</t>
+  </si>
+  <si>
+    <t>Sofia Passos</t>
+  </si>
+  <si>
+    <t>2:19 PM – 2:35 PM</t>
+  </si>
+  <si>
+    <t>Malin Janna Vega</t>
+  </si>
+  <si>
+    <t>Rohan Peddamallu</t>
+  </si>
+  <si>
+    <t>Can Nalbantoglu</t>
+  </si>
+  <si>
+    <t>2:35 PM – 2:51 PM</t>
+  </si>
+  <si>
+    <t>Sarah Dingli</t>
+  </si>
+  <si>
+    <t>Nabet El Hajjar</t>
+  </si>
+  <si>
+    <t>Daniel Guo</t>
+  </si>
+  <si>
+    <t>Break (2:45 PM – 3:15 PM)</t>
+  </si>
+  <si>
+    <t>Block T4 (3:15 PM – 4:45 PM)</t>
+  </si>
+  <si>
+    <t>3:15 PM – 3:31 PM</t>
+  </si>
+  <si>
+    <t>Sophia Zhao</t>
+  </si>
+  <si>
+    <t>Mahima Lele</t>
+  </si>
+  <si>
+    <t>Alex Ren</t>
+  </si>
+  <si>
+    <t>3:31 PM – 3:47 PM</t>
+  </si>
+  <si>
+    <t>Yong Ding</t>
+  </si>
+  <si>
+    <t>Cooper Ho</t>
+  </si>
+  <si>
+    <t>Amogh Dattatri</t>
+  </si>
+  <si>
+    <t>3:47 PM – 4:03 PM</t>
+  </si>
+  <si>
+    <t>Dhruv Jain</t>
+  </si>
+  <si>
+    <t>Lillie Lin Li</t>
+  </si>
+  <si>
+    <t>Chloe Giglio</t>
+  </si>
+  <si>
+    <t>4:03 PM – 4:19 PM</t>
+  </si>
+  <si>
+    <t>Aaryan Patel</t>
+  </si>
+  <si>
+    <t>Lara Otico</t>
+  </si>
+  <si>
+    <t>Ipek Zeynioğlu</t>
+  </si>
+  <si>
+    <t>4:19 PM – 4:35 PM</t>
+  </si>
+  <si>
+    <t>Andy Jo</t>
+  </si>
+  <si>
+    <t>Jordan Chong</t>
+  </si>
+  <si>
+    <t>Tristan Sun</t>
+  </si>
+  <si>
+    <t>4:35 PM – 4:51 PM</t>
+  </si>
+  <si>
+    <t>Jay Desai</t>
+  </si>
+  <si>
+    <t>Amritha Praveen</t>
+  </si>
+  <si>
+    <t>Álvaro Daniel Villafuerte González</t>
+  </si>
+  <si>
+    <t>Friday, August 7, 2026</t>
+  </si>
+  <si>
+    <t>Block F1 (9:00 AM – 10:30 AM)</t>
+  </si>
+  <si>
+    <t>Diya Gandhi</t>
+  </si>
+  <si>
+    <t>Abigail Qi</t>
+  </si>
+  <si>
+    <t>Sowmya Sankaran</t>
+  </si>
+  <si>
+    <t>David Shi</t>
+  </si>
+  <si>
+    <t>Luke Itomura</t>
+  </si>
+  <si>
+    <t>Tanay Arora</t>
+  </si>
+  <si>
+    <t>David Wang</t>
+  </si>
+  <si>
+    <t>Alexis Cho</t>
+  </si>
+  <si>
+    <t>Izabella Craciun</t>
+  </si>
+  <si>
+    <t>Azaria Tsegaye</t>
+  </si>
+  <si>
+    <t>Hannah Thomas</t>
+  </si>
+  <si>
+    <t>Karim Mrad</t>
+  </si>
+  <si>
+    <t>Yernar Doskhan</t>
+  </si>
+  <si>
+    <t>Logan Duran</t>
+  </si>
+  <si>
+    <t>Lucia Chen</t>
+  </si>
+  <si>
+    <t>Haya Mekdash</t>
+  </si>
+  <si>
+    <t>Ahmed Sultan</t>
+  </si>
+  <si>
+    <t>Yoon Seo Pyo</t>
+  </si>
+  <si>
+    <t>Block F2 (11:00 AM – 12:00 PM)</t>
+  </si>
+  <si>
+    <t>Raquel Gomez Junco Lobo</t>
+  </si>
+  <si>
+    <t>Annika Chadha</t>
+  </si>
+  <si>
+    <t>Avery Wang</t>
+  </si>
+  <si>
+    <t>Matthew Lo</t>
+  </si>
+  <si>
+    <t>Dex Theisen</t>
+  </si>
+  <si>
+    <t>Ngawang Namgyal</t>
+  </si>
+  <si>
+    <t>Sarah Park</t>
+  </si>
+  <si>
+    <t>Karl Chu</t>
+  </si>
+  <si>
+    <t>Ruchika Ramachandran</t>
+  </si>
+  <si>
+    <t>Selene Manzo</t>
+  </si>
+  <si>
     <t>Full Name</t>
   </si>
   <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Mentor</t>
-  </si>
-  <si>
-    <t>Field</t>
-  </si>
-  <si>
     <t>First Pron</t>
   </si>
   <si>
@@ -63,9 +489,6 @@
     <t>Kerb</t>
   </si>
   <si>
-    <t>Aaryan Patel</t>
-  </si>
-  <si>
     <t>TailSeeker: Optimizing Molecular Structure Generation for Fibrodysplasia Ossificans Progressiva</t>
   </si>
   <si>
@@ -87,9 +510,6 @@
     <t>aaru0302</t>
   </si>
   <si>
-    <t>Abigail Qi</t>
-  </si>
-  <si>
     <t>Optimization of a Yeast-Based High-Throughput Screening Platform to Identify PfPDEγ Inhibitor Candidates</t>
   </si>
   <si>
@@ -111,9 +531,6 @@
     <t>abihqi</t>
   </si>
   <si>
-    <t>Ahmed Sultan</t>
-  </si>
-  <si>
     <t>Characterizing Myo15-Cre Recombination in Cochlear Hair Cells to Validate Disease Models for Usher Syndrome Type 1F Gene Therapy</t>
   </si>
   <si>
@@ -132,9 +549,6 @@
     <t>a_sultan</t>
   </si>
   <si>
-    <t>Alejandra Stephanie Perry</t>
-  </si>
-  <si>
     <t>Critical Windows for Neuromodulatory Recovery: Reversible UNC-31 Depletion in Caenorhabditis elegans Development</t>
   </si>
   <si>
@@ -153,9 +567,6 @@
     <t>asperry</t>
   </si>
   <si>
-    <t>Alejandro Mayorga</t>
-  </si>
-  <si>
     <t>Liquid Foundation Models as Medical Assistants</t>
   </si>
   <si>
@@ -174,9 +585,6 @@
     <t>alej0</t>
   </si>
   <si>
-    <t>Alex Ren</t>
-  </si>
-  <si>
     <t>Investigating cognitive decline in HIV</t>
   </si>
   <si>
@@ -195,9 +603,6 @@
     <t>alexren</t>
   </si>
   <si>
-    <t>Alexis Cho</t>
-  </si>
-  <si>
     <t>Interactions of lipid droplets and Them1-containing condensates to regulate metabolism</t>
   </si>
   <si>
@@ -216,9 +621,6 @@
     <t>alexicho</t>
   </si>
   <si>
-    <t>Amogh Dattatri</t>
-  </si>
-  <si>
     <t>Dissecting the effects of non-coding genetic variation on neuropsychiatric disorder susceptibility</t>
   </si>
   <si>
@@ -234,9 +636,6 @@
     <t>amogh28</t>
   </si>
   <si>
-    <t>Amritha Praveen</t>
-  </si>
-  <si>
     <t>Analyzing the Correlation of SBayesRC Calculated Weights for Polygenic Risk Scores and Body Mass Index</t>
   </si>
   <si>
@@ -255,9 +654,6 @@
     <t>amritha9</t>
   </si>
   <si>
-    <t>Andy Jo</t>
-  </si>
-  <si>
     <t>Affine-Normalized Geometry of Protein Ensembles</t>
   </si>
   <si>
@@ -273,9 +669,6 @@
     <t>minkyujo</t>
   </si>
   <si>
-    <t>Annika Chadha</t>
-  </si>
-  <si>
     <t>Reproducing the Energy Landscape of Nanoparticle-Induced Lipid Membrane Deformation</t>
   </si>
   <si>
@@ -297,9 +690,6 @@
     <t>annika8</t>
   </si>
   <si>
-    <t>Anushka Tonapi</t>
-  </si>
-  <si>
     <t>On Counting Prime Solutions to Quadratic Forms via the Hardy-Littlewood Circle Method</t>
   </si>
   <si>
@@ -321,9 +711,6 @@
     <t>avtonapi</t>
   </si>
   <si>
-    <t>Asher Wang</t>
-  </si>
-  <si>
     <t>Sinusoidal Representation Networks for Neural Renormalization-Group Flows on the1D and 2D Ising Models</t>
   </si>
   <si>
@@ -345,9 +732,6 @@
     <t>aowang11</t>
   </si>
   <si>
-    <t>Atharva Tyagi</t>
-  </si>
-  <si>
     <t>Temporal Mapping of Doxorubicin-Induced Alterations in Autophagic Flux in hiPSC-Derived Cardiomyocytes</t>
   </si>
   <si>
@@ -366,9 +750,6 @@
     <t>a1wang</t>
   </si>
   <si>
-    <t>Avery Wang</t>
-  </si>
-  <si>
     <t>Navier–Stokes Characteristic Boundary Conditions for Limited-Area Numerical Weather Prediction</t>
   </si>
   <si>
@@ -387,9 +768,6 @@
     <t>atyagi11</t>
   </si>
   <si>
-    <t>Ayush Vispute</t>
-  </si>
-  <si>
     <t>Optimizing Quasi Geostrophic Flow Solving An Embedded Neural Network</t>
   </si>
   <si>
@@ -405,9 +783,6 @@
     <t>avispute</t>
   </si>
   <si>
-    <t>Azaria Tsegaye</t>
-  </si>
-  <si>
     <t>Observing Landau Levels in Simulated Strained Graphene</t>
   </si>
   <si>
@@ -426,9 +801,6 @@
     <t>azariart</t>
   </si>
   <si>
-    <t>Benson Hsueh</t>
-  </si>
-  <si>
     <t>The Center Configuration Problem for Single-Robot Reconfiguration</t>
   </si>
   <si>
@@ -447,9 +819,6 @@
     <t>bensonh</t>
   </si>
   <si>
-    <t>Bryan Cho</t>
-  </si>
-  <si>
     <t>Parametric study of regime transitions in quasi-turbulence</t>
   </si>
   <si>
@@ -462,9 +831,6 @@
     <t>cho0707</t>
   </si>
   <si>
-    <t>Can Nalbantoglu</t>
-  </si>
-  <si>
     <t>Schrodinger Bridges for Graph Interpolations</t>
   </si>
   <si>
@@ -483,9 +849,6 @@
     <t>can_nlbt</t>
   </si>
   <si>
-    <t>Cassidy Stocker</t>
-  </si>
-  <si>
     <t>Effect of ZAP70 Mutations on CAR T-Cell Effectiveness Targeting GD2 in Brain Tumors</t>
   </si>
   <si>
@@ -504,9 +867,6 @@
     <t>mariac08</t>
   </si>
   <si>
-    <t>Chloe Giglio</t>
-  </si>
-  <si>
     <t>Mapping the transcriptional and phenotypic heterogeneity of lung adenocarcinoma progression</t>
   </si>
   <si>
@@ -522,9 +882,6 @@
     <t>chloegig</t>
   </si>
   <si>
-    <t>Claire Zhan</t>
-  </si>
-  <si>
     <t>Efficient Patching for Generative Super Resolution of Turbulent Flow Fields</t>
   </si>
   <si>
@@ -540,9 +897,6 @@
     <t>cfyzhan</t>
   </si>
   <si>
-    <t>Cooper Ho</t>
-  </si>
-  <si>
     <t>Detecting Long-Transit Exoplanets via Better Detrending TESS Light Curves</t>
   </si>
   <si>
@@ -564,9 +918,6 @@
     <t>cyh</t>
   </si>
   <si>
-    <t>Daniel Guo</t>
-  </si>
-  <si>
     <t>Improving the Reliability of Hypersonic Airplane Engines Through Bleed Configurations</t>
   </si>
   <si>
@@ -588,9 +939,6 @@
     <t>dguo103</t>
   </si>
   <si>
-    <t>Danu Kim</t>
-  </si>
-  <si>
     <t>The Feedback Horizon: When Physical Foreknowledge Becomes Decisive in Robotic Manipulation</t>
   </si>
   <si>
@@ -609,9 +957,6 @@
     <t>dkim081</t>
   </si>
   <si>
-    <t>David Shi</t>
-  </si>
-  <si>
     <t>The Grammar of Natural Systems: Compositional Material Design Across Scales</t>
   </si>
   <si>
@@ -630,9 +975,6 @@
     <t>davidw09</t>
   </si>
   <si>
-    <t>David Wang</t>
-  </si>
-  <si>
     <t>Predicting Peptide Self-Assembly Phase from LLM Extracted Experimental Conditions</t>
   </si>
   <si>
@@ -642,9 +984,6 @@
     <t>dashii</t>
   </si>
   <si>
-    <t>Dex Theisen</t>
-  </si>
-  <si>
     <t>Understanding the Influence of Receptor Transport on Nanoparticle-Cell-Membrane Interactions</t>
   </si>
   <si>
@@ -660,9 +999,6 @@
     <t>dtheisen</t>
   </si>
   <si>
-    <t>Dhruv Jain</t>
-  </si>
-  <si>
     <t>Structure Analysis using Partial Grotrian Diagram Construction and Isotope-Shift Systematics of Pa I,II,IV,V and Statistical Synthesis of Comagnetometer Constants</t>
   </si>
   <si>
@@ -681,9 +1017,6 @@
     <t>dhruvj07</t>
   </si>
   <si>
-    <t>Diya Gandhi</t>
-  </si>
-  <si>
     <t>The Effect of Mergers on the Generic Drug Market</t>
   </si>
   <si>
@@ -705,9 +1038,6 @@
     <t>dagandhi</t>
   </si>
   <si>
-    <t>Eason Turner</t>
-  </si>
-  <si>
     <t>Searching for Eclipses in X-Ray Sources</t>
   </si>
   <si>
@@ -726,9 +1056,6 @@
     <t>eason</t>
   </si>
   <si>
-    <t>Eric Buehler</t>
-  </si>
-  <si>
     <t>Teaching a Medical Vision-Language Model with Automatic Feedback</t>
   </si>
   <si>
@@ -744,9 +1071,6 @@
     <t>ebuehler</t>
   </si>
   <si>
-    <t>Ferris Li</t>
-  </si>
-  <si>
     <t>Building a Machine Learning Model to Track Many C. elegans Worms Simultaneously and Resolve Collisions</t>
   </si>
   <si>
@@ -762,9 +1086,6 @@
     <t>hl888</t>
   </si>
   <si>
-    <t>Greeshma Vinoy</t>
-  </si>
-  <si>
     <t>APOE e4-Associated Microglial Transcriptional Signature Across Neurodegenerative Diseases</t>
   </si>
   <si>
@@ -783,9 +1104,6 @@
     <t>gsvinoy</t>
   </si>
   <si>
-    <t>Grisham Paimagam</t>
-  </si>
-  <si>
     <t>Sphere Packing on Grassmannians</t>
   </si>
   <si>
@@ -801,9 +1119,6 @@
     <t>grishpai</t>
   </si>
   <si>
-    <t>Hannah Thomas</t>
-  </si>
-  <si>
     <t>The Role of Them1 in Metabolic Gene Regulation</t>
   </si>
   <si>
@@ -819,9 +1134,6 @@
     <t>hannahgt</t>
   </si>
   <si>
-    <t>Haya Mekdash</t>
-  </si>
-  <si>
     <t>Development of a novel assay to measure radiation sensitivity of tumor cells</t>
   </si>
   <si>
@@ -840,9 +1152,6 @@
     <t>haya_m24</t>
   </si>
   <si>
-    <t>Ipek Zeynioğlu</t>
-  </si>
-  <si>
     <t>Efficient Binding Free Energy Estimation through Conformational Sampling of Intermediate States</t>
   </si>
   <si>
@@ -864,6 +1173,9 @@
     <t>Prof. Ambika Bajpayee</t>
   </si>
   <si>
+    <t>IZ-ah-BELL-ah</t>
+  </si>
+  <si>
     <t>kra-CHOON</t>
   </si>
   <si>
@@ -873,9 +1185,6 @@
     <t>iza_c397</t>
   </si>
   <si>
-    <t>Jay Athipatla</t>
-  </si>
-  <si>
     <t>DC-MTNN: A Drug-Conditioned Multi-Task Neural Network for Predicting Drug Resistance in Mycobacterium tuberculosis Using Genomic Data</t>
   </si>
   <si>
@@ -894,9 +1203,6 @@
     <t>jaydesai</t>
   </si>
   <si>
-    <t>Jay Desai</t>
-  </si>
-  <si>
     <t>Effective Computation of Free Resolutions and Cohomology for Quotients of Braid Groups</t>
   </si>
   <si>
@@ -909,9 +1215,6 @@
     <t>jayant69</t>
   </si>
   <si>
-    <t>Jordan Chong</t>
-  </si>
-  <si>
     <t>Arsenic Leaching from Granular Activated Carbon Electrodes in Water Treatment</t>
   </si>
   <si>
@@ -930,9 +1233,6 @@
     <t>jordanrc</t>
   </si>
   <si>
-    <t>Kai Xuen Toh</t>
-  </si>
-  <si>
     <t>Detecting Life in the Clouds: The Feasibility of Using UV Phase Delay Sensing on Venus</t>
   </si>
   <si>
@@ -951,9 +1251,6 @@
     <t>tohk140</t>
   </si>
   <si>
-    <t>Karim Mrad</t>
-  </si>
-  <si>
     <t>Strategic Use of the KR Alpha Synuclein Mutant (G14R + E46K) to Develop Experimental Models of Parkinson's Disease</t>
   </si>
   <si>
@@ -972,9 +1269,6 @@
     <t>kmradddd</t>
   </si>
   <si>
-    <t>Karl Chu</t>
-  </si>
-  <si>
     <t>Evaluating Dyadic Foraging Optimization Through the Marginal Value Theorem</t>
   </si>
   <si>
@@ -996,9 +1290,6 @@
     <t>karlc24</t>
   </si>
   <si>
-    <t>Katrina Liu</t>
-  </si>
-  <si>
     <t>Temporal Preferential Attachment Trees</t>
   </si>
   <si>
@@ -1017,9 +1308,6 @@
     <t>liukz</t>
   </si>
   <si>
-    <t>Lara Otico</t>
-  </si>
-  <si>
     <t>Evaluating the Efficacy of RAP-Mediated Steric Hinderance on LRP-1 to Inhibit TcdB Endocytosis and Limit C. difficile Pathogenesis</t>
   </si>
   <si>
@@ -1038,9 +1326,6 @@
     <t>larao369</t>
   </si>
   <si>
-    <t>Layth Alzahrani</t>
-  </si>
-  <si>
     <t>Crown–Root Segmentation in Dental CBCT Using Anatomically Guided Synthetic Annotation</t>
   </si>
   <si>
@@ -1056,9 +1341,6 @@
     <t>layth224</t>
   </si>
   <si>
-    <t>Leonardo Bartoccini</t>
-  </si>
-  <si>
     <t>Learning Reciprocity: Value-Based Intrinsic Rewards for Cooperation in Sequential Social Dilemmas</t>
   </si>
   <si>
@@ -1074,9 +1356,6 @@
     <t>leobart</t>
   </si>
   <si>
-    <t>Leyu Girma</t>
-  </si>
-  <si>
     <t>Explicit Free Resolutions for Central Quotients of Cyclic Amalgams</t>
   </si>
   <si>
@@ -1092,9 +1371,6 @@
     <t>leyug</t>
   </si>
   <si>
-    <t>Lillie Lin Li</t>
-  </si>
-  <si>
     <t>Neptunian Ridge around faint stars</t>
   </si>
   <si>
@@ -1107,9 +1383,6 @@
     <t>lillieli</t>
   </si>
   <si>
-    <t>Lincoln Liu</t>
-  </si>
-  <si>
     <t>Heat Evolution on Graphs</t>
   </si>
   <si>
@@ -1125,9 +1398,6 @@
     <t>lliu320</t>
   </si>
   <si>
-    <t>Lluc Simon</t>
-  </si>
-  <si>
     <t>Hybrid controls strategy for Automatic Laser Beam Alignment</t>
   </si>
   <si>
@@ -1146,9 +1416,6 @@
     <t>lluc</t>
   </si>
   <si>
-    <t>Logan Duran</t>
-  </si>
-  <si>
     <t>Effects of material and surface chemistry in heat exchanger</t>
   </si>
   <si>
@@ -1167,9 +1434,6 @@
     <t>lwduran</t>
   </si>
   <si>
-    <t>Lucia Chen</t>
-  </si>
-  <si>
     <t>Understanding the Rules of Gene Perturbation Responses</t>
   </si>
   <si>
@@ -1188,9 +1452,6 @@
     <t>lucichen</t>
   </si>
   <si>
-    <t>Luke Itomura</t>
-  </si>
-  <si>
     <t>Yeast-Based High-Throughput Screening for _Plasmodium falciparum_ PDEα Inhibitor Discovery</t>
   </si>
   <si>
@@ -1206,9 +1467,6 @@
     <t>litomura</t>
   </si>
   <si>
-    <t>Mahi Kohli</t>
-  </si>
-  <si>
     <t>Worming Our Way Out: Analyzing How Developmental Exposure to UNC-31 Degradation and TIR1 affect brain dynamics of C. elegans</t>
   </si>
   <si>
@@ -1224,9 +1482,6 @@
     <t>mahi_k19</t>
   </si>
   <si>
-    <t>Mahima Lele</t>
-  </si>
-  <si>
     <t>Evaluating the FDA’s 510(k) Pathway for Approving AI/ML Medical Devices</t>
   </si>
   <si>
@@ -1245,9 +1500,6 @@
     <t>mlele123</t>
   </si>
   <si>
-    <t>Malin Janna Vega</t>
-  </si>
-  <si>
     <t>GPU-Accelerated Numerical Modeling of Idealized Ocean Circulation</t>
   </si>
   <si>
@@ -1263,9 +1515,6 @@
     <t>mjmvega</t>
   </si>
   <si>
-    <t>Matey Minev</t>
-  </si>
-  <si>
     <t>Before the Final Assembly: Temporal Leakage and Process Privacy in Covert Tile Automata</t>
   </si>
   <si>
@@ -1281,9 +1530,6 @@
     <t>matey</t>
   </si>
   <si>
-    <t>Matthew Lo</t>
-  </si>
-  <si>
     <t>Immunological Modeling of Anti-Idiotypic Network Dynamics to Explain Neonatal Tolerance and Adult Responsiveness</t>
   </si>
   <si>
@@ -1302,9 +1548,6 @@
     <t>mattlo</t>
   </si>
   <si>
-    <t>Michael Luo</t>
-  </si>
-  <si>
     <t>Resolving a Conjecture on Stack-Sorting</t>
   </si>
   <si>
@@ -1323,9 +1566,6 @@
     <t>mluo928</t>
   </si>
   <si>
-    <t>Miguel Shim</t>
-  </si>
-  <si>
     <t>Information Flow in Self Organizing Systems</t>
   </si>
   <si>
@@ -1344,9 +1584,6 @@
     <t>shim112</t>
   </si>
   <si>
-    <t>Mikołaj Stefaniak</t>
-  </si>
-  <si>
     <t>Optical pulse shaping for quantum-enhanced clocks</t>
   </si>
   <si>
@@ -1362,9 +1599,6 @@
     <t>mikolaj</t>
   </si>
   <si>
-    <t>Mira Cakmak</t>
-  </si>
-  <si>
     <t>Visualizing Neuropsychological Profiles in Patients with Alzheimer's Disease</t>
   </si>
   <si>
@@ -1383,9 +1617,6 @@
     <t>mira_c36</t>
   </si>
   <si>
-    <t>Mustafa Bakhodirov</t>
-  </si>
-  <si>
     <t>Patient-Specific Modeling of Brain and Cerebrospinal Fluid Response to Rapid Head Acceleration in Chiari I Malformation</t>
   </si>
   <si>
@@ -1404,9 +1635,6 @@
     <t>mbakhod</t>
   </si>
   <si>
-    <t>Nabet El Hajjar</t>
-  </si>
-  <si>
     <t>Neighborhood Disadvantage, White Matter Development, and Child Outcomes: Evidence from the ABCD Study</t>
   </si>
   <si>
@@ -1425,9 +1653,6 @@
     <t>nabet</t>
   </si>
   <si>
-    <t>Namie Djaja</t>
-  </si>
-  <si>
     <t>A Teleoperation System as a Data Engine for Learning System Dynamics</t>
   </si>
   <si>
@@ -1443,9 +1668,6 @@
     <t>namie</t>
   </si>
   <si>
-    <t>Ngawang Namgyal</t>
-  </si>
-  <si>
     <t>W-Flow: Continuous-variable Quantum State Tomography via Flow-based Generative Modeling</t>
   </si>
   <si>
@@ -1461,9 +1683,6 @@
     <t>ngawang1</t>
   </si>
   <si>
-    <t>Nikola Veselinov</t>
-  </si>
-  <si>
     <t>On Supersingular Isogeny Graphs of Drinfeld Modules</t>
   </si>
   <si>
@@ -1482,9 +1701,6 @@
     <t>nveselin</t>
   </si>
   <si>
-    <t>Pavan Subramani</t>
-  </si>
-  <si>
     <t>The computational conversion of a singular apo structure to an ensemble of holo structures for more accurate molecular docking</t>
   </si>
   <si>
@@ -1503,12 +1719,6 @@
     <t>psubra18</t>
   </si>
   <si>
-    <t>Raquel Gomez Junco Lobo</t>
-  </si>
-  <si>
-    <t>Rational Minigene Design Toward AAV Gene Therapy for Bainbridge-Ropers Syndrome</t>
-  </si>
-  <si>
     <t>Prof. Fengfeng Bei</t>
   </si>
   <si>
@@ -1524,15 +1734,9 @@
     <t>raquelgj</t>
   </si>
   <si>
-    <t>Rishi Pampati</t>
-  </si>
-  <si>
     <t>Functional Neural Connectivity During Inactivation of the Anterior Insula in Fentanyl-Administered Rats</t>
   </si>
   <si>
-    <t>Dr. Sarah Bricault and Prof. Alan Pradip Jasanoff (PI)</t>
-  </si>
-  <si>
     <t>RIH-shee</t>
   </si>
   <si>
@@ -1545,9 +1749,6 @@
     <t>rishi007</t>
   </si>
   <si>
-    <t>Riya Mehrotra</t>
-  </si>
-  <si>
     <t>Simplified Volume Formulas for Tetrahedron by Edge-length Symmetry Class</t>
   </si>
   <si>
@@ -1566,9 +1767,6 @@
     <t>riyam114</t>
   </si>
   <si>
-    <t>Rohan Peddamallu</t>
-  </si>
-  <si>
     <t>Neural CBF-based Safe RL for Robot Locomotion</t>
   </si>
   <si>
@@ -1584,9 +1782,6 @@
     <t>rohanpr</t>
   </si>
   <si>
-    <t>Ruchika Ramachandran</t>
-  </si>
-  <si>
     <t>Investigating the Role of Alternative Polyadenylation in Obesity-Induced Cardiac Endothelial Inflammation</t>
   </si>
   <si>
@@ -1605,9 +1800,6 @@
     <t>ruchram8</t>
   </si>
   <si>
-    <t>Sara Mitchell</t>
-  </si>
-  <si>
     <t>Identifying Alternative Stimulatory Receptors for TCR-independent Activation of T-cells</t>
   </si>
   <si>
@@ -1623,9 +1815,6 @@
     <t>sarmit21</t>
   </si>
   <si>
-    <t>Sarah Dingli</t>
-  </si>
-  <si>
     <t>Computational and mathematical modeling of cellular dynamics in hydrogels to optimize large-scale bioprinting</t>
   </si>
   <si>
@@ -1644,9 +1833,6 @@
     <t>srdingli</t>
   </si>
   <si>
-    <t>Sarah Park</t>
-  </si>
-  <si>
     <t>The Mitotic Basis of the Human Mind</t>
   </si>
   <si>
@@ -1659,9 +1845,6 @@
     <t>sgpark</t>
   </si>
   <si>
-    <t>Selene Manzo</t>
-  </si>
-  <si>
     <t>Frog Search: A New Way to Measure Guidance by Color in Visual Search</t>
   </si>
   <si>
@@ -1677,9 +1860,6 @@
     <t>selenem</t>
   </si>
   <si>
-    <t>Shaden Alharbi</t>
-  </si>
-  <si>
     <t>Characterization of Nanobody Binding to HIV-1 Capsid-Like Particles via Biolayer Interferometry</t>
   </si>
   <si>
@@ -1698,9 +1878,6 @@
     <t>shadenfm</t>
   </si>
   <si>
-    <t>Shrivali Gupta</t>
-  </si>
-  <si>
     <t>Examining the Relationship Between Executive Function and Behavioural Outcomes in Children</t>
   </si>
   <si>
@@ -1719,9 +1896,6 @@
     <t>shrivali</t>
   </si>
   <si>
-    <t>Siddhi Kochar</t>
-  </si>
-  <si>
     <t>Constraints on Cosmic Reionization and the Thomson Optical Depth via the Population III.1 Flash Model</t>
   </si>
   <si>
@@ -1740,9 +1914,6 @@
     <t>siddhik</t>
   </si>
   <si>
-    <t>Sirius Sun</t>
-  </si>
-  <si>
     <t>Critical Groups of Signed Subdivided Wheels</t>
   </si>
   <si>
@@ -1758,9 +1929,6 @@
     <t>sirius_s</t>
   </si>
   <si>
-    <t>Sofia Passos</t>
-  </si>
-  <si>
     <t>Predicted glycolytic reprogramming in a microglial substate across neurodegenerative diseases.</t>
   </si>
   <si>
@@ -1776,9 +1944,6 @@
     <t>sofia937</t>
   </si>
   <si>
-    <t>Sophia Zhao</t>
-  </si>
-  <si>
     <t>Reachability-Based Path Planning Across Autonomous Ocean Vehicles Platforms</t>
   </si>
   <si>
@@ -1791,9 +1956,6 @@
     <t>sophiawz</t>
   </si>
   <si>
-    <t>Sowmya Sankaran</t>
-  </si>
-  <si>
     <t>The Talking Risk Calculator: An Agentic Pipeline for Multi-Factor Cancer Risk Assessment</t>
   </si>
   <si>
@@ -1812,9 +1974,6 @@
     <t>sowmya44</t>
   </si>
   <si>
-    <t>Sylvia Lee</t>
-  </si>
-  <si>
     <t>Life is a Game: Learning Dynamical Systems with Neural Cellular Automata</t>
   </si>
   <si>
@@ -1827,9 +1986,6 @@
     <t>szl129</t>
   </si>
   <si>
-    <t>Tanay Arora</t>
-  </si>
-  <si>
     <t>AutoOnboarding Agentic LLMs</t>
   </si>
   <si>
@@ -1845,9 +2001,6 @@
     <t>tarora</t>
   </si>
   <si>
-    <t>Tara Saini</t>
-  </si>
-  <si>
     <t>Enumerating Index-Two and Index-Three Nilpotent Matrices in Symplectic Lie Algebras</t>
   </si>
   <si>
@@ -1863,9 +2016,6 @@
     <t>tsaini</t>
   </si>
   <si>
-    <t>Timothy Chen</t>
-  </si>
-  <si>
     <t>Open Cases of the Colmez Conjecture</t>
   </si>
   <si>
@@ -1878,9 +2028,6 @@
     <t>ctimothy</t>
   </si>
   <si>
-    <t>Tony Lu</t>
-  </si>
-  <si>
     <t>Asymptotics for Curve Shortening Flow with Boundary</t>
   </si>
   <si>
@@ -1896,9 +2043,6 @@
     <t>tlu27</t>
   </si>
   <si>
-    <t>Tristan Sun</t>
-  </si>
-  <si>
     <t>Comorbidity-shaped cell states in Alzheimer’s disease: a single-nucleus dissection of 15 clinical phenotypes</t>
   </si>
   <si>
@@ -1911,9 +2055,6 @@
     <t>tris</t>
   </si>
   <si>
-    <t>Xindi Luo</t>
-  </si>
-  <si>
     <t>Triangular Taxicabs</t>
   </si>
   <si>
@@ -1926,9 +2067,6 @@
     <t>xindi578</t>
   </si>
   <si>
-    <t>Yernar Doskhan</t>
-  </si>
-  <si>
     <t>Vibration Mitigation for Atomic-Resolution Imaging in Scanning Four-Probe Microscopy</t>
   </si>
   <si>
@@ -1947,9 +2085,6 @@
     <t>doskhan</t>
   </si>
   <si>
-    <t>Yong Ding</t>
-  </si>
-  <si>
     <t>Quantifying Information Propagation in Diffusion Posterior Sampling for Ocean Flows</t>
   </si>
   <si>
@@ -1965,9 +2100,6 @@
     <t>yding27</t>
   </si>
   <si>
-    <t>Yoon Seo Pyo</t>
-  </si>
-  <si>
     <t>Forecasting Seizure Spread in Epilepsy Patients Using Deep Learning Models of Electroencephalographic Activity</t>
   </si>
   <si>
@@ -1986,9 +2118,6 @@
     <t>yspyo</t>
   </si>
   <si>
-    <t>Zephyr Larson</t>
-  </si>
-  <si>
     <t>Understanding the Role of Radiative Feedbacks and Forcings in the Land-Sea Warming Contrast</t>
   </si>
   <si>
@@ -2007,9 +2136,6 @@
     <t>zephyr27</t>
   </si>
   <si>
-    <t>Álvaro Daniel Villafuerte González</t>
-  </si>
-  <si>
     <t>Towards Scaling Laws For Long-Horizon Software Engineering Agents</t>
   </si>
   <si>
@@ -2025,136 +2151,10 @@
     <t>advg</t>
   </si>
   <si>
-    <t>RSI 2026 Symposium Schedule</t>
-  </si>
-  <si>
-    <t>Edit a Name cell to reassign a slot -- Field / Title / Mentor update automatically.</t>
-  </si>
-  <si>
-    <t>Thursday, August 6, 2026</t>
-  </si>
-  <si>
-    <t>Block T1 (9:00 AM – 10:30 AM)</t>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
-    <t>Room 32-124</t>
-  </si>
-  <si>
-    <t>Room 32-141</t>
-  </si>
-  <si>
-    <t>Room 32-155</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>9:00 AM – 9:16 AM</t>
-  </si>
-  <si>
-    <t>9:16 AM – 9:32 AM</t>
-  </si>
-  <si>
-    <t>9:32 AM – 9:48 AM</t>
-  </si>
-  <si>
-    <t>9:48 AM – 10:04 AM</t>
-  </si>
-  <si>
-    <t>10:04 AM – 10:20 AM</t>
-  </si>
-  <si>
-    <t>10:20 AM – 10:36 AM</t>
-  </si>
-  <si>
-    <t>Break (10:30 AM – 11:00 AM)</t>
-  </si>
-  <si>
-    <t>Block T2 (11:00 AM – 12:30 PM)</t>
-  </si>
-  <si>
-    <t>11:00 AM – 11:16 AM</t>
-  </si>
-  <si>
-    <t>11:16 AM – 11:32 AM</t>
-  </si>
-  <si>
-    <t>11:32 AM – 11:48 AM</t>
-  </si>
-  <si>
-    <t>11:48 AM – 12:04 PM</t>
-  </si>
-  <si>
-    <t>12:04 PM – 12:20 PM</t>
-  </si>
-  <si>
-    <t>12:20 PM – 12:36 PM</t>
-  </si>
-  <si>
-    <t>Lunch Break (12:30 PM – 1:15 PM)</t>
-  </si>
-  <si>
-    <t>Block T3 (1:15 PM – 2:45 PM)</t>
-  </si>
-  <si>
-    <t>1:15 PM – 1:31 PM</t>
-  </si>
-  <si>
-    <t>1:31 PM – 1:47 PM</t>
-  </si>
-  <si>
-    <t>1:47 PM – 2:03 PM</t>
-  </si>
-  <si>
-    <t>2:03 PM – 2:19 PM</t>
-  </si>
-  <si>
-    <t>2:19 PM – 2:35 PM</t>
-  </si>
-  <si>
-    <t>2:35 PM – 2:51 PM</t>
-  </si>
-  <si>
-    <t>Break (2:45 PM – 3:15 PM)</t>
-  </si>
-  <si>
-    <t>Block T4 (3:15 PM – 4:45 PM)</t>
-  </si>
-  <si>
-    <t>3:15 PM – 3:31 PM</t>
-  </si>
-  <si>
-    <t>3:31 PM – 3:47 PM</t>
-  </si>
-  <si>
-    <t>3:47 PM – 4:03 PM</t>
-  </si>
-  <si>
-    <t>4:03 PM – 4:19 PM</t>
-  </si>
-  <si>
-    <t>4:19 PM – 4:35 PM</t>
-  </si>
-  <si>
-    <t>4:35 PM – 4:51 PM</t>
-  </si>
-  <si>
-    <t>Friday, August 7, 2026</t>
-  </si>
-  <si>
-    <t>Block F1 (9:00 AM – 10:30 AM)</t>
-  </si>
-  <si>
-    <t>Block F2 (11:00 AM – 12:00 PM)</t>
-  </si>
-  <si>
-    <t>Izabella Craciun</t>
-  </si>
-  <si>
-    <t>IZ-ah-BELL-ah</t>
+    <t>Reference-Anchored Computational Design of Domain-Preserving ASXL3 Minigenes for AAV Gene Therapy in Bainbridge-Ropers Syndrome</t>
+  </si>
+  <si>
+    <t>Dr. Sarah Bricault</t>
   </si>
 </sst>
 </file>
@@ -2174,44 +2174,52 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FF1E293B"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF64748B"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF1E293B"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -2219,6 +2227,7 @@
       <sz val="11"/>
       <color rgb="FF92400E"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -2993,2628 +3002,2628 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>146</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>147</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>148</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>150</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>151</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>153</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>154</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>155</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>117</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>157</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>158</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>162</v>
       </c>
       <c r="H3" t="s">
-        <v>23</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>132</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>164</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>165</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>166</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>167</v>
       </c>
       <c r="G4" t="s">
-        <v>29</v>
+        <v>168</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>170</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>171</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>172</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>173</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>174</v>
       </c>
       <c r="H5" t="s">
-        <v>37</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>176</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>177</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="E6" t="s">
-        <v>41</v>
+        <v>178</v>
       </c>
       <c r="F6" t="s">
-        <v>42</v>
+        <v>179</v>
       </c>
       <c r="G6" t="s">
-        <v>43</v>
+        <v>180</v>
       </c>
       <c r="H6" t="s">
-        <v>44</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>93</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>182</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>183</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E7" t="s">
-        <v>48</v>
+        <v>184</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>185</v>
       </c>
       <c r="G7" t="s">
-        <v>50</v>
+        <v>186</v>
       </c>
       <c r="H7" t="s">
-        <v>51</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>188</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>189</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E8" t="s">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>191</v>
       </c>
       <c r="G8" t="s">
-        <v>57</v>
+        <v>192</v>
       </c>
       <c r="H8" t="s">
-        <v>58</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>194</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>183</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E9" t="s">
-        <v>61</v>
+        <v>195</v>
       </c>
       <c r="F9" t="s">
-        <v>62</v>
+        <v>196</v>
       </c>
       <c r="G9" t="s">
-        <v>63</v>
+        <v>197</v>
       </c>
       <c r="H9" t="s">
-        <v>64</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>199</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>200</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E10" t="s">
-        <v>68</v>
+        <v>201</v>
       </c>
       <c r="F10" t="s">
-        <v>69</v>
+        <v>202</v>
       </c>
       <c r="G10" t="s">
-        <v>70</v>
+        <v>203</v>
       </c>
       <c r="H10" t="s">
-        <v>71</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>205</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>151</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E11" t="s">
-        <v>74</v>
+        <v>206</v>
       </c>
       <c r="F11" t="s">
-        <v>75</v>
+        <v>207</v>
       </c>
       <c r="G11" t="s">
-        <v>76</v>
+        <v>208</v>
       </c>
       <c r="H11" t="s">
-        <v>77</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>210</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>211</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>212</v>
       </c>
       <c r="E12" t="s">
-        <v>82</v>
+        <v>213</v>
       </c>
       <c r="F12" t="s">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="G12" t="s">
-        <v>84</v>
+        <v>215</v>
       </c>
       <c r="H12" t="s">
-        <v>85</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>217</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>218</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>219</v>
       </c>
       <c r="E13" t="s">
-        <v>90</v>
+        <v>220</v>
       </c>
       <c r="F13" t="s">
-        <v>91</v>
+        <v>221</v>
       </c>
       <c r="G13" t="s">
-        <v>92</v>
+        <v>222</v>
       </c>
       <c r="H13" t="s">
-        <v>93</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>95</v>
+        <v>224</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>225</v>
       </c>
       <c r="D14" t="s">
-        <v>97</v>
+        <v>226</v>
       </c>
       <c r="E14" t="s">
-        <v>98</v>
+        <v>227</v>
       </c>
       <c r="F14" t="s">
-        <v>99</v>
+        <v>228</v>
       </c>
       <c r="G14" t="s">
-        <v>100</v>
+        <v>229</v>
       </c>
       <c r="H14" t="s">
-        <v>101</v>
+        <v>230</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
-        <v>103</v>
+        <v>231</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>232</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E15" t="s">
-        <v>105</v>
+        <v>233</v>
       </c>
       <c r="F15" t="s">
-        <v>106</v>
+        <v>234</v>
       </c>
       <c r="G15" t="s">
-        <v>107</v>
+        <v>235</v>
       </c>
       <c r="H15" t="s">
-        <v>108</v>
+        <v>236</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="B16" t="s">
-        <v>110</v>
+        <v>237</v>
       </c>
       <c r="C16" t="s">
-        <v>111</v>
+        <v>238</v>
       </c>
       <c r="D16" t="s">
-        <v>112</v>
+        <v>239</v>
       </c>
       <c r="E16" t="s">
-        <v>113</v>
+        <v>240</v>
       </c>
       <c r="F16" t="s">
-        <v>99</v>
+        <v>228</v>
       </c>
       <c r="G16" t="s">
-        <v>114</v>
+        <v>241</v>
       </c>
       <c r="H16" t="s">
-        <v>115</v>
+        <v>242</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>116</v>
+        <v>69</v>
       </c>
       <c r="B17" t="s">
-        <v>117</v>
+        <v>243</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>232</v>
       </c>
       <c r="D17" t="s">
-        <v>112</v>
+        <v>239</v>
       </c>
       <c r="E17" t="s">
-        <v>118</v>
+        <v>244</v>
       </c>
       <c r="F17" t="s">
-        <v>119</v>
+        <v>245</v>
       </c>
       <c r="G17" t="s">
-        <v>120</v>
+        <v>246</v>
       </c>
       <c r="H17" t="s">
-        <v>121</v>
+        <v>247</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B18" t="s">
-        <v>123</v>
+        <v>248</v>
       </c>
       <c r="C18" t="s">
-        <v>124</v>
+        <v>249</v>
       </c>
       <c r="D18" t="s">
-        <v>97</v>
+        <v>226</v>
       </c>
       <c r="E18" t="s">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="F18" t="s">
-        <v>126</v>
+        <v>251</v>
       </c>
       <c r="G18" t="s">
-        <v>127</v>
+        <v>252</v>
       </c>
       <c r="H18" t="s">
-        <v>128</v>
+        <v>253</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>129</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>130</v>
+        <v>254</v>
       </c>
       <c r="C19" t="s">
-        <v>131</v>
+        <v>255</v>
       </c>
       <c r="D19" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="E19" t="s">
-        <v>132</v>
+        <v>256</v>
       </c>
       <c r="F19" t="s">
-        <v>133</v>
+        <v>257</v>
       </c>
       <c r="G19" t="s">
-        <v>134</v>
+        <v>258</v>
       </c>
       <c r="H19" t="s">
-        <v>135</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>136</v>
+        <v>73</v>
       </c>
       <c r="B20" t="s">
-        <v>137</v>
+        <v>260</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>232</v>
       </c>
       <c r="D20" t="s">
-        <v>112</v>
+        <v>239</v>
       </c>
       <c r="E20" t="s">
-        <v>138</v>
+        <v>261</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>191</v>
       </c>
       <c r="G20" t="s">
-        <v>139</v>
+        <v>262</v>
       </c>
       <c r="H20" t="s">
-        <v>140</v>
+        <v>263</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>142</v>
+        <v>264</v>
       </c>
       <c r="C21" t="s">
-        <v>143</v>
+        <v>265</v>
       </c>
       <c r="D21" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="E21" t="s">
-        <v>144</v>
+        <v>266</v>
       </c>
       <c r="F21" t="s">
-        <v>145</v>
+        <v>267</v>
       </c>
       <c r="G21" t="s">
-        <v>146</v>
+        <v>268</v>
       </c>
       <c r="H21" t="s">
-        <v>147</v>
+        <v>269</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>148</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>149</v>
+        <v>270</v>
       </c>
       <c r="C22" t="s">
-        <v>150</v>
+        <v>271</v>
       </c>
       <c r="D22" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E22" t="s">
-        <v>151</v>
+        <v>272</v>
       </c>
       <c r="F22" t="s">
-        <v>152</v>
+        <v>273</v>
       </c>
       <c r="G22" t="s">
-        <v>153</v>
+        <v>274</v>
       </c>
       <c r="H22" t="s">
-        <v>154</v>
+        <v>275</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>156</v>
+        <v>276</v>
       </c>
       <c r="C23" t="s">
-        <v>47</v>
+        <v>183</v>
       </c>
       <c r="D23" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E23" t="s">
-        <v>157</v>
+        <v>277</v>
       </c>
       <c r="F23" t="s">
-        <v>158</v>
+        <v>278</v>
       </c>
       <c r="G23" t="s">
-        <v>159</v>
+        <v>279</v>
       </c>
       <c r="H23" t="s">
-        <v>160</v>
+        <v>280</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="B24" t="s">
-        <v>162</v>
+        <v>281</v>
       </c>
       <c r="C24" t="s">
-        <v>104</v>
+        <v>232</v>
       </c>
       <c r="D24" t="s">
-        <v>112</v>
+        <v>239</v>
       </c>
       <c r="E24" t="s">
-        <v>163</v>
+        <v>282</v>
       </c>
       <c r="F24" t="s">
-        <v>164</v>
+        <v>283</v>
       </c>
       <c r="G24" t="s">
-        <v>165</v>
+        <v>284</v>
       </c>
       <c r="H24" t="s">
-        <v>166</v>
+        <v>285</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>167</v>
+        <v>96</v>
       </c>
       <c r="B25" t="s">
-        <v>168</v>
+        <v>286</v>
       </c>
       <c r="C25" t="s">
-        <v>169</v>
+        <v>287</v>
       </c>
       <c r="D25" t="s">
-        <v>170</v>
+        <v>288</v>
       </c>
       <c r="E25" t="s">
-        <v>171</v>
+        <v>289</v>
       </c>
       <c r="F25" t="s">
-        <v>172</v>
+        <v>290</v>
       </c>
       <c r="G25" t="s">
-        <v>173</v>
+        <v>291</v>
       </c>
       <c r="H25" t="s">
-        <v>174</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>175</v>
+        <v>87</v>
       </c>
       <c r="B26" t="s">
-        <v>176</v>
+        <v>293</v>
       </c>
       <c r="C26" t="s">
-        <v>177</v>
+        <v>294</v>
       </c>
       <c r="D26" t="s">
-        <v>178</v>
+        <v>295</v>
       </c>
       <c r="E26" t="s">
-        <v>179</v>
+        <v>296</v>
       </c>
       <c r="F26" t="s">
-        <v>180</v>
+        <v>297</v>
       </c>
       <c r="G26" t="s">
-        <v>181</v>
+        <v>298</v>
       </c>
       <c r="H26" t="s">
-        <v>182</v>
+        <v>299</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>183</v>
+        <v>70</v>
       </c>
       <c r="B27" t="s">
-        <v>184</v>
+        <v>300</v>
       </c>
       <c r="C27" t="s">
-        <v>185</v>
+        <v>301</v>
       </c>
       <c r="D27" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="E27" t="s">
-        <v>186</v>
+        <v>302</v>
       </c>
       <c r="F27" t="s">
-        <v>187</v>
+        <v>303</v>
       </c>
       <c r="G27" t="s">
-        <v>188</v>
+        <v>304</v>
       </c>
       <c r="H27" t="s">
-        <v>189</v>
+        <v>305</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>190</v>
+        <v>119</v>
       </c>
       <c r="B28" t="s">
-        <v>191</v>
+        <v>306</v>
       </c>
       <c r="C28" t="s">
-        <v>192</v>
+        <v>307</v>
       </c>
       <c r="D28" t="s">
-        <v>81</v>
+        <v>212</v>
       </c>
       <c r="E28" t="s">
-        <v>193</v>
+        <v>308</v>
       </c>
       <c r="F28" t="s">
-        <v>194</v>
+        <v>309</v>
       </c>
       <c r="G28" t="s">
-        <v>195</v>
+        <v>310</v>
       </c>
       <c r="H28" t="s">
-        <v>196</v>
+        <v>311</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>197</v>
+        <v>122</v>
       </c>
       <c r="B29" t="s">
-        <v>198</v>
+        <v>312</v>
       </c>
       <c r="C29" t="s">
-        <v>192</v>
+        <v>307</v>
       </c>
       <c r="D29" t="s">
-        <v>81</v>
+        <v>212</v>
       </c>
       <c r="E29" t="s">
-        <v>193</v>
+        <v>308</v>
       </c>
       <c r="F29" t="s">
-        <v>99</v>
+        <v>228</v>
       </c>
       <c r="G29" t="s">
-        <v>199</v>
+        <v>313</v>
       </c>
       <c r="H29" t="s">
-        <v>200</v>
+        <v>314</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>201</v>
+        <v>139</v>
       </c>
       <c r="B30" t="s">
-        <v>202</v>
+        <v>315</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>211</v>
       </c>
       <c r="D30" t="s">
-        <v>81</v>
+        <v>212</v>
       </c>
       <c r="E30" t="s">
-        <v>203</v>
+        <v>316</v>
       </c>
       <c r="F30" t="s">
-        <v>204</v>
+        <v>317</v>
       </c>
       <c r="G30" t="s">
-        <v>205</v>
+        <v>318</v>
       </c>
       <c r="H30" t="s">
-        <v>206</v>
+        <v>319</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>207</v>
+        <v>99</v>
       </c>
       <c r="B31" t="s">
-        <v>208</v>
+        <v>320</v>
       </c>
       <c r="C31" t="s">
-        <v>209</v>
+        <v>321</v>
       </c>
       <c r="D31" t="s">
-        <v>97</v>
+        <v>226</v>
       </c>
       <c r="E31" t="s">
-        <v>210</v>
+        <v>322</v>
       </c>
       <c r="F31" t="s">
-        <v>211</v>
+        <v>323</v>
       </c>
       <c r="G31" t="s">
-        <v>212</v>
+        <v>324</v>
       </c>
       <c r="H31" t="s">
-        <v>213</v>
+        <v>325</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>214</v>
+        <v>116</v>
       </c>
       <c r="B32" t="s">
-        <v>215</v>
+        <v>326</v>
       </c>
       <c r="C32" t="s">
-        <v>216</v>
+        <v>327</v>
       </c>
       <c r="D32" t="s">
-        <v>217</v>
+        <v>328</v>
       </c>
       <c r="E32" t="s">
-        <v>218</v>
+        <v>329</v>
       </c>
       <c r="F32" t="s">
-        <v>219</v>
+        <v>330</v>
       </c>
       <c r="G32" t="s">
-        <v>220</v>
+        <v>331</v>
       </c>
       <c r="H32" t="s">
-        <v>221</v>
+        <v>332</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>222</v>
+        <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>223</v>
+        <v>333</v>
       </c>
       <c r="C33" t="s">
-        <v>224</v>
+        <v>334</v>
       </c>
       <c r="D33" t="s">
-        <v>170</v>
+        <v>288</v>
       </c>
       <c r="E33" t="s">
-        <v>225</v>
+        <v>335</v>
       </c>
       <c r="F33" t="s">
-        <v>226</v>
+        <v>336</v>
       </c>
       <c r="G33" t="s">
-        <v>227</v>
+        <v>337</v>
       </c>
       <c r="H33" t="s">
-        <v>228</v>
+        <v>338</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>229</v>
+        <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>230</v>
+        <v>339</v>
       </c>
       <c r="C34" t="s">
-        <v>40</v>
+        <v>177</v>
       </c>
       <c r="D34" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="E34" t="s">
-        <v>231</v>
+        <v>340</v>
       </c>
       <c r="F34" t="s">
-        <v>232</v>
+        <v>341</v>
       </c>
       <c r="G34" t="s">
-        <v>233</v>
+        <v>342</v>
       </c>
       <c r="H34" t="s">
-        <v>234</v>
+        <v>343</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>235</v>
+        <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>236</v>
+        <v>344</v>
       </c>
       <c r="C35" t="s">
-        <v>33</v>
+        <v>171</v>
       </c>
       <c r="D35" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="E35" t="s">
-        <v>237</v>
+        <v>345</v>
       </c>
       <c r="F35" t="s">
-        <v>238</v>
+        <v>346</v>
       </c>
       <c r="G35" t="s">
-        <v>239</v>
+        <v>347</v>
       </c>
       <c r="H35" t="s">
-        <v>240</v>
+        <v>348</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>241</v>
+        <v>75</v>
       </c>
       <c r="B36" t="s">
-        <v>242</v>
+        <v>349</v>
       </c>
       <c r="C36" t="s">
-        <v>243</v>
+        <v>350</v>
       </c>
       <c r="D36" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E36" t="s">
-        <v>244</v>
+        <v>351</v>
       </c>
       <c r="F36" t="s">
-        <v>245</v>
+        <v>352</v>
       </c>
       <c r="G36" t="s">
-        <v>246</v>
+        <v>353</v>
       </c>
       <c r="H36" t="s">
-        <v>247</v>
+        <v>354</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>248</v>
+        <v>19</v>
       </c>
       <c r="B37" t="s">
-        <v>249</v>
+        <v>355</v>
       </c>
       <c r="C37" t="s">
-        <v>88</v>
+        <v>218</v>
       </c>
       <c r="D37" t="s">
-        <v>89</v>
+        <v>219</v>
       </c>
       <c r="E37" t="s">
-        <v>250</v>
+        <v>356</v>
       </c>
       <c r="F37" t="s">
-        <v>251</v>
+        <v>357</v>
       </c>
       <c r="G37" t="s">
-        <v>252</v>
+        <v>358</v>
       </c>
       <c r="H37" t="s">
-        <v>253</v>
+        <v>359</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>254</v>
+        <v>126</v>
       </c>
       <c r="B38" t="s">
-        <v>255</v>
+        <v>360</v>
       </c>
       <c r="C38" t="s">
-        <v>54</v>
+        <v>189</v>
       </c>
       <c r="D38" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E38" t="s">
-        <v>256</v>
+        <v>361</v>
       </c>
       <c r="F38" t="s">
-        <v>257</v>
+        <v>362</v>
       </c>
       <c r="G38" t="s">
-        <v>258</v>
+        <v>363</v>
       </c>
       <c r="H38" t="s">
-        <v>259</v>
+        <v>364</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>260</v>
+        <v>131</v>
       </c>
       <c r="B39" t="s">
-        <v>261</v>
+        <v>365</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>366</v>
       </c>
       <c r="D39" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E39" t="s">
-        <v>263</v>
+        <v>367</v>
       </c>
       <c r="F39" t="s">
-        <v>264</v>
+        <v>368</v>
       </c>
       <c r="G39" t="s">
-        <v>265</v>
+        <v>369</v>
       </c>
       <c r="H39" t="s">
-        <v>266</v>
+        <v>370</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>267</v>
+        <v>105</v>
       </c>
       <c r="B40" t="s">
-        <v>268</v>
+        <v>371</v>
       </c>
       <c r="C40" t="s">
-        <v>47</v>
+        <v>183</v>
       </c>
       <c r="D40" t="s">
-        <v>81</v>
+        <v>212</v>
       </c>
       <c r="E40" t="s">
-        <v>269</v>
+        <v>372</v>
       </c>
       <c r="F40" t="s">
-        <v>270</v>
+        <v>373</v>
       </c>
       <c r="G40" t="s">
-        <v>271</v>
+        <v>374</v>
       </c>
       <c r="H40" t="s">
-        <v>272</v>
+        <v>375</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>704</v>
+        <v>124</v>
       </c>
       <c r="B41" t="s">
-        <v>273</v>
+        <v>376</v>
       </c>
       <c r="C41" t="s">
-        <v>274</v>
+        <v>377</v>
       </c>
       <c r="D41" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E41" t="s">
-        <v>705</v>
+        <v>378</v>
       </c>
       <c r="F41" t="s">
-        <v>275</v>
+        <v>379</v>
       </c>
       <c r="G41" t="s">
-        <v>276</v>
+        <v>380</v>
       </c>
       <c r="H41" t="s">
-        <v>277</v>
+        <v>381</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>278</v>
+        <v>53</v>
       </c>
       <c r="B42" t="s">
-        <v>279</v>
+        <v>382</v>
       </c>
       <c r="C42" t="s">
-        <v>280</v>
+        <v>383</v>
       </c>
       <c r="D42" t="s">
-        <v>11</v>
+        <v>219</v>
       </c>
       <c r="E42" t="s">
-        <v>281</v>
+        <v>384</v>
       </c>
       <c r="F42" t="s">
-        <v>282</v>
+        <v>385</v>
       </c>
       <c r="G42" t="s">
-        <v>283</v>
+        <v>386</v>
       </c>
       <c r="H42" t="s">
-        <v>284</v>
+        <v>387</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>285</v>
+        <v>111</v>
       </c>
       <c r="B43" t="s">
-        <v>286</v>
+        <v>388</v>
       </c>
       <c r="C43" t="s">
-        <v>10</v>
+        <v>151</v>
       </c>
       <c r="D43" t="s">
-        <v>89</v>
+        <v>219</v>
       </c>
       <c r="E43" t="s">
-        <v>281</v>
+        <v>384</v>
       </c>
       <c r="F43" t="s">
-        <v>287</v>
+        <v>389</v>
       </c>
       <c r="G43" t="s">
-        <v>288</v>
+        <v>390</v>
       </c>
       <c r="H43" t="s">
-        <v>289</v>
+        <v>391</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>290</v>
+        <v>108</v>
       </c>
       <c r="B44" t="s">
-        <v>291</v>
+        <v>392</v>
       </c>
       <c r="C44" t="s">
-        <v>292</v>
+        <v>393</v>
       </c>
       <c r="D44" t="s">
-        <v>178</v>
+        <v>295</v>
       </c>
       <c r="E44" t="s">
-        <v>293</v>
+        <v>394</v>
       </c>
       <c r="F44" t="s">
-        <v>294</v>
+        <v>395</v>
       </c>
       <c r="G44" t="s">
-        <v>295</v>
+        <v>396</v>
       </c>
       <c r="H44" t="s">
-        <v>296</v>
+        <v>397</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>297</v>
+        <v>33</v>
       </c>
       <c r="B45" t="s">
-        <v>298</v>
+        <v>398</v>
       </c>
       <c r="C45" t="s">
-        <v>299</v>
+        <v>399</v>
       </c>
       <c r="D45" t="s">
-        <v>170</v>
+        <v>288</v>
       </c>
       <c r="E45" t="s">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F45" t="s">
-        <v>301</v>
+        <v>401</v>
       </c>
       <c r="G45" t="s">
-        <v>302</v>
+        <v>402</v>
       </c>
       <c r="H45" t="s">
-        <v>303</v>
+        <v>403</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>304</v>
+        <v>127</v>
       </c>
       <c r="B46" t="s">
-        <v>305</v>
+        <v>404</v>
       </c>
       <c r="C46" t="s">
-        <v>306</v>
+        <v>405</v>
       </c>
       <c r="D46" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E46" t="s">
-        <v>307</v>
+        <v>406</v>
       </c>
       <c r="F46" t="s">
-        <v>308</v>
+        <v>407</v>
       </c>
       <c r="G46" t="s">
-        <v>309</v>
+        <v>408</v>
       </c>
       <c r="H46" t="s">
-        <v>310</v>
+        <v>409</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>311</v>
+        <v>142</v>
       </c>
       <c r="B47" t="s">
-        <v>312</v>
+        <v>410</v>
       </c>
       <c r="C47" t="s">
-        <v>313</v>
+        <v>411</v>
       </c>
       <c r="D47" t="s">
-        <v>314</v>
+        <v>412</v>
       </c>
       <c r="E47" t="s">
-        <v>315</v>
+        <v>413</v>
       </c>
       <c r="F47" t="s">
-        <v>316</v>
+        <v>414</v>
       </c>
       <c r="G47" t="s">
-        <v>317</v>
+        <v>415</v>
       </c>
       <c r="H47" t="s">
-        <v>318</v>
+        <v>416</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>319</v>
+        <v>23</v>
       </c>
       <c r="B48" t="s">
-        <v>320</v>
+        <v>417</v>
       </c>
       <c r="C48" t="s">
-        <v>321</v>
+        <v>418</v>
       </c>
       <c r="D48" t="s">
-        <v>89</v>
+        <v>219</v>
       </c>
       <c r="E48" t="s">
-        <v>322</v>
+        <v>419</v>
       </c>
       <c r="F48" t="s">
-        <v>323</v>
+        <v>420</v>
       </c>
       <c r="G48" t="s">
-        <v>324</v>
+        <v>421</v>
       </c>
       <c r="H48" t="s">
-        <v>325</v>
+        <v>422</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>326</v>
+        <v>104</v>
       </c>
       <c r="B49" t="s">
-        <v>327</v>
+        <v>423</v>
       </c>
       <c r="C49" t="s">
-        <v>328</v>
+        <v>424</v>
       </c>
       <c r="D49" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E49" t="s">
-        <v>329</v>
+        <v>425</v>
       </c>
       <c r="F49" t="s">
-        <v>330</v>
+        <v>426</v>
       </c>
       <c r="G49" t="s">
-        <v>331</v>
+        <v>427</v>
       </c>
       <c r="H49" t="s">
-        <v>332</v>
+        <v>428</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>333</v>
+        <v>29</v>
       </c>
       <c r="B50" t="s">
-        <v>334</v>
+        <v>429</v>
       </c>
       <c r="C50" t="s">
-        <v>40</v>
+        <v>177</v>
       </c>
       <c r="D50" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="E50" t="s">
-        <v>335</v>
+        <v>430</v>
       </c>
       <c r="F50" t="s">
-        <v>336</v>
+        <v>431</v>
       </c>
       <c r="G50" t="s">
-        <v>337</v>
+        <v>432</v>
       </c>
       <c r="H50" t="s">
-        <v>338</v>
+        <v>433</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>339</v>
+        <v>74</v>
       </c>
       <c r="B51" t="s">
-        <v>340</v>
+        <v>434</v>
       </c>
       <c r="C51" t="s">
-        <v>185</v>
+        <v>301</v>
       </c>
       <c r="D51" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="E51" t="s">
-        <v>341</v>
+        <v>435</v>
       </c>
       <c r="F51" t="s">
-        <v>342</v>
+        <v>436</v>
       </c>
       <c r="G51" t="s">
-        <v>343</v>
+        <v>437</v>
       </c>
       <c r="H51" t="s">
-        <v>344</v>
+        <v>438</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>345</v>
+        <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>346</v>
+        <v>439</v>
       </c>
       <c r="C52" t="s">
-        <v>280</v>
+        <v>383</v>
       </c>
       <c r="D52" t="s">
-        <v>89</v>
+        <v>219</v>
       </c>
       <c r="E52" t="s">
-        <v>347</v>
+        <v>440</v>
       </c>
       <c r="F52" t="s">
-        <v>348</v>
+        <v>441</v>
       </c>
       <c r="G52" t="s">
-        <v>349</v>
+        <v>442</v>
       </c>
       <c r="H52" t="s">
-        <v>350</v>
+        <v>443</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>351</v>
+        <v>100</v>
       </c>
       <c r="B53" t="s">
-        <v>352</v>
+        <v>444</v>
       </c>
       <c r="C53" t="s">
-        <v>169</v>
+        <v>287</v>
       </c>
       <c r="D53" t="s">
-        <v>170</v>
+        <v>288</v>
       </c>
       <c r="E53" t="s">
-        <v>353</v>
+        <v>445</v>
       </c>
       <c r="F53" t="s">
-        <v>238</v>
+        <v>346</v>
       </c>
       <c r="G53" t="s">
-        <v>354</v>
+        <v>446</v>
       </c>
       <c r="H53" t="s">
-        <v>355</v>
+        <v>447</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>356</v>
+        <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>357</v>
+        <v>448</v>
       </c>
       <c r="C54" t="s">
-        <v>358</v>
+        <v>449</v>
       </c>
       <c r="D54" t="s">
-        <v>89</v>
+        <v>219</v>
       </c>
       <c r="E54" t="s">
-        <v>359</v>
+        <v>450</v>
       </c>
       <c r="F54" t="s">
-        <v>323</v>
+        <v>420</v>
       </c>
       <c r="G54" t="s">
-        <v>360</v>
+        <v>451</v>
       </c>
       <c r="H54" t="s">
-        <v>361</v>
+        <v>452</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>362</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>363</v>
+        <v>453</v>
       </c>
       <c r="C55" t="s">
-        <v>364</v>
+        <v>454</v>
       </c>
       <c r="D55" t="s">
-        <v>97</v>
+        <v>226</v>
       </c>
       <c r="E55" t="s">
-        <v>365</v>
+        <v>455</v>
       </c>
       <c r="F55" t="s">
-        <v>366</v>
+        <v>456</v>
       </c>
       <c r="G55" t="s">
-        <v>367</v>
+        <v>457</v>
       </c>
       <c r="H55" t="s">
-        <v>368</v>
+        <v>458</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>369</v>
+        <v>129</v>
       </c>
       <c r="B56" t="s">
-        <v>370</v>
+        <v>459</v>
       </c>
       <c r="C56" t="s">
-        <v>371</v>
+        <v>460</v>
       </c>
       <c r="D56" t="s">
-        <v>178</v>
+        <v>295</v>
       </c>
       <c r="E56" t="s">
-        <v>372</v>
+        <v>461</v>
       </c>
       <c r="F56" t="s">
-        <v>373</v>
+        <v>462</v>
       </c>
       <c r="G56" t="s">
-        <v>374</v>
+        <v>463</v>
       </c>
       <c r="H56" t="s">
-        <v>375</v>
+        <v>464</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>376</v>
+        <v>130</v>
       </c>
       <c r="B57" t="s">
-        <v>377</v>
+        <v>465</v>
       </c>
       <c r="C57" t="s">
-        <v>378</v>
+        <v>466</v>
       </c>
       <c r="D57" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E57" t="s">
-        <v>379</v>
+        <v>467</v>
       </c>
       <c r="F57" t="s">
-        <v>380</v>
+        <v>468</v>
       </c>
       <c r="G57" t="s">
-        <v>381</v>
+        <v>469</v>
       </c>
       <c r="H57" t="s">
-        <v>382</v>
+        <v>470</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>383</v>
+        <v>120</v>
       </c>
       <c r="B58" t="s">
-        <v>384</v>
+        <v>471</v>
       </c>
       <c r="C58" t="s">
-        <v>18</v>
+        <v>158</v>
       </c>
       <c r="D58" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E58" t="s">
-        <v>385</v>
+        <v>472</v>
       </c>
       <c r="F58" t="s">
-        <v>386</v>
+        <v>473</v>
       </c>
       <c r="G58" t="s">
-        <v>387</v>
+        <v>474</v>
       </c>
       <c r="H58" t="s">
-        <v>388</v>
+        <v>475</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>389</v>
+        <v>14</v>
       </c>
       <c r="B59" t="s">
-        <v>390</v>
+        <v>476</v>
       </c>
       <c r="C59" t="s">
-        <v>33</v>
+        <v>171</v>
       </c>
       <c r="D59" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E59" t="s">
-        <v>391</v>
+        <v>477</v>
       </c>
       <c r="F59" t="s">
-        <v>392</v>
+        <v>478</v>
       </c>
       <c r="G59" t="s">
-        <v>393</v>
+        <v>479</v>
       </c>
       <c r="H59" t="s">
-        <v>394</v>
+        <v>480</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>395</v>
+        <v>92</v>
       </c>
       <c r="B60" t="s">
-        <v>396</v>
+        <v>481</v>
       </c>
       <c r="C60" t="s">
-        <v>397</v>
+        <v>482</v>
       </c>
       <c r="D60" t="s">
-        <v>217</v>
+        <v>328</v>
       </c>
       <c r="E60" t="s">
-        <v>398</v>
+        <v>483</v>
       </c>
       <c r="F60" t="s">
-        <v>399</v>
+        <v>484</v>
       </c>
       <c r="G60" t="s">
-        <v>400</v>
+        <v>485</v>
       </c>
       <c r="H60" t="s">
-        <v>401</v>
+        <v>486</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>402</v>
+        <v>81</v>
       </c>
       <c r="B61" t="s">
-        <v>403</v>
+        <v>487</v>
       </c>
       <c r="C61" t="s">
-        <v>104</v>
+        <v>232</v>
       </c>
       <c r="D61" t="s">
-        <v>112</v>
+        <v>239</v>
       </c>
       <c r="E61" t="s">
-        <v>404</v>
+        <v>488</v>
       </c>
       <c r="F61" t="s">
-        <v>405</v>
+        <v>489</v>
       </c>
       <c r="G61" t="s">
-        <v>406</v>
+        <v>490</v>
       </c>
       <c r="H61" t="s">
-        <v>407</v>
+        <v>491</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>408</v>
+        <v>30</v>
       </c>
       <c r="B62" t="s">
-        <v>409</v>
+        <v>492</v>
       </c>
       <c r="C62" t="s">
-        <v>131</v>
+        <v>255</v>
       </c>
       <c r="D62" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="E62" t="s">
-        <v>410</v>
+        <v>493</v>
       </c>
       <c r="F62" t="s">
-        <v>411</v>
+        <v>494</v>
       </c>
       <c r="G62" t="s">
-        <v>412</v>
+        <v>495</v>
       </c>
       <c r="H62" t="s">
-        <v>413</v>
+        <v>496</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>414</v>
+        <v>138</v>
       </c>
       <c r="B63" t="s">
-        <v>415</v>
+        <v>497</v>
       </c>
       <c r="C63" t="s">
-        <v>416</v>
+        <v>498</v>
       </c>
       <c r="D63" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E63" t="s">
-        <v>417</v>
+        <v>499</v>
       </c>
       <c r="F63" t="s">
-        <v>418</v>
+        <v>500</v>
       </c>
       <c r="G63" t="s">
-        <v>419</v>
+        <v>501</v>
       </c>
       <c r="H63" t="s">
-        <v>420</v>
+        <v>502</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>421</v>
+        <v>35</v>
       </c>
       <c r="B64" t="s">
-        <v>422</v>
+        <v>503</v>
       </c>
       <c r="C64" t="s">
-        <v>423</v>
+        <v>504</v>
       </c>
       <c r="D64" t="s">
-        <v>89</v>
+        <v>219</v>
       </c>
       <c r="E64" t="s">
-        <v>424</v>
+        <v>505</v>
       </c>
       <c r="F64" t="s">
-        <v>425</v>
+        <v>506</v>
       </c>
       <c r="G64" t="s">
-        <v>426</v>
+        <v>507</v>
       </c>
       <c r="H64" t="s">
-        <v>427</v>
+        <v>508</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>428</v>
+        <v>43</v>
       </c>
       <c r="B65" t="s">
-        <v>429</v>
+        <v>509</v>
       </c>
       <c r="C65" t="s">
-        <v>430</v>
+        <v>510</v>
       </c>
       <c r="D65" t="s">
-        <v>97</v>
+        <v>226</v>
       </c>
       <c r="E65" t="s">
-        <v>431</v>
+        <v>511</v>
       </c>
       <c r="F65" t="s">
-        <v>432</v>
+        <v>512</v>
       </c>
       <c r="G65" t="s">
-        <v>433</v>
+        <v>513</v>
       </c>
       <c r="H65" t="s">
-        <v>434</v>
+        <v>514</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>435</v>
+        <v>44</v>
       </c>
       <c r="B66" t="s">
-        <v>436</v>
+        <v>515</v>
       </c>
       <c r="C66" t="s">
-        <v>364</v>
+        <v>454</v>
       </c>
       <c r="D66" t="s">
-        <v>97</v>
+        <v>226</v>
       </c>
       <c r="E66" t="s">
-        <v>437</v>
+        <v>516</v>
       </c>
       <c r="F66" t="s">
-        <v>438</v>
+        <v>517</v>
       </c>
       <c r="G66" t="s">
-        <v>439</v>
+        <v>518</v>
       </c>
       <c r="H66" t="s">
-        <v>440</v>
+        <v>519</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>441</v>
+        <v>13</v>
       </c>
       <c r="B67" t="s">
-        <v>442</v>
+        <v>520</v>
       </c>
       <c r="C67" t="s">
-        <v>443</v>
+        <v>521</v>
       </c>
       <c r="D67" t="s">
-        <v>314</v>
+        <v>412</v>
       </c>
       <c r="E67" t="s">
-        <v>444</v>
+        <v>522</v>
       </c>
       <c r="F67" t="s">
-        <v>445</v>
+        <v>523</v>
       </c>
       <c r="G67" t="s">
-        <v>446</v>
+        <v>524</v>
       </c>
       <c r="H67" t="s">
-        <v>447</v>
+        <v>525</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>448</v>
+        <v>48</v>
       </c>
       <c r="B68" t="s">
-        <v>449</v>
+        <v>526</v>
       </c>
       <c r="C68" t="s">
-        <v>450</v>
+        <v>527</v>
       </c>
       <c r="D68" t="s">
-        <v>178</v>
+        <v>295</v>
       </c>
       <c r="E68" t="s">
-        <v>451</v>
+        <v>528</v>
       </c>
       <c r="F68" t="s">
-        <v>452</v>
+        <v>529</v>
       </c>
       <c r="G68" t="s">
-        <v>453</v>
+        <v>530</v>
       </c>
       <c r="H68" t="s">
-        <v>454</v>
+        <v>531</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>455</v>
+        <v>86</v>
       </c>
       <c r="B69" t="s">
-        <v>456</v>
+        <v>532</v>
       </c>
       <c r="C69" t="s">
-        <v>457</v>
+        <v>533</v>
       </c>
       <c r="D69" t="s">
-        <v>314</v>
+        <v>412</v>
       </c>
       <c r="E69" t="s">
-        <v>458</v>
+        <v>534</v>
       </c>
       <c r="F69" t="s">
-        <v>459</v>
+        <v>535</v>
       </c>
       <c r="G69" t="s">
-        <v>460</v>
+        <v>536</v>
       </c>
       <c r="H69" t="s">
-        <v>461</v>
+        <v>537</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>462</v>
+        <v>78</v>
       </c>
       <c r="B70" t="s">
-        <v>463</v>
+        <v>538</v>
       </c>
       <c r="C70" t="s">
-        <v>185</v>
+        <v>301</v>
       </c>
       <c r="D70" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="E70" t="s">
-        <v>464</v>
+        <v>539</v>
       </c>
       <c r="F70" t="s">
-        <v>465</v>
+        <v>540</v>
       </c>
       <c r="G70" t="s">
-        <v>466</v>
+        <v>541</v>
       </c>
       <c r="H70" t="s">
-        <v>467</v>
+        <v>542</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>468</v>
+        <v>140</v>
       </c>
       <c r="B71" t="s">
-        <v>469</v>
+        <v>543</v>
       </c>
       <c r="C71" t="s">
-        <v>111</v>
+        <v>238</v>
       </c>
       <c r="D71" t="s">
-        <v>97</v>
+        <v>226</v>
       </c>
       <c r="E71" t="s">
-        <v>470</v>
+        <v>544</v>
       </c>
       <c r="F71" t="s">
-        <v>471</v>
+        <v>545</v>
       </c>
       <c r="G71" t="s">
-        <v>472</v>
+        <v>546</v>
       </c>
       <c r="H71" t="s">
-        <v>473</v>
+        <v>547</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>474</v>
+        <v>45</v>
       </c>
       <c r="B72" t="s">
-        <v>475</v>
+        <v>548</v>
       </c>
       <c r="C72" t="s">
-        <v>476</v>
+        <v>549</v>
       </c>
       <c r="D72" t="s">
-        <v>89</v>
+        <v>219</v>
       </c>
       <c r="E72" t="s">
-        <v>477</v>
+        <v>550</v>
       </c>
       <c r="F72" t="s">
-        <v>478</v>
+        <v>551</v>
       </c>
       <c r="G72" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="H72" t="s">
-        <v>480</v>
+        <v>553</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>481</v>
+        <v>51</v>
       </c>
       <c r="B73" t="s">
-        <v>482</v>
+        <v>554</v>
       </c>
       <c r="C73" t="s">
-        <v>483</v>
+        <v>555</v>
       </c>
       <c r="D73" t="s">
-        <v>81</v>
+        <v>212</v>
       </c>
       <c r="E73" t="s">
-        <v>484</v>
+        <v>556</v>
       </c>
       <c r="F73" t="s">
-        <v>485</v>
+        <v>557</v>
       </c>
       <c r="G73" t="s">
-        <v>486</v>
+        <v>558</v>
       </c>
       <c r="H73" t="s">
-        <v>487</v>
+        <v>559</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>488</v>
+        <v>135</v>
       </c>
       <c r="B74" t="s">
-        <v>489</v>
+        <v>704</v>
       </c>
       <c r="C74" t="s">
-        <v>490</v>
+        <v>560</v>
       </c>
       <c r="D74" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E74" t="s">
-        <v>491</v>
+        <v>561</v>
       </c>
       <c r="F74" t="s">
-        <v>492</v>
+        <v>562</v>
       </c>
       <c r="G74" t="s">
-        <v>493</v>
+        <v>563</v>
       </c>
       <c r="H74" t="s">
-        <v>494</v>
+        <v>564</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>495</v>
+        <v>56</v>
       </c>
       <c r="B75" t="s">
-        <v>496</v>
+        <v>565</v>
       </c>
       <c r="C75" t="s">
-        <v>497</v>
+        <v>705</v>
       </c>
       <c r="D75" t="s">
-        <v>314</v>
+        <v>412</v>
       </c>
       <c r="E75" t="s">
-        <v>498</v>
+        <v>566</v>
       </c>
       <c r="F75" t="s">
-        <v>499</v>
+        <v>567</v>
       </c>
       <c r="G75" t="s">
-        <v>500</v>
+        <v>568</v>
       </c>
       <c r="H75" t="s">
-        <v>501</v>
+        <v>569</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>502</v>
+        <v>61</v>
       </c>
       <c r="B76" t="s">
-        <v>503</v>
+        <v>570</v>
       </c>
       <c r="C76" t="s">
-        <v>504</v>
+        <v>571</v>
       </c>
       <c r="D76" t="s">
-        <v>89</v>
+        <v>219</v>
       </c>
       <c r="E76" t="s">
-        <v>505</v>
+        <v>572</v>
       </c>
       <c r="F76" t="s">
-        <v>506</v>
+        <v>573</v>
       </c>
       <c r="G76" t="s">
-        <v>507</v>
+        <v>574</v>
       </c>
       <c r="H76" t="s">
-        <v>508</v>
+        <v>575</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>509</v>
+        <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>510</v>
+        <v>576</v>
       </c>
       <c r="C77" t="s">
-        <v>185</v>
+        <v>301</v>
       </c>
       <c r="D77" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="E77" t="s">
-        <v>511</v>
+        <v>577</v>
       </c>
       <c r="F77" t="s">
-        <v>512</v>
+        <v>578</v>
       </c>
       <c r="G77" t="s">
-        <v>513</v>
+        <v>579</v>
       </c>
       <c r="H77" t="s">
-        <v>514</v>
+        <v>580</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>515</v>
+        <v>143</v>
       </c>
       <c r="B78" t="s">
-        <v>516</v>
+        <v>581</v>
       </c>
       <c r="C78" t="s">
-        <v>517</v>
+        <v>582</v>
       </c>
       <c r="D78" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E78" t="s">
-        <v>518</v>
+        <v>583</v>
       </c>
       <c r="F78" t="s">
-        <v>519</v>
+        <v>584</v>
       </c>
       <c r="G78" t="s">
-        <v>520</v>
+        <v>585</v>
       </c>
       <c r="H78" t="s">
-        <v>521</v>
+        <v>586</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>522</v>
+        <v>59</v>
       </c>
       <c r="B79" t="s">
-        <v>523</v>
+        <v>587</v>
       </c>
       <c r="C79" t="s">
-        <v>150</v>
+        <v>271</v>
       </c>
       <c r="D79" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E79" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="F79" t="s">
-        <v>525</v>
+        <v>589</v>
       </c>
       <c r="G79" t="s">
-        <v>526</v>
+        <v>590</v>
       </c>
       <c r="H79" t="s">
-        <v>527</v>
+        <v>591</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>528</v>
+        <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>529</v>
+        <v>592</v>
       </c>
       <c r="C80" t="s">
-        <v>530</v>
+        <v>593</v>
       </c>
       <c r="D80" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E80" t="s">
-        <v>531</v>
+        <v>594</v>
       </c>
       <c r="F80" t="s">
-        <v>532</v>
+        <v>595</v>
       </c>
       <c r="G80" t="s">
-        <v>533</v>
+        <v>596</v>
       </c>
       <c r="H80" t="s">
-        <v>534</v>
+        <v>597</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>535</v>
+        <v>141</v>
       </c>
       <c r="B81" t="s">
-        <v>536</v>
+        <v>598</v>
       </c>
       <c r="C81" t="s">
-        <v>416</v>
+        <v>498</v>
       </c>
       <c r="D81" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E81" t="s">
-        <v>531</v>
+        <v>594</v>
       </c>
       <c r="F81" t="s">
-        <v>537</v>
+        <v>599</v>
       </c>
       <c r="G81" t="s">
-        <v>538</v>
+        <v>600</v>
       </c>
       <c r="H81" t="s">
-        <v>539</v>
+        <v>601</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>540</v>
+        <v>144</v>
       </c>
       <c r="B82" t="s">
-        <v>541</v>
+        <v>602</v>
       </c>
       <c r="C82" t="s">
-        <v>313</v>
+        <v>411</v>
       </c>
       <c r="D82" t="s">
-        <v>314</v>
+        <v>412</v>
       </c>
       <c r="E82" t="s">
-        <v>542</v>
+        <v>603</v>
       </c>
       <c r="F82" t="s">
-        <v>543</v>
+        <v>604</v>
       </c>
       <c r="G82" t="s">
-        <v>544</v>
+        <v>605</v>
       </c>
       <c r="H82" t="s">
-        <v>545</v>
+        <v>606</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>546</v>
+        <v>60</v>
       </c>
       <c r="B83" t="s">
-        <v>547</v>
+        <v>607</v>
       </c>
       <c r="C83" t="s">
-        <v>548</v>
+        <v>608</v>
       </c>
       <c r="D83" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E83" t="s">
-        <v>549</v>
+        <v>609</v>
       </c>
       <c r="F83" t="s">
-        <v>550</v>
+        <v>610</v>
       </c>
       <c r="G83" t="s">
-        <v>551</v>
+        <v>611</v>
       </c>
       <c r="H83" t="s">
-        <v>552</v>
+        <v>612</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>553</v>
+        <v>66</v>
       </c>
       <c r="B84" t="s">
-        <v>554</v>
+        <v>613</v>
       </c>
       <c r="C84" t="s">
-        <v>555</v>
+        <v>614</v>
       </c>
       <c r="D84" t="s">
-        <v>314</v>
+        <v>412</v>
       </c>
       <c r="E84" t="s">
-        <v>556</v>
+        <v>615</v>
       </c>
       <c r="F84" t="s">
-        <v>557</v>
+        <v>616</v>
       </c>
       <c r="G84" t="s">
-        <v>558</v>
+        <v>617</v>
       </c>
       <c r="H84" t="s">
-        <v>559</v>
+        <v>618</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>560</v>
+        <v>34</v>
       </c>
       <c r="B85" t="s">
-        <v>561</v>
+        <v>619</v>
       </c>
       <c r="C85" t="s">
-        <v>562</v>
+        <v>620</v>
       </c>
       <c r="D85" t="s">
-        <v>170</v>
+        <v>288</v>
       </c>
       <c r="E85" t="s">
-        <v>563</v>
+        <v>621</v>
       </c>
       <c r="F85" t="s">
-        <v>564</v>
+        <v>622</v>
       </c>
       <c r="G85" t="s">
-        <v>565</v>
+        <v>623</v>
       </c>
       <c r="H85" t="s">
-        <v>566</v>
+        <v>624</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>567</v>
+        <v>41</v>
       </c>
       <c r="B86" t="s">
-        <v>568</v>
+        <v>625</v>
       </c>
       <c r="C86" t="s">
-        <v>423</v>
+        <v>504</v>
       </c>
       <c r="D86" t="s">
-        <v>89</v>
+        <v>219</v>
       </c>
       <c r="E86" t="s">
-        <v>569</v>
+        <v>626</v>
       </c>
       <c r="F86" t="s">
-        <v>570</v>
+        <v>627</v>
       </c>
       <c r="G86" t="s">
-        <v>571</v>
+        <v>628</v>
       </c>
       <c r="H86" t="s">
-        <v>572</v>
+        <v>629</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>573</v>
+        <v>79</v>
       </c>
       <c r="B87" t="s">
-        <v>574</v>
+        <v>630</v>
       </c>
       <c r="C87" t="s">
-        <v>243</v>
+        <v>350</v>
       </c>
       <c r="D87" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E87" t="s">
-        <v>575</v>
+        <v>631</v>
       </c>
       <c r="F87" t="s">
-        <v>576</v>
+        <v>632</v>
       </c>
       <c r="G87" t="s">
-        <v>577</v>
+        <v>633</v>
       </c>
       <c r="H87" t="s">
-        <v>578</v>
+        <v>634</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>579</v>
+        <v>91</v>
       </c>
       <c r="B88" t="s">
-        <v>580</v>
+        <v>635</v>
       </c>
       <c r="C88" t="s">
-        <v>104</v>
+        <v>232</v>
       </c>
       <c r="D88" t="s">
-        <v>112</v>
+        <v>239</v>
       </c>
       <c r="E88" t="s">
-        <v>575</v>
+        <v>631</v>
       </c>
       <c r="F88" t="s">
-        <v>581</v>
+        <v>636</v>
       </c>
       <c r="G88" t="s">
-        <v>582</v>
+        <v>637</v>
       </c>
       <c r="H88" t="s">
-        <v>583</v>
+        <v>638</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>584</v>
+        <v>118</v>
       </c>
       <c r="B89" t="s">
-        <v>585</v>
+        <v>639</v>
       </c>
       <c r="C89" t="s">
-        <v>586</v>
+        <v>640</v>
       </c>
       <c r="D89" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="E89" t="s">
-        <v>587</v>
+        <v>641</v>
       </c>
       <c r="F89" t="s">
-        <v>588</v>
+        <v>642</v>
       </c>
       <c r="G89" t="s">
-        <v>589</v>
+        <v>643</v>
       </c>
       <c r="H89" t="s">
-        <v>590</v>
+        <v>644</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>591</v>
+        <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>592</v>
+        <v>645</v>
       </c>
       <c r="C90" t="s">
-        <v>430</v>
+        <v>510</v>
       </c>
       <c r="D90" t="s">
-        <v>97</v>
+        <v>226</v>
       </c>
       <c r="E90" t="s">
-        <v>593</v>
+        <v>646</v>
       </c>
       <c r="F90" t="s">
-        <v>238</v>
+        <v>346</v>
       </c>
       <c r="G90" t="s">
-        <v>594</v>
+        <v>647</v>
       </c>
       <c r="H90" t="s">
-        <v>595</v>
+        <v>648</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>596</v>
+        <v>121</v>
       </c>
       <c r="B91" t="s">
-        <v>597</v>
+        <v>649</v>
       </c>
       <c r="C91" t="s">
-        <v>586</v>
+        <v>640</v>
       </c>
       <c r="D91" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="E91" t="s">
-        <v>598</v>
+        <v>650</v>
       </c>
       <c r="F91" t="s">
-        <v>599</v>
+        <v>651</v>
       </c>
       <c r="G91" t="s">
-        <v>600</v>
+        <v>652</v>
       </c>
       <c r="H91" t="s">
-        <v>601</v>
+        <v>653</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>602</v>
+        <v>67</v>
       </c>
       <c r="B92" t="s">
-        <v>603</v>
+        <v>654</v>
       </c>
       <c r="C92" t="s">
-        <v>504</v>
+        <v>571</v>
       </c>
       <c r="D92" t="s">
-        <v>89</v>
+        <v>219</v>
       </c>
       <c r="E92" t="s">
-        <v>604</v>
+        <v>655</v>
       </c>
       <c r="F92" t="s">
-        <v>605</v>
+        <v>656</v>
       </c>
       <c r="G92" t="s">
-        <v>606</v>
+        <v>657</v>
       </c>
       <c r="H92" t="s">
-        <v>607</v>
+        <v>658</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>608</v>
+        <v>49</v>
       </c>
       <c r="B93" t="s">
-        <v>609</v>
+        <v>659</v>
       </c>
       <c r="C93" t="s">
-        <v>476</v>
+        <v>549</v>
       </c>
       <c r="D93" t="s">
-        <v>89</v>
+        <v>219</v>
       </c>
       <c r="E93" t="s">
-        <v>610</v>
+        <v>660</v>
       </c>
       <c r="F93" t="s">
-        <v>380</v>
+        <v>468</v>
       </c>
       <c r="G93" t="s">
-        <v>611</v>
+        <v>661</v>
       </c>
       <c r="H93" t="s">
-        <v>612</v>
+        <v>662</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>613</v>
+        <v>31</v>
       </c>
       <c r="B94" t="s">
-        <v>614</v>
+        <v>663</v>
       </c>
       <c r="C94" t="s">
-        <v>358</v>
+        <v>449</v>
       </c>
       <c r="D94" t="s">
-        <v>89</v>
+        <v>219</v>
       </c>
       <c r="E94" t="s">
-        <v>615</v>
+        <v>664</v>
       </c>
       <c r="F94" t="s">
-        <v>616</v>
+        <v>665</v>
       </c>
       <c r="G94" t="s">
-        <v>617</v>
+        <v>666</v>
       </c>
       <c r="H94" t="s">
-        <v>618</v>
+        <v>667</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>619</v>
+        <v>109</v>
       </c>
       <c r="B95" t="s">
-        <v>620</v>
+        <v>668</v>
       </c>
       <c r="C95" t="s">
-        <v>47</v>
+        <v>183</v>
       </c>
       <c r="D95" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="E95" t="s">
-        <v>621</v>
+        <v>669</v>
       </c>
       <c r="F95" t="s">
-        <v>570</v>
+        <v>627</v>
       </c>
       <c r="G95" t="s">
-        <v>622</v>
+        <v>670</v>
       </c>
       <c r="H95" t="s">
-        <v>623</v>
+        <v>671</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>624</v>
+        <v>71</v>
       </c>
       <c r="B96" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C96" t="s">
-        <v>504</v>
+        <v>571</v>
       </c>
       <c r="D96" t="s">
-        <v>89</v>
+        <v>219</v>
       </c>
       <c r="E96" t="s">
-        <v>626</v>
+        <v>673</v>
       </c>
       <c r="F96" t="s">
-        <v>425</v>
+        <v>506</v>
       </c>
       <c r="G96" t="s">
-        <v>627</v>
+        <v>674</v>
       </c>
       <c r="H96" t="s">
-        <v>628</v>
+        <v>675</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>629</v>
+        <v>128</v>
       </c>
       <c r="B97" t="s">
-        <v>630</v>
+        <v>676</v>
       </c>
       <c r="C97" t="s">
-        <v>631</v>
+        <v>677</v>
       </c>
       <c r="D97" t="s">
-        <v>97</v>
+        <v>226</v>
       </c>
       <c r="E97" t="s">
-        <v>632</v>
+        <v>678</v>
       </c>
       <c r="F97" t="s">
-        <v>633</v>
+        <v>679</v>
       </c>
       <c r="G97" t="s">
-        <v>634</v>
+        <v>680</v>
       </c>
       <c r="H97" t="s">
-        <v>635</v>
+        <v>681</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>636</v>
+        <v>95</v>
       </c>
       <c r="B98" t="s">
-        <v>637</v>
+        <v>682</v>
       </c>
       <c r="C98" t="s">
-        <v>104</v>
+        <v>232</v>
       </c>
       <c r="D98" t="s">
-        <v>112</v>
+        <v>239</v>
       </c>
       <c r="E98" t="s">
-        <v>638</v>
+        <v>683</v>
       </c>
       <c r="F98" t="s">
-        <v>639</v>
+        <v>684</v>
       </c>
       <c r="G98" t="s">
-        <v>640</v>
+        <v>685</v>
       </c>
       <c r="H98" t="s">
-        <v>641</v>
+        <v>686</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>642</v>
+        <v>133</v>
       </c>
       <c r="B99" t="s">
-        <v>643</v>
+        <v>687</v>
       </c>
       <c r="C99" t="s">
-        <v>644</v>
+        <v>688</v>
       </c>
       <c r="D99" t="s">
-        <v>314</v>
+        <v>412</v>
       </c>
       <c r="E99" t="s">
-        <v>645</v>
+        <v>689</v>
       </c>
       <c r="F99" t="s">
-        <v>646</v>
+        <v>690</v>
       </c>
       <c r="G99" t="s">
-        <v>647</v>
+        <v>691</v>
       </c>
       <c r="H99" t="s">
-        <v>648</v>
+        <v>692</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>649</v>
+        <v>17</v>
       </c>
       <c r="B100" t="s">
-        <v>650</v>
+        <v>693</v>
       </c>
       <c r="C100" t="s">
-        <v>651</v>
+        <v>694</v>
       </c>
       <c r="D100" t="s">
-        <v>112</v>
+        <v>239</v>
       </c>
       <c r="E100" t="s">
-        <v>652</v>
+        <v>695</v>
       </c>
       <c r="F100" t="s">
-        <v>653</v>
+        <v>696</v>
       </c>
       <c r="G100" t="s">
-        <v>654</v>
+        <v>697</v>
       </c>
       <c r="H100" t="s">
-        <v>655</v>
+        <v>698</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>656</v>
+        <v>113</v>
       </c>
       <c r="B101" t="s">
-        <v>657</v>
+        <v>699</v>
       </c>
       <c r="C101" t="s">
-        <v>47</v>
+        <v>183</v>
       </c>
       <c r="D101" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="E101" t="s">
-        <v>658</v>
+        <v>700</v>
       </c>
       <c r="F101" t="s">
-        <v>659</v>
+        <v>701</v>
       </c>
       <c r="G101" t="s">
-        <v>660</v>
+        <v>702</v>
       </c>
       <c r="H101" t="s">
-        <v>661</v>
+        <v>703</v>
       </c>
     </row>
   </sheetData>
@@ -5641,9 +5650,9 @@
     <col min="13" max="13" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
-        <v>662</v>
+        <v>0</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -5660,7 +5669,7 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
-        <v>663</v>
+        <v>1</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -5675,9 +5684,9 @@
       <c r="L2" s="8"/>
       <c r="M2" s="8"/>
     </row>
-    <row r="5" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
-        <v>664</v>
+        <v>2</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -5694,7 +5703,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>665</v>
+        <v>3</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -5711,22 +5720,22 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>666</v>
+        <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>667</v>
+        <v>5</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="7" t="s">
-        <v>668</v>
+        <v>6</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
       <c r="J7" s="7" t="s">
-        <v>669</v>
+        <v>7</v>
       </c>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
@@ -5734,48 +5743,48 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
-        <v>670</v>
+        <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>670</v>
+        <v>8</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>670</v>
+        <v>8</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>671</v>
+        <v>12</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>441</v>
+        <v>13</v>
       </c>
       <c r="C9" s="6" t="str">
         <f>IFERROR(VLOOKUP($B9,Data!$A:$D,4,FALSE),"")</f>
@@ -5790,7 +5799,7 @@
         <v>Dr. Daniel Press and Dr. Hsueh-Sheng Chiang</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>389</v>
+        <v>14</v>
       </c>
       <c r="G9" s="6" t="str">
         <f>IFERROR(VLOOKUP($F9,Data!$A:$D,4,FALSE),"")</f>
@@ -5805,7 +5814,7 @@
         <v>Prof. Vivek Venkatachalam</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>421</v>
+        <v>15</v>
       </c>
       <c r="K9" s="6" t="str">
         <f>IFERROR(VLOOKUP($J9,Data!$A:$D,4,FALSE),"")</f>
@@ -5813,19 +5822,19 @@
       </c>
       <c r="L9" s="6" t="str">
         <f>IFERROR(VLOOKUP($J9,Data!$A:$D,2,FALSE),"")</f>
-        <v>Resolving a Conjecture on Stack-Sorting</v>
+        <v>On Counting Prime Solutions to Quadratic Forms via the Hardy-Littlewood Circle Method</v>
       </c>
       <c r="M9" s="6" t="str">
         <f>IFERROR(VLOOKUP($J9,Data!$A:$D,3,FALSE),"")</f>
-        <v>Ryota Inagaki</v>
+        <v>Siqi Wu</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>672</v>
+        <v>16</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>649</v>
+        <v>17</v>
       </c>
       <c r="C10" s="6" t="str">
         <f>IFERROR(VLOOKUP($B10,Data!$A:$D,4,FALSE),"")</f>
@@ -5840,7 +5849,7 @@
         <v>Prof. Paul O'Gorman</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="G10" s="6" t="str">
         <f>IFERROR(VLOOKUP($F10,Data!$A:$D,4,FALSE),"")</f>
@@ -5855,7 +5864,7 @@
         <v>Prof. Vivek Venkatachalam</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>567</v>
+        <v>19</v>
       </c>
       <c r="K10" s="6" t="str">
         <f>IFERROR(VLOOKUP($J10,Data!$A:$D,4,FALSE),"")</f>
@@ -5863,34 +5872,34 @@
       </c>
       <c r="L10" s="6" t="str">
         <f>IFERROR(VLOOKUP($J10,Data!$A:$D,2,FALSE),"")</f>
-        <v>Critical Groups of Signed Subdivided Wheels</v>
+        <v>Sphere Packing on Grassmannians</v>
       </c>
       <c r="M10" s="6" t="str">
         <f>IFERROR(VLOOKUP($J10,Data!$A:$D,3,FALSE),"")</f>
-        <v>Ryota Inagaki</v>
+        <v>Siqi Wu</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>673</v>
+        <v>20</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>502</v>
+        <v>21</v>
       </c>
       <c r="C11" s="6" t="str">
         <f>IFERROR(VLOOKUP($B11,Data!$A:$D,4,FALSE),"")</f>
-        <v>Math</v>
+        <v>Computer Science &amp; AI</v>
       </c>
       <c r="D11" s="6" t="str">
         <f>IFERROR(VLOOKUP($B11,Data!$A:$D,2,FALSE),"")</f>
-        <v>Simplified Volume Formulas for Tetrahedron by Edge-length Symmetry Class</v>
+        <v>Liquid Foundation Models as Medical Assistants</v>
       </c>
       <c r="E11" s="6" t="str">
         <f>IFERROR(VLOOKUP($B11,Data!$A:$D,3,FALSE),"")</f>
-        <v>Prof. Eric Grinberg</v>
+        <v>Dr. Bo Wu</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>235</v>
+        <v>22</v>
       </c>
       <c r="G11" s="6" t="str">
         <f>IFERROR(VLOOKUP($F11,Data!$A:$D,4,FALSE),"")</f>
@@ -5905,7 +5914,7 @@
         <v>Prof. Vivek Venkatachalam</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="K11" s="6" t="str">
         <f>IFERROR(VLOOKUP($J11,Data!$A:$D,4,FALSE),"")</f>
@@ -5913,49 +5922,49 @@
       </c>
       <c r="L11" s="6" t="str">
         <f>IFERROR(VLOOKUP($J11,Data!$A:$D,2,FALSE),"")</f>
-        <v>On Counting Prime Solutions to Quadratic Forms via the Hardy-Littlewood Circle Method</v>
+        <v>Temporal Preferential Attachment Trees</v>
       </c>
       <c r="M11" s="6" t="str">
         <f>IFERROR(VLOOKUP($J11,Data!$A:$D,3,FALSE),"")</f>
-        <v>Siqi Wu</v>
+        <v>Hang Du</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>674</v>
+        <v>24</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>602</v>
+        <v>25</v>
       </c>
       <c r="C12" s="6" t="str">
         <f>IFERROR(VLOOKUP($B12,Data!$A:$D,4,FALSE),"")</f>
-        <v>Math</v>
+        <v>Computer Science &amp; AI</v>
       </c>
       <c r="D12" s="6" t="str">
         <f>IFERROR(VLOOKUP($B12,Data!$A:$D,2,FALSE),"")</f>
-        <v>Enumerating Index-Two and Index-Three Nilpotent Matrices in Symplectic Lie Algebras</v>
+        <v>Teaching a Medical Vision-Language Model with Automatic Feedback</v>
       </c>
       <c r="E12" s="6" t="str">
         <f>IFERROR(VLOOKUP($B12,Data!$A:$D,3,FALSE),"")</f>
-        <v>Prof. Eric Grinberg</v>
+        <v>Dr. Bo Wu</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>356</v>
+        <v>26</v>
       </c>
       <c r="G12" s="6" t="str">
         <f>IFERROR(VLOOKUP($F12,Data!$A:$D,4,FALSE),"")</f>
-        <v>Math</v>
+        <v>Computer Science &amp; AI</v>
       </c>
       <c r="H12" s="6" t="str">
         <f>IFERROR(VLOOKUP($F12,Data!$A:$D,2,FALSE),"")</f>
-        <v>Heat Evolution on Graphs</v>
+        <v>The Center Configuration Problem for Single-Robot Reconfiguration</v>
       </c>
       <c r="I12" s="6" t="str">
         <f>IFERROR(VLOOKUP($F12,Data!$A:$D,3,FALSE),"")</f>
-        <v>Alexander McWeeney</v>
+        <v>Timothy Gomez</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>248</v>
+        <v>27</v>
       </c>
       <c r="K12" s="6" t="str">
         <f>IFERROR(VLOOKUP($J12,Data!$A:$D,4,FALSE),"")</f>
@@ -5963,69 +5972,69 @@
       </c>
       <c r="L12" s="6" t="str">
         <f>IFERROR(VLOOKUP($J12,Data!$A:$D,2,FALSE),"")</f>
-        <v>Sphere Packing on Grassmannians</v>
+        <v>Heat Evolution on Graphs</v>
       </c>
       <c r="M12" s="6" t="str">
         <f>IFERROR(VLOOKUP($J12,Data!$A:$D,3,FALSE),"")</f>
-        <v>Siqi Wu</v>
+        <v>Alexander McWeeney</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>675</v>
+        <v>28</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>624</v>
+        <v>29</v>
       </c>
       <c r="C13" s="6" t="str">
         <f>IFERROR(VLOOKUP($B13,Data!$A:$D,4,FALSE),"")</f>
-        <v>Math</v>
+        <v>Computer Science &amp; AI</v>
       </c>
       <c r="D13" s="6" t="str">
         <f>IFERROR(VLOOKUP($B13,Data!$A:$D,2,FALSE),"")</f>
-        <v>Triangular Taxicabs</v>
+        <v>Crown–Root Segmentation in Dental CBCT Using Anatomically Guided Synthetic Annotation</v>
       </c>
       <c r="E13" s="6" t="str">
         <f>IFERROR(VLOOKUP($B13,Data!$A:$D,3,FALSE),"")</f>
-        <v>Prof. Eric Grinberg</v>
+        <v>Dr. Bo Wu</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>613</v>
+        <v>30</v>
       </c>
       <c r="G13" s="6" t="str">
         <f>IFERROR(VLOOKUP($F13,Data!$A:$D,4,FALSE),"")</f>
-        <v>Math</v>
+        <v>Computer Science &amp; AI</v>
       </c>
       <c r="H13" s="6" t="str">
         <f>IFERROR(VLOOKUP($F13,Data!$A:$D,2,FALSE),"")</f>
-        <v>Asymptotics for Curve Shortening Flow with Boundary</v>
+        <v>Before the Final Assembly: Temporal Leakage and Process Privacy in Covert Tile Automata</v>
       </c>
       <c r="I13" s="6" t="str">
         <f>IFERROR(VLOOKUP($F13,Data!$A:$D,3,FALSE),"")</f>
-        <v>Alexander McWeeney</v>
+        <v>Timothy Gomez</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>129</v>
+        <v>31</v>
       </c>
       <c r="K13" s="6" t="str">
         <f>IFERROR(VLOOKUP($J13,Data!$A:$D,4,FALSE),"")</f>
-        <v>Computer Science &amp; AI</v>
+        <v>Math</v>
       </c>
       <c r="L13" s="6" t="str">
         <f>IFERROR(VLOOKUP($J13,Data!$A:$D,2,FALSE),"")</f>
-        <v>The Center Configuration Problem for Single-Robot Reconfiguration</v>
+        <v>Asymptotics for Curve Shortening Flow with Boundary</v>
       </c>
       <c r="M13" s="6" t="str">
         <f>IFERROR(VLOOKUP($J13,Data!$A:$D,3,FALSE),"")</f>
-        <v>Timothy Gomez</v>
+        <v>Alexander McWeeney</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>676</v>
+        <v>32</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>297</v>
+        <v>33</v>
       </c>
       <c r="C14" s="6" t="str">
         <f>IFERROR(VLOOKUP($B14,Data!$A:$D,4,FALSE),"")</f>
@@ -6040,7 +6049,7 @@
         <v>Prof. Sara Seager</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>560</v>
+        <v>34</v>
       </c>
       <c r="G14" s="6" t="str">
         <f>IFERROR(VLOOKUP($F14,Data!$A:$D,4,FALSE),"")</f>
@@ -6055,24 +6064,24 @@
         <v>Dr. James Sullivan</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>408</v>
+        <v>35</v>
       </c>
       <c r="K14" s="6" t="str">
         <f>IFERROR(VLOOKUP($J14,Data!$A:$D,4,FALSE),"")</f>
-        <v>Computer Science &amp; AI</v>
+        <v>Math</v>
       </c>
       <c r="L14" s="6" t="str">
         <f>IFERROR(VLOOKUP($J14,Data!$A:$D,2,FALSE),"")</f>
-        <v>Before the Final Assembly: Temporal Leakage and Process Privacy in Covert Tile Automata</v>
+        <v>Resolving a Conjecture on Stack-Sorting</v>
       </c>
       <c r="M14" s="6" t="str">
         <f>IFERROR(VLOOKUP($J14,Data!$A:$D,3,FALSE),"")</f>
-        <v>Timothy Gomez</v>
+        <v>Ryota Inagaki</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
-        <v>677</v>
+        <v>36</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -6089,7 +6098,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
-        <v>678</v>
+        <v>37</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -6106,22 +6115,22 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>666</v>
+        <v>4</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>667</v>
+        <v>5</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
       <c r="F17" s="7" t="s">
-        <v>668</v>
+        <v>6</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
       <c r="J17" s="7" t="s">
-        <v>669</v>
+        <v>7</v>
       </c>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
@@ -6129,98 +6138,98 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B18" s="3" t="s">
-        <v>670</v>
+        <v>8</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>670</v>
+        <v>8</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>670</v>
+        <v>8</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>679</v>
+        <v>38</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>319</v>
+        <v>39</v>
       </c>
       <c r="C19" s="6" t="str">
         <f>IFERROR(VLOOKUP($B19,Data!$A:$D,4,FALSE),"")</f>
-        <v>Math</v>
+        <v>Astronomy &amp; Planetary Science</v>
       </c>
       <c r="D19" s="6" t="str">
         <f>IFERROR(VLOOKUP($B19,Data!$A:$D,2,FALSE),"")</f>
-        <v>Temporal Preferential Attachment Trees</v>
+        <v>Searching for Eclipses in X-Ray Sources</v>
       </c>
       <c r="E19" s="6" t="str">
         <f>IFERROR(VLOOKUP($B19,Data!$A:$D,3,FALSE),"")</f>
-        <v>Hang Du</v>
+        <v>Dr. Rosanne Di Stefano</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>474</v>
+        <v>40</v>
       </c>
       <c r="G19" s="6" t="str">
         <f>IFERROR(VLOOKUP($F19,Data!$A:$D,4,FALSE),"")</f>
-        <v>Math</v>
+        <v>Physics</v>
       </c>
       <c r="H19" s="6" t="str">
         <f>IFERROR(VLOOKUP($F19,Data!$A:$D,2,FALSE),"")</f>
-        <v>On Supersingular Isogeny Graphs of Drinfeld Modules</v>
+        <v>Hybrid controls strategy for Automatic Laser Beam Alignment</v>
       </c>
       <c r="I19" s="6" t="str">
         <f>IFERROR(VLOOKUP($F19,Data!$A:$D,3,FALSE),"")</f>
-        <v>Ayan Nath</v>
+        <v>Prof. Vladan Vuletic</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>222</v>
+        <v>41</v>
       </c>
       <c r="K19" s="6" t="str">
         <f>IFERROR(VLOOKUP($J19,Data!$A:$D,4,FALSE),"")</f>
-        <v>Astronomy &amp; Planetary Science</v>
+        <v>Math</v>
       </c>
       <c r="L19" s="6" t="str">
         <f>IFERROR(VLOOKUP($J19,Data!$A:$D,2,FALSE),"")</f>
-        <v>Searching for Eclipses in X-Ray Sources</v>
+        <v>Critical Groups of Signed Subdivided Wheels</v>
       </c>
       <c r="M19" s="6" t="str">
         <f>IFERROR(VLOOKUP($J19,Data!$A:$D,3,FALSE),"")</f>
-        <v>Dr. Rosanne Di Stefano</v>
+        <v>Ryota Inagaki</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>680</v>
+        <v>42</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>428</v>
+        <v>43</v>
       </c>
       <c r="C20" s="6" t="str">
         <f>IFERROR(VLOOKUP($B20,Data!$A:$D,4,FALSE),"")</f>
@@ -6235,42 +6244,42 @@
         <v>Ashu Tripathi</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>608</v>
+        <v>44</v>
       </c>
       <c r="G20" s="6" t="str">
         <f>IFERROR(VLOOKUP($F20,Data!$A:$D,4,FALSE),"")</f>
-        <v>Math</v>
+        <v>Physics</v>
       </c>
       <c r="H20" s="6" t="str">
         <f>IFERROR(VLOOKUP($F20,Data!$A:$D,2,FALSE),"")</f>
-        <v>Open Cases of the Colmez Conjecture</v>
+        <v>Optical pulse shaping for quantum-enhanced clocks</v>
       </c>
       <c r="I20" s="6" t="str">
         <f>IFERROR(VLOOKUP($F20,Data!$A:$D,3,FALSE),"")</f>
-        <v>Ayan Nath</v>
+        <v>Prof. Vladan Vuletic</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>362</v>
+        <v>45</v>
       </c>
       <c r="K20" s="6" t="str">
         <f>IFERROR(VLOOKUP($J20,Data!$A:$D,4,FALSE),"")</f>
-        <v>Physics</v>
+        <v>Math</v>
       </c>
       <c r="L20" s="6" t="str">
         <f>IFERROR(VLOOKUP($J20,Data!$A:$D,2,FALSE),"")</f>
-        <v>Hybrid controls strategy for Automatic Laser Beam Alignment</v>
+        <v>On Supersingular Isogeny Graphs of Drinfeld Modules</v>
       </c>
       <c r="M20" s="6" t="str">
         <f>IFERROR(VLOOKUP($J20,Data!$A:$D,3,FALSE),"")</f>
-        <v>Prof. Vladan Vuletic</v>
+        <v>Ayan Nath</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>681</v>
+        <v>46</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>591</v>
+        <v>47</v>
       </c>
       <c r="C21" s="6" t="str">
         <f>IFERROR(VLOOKUP($B21,Data!$A:$D,4,FALSE),"")</f>
@@ -6285,7 +6294,7 @@
         <v>Ashu Tripathi</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>448</v>
+        <v>48</v>
       </c>
       <c r="G21" s="6" t="str">
         <f>IFERROR(VLOOKUP($F21,Data!$A:$D,4,FALSE),"")</f>
@@ -6300,27 +6309,27 @@
         <v>Prof. Francis Loth and Hannah Higgins</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>435</v>
+        <v>49</v>
       </c>
       <c r="K21" s="6" t="str">
         <f>IFERROR(VLOOKUP($J21,Data!$A:$D,4,FALSE),"")</f>
-        <v>Physics</v>
+        <v>Math</v>
       </c>
       <c r="L21" s="6" t="str">
         <f>IFERROR(VLOOKUP($J21,Data!$A:$D,2,FALSE),"")</f>
-        <v>Optical pulse shaping for quantum-enhanced clocks</v>
+        <v>Open Cases of the Colmez Conjecture</v>
       </c>
       <c r="M21" s="6" t="str">
         <f>IFERROR(VLOOKUP($J21,Data!$A:$D,3,FALSE),"")</f>
-        <v>Prof. Vladan Vuletic</v>
+        <v>Ayan Nath</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>682</v>
+        <v>50</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>481</v>
+        <v>51</v>
       </c>
       <c r="C22" s="6" t="str">
         <f>IFERROR(VLOOKUP($B22,Data!$A:$D,4,FALSE),"")</f>
@@ -6335,7 +6344,7 @@
         <v>Dr. Mrinal Shekhar</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="G22" s="6" t="str">
         <f>IFERROR(VLOOKUP($F22,Data!$A:$D,4,FALSE),"")</f>
@@ -6350,27 +6359,27 @@
         <v>Dr. Howard Chen</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="K22" s="6" t="str">
         <f>IFERROR(VLOOKUP($J22,Data!$A:$D,4,FALSE),"")</f>
-        <v>Computer Science &amp; AI</v>
+        <v>Math</v>
       </c>
       <c r="L22" s="6" t="str">
         <f>IFERROR(VLOOKUP($J22,Data!$A:$D,2,FALSE),"")</f>
-        <v>Liquid Foundation Models as Medical Assistants</v>
+        <v>DC-MTNN: A Drug-Conditioned Multi-Task Neural Network for Predicting Drug Resistance in Mycobacterium tuberculosis Using Genomic Data</v>
       </c>
       <c r="M22" s="6" t="str">
         <f>IFERROR(VLOOKUP($J22,Data!$A:$D,3,FALSE),"")</f>
-        <v>Dr. Bo Wu</v>
+        <v>Dr. Sean Carroll</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>683</v>
+        <v>54</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>148</v>
+        <v>55</v>
       </c>
       <c r="C23" s="6" t="str">
         <f>IFERROR(VLOOKUP($B23,Data!$A:$D,4,FALSE),"")</f>
@@ -6385,42 +6394,42 @@
         <v>Dr. Robbie G. Majzner</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>278</v>
+        <v>56</v>
       </c>
       <c r="G23" s="6" t="str">
         <f>IFERROR(VLOOKUP($F23,Data!$A:$D,4,FALSE),"")</f>
-        <v>Computer Science &amp; AI</v>
+        <v>Neuroscience &amp; Psychology</v>
       </c>
       <c r="H23" s="6" t="str">
         <f>IFERROR(VLOOKUP($F23,Data!$A:$D,2,FALSE),"")</f>
-        <v>DC-MTNN: A Drug-Conditioned Multi-Task Neural Network for Predicting Drug Resistance in Mycobacterium tuberculosis Using Genomic Data</v>
+        <v>Functional Neural Connectivity During Inactivation of the Anterior Insula in Fentanyl-Administered Rats</v>
       </c>
       <c r="I23" s="6" t="str">
         <f>IFERROR(VLOOKUP($F23,Data!$A:$D,3,FALSE),"")</f>
-        <v>Dr. Sean Carroll</v>
+        <v>Dr. Sarah Bricault</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>229</v>
+        <v>57</v>
       </c>
       <c r="K23" s="6" t="str">
         <f>IFERROR(VLOOKUP($J23,Data!$A:$D,4,FALSE),"")</f>
-        <v>Computer Science &amp; AI</v>
+        <v>Math</v>
       </c>
       <c r="L23" s="6" t="str">
         <f>IFERROR(VLOOKUP($J23,Data!$A:$D,2,FALSE),"")</f>
-        <v>Teaching a Medical Vision-Language Model with Automatic Feedback</v>
+        <v>Explicit Free Resolutions for Central Quotients of Cyclic Amalgams</v>
       </c>
       <c r="M23" s="6" t="str">
         <f>IFERROR(VLOOKUP($J23,Data!$A:$D,3,FALSE),"")</f>
-        <v>Dr. Bo Wu</v>
+        <v>Dr. Sean Carroll</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>684</v>
+        <v>58</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>522</v>
+        <v>59</v>
       </c>
       <c r="C24" s="6" t="str">
         <f>IFERROR(VLOOKUP($B24,Data!$A:$D,4,FALSE),"")</f>
@@ -6435,39 +6444,39 @@
         <v>Dr. Robbie G. Majzner</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>345</v>
+        <v>60</v>
       </c>
       <c r="G24" s="6" t="str">
         <f>IFERROR(VLOOKUP($F24,Data!$A:$D,4,FALSE),"")</f>
-        <v>Math</v>
+        <v>Biology &amp; Medicine</v>
       </c>
       <c r="H24" s="6" t="str">
         <f>IFERROR(VLOOKUP($F24,Data!$A:$D,2,FALSE),"")</f>
-        <v>Explicit Free Resolutions for Central Quotients of Cyclic Amalgams</v>
+        <v>Characterization of Nanobody Binding to HIV-1 Capsid-Like Particles via Biolayer Interferometry</v>
       </c>
       <c r="I24" s="6" t="str">
         <f>IFERROR(VLOOKUP($F24,Data!$A:$D,3,FALSE),"")</f>
-        <v>Dr. Sean Carroll</v>
+        <v>Dr. Ky Lowenhaupt</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>333</v>
+        <v>61</v>
       </c>
       <c r="K24" s="6" t="str">
         <f>IFERROR(VLOOKUP($J24,Data!$A:$D,4,FALSE),"")</f>
-        <v>Computer Science &amp; AI</v>
+        <v>Math</v>
       </c>
       <c r="L24" s="6" t="str">
         <f>IFERROR(VLOOKUP($J24,Data!$A:$D,2,FALSE),"")</f>
-        <v>Crown–Root Segmentation in Dental CBCT Using Anatomically Guided Synthetic Annotation</v>
+        <v>Simplified Volume Formulas for Tetrahedron by Edge-length Symmetry Class</v>
       </c>
       <c r="M24" s="6" t="str">
         <f>IFERROR(VLOOKUP($J24,Data!$A:$D,3,FALSE),"")</f>
-        <v>Dr. Bo Wu</v>
+        <v>Prof. Eric Grinberg</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="10" t="s">
-        <v>685</v>
+        <v>62</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
@@ -6484,7 +6493,7 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
-        <v>686</v>
+        <v>63</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -6501,22 +6510,22 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>666</v>
+        <v>4</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>667</v>
+        <v>5</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
       <c r="F27" s="7" t="s">
-        <v>668</v>
+        <v>6</v>
       </c>
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
       <c r="J27" s="7" t="s">
-        <v>669</v>
+        <v>7</v>
       </c>
       <c r="K27" s="8"/>
       <c r="L27" s="8"/>
@@ -6524,48 +6533,48 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B28" s="3" t="s">
-        <v>670</v>
+        <v>8</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>670</v>
+        <v>8</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>670</v>
+        <v>8</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>687</v>
+        <v>64</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="C29" s="6" t="str">
         <f>IFERROR(VLOOKUP($B29,Data!$A:$D,4,FALSE),"")</f>
@@ -6580,7 +6589,7 @@
         <v>Prof. Pierre F.J Lermusiaux</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>553</v>
+        <v>66</v>
       </c>
       <c r="G29" s="6" t="str">
         <f>IFERROR(VLOOKUP($F29,Data!$A:$D,4,FALSE),"")</f>
@@ -6595,27 +6604,27 @@
         <v>Prof. John D. E. Gabrieli</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>495</v>
+        <v>67</v>
       </c>
       <c r="K29" s="6" t="str">
         <f>IFERROR(VLOOKUP($J29,Data!$A:$D,4,FALSE),"")</f>
-        <v>Neuroscience &amp; Psychology</v>
+        <v>Math</v>
       </c>
       <c r="L29" s="6" t="str">
         <f>IFERROR(VLOOKUP($J29,Data!$A:$D,2,FALSE),"")</f>
-        <v>Functional Neural Connectivity During Inactivation of the Anterior Insula in Fentanyl-Administered Rats</v>
+        <v>Enumerating Index-Two and Index-Three Nilpotent Matrices in Symplectic Lie Algebras</v>
       </c>
       <c r="M29" s="6" t="str">
         <f>IFERROR(VLOOKUP($J29,Data!$A:$D,3,FALSE),"")</f>
-        <v>Dr. Sarah Bricault and Prof. Alan Pradip Jasanoff (PI)</v>
+        <v>Prof. Eric Grinberg</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>688</v>
+        <v>68</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>116</v>
+        <v>69</v>
       </c>
       <c r="C30" s="6" t="str">
         <f>IFERROR(VLOOKUP($B30,Data!$A:$D,4,FALSE),"")</f>
@@ -6630,7 +6639,7 @@
         <v>Prof. Pierre F.J Lermusiaux</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>183</v>
+        <v>70</v>
       </c>
       <c r="G30" s="6" t="str">
         <f>IFERROR(VLOOKUP($F30,Data!$A:$D,4,FALSE),"")</f>
@@ -6645,27 +6654,27 @@
         <v>Prof. Chuchu Fan</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>546</v>
+        <v>71</v>
       </c>
       <c r="K30" s="6" t="str">
         <f>IFERROR(VLOOKUP($J30,Data!$A:$D,4,FALSE),"")</f>
-        <v>Biology &amp; Medicine</v>
+        <v>Math</v>
       </c>
       <c r="L30" s="6" t="str">
         <f>IFERROR(VLOOKUP($J30,Data!$A:$D,2,FALSE),"")</f>
-        <v>Characterization of Nanobody Binding to HIV-1 Capsid-Like Particles via Biolayer Interferometry</v>
+        <v>Triangular Taxicabs</v>
       </c>
       <c r="M30" s="6" t="str">
         <f>IFERROR(VLOOKUP($J30,Data!$A:$D,3,FALSE),"")</f>
-        <v>Dr. Ky Lowenhaupt</v>
+        <v>Prof. Eric Grinberg</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>689</v>
+        <v>72</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>136</v>
+        <v>73</v>
       </c>
       <c r="C31" s="6" t="str">
         <f>IFERROR(VLOOKUP($B31,Data!$A:$D,4,FALSE),"")</f>
@@ -6680,7 +6689,7 @@
         <v>Prof. Pierre F.J Lermusiaux</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>339</v>
+        <v>74</v>
       </c>
       <c r="G31" s="6" t="str">
         <f>IFERROR(VLOOKUP($F31,Data!$A:$D,4,FALSE),"")</f>
@@ -6695,7 +6704,7 @@
         <v>Prof. Chuchu Fan</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>241</v>
+        <v>75</v>
       </c>
       <c r="K31" s="6" t="str">
         <f>IFERROR(VLOOKUP($J31,Data!$A:$D,4,FALSE),"")</f>
@@ -6712,10 +6721,10 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>690</v>
+        <v>76</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="C32" s="6" t="str">
         <f>IFERROR(VLOOKUP($B32,Data!$A:$D,4,FALSE),"")</f>
@@ -6730,7 +6739,7 @@
         <v>Prof. Pierre F.J Lermusiaux</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>462</v>
+        <v>78</v>
       </c>
       <c r="G32" s="6" t="str">
         <f>IFERROR(VLOOKUP($F32,Data!$A:$D,4,FALSE),"")</f>
@@ -6745,7 +6754,7 @@
         <v>Prof. Chuchu Fan</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>573</v>
+        <v>79</v>
       </c>
       <c r="K32" s="6" t="str">
         <f>IFERROR(VLOOKUP($J32,Data!$A:$D,4,FALSE),"")</f>
@@ -6762,10 +6771,10 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>691</v>
+        <v>80</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>402</v>
+        <v>81</v>
       </c>
       <c r="C33" s="6" t="str">
         <f>IFERROR(VLOOKUP($B33,Data!$A:$D,4,FALSE),"")</f>
@@ -6780,7 +6789,7 @@
         <v>Prof. Pierre F.J Lermusiaux</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>509</v>
+        <v>82</v>
       </c>
       <c r="G33" s="6" t="str">
         <f>IFERROR(VLOOKUP($F33,Data!$A:$D,4,FALSE),"")</f>
@@ -6795,7 +6804,7 @@
         <v>Prof. Chuchu Fan</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="K33" s="6" t="str">
         <f>IFERROR(VLOOKUP($J33,Data!$A:$D,4,FALSE),"")</f>
@@ -6812,25 +6821,25 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>692</v>
+        <v>84</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>528</v>
+        <v>95</v>
       </c>
       <c r="C34" s="6" t="str">
         <f>IFERROR(VLOOKUP($B34,Data!$A:$D,4,FALSE),"")</f>
-        <v>Biology &amp; Medicine</v>
+        <v>Earth, Ocean &amp; Climate</v>
       </c>
       <c r="D34" s="6" t="str">
         <f>IFERROR(VLOOKUP($B34,Data!$A:$D,2,FALSE),"")</f>
-        <v>Computational and mathematical modeling of cellular dynamics in hydrogels to optimize large-scale bioprinting</v>
+        <v>Quantifying Information Propagation in Diffusion Posterior Sampling for Ocean Flows</v>
       </c>
       <c r="E34" s="6" t="str">
         <f>IFERROR(VLOOKUP($B34,Data!$A:$D,3,FALSE),"")</f>
-        <v>Prof. Ron Weiss</v>
+        <v>Prof. Pierre F.J Lermusiaux</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>455</v>
+        <v>86</v>
       </c>
       <c r="G34" s="6" t="str">
         <f>IFERROR(VLOOKUP($F34,Data!$A:$D,4,FALSE),"")</f>
@@ -6845,7 +6854,7 @@
         <v>Dr. Yogesh Rathi, Dr. Sinead Marie Kelly, Dr. Lipeng Ning</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>175</v>
+        <v>87</v>
       </c>
       <c r="K34" s="6" t="str">
         <f>IFERROR(VLOOKUP($J34,Data!$A:$D,4,FALSE),"")</f>
@@ -6862,7 +6871,7 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" s="10" t="s">
-        <v>693</v>
+        <v>88</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -6879,7 +6888,7 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
-        <v>694</v>
+        <v>89</v>
       </c>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -6896,22 +6905,22 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>666</v>
+        <v>4</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>667</v>
+        <v>5</v>
       </c>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
       <c r="F37" s="7" t="s">
-        <v>668</v>
+        <v>6</v>
       </c>
       <c r="G37" s="8"/>
       <c r="H37" s="8"/>
       <c r="I37" s="8"/>
       <c r="J37" s="7" t="s">
-        <v>669</v>
+        <v>7</v>
       </c>
       <c r="K37" s="8"/>
       <c r="L37" s="8"/>
@@ -6919,48 +6928,48 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B38" s="3" t="s">
-        <v>670</v>
+        <v>8</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>670</v>
+        <v>8</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>670</v>
+        <v>8</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>695</v>
+        <v>90</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>579</v>
+        <v>91</v>
       </c>
       <c r="C39" s="6" t="str">
         <f>IFERROR(VLOOKUP($B39,Data!$A:$D,4,FALSE),"")</f>
@@ -6975,7 +6984,7 @@
         <v>Prof. Pierre F.J Lermusiaux</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>395</v>
+        <v>92</v>
       </c>
       <c r="G39" s="6" t="str">
         <f>IFERROR(VLOOKUP($F39,Data!$A:$D,4,FALSE),"")</f>
@@ -6990,7 +6999,7 @@
         <v>Prof. Timothy Miller</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>45</v>
+        <v>93</v>
       </c>
       <c r="K39" s="6" t="str">
         <f>IFERROR(VLOOKUP($J39,Data!$A:$D,4,FALSE),"")</f>
@@ -7007,25 +7016,25 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>696</v>
+        <v>94</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>636</v>
+        <v>85</v>
       </c>
       <c r="C40" s="6" t="str">
         <f>IFERROR(VLOOKUP($B40,Data!$A:$D,4,FALSE),"")</f>
-        <v>Earth, Ocean &amp; Climate</v>
+        <v>Biology &amp; Medicine</v>
       </c>
       <c r="D40" s="6" t="str">
         <f>IFERROR(VLOOKUP($B40,Data!$A:$D,2,FALSE),"")</f>
-        <v>Quantifying Information Propagation in Diffusion Posterior Sampling for Ocean Flows</v>
+        <v>Computational and mathematical modeling of cellular dynamics in hydrogels to optimize large-scale bioprinting</v>
       </c>
       <c r="E40" s="6" t="str">
         <f>IFERROR(VLOOKUP($B40,Data!$A:$D,3,FALSE),"")</f>
-        <v>Prof. Pierre F.J Lermusiaux</v>
+        <v>Prof. Ron Weiss</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>167</v>
+        <v>96</v>
       </c>
       <c r="G40" s="6" t="str">
         <f>IFERROR(VLOOKUP($F40,Data!$A:$D,4,FALSE),"")</f>
@@ -7040,7 +7049,7 @@
         <v>Katharine Hesse</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="K40" s="6" t="str">
         <f>IFERROR(VLOOKUP($J40,Data!$A:$D,4,FALSE),"")</f>
@@ -7057,10 +7066,10 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>697</v>
+        <v>98</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>207</v>
+        <v>99</v>
       </c>
       <c r="C41" s="6" t="str">
         <f>IFERROR(VLOOKUP($B41,Data!$A:$D,4,FALSE),"")</f>
@@ -7075,7 +7084,7 @@
         <v>Dr. Prajwal T. Mohan Murthy</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>351</v>
+        <v>100</v>
       </c>
       <c r="G41" s="6" t="str">
         <f>IFERROR(VLOOKUP($F41,Data!$A:$D,4,FALSE),"")</f>
@@ -7090,7 +7099,7 @@
         <v>Katharine Hesse</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="K41" s="6" t="str">
         <f>IFERROR(VLOOKUP($J41,Data!$A:$D,4,FALSE),"")</f>
@@ -7107,10 +7116,10 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>698</v>
+        <v>102</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="C42" s="6" t="str">
         <f>IFERROR(VLOOKUP($B42,Data!$A:$D,4,FALSE),"")</f>
@@ -7125,7 +7134,7 @@
         <v>Prof. Gil Alterovitz</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>326</v>
+        <v>104</v>
       </c>
       <c r="G42" s="6" t="str">
         <f>IFERROR(VLOOKUP($F42,Data!$A:$D,4,FALSE),"")</f>
@@ -7140,7 +7149,7 @@
         <v>Prof. Min Dong</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>267</v>
+        <v>105</v>
       </c>
       <c r="K42" s="6" t="str">
         <f>IFERROR(VLOOKUP($J42,Data!$A:$D,4,FALSE),"")</f>
@@ -7157,10 +7166,10 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
-        <v>699</v>
+        <v>106</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="C43" s="6" t="str">
         <f>IFERROR(VLOOKUP($B43,Data!$A:$D,4,FALSE),"")</f>
@@ -7175,7 +7184,7 @@
         <v>Prof. Gil Alterovitz</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>290</v>
+        <v>108</v>
       </c>
       <c r="G43" s="6" t="str">
         <f>IFERROR(VLOOKUP($F43,Data!$A:$D,4,FALSE),"")</f>
@@ -7190,7 +7199,7 @@
         <v>Dr. Muhammad Fahad Ehsan</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>619</v>
+        <v>109</v>
       </c>
       <c r="K43" s="6" t="str">
         <f>IFERROR(VLOOKUP($J43,Data!$A:$D,4,FALSE),"")</f>
@@ -7207,10 +7216,10 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>700</v>
+        <v>110</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>285</v>
+        <v>111</v>
       </c>
       <c r="C44" s="6" t="str">
         <f>IFERROR(VLOOKUP($B44,Data!$A:$D,4,FALSE),"")</f>
@@ -7225,7 +7234,7 @@
         <v>Prof. Gil Alterovitz</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="G44" s="6" t="str">
         <f>IFERROR(VLOOKUP($F44,Data!$A:$D,4,FALSE),"")</f>
@@ -7240,7 +7249,7 @@
         <v>Dr. Buu Truong</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>656</v>
+        <v>113</v>
       </c>
       <c r="K44" s="6" t="str">
         <f>IFERROR(VLOOKUP($J44,Data!$A:$D,4,FALSE),"")</f>
@@ -7255,9 +7264,9 @@
         <v>Prof. Manolis Kellis</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:13" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="9" t="s">
-        <v>701</v>
+        <v>114</v>
       </c>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
@@ -7274,7 +7283,7 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" s="11" t="s">
-        <v>702</v>
+        <v>115</v>
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -7291,22 +7300,22 @@
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>666</v>
+        <v>4</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>667</v>
+        <v>5</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
       <c r="F49" s="7" t="s">
-        <v>668</v>
+        <v>6</v>
       </c>
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
       <c r="J49" s="7" t="s">
-        <v>669</v>
+        <v>7</v>
       </c>
       <c r="K49" s="8"/>
       <c r="L49" s="8"/>
@@ -7314,48 +7323,48 @@
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B50" s="3" t="s">
-        <v>670</v>
+        <v>8</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>670</v>
+        <v>8</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>670</v>
+        <v>8</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="26" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>671</v>
+        <v>12</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>214</v>
+        <v>116</v>
       </c>
       <c r="C51" s="6" t="str">
         <f>IFERROR(VLOOKUP($B51,Data!$A:$D,4,FALSE),"")</f>
@@ -7370,7 +7379,7 @@
         <v>Dr. Aaron Kesselheim</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>16</v>
+        <v>117</v>
       </c>
       <c r="G51" s="6" t="str">
         <f>IFERROR(VLOOKUP($F51,Data!$A:$D,4,FALSE),"")</f>
@@ -7385,7 +7394,7 @@
         <v>Prof. Charles Hoffman</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>584</v>
+        <v>118</v>
       </c>
       <c r="K51" s="6" t="str">
         <f>IFERROR(VLOOKUP($J51,Data!$A:$D,4,FALSE),"")</f>
@@ -7400,12 +7409,12 @@
         <v>Dr. Cong Liu, Dr. Kamalakkannan Ravi</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="26" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>672</v>
+        <v>16</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>190</v>
+        <v>119</v>
       </c>
       <c r="C52" s="6" t="str">
         <f>IFERROR(VLOOKUP($B52,Data!$A:$D,4,FALSE),"")</f>
@@ -7420,7 +7429,7 @@
         <v>Prof. Markus Buehler</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>383</v>
+        <v>120</v>
       </c>
       <c r="G52" s="6" t="str">
         <f>IFERROR(VLOOKUP($F52,Data!$A:$D,4,FALSE),"")</f>
@@ -7435,7 +7444,7 @@
         <v>Prof. Charles Hoffman</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>596</v>
+        <v>121</v>
       </c>
       <c r="K52" s="6" t="str">
         <f>IFERROR(VLOOKUP($J52,Data!$A:$D,4,FALSE),"")</f>
@@ -7450,12 +7459,12 @@
         <v>Dr. Cong Liu, Dr. Kamalakkannan Ravi</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="39" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>673</v>
+        <v>20</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>197</v>
+        <v>122</v>
       </c>
       <c r="C53" s="6" t="str">
         <f>IFERROR(VLOOKUP($B53,Data!$A:$D,4,FALSE),"")</f>
@@ -7470,7 +7479,7 @@
         <v>Prof. Markus Buehler</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>52</v>
+        <v>123</v>
       </c>
       <c r="G53" s="6" t="str">
         <f>IFERROR(VLOOKUP($F53,Data!$A:$D,4,FALSE),"")</f>
@@ -7485,7 +7494,7 @@
         <v>Prof. Susan Hagen, Dr. Xu Xu</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>704</v>
+        <v>124</v>
       </c>
       <c r="K53" s="6" t="str">
         <f>IFERROR(VLOOKUP($J53,Data!$A:$D,4,FALSE),"")</f>
@@ -7500,12 +7509,12 @@
         <v>Prof. Ambika Bajpayee</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="26" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>674</v>
+        <v>24</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C54" s="6" t="str">
         <f>IFERROR(VLOOKUP($B54,Data!$A:$D,4,FALSE),"")</f>
@@ -7520,7 +7529,7 @@
         <v>Prof. Jenny Hoffman, Sarah Ziegler</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>254</v>
+        <v>126</v>
       </c>
       <c r="G54" s="6" t="str">
         <f>IFERROR(VLOOKUP($F54,Data!$A:$D,4,FALSE),"")</f>
@@ -7535,7 +7544,7 @@
         <v>Prof. Susan Hagen, Dr. Xu Xu</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>304</v>
+        <v>127</v>
       </c>
       <c r="K54" s="6" t="str">
         <f>IFERROR(VLOOKUP($J54,Data!$A:$D,4,FALSE),"")</f>
@@ -7550,12 +7559,12 @@
         <v>Prof. Ulf Dettmer</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="26" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
-        <v>675</v>
+        <v>28</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>629</v>
+        <v>128</v>
       </c>
       <c r="C55" s="6" t="str">
         <f>IFERROR(VLOOKUP($B55,Data!$A:$D,4,FALSE),"")</f>
@@ -7570,7 +7579,7 @@
         <v>Prof. Jenny Hoffman</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>369</v>
+        <v>129</v>
       </c>
       <c r="G55" s="6" t="str">
         <f>IFERROR(VLOOKUP($F55,Data!$A:$D,4,FALSE),"")</f>
@@ -7585,7 +7594,7 @@
         <v>Prof. Koroush Shirvan</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>376</v>
+        <v>130</v>
       </c>
       <c r="K55" s="6" t="str">
         <f>IFERROR(VLOOKUP($J55,Data!$A:$D,4,FALSE),"")</f>
@@ -7600,12 +7609,12 @@
         <v>Dr. Sumaiya Nazeen</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="39" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
-        <v>676</v>
+        <v>32</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>260</v>
+        <v>131</v>
       </c>
       <c r="C56" s="6" t="str">
         <f>IFERROR(VLOOKUP($B56,Data!$A:$D,4,FALSE),"")</f>
@@ -7620,7 +7629,7 @@
         <v>Dr. David T. Miyamoto</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>24</v>
+        <v>132</v>
       </c>
       <c r="G56" s="6" t="str">
         <f>IFERROR(VLOOKUP($F56,Data!$A:$D,4,FALSE),"")</f>
@@ -7635,7 +7644,7 @@
         <v>Dr. Artur A. Indzhykulian</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>642</v>
+        <v>133</v>
       </c>
       <c r="K56" s="6" t="str">
         <f>IFERROR(VLOOKUP($J56,Data!$A:$D,4,FALSE),"")</f>
@@ -7652,7 +7661,7 @@
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57" s="10" t="s">
-        <v>677</v>
+        <v>36</v>
       </c>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
@@ -7669,7 +7678,7 @@
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58" s="11" t="s">
-        <v>703</v>
+        <v>134</v>
       </c>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
@@ -7686,22 +7695,22 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>666</v>
+        <v>4</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>667</v>
+        <v>5</v>
       </c>
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
       <c r="E59" s="8"/>
       <c r="F59" s="7" t="s">
-        <v>668</v>
+        <v>6</v>
       </c>
       <c r="G59" s="8"/>
       <c r="H59" s="8"/>
       <c r="I59" s="8"/>
       <c r="J59" s="7" t="s">
-        <v>669</v>
+        <v>7</v>
       </c>
       <c r="K59" s="8"/>
       <c r="L59" s="8"/>
@@ -7709,48 +7718,48 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B60" s="3" t="s">
-        <v>670</v>
+        <v>8</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>670</v>
+        <v>8</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>670</v>
+        <v>8</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="26" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
-        <v>679</v>
+        <v>38</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>488</v>
+        <v>135</v>
       </c>
       <c r="C61" s="6" t="str">
         <f>IFERROR(VLOOKUP($B61,Data!$A:$D,4,FALSE),"")</f>
@@ -7758,14 +7767,14 @@
       </c>
       <c r="D61" s="6" t="str">
         <f>IFERROR(VLOOKUP($B61,Data!$A:$D,2,FALSE),"")</f>
-        <v>Rational Minigene Design Toward AAV Gene Therapy for Bainbridge-Ropers Syndrome</v>
+        <v>Reference-Anchored Computational Design of Domain-Preserving ASXL3 Minigenes for AAV Gene Therapy in Bainbridge-Ropers Syndrome</v>
       </c>
       <c r="E61" s="6" t="str">
         <f>IFERROR(VLOOKUP($B61,Data!$A:$D,3,FALSE),"")</f>
         <v>Prof. Fengfeng Bei</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="G61" s="6" t="str">
         <f>IFERROR(VLOOKUP($F61,Data!$A:$D,4,FALSE),"")</f>
@@ -7780,7 +7789,7 @@
         <v>Prof. Maggie Qi, Shu Yang</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="K61" s="6" t="str">
         <f>IFERROR(VLOOKUP($J61,Data!$A:$D,4,FALSE),"")</f>
@@ -7795,12 +7804,12 @@
         <v>Prof. Peter Lu, Oreoluwa Alao</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="26" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
-        <v>680</v>
+        <v>42</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>414</v>
+        <v>138</v>
       </c>
       <c r="C62" s="6" t="str">
         <f>IFERROR(VLOOKUP($B62,Data!$A:$D,4,FALSE),"")</f>
@@ -7815,7 +7824,7 @@
         <v>Prof. James Michaelson</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>201</v>
+        <v>139</v>
       </c>
       <c r="G62" s="6" t="str">
         <f>IFERROR(VLOOKUP($F62,Data!$A:$D,4,FALSE),"")</f>
@@ -7830,7 +7839,7 @@
         <v>Prof. Maggie Qi, Shu Yang</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>468</v>
+        <v>140</v>
       </c>
       <c r="K62" s="6" t="str">
         <f>IFERROR(VLOOKUP($J62,Data!$A:$D,4,FALSE),"")</f>
@@ -7845,12 +7854,12 @@
         <v>Prof. Peter Lu, Oreoluwa Alao</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="26" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>681</v>
+        <v>46</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>535</v>
+        <v>141</v>
       </c>
       <c r="C63" s="6" t="str">
         <f>IFERROR(VLOOKUP($B63,Data!$A:$D,4,FALSE),"")</f>
@@ -7865,7 +7874,7 @@
         <v>Prof. James Michaelson</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>311</v>
+        <v>142</v>
       </c>
       <c r="G63" s="6" t="str">
         <f>IFERROR(VLOOKUP($F63,Data!$A:$D,4,FALSE),"")</f>
@@ -7893,12 +7902,12 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="26" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
-        <v>682</v>
+        <v>50</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>515</v>
+        <v>143</v>
       </c>
       <c r="C64" s="6" t="str">
         <f>IFERROR(VLOOKUP($B64,Data!$A:$D,4,FALSE),"")</f>
@@ -7913,7 +7922,7 @@
         <v>Dr. Basak Icli</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>540</v>
+        <v>144</v>
       </c>
       <c r="G64" s="6" t="str">
         <f>IFERROR(VLOOKUP($F64,Data!$A:$D,4,FALSE),"")</f>
@@ -7949,32 +7958,32 @@
     <mergeCell ref="F59:I59"/>
     <mergeCell ref="A25:M25"/>
     <mergeCell ref="A16:M16"/>
+    <mergeCell ref="J7:M7"/>
     <mergeCell ref="J49:M49"/>
     <mergeCell ref="J27:M27"/>
     <mergeCell ref="B17:E17"/>
     <mergeCell ref="F17:I17"/>
     <mergeCell ref="A26:M26"/>
     <mergeCell ref="B37:E37"/>
-    <mergeCell ref="J7:M7"/>
+    <mergeCell ref="A57:M57"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A47:M47"/>
+    <mergeCell ref="A58:M58"/>
+    <mergeCell ref="A48:M48"/>
+    <mergeCell ref="B7:E7"/>
     <mergeCell ref="B59:E59"/>
     <mergeCell ref="A15:M15"/>
     <mergeCell ref="J37:M37"/>
     <mergeCell ref="J59:M59"/>
     <mergeCell ref="A36:M36"/>
     <mergeCell ref="B27:E27"/>
-    <mergeCell ref="A57:M57"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A35:M35"/>
+    <mergeCell ref="F37:I37"/>
     <mergeCell ref="F49:I49"/>
     <mergeCell ref="J17:M17"/>
-    <mergeCell ref="A58:M58"/>
-    <mergeCell ref="A48:M48"/>
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="A5:M5"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="A35:M35"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="B7:E7"/>
   </mergeCells>
   <conditionalFormatting sqref="C4:C71">
     <cfRule type="cellIs" dxfId="32" priority="13" operator="equal">
@@ -8082,17 +8091,5 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
-          <x14:formula1>
-            <xm:f>Data!$A$2:$A$101</xm:f>
-          </x14:formula1>
-          <xm:sqref>B9:B14 B19:B24 B29:B34 B39:B44 B51:B56 B61:B64 F9:F14 F19:F24 F29:F34 F39:F44 F51:F56 F61:F64 J9:J14 J19:J24 J29:J34 J39:J44 J51:J56 J61:J64</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
--- a/RSI_2026_Schedule.xlsx
+++ b/RSI_2026_Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/evanlim/Documents/rsi-symposium/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92E78BE2-5E89-3F43-898F-6D7AD94E25E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B6D56D2-C94F-1D47-A01B-148C69B92261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2161,7 +2161,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2229,6 +2229,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -2290,7 +2297,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2304,25 +2311,26 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5651,7 +5659,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="8"/>
@@ -5668,7 +5676,7 @@
       <c r="M1" s="8"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="8"/>
@@ -5685,7 +5693,7 @@
       <c r="M2" s="8"/>
     </row>
     <row r="5" spans="1:13" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="13" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="8"/>
@@ -5702,7 +5710,7 @@
       <c r="M5" s="8"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="10" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="8"/>
@@ -5722,19 +5730,19 @@
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="9" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="9" t="s">
         <v>6</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="9" t="s">
         <v>7</v>
       </c>
       <c r="K7" s="8"/>
@@ -5779,7 +5787,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="39" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>12</v>
       </c>
@@ -5829,7 +5837,7 @@
         <v>Siqi Wu</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>16</v>
       </c>
@@ -5879,7 +5887,7 @@
         <v>Siqi Wu</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>20</v>
       </c>
@@ -5914,7 +5922,7 @@
         <v>Prof. Vivek Venkatachalam</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="K11" s="6" t="str">
         <f>IFERROR(VLOOKUP($J11,Data!$A:$D,4,FALSE),"")</f>
@@ -5922,14 +5930,14 @@
       </c>
       <c r="L11" s="6" t="str">
         <f>IFERROR(VLOOKUP($J11,Data!$A:$D,2,FALSE),"")</f>
-        <v>Temporal Preferential Attachment Trees</v>
+        <v>Critical Groups of Signed Subdivided Wheels</v>
       </c>
       <c r="M11" s="6" t="str">
         <f>IFERROR(VLOOKUP($J11,Data!$A:$D,3,FALSE),"")</f>
-        <v>Hang Du</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+        <v>Ryota Inagaki</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>24</v>
       </c>
@@ -5963,8 +5971,8 @@
         <f>IFERROR(VLOOKUP($F12,Data!$A:$D,3,FALSE),"")</f>
         <v>Timothy Gomez</v>
       </c>
-      <c r="J12" s="5" t="s">
-        <v>27</v>
+      <c r="J12" s="14" t="s">
+        <v>35</v>
       </c>
       <c r="K12" s="6" t="str">
         <f>IFERROR(VLOOKUP($J12,Data!$A:$D,4,FALSE),"")</f>
@@ -5972,14 +5980,14 @@
       </c>
       <c r="L12" s="6" t="str">
         <f>IFERROR(VLOOKUP($J12,Data!$A:$D,2,FALSE),"")</f>
-        <v>Heat Evolution on Graphs</v>
+        <v>Resolving a Conjecture on Stack-Sorting</v>
       </c>
       <c r="M12" s="6" t="str">
         <f>IFERROR(VLOOKUP($J12,Data!$A:$D,3,FALSE),"")</f>
-        <v>Alexander McWeeney</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+        <v>Ryota Inagaki</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>28</v>
       </c>
@@ -6029,7 +6037,7 @@
         <v>Alexander McWeeney</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>32</v>
       </c>
@@ -6064,7 +6072,7 @@
         <v>Dr. James Sullivan</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K14" s="6" t="str">
         <f>IFERROR(VLOOKUP($J14,Data!$A:$D,4,FALSE),"")</f>
@@ -6072,15 +6080,15 @@
       </c>
       <c r="L14" s="6" t="str">
         <f>IFERROR(VLOOKUP($J14,Data!$A:$D,2,FALSE),"")</f>
-        <v>Resolving a Conjecture on Stack-Sorting</v>
+        <v>Heat Evolution on Graphs</v>
       </c>
       <c r="M14" s="6" t="str">
         <f>IFERROR(VLOOKUP($J14,Data!$A:$D,3,FALSE),"")</f>
-        <v>Ryota Inagaki</v>
+        <v>Alexander McWeeney</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="11" t="s">
         <v>36</v>
       </c>
       <c r="B15" s="8"/>
@@ -6097,7 +6105,7 @@
       <c r="M15" s="8"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="10" t="s">
         <v>37</v>
       </c>
       <c r="B16" s="8"/>
@@ -6117,19 +6125,19 @@
       <c r="A17" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="9" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="9" t="s">
         <v>6</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
-      <c r="J17" s="7" t="s">
+      <c r="J17" s="9" t="s">
         <v>7</v>
       </c>
       <c r="K17" s="8"/>
@@ -6174,7 +6182,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>38</v>
       </c>
@@ -6209,7 +6217,7 @@
         <v>Prof. Vladan Vuletic</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="K19" s="6" t="str">
         <f>IFERROR(VLOOKUP($J19,Data!$A:$D,4,FALSE),"")</f>
@@ -6217,11 +6225,11 @@
       </c>
       <c r="L19" s="6" t="str">
         <f>IFERROR(VLOOKUP($J19,Data!$A:$D,2,FALSE),"")</f>
-        <v>Critical Groups of Signed Subdivided Wheels</v>
+        <v>Temporal Preferential Attachment Trees</v>
       </c>
       <c r="M19" s="6" t="str">
         <f>IFERROR(VLOOKUP($J19,Data!$A:$D,3,FALSE),"")</f>
-        <v>Ryota Inagaki</v>
+        <v>Hang Du</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
@@ -6274,7 +6282,7 @@
         <v>Ayan Nath</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>46</v>
       </c>
@@ -6324,7 +6332,7 @@
         <v>Ayan Nath</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" ht="39" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>50</v>
       </c>
@@ -6374,7 +6382,7 @@
         <v>Dr. Sean Carroll</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>54</v>
       </c>
@@ -6424,7 +6432,7 @@
         <v>Dr. Sean Carroll</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>58</v>
       </c>
@@ -6475,7 +6483,7 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="11" t="s">
         <v>62</v>
       </c>
       <c r="B25" s="8"/>
@@ -6492,7 +6500,7 @@
       <c r="M25" s="8"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="10" t="s">
         <v>63</v>
       </c>
       <c r="B26" s="8"/>
@@ -6512,19 +6520,19 @@
       <c r="A27" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="9" t="s">
         <v>5</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="9" t="s">
         <v>6</v>
       </c>
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
-      <c r="J27" s="7" t="s">
+      <c r="J27" s="9" t="s">
         <v>7</v>
       </c>
       <c r="K27" s="8"/>
@@ -6569,7 +6577,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>64</v>
       </c>
@@ -6619,7 +6627,7 @@
         <v>Prof. Eric Grinberg</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>68</v>
       </c>
@@ -6669,7 +6677,7 @@
         <v>Prof. Eric Grinberg</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>72</v>
       </c>
@@ -6719,7 +6727,7 @@
         <v>Dr. Sudeshna Das</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>76</v>
       </c>
@@ -6769,7 +6777,7 @@
         <v>Dr. Sudeshna Das</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>80</v>
       </c>
@@ -6819,7 +6827,7 @@
         <v>Prof. Justin Solomon</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>84</v>
       </c>
@@ -6870,7 +6878,7 @@
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="11" t="s">
         <v>88</v>
       </c>
       <c r="B35" s="8"/>
@@ -6887,7 +6895,7 @@
       <c r="M35" s="8"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="10" t="s">
         <v>89</v>
       </c>
       <c r="B36" s="8"/>
@@ -6907,19 +6915,19 @@
       <c r="A37" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="9" t="s">
         <v>5</v>
       </c>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
-      <c r="F37" s="7" t="s">
+      <c r="F37" s="9" t="s">
         <v>6</v>
       </c>
       <c r="G37" s="8"/>
       <c r="H37" s="8"/>
       <c r="I37" s="8"/>
-      <c r="J37" s="7" t="s">
+      <c r="J37" s="9" t="s">
         <v>7</v>
       </c>
       <c r="K37" s="8"/>
@@ -6964,7 +6972,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>90</v>
       </c>
@@ -7014,7 +7022,7 @@
         <v>Prof. Manolis Kellis</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>94</v>
       </c>
@@ -7064,7 +7072,7 @@
         <v>Prof. Manolis Kellis</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:13" ht="39" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>98</v>
       </c>
@@ -7114,7 +7122,7 @@
         <v>Prof. Manolis Kellis</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13" ht="39" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>102</v>
       </c>
@@ -7164,7 +7172,7 @@
         <v>Prof. Manolis Kellis</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>106</v>
       </c>
@@ -7214,7 +7222,7 @@
         <v>Prof. Manolis Kellis</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>110</v>
       </c>
@@ -7265,7 +7273,7 @@
       </c>
     </row>
     <row r="47" spans="1:13" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="9" t="s">
+      <c r="A47" s="13" t="s">
         <v>114</v>
       </c>
       <c r="B47" s="8"/>
@@ -7282,7 +7290,7 @@
       <c r="M47" s="8"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A48" s="11" t="s">
+      <c r="A48" s="10" t="s">
         <v>115</v>
       </c>
       <c r="B48" s="8"/>
@@ -7302,19 +7310,19 @@
       <c r="A49" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="9" t="s">
         <v>5</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
-      <c r="F49" s="7" t="s">
+      <c r="F49" s="9" t="s">
         <v>6</v>
       </c>
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
-      <c r="J49" s="7" t="s">
+      <c r="J49" s="9" t="s">
         <v>7</v>
       </c>
       <c r="K49" s="8"/>
@@ -7660,7 +7668,7 @@
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A57" s="10" t="s">
+      <c r="A57" s="11" t="s">
         <v>36</v>
       </c>
       <c r="B57" s="8"/>
@@ -7677,7 +7685,7 @@
       <c r="M57" s="8"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A58" s="11" t="s">
+      <c r="A58" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B58" s="8"/>
@@ -7697,19 +7705,19 @@
       <c r="A59" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B59" s="9" t="s">
         <v>5</v>
       </c>
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
       <c r="E59" s="8"/>
-      <c r="F59" s="7" t="s">
+      <c r="F59" s="9" t="s">
         <v>6</v>
       </c>
       <c r="G59" s="8"/>
       <c r="H59" s="8"/>
       <c r="I59" s="8"/>
-      <c r="J59" s="7" t="s">
+      <c r="J59" s="9" t="s">
         <v>7</v>
       </c>
       <c r="K59" s="8"/>
@@ -7952,6 +7960,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A35:M35"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="F49:I49"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="A58:M58"/>
+    <mergeCell ref="A48:M48"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="J59:M59"/>
+    <mergeCell ref="A36:M36"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="B49:E49"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="F7:I7"/>
     <mergeCell ref="A6:M6"/>
@@ -7968,22 +7992,6 @@
     <mergeCell ref="A57:M57"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A47:M47"/>
-    <mergeCell ref="A58:M58"/>
-    <mergeCell ref="A48:M48"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="J59:M59"/>
-    <mergeCell ref="A36:M36"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="A5:M5"/>
-    <mergeCell ref="A35:M35"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="F49:I49"/>
-    <mergeCell ref="J17:M17"/>
   </mergeCells>
   <conditionalFormatting sqref="C4:C71">
     <cfRule type="cellIs" dxfId="32" priority="13" operator="equal">

--- a/RSI_2026_Schedule.xlsx
+++ b/RSI_2026_Schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/evanlim/Documents/rsi-symposium/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B6D56D2-C94F-1D47-A01B-148C69B92261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F4999B-D936-F546-BC67-D41FFE4EF26E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -849,9 +849,6 @@
     <t>can_nlbt</t>
   </si>
   <si>
-    <t>Effect of ZAP70 Mutations on CAR T-Cell Effectiveness Targeting GD2 in Brain Tumors</t>
-  </si>
-  <si>
     <t>Dr. Robbie G. Majzner</t>
   </si>
   <si>
@@ -2055,9 +2052,6 @@
     <t>tris</t>
   </si>
   <si>
-    <t>Triangular Taxicabs</t>
-  </si>
-  <si>
     <t>SHIN-dee</t>
   </si>
   <si>
@@ -2155,6 +2149,12 @@
   </si>
   <si>
     <t>Dr. Sarah Bricault</t>
+  </si>
+  <si>
+    <t>A Taxicab Journey to Triangle Centres</t>
+  </si>
+  <si>
+    <t>Effect of ZAP70 Mutations on CAR T-Cell Effectiveness Targeting GD2 in Brain Tumors and N6 Leukemia Cells</t>
   </si>
 </sst>
 </file>
@@ -2361,11 +2361,121 @@
     <dxf>
       <font>
         <sz val="9"/>
+        <color rgb="FF0F766E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCCFBF1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FFBE185D"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE7F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FF047857"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD1FAE5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FFB45309"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FFC2410C"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEDD5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FF0E7490"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCFFAFE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FF4338CA"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE0E7FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FF6D28D9"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEDE9FE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
         <color rgb="FF1D4ED8"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFDBEAFE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FF475569"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1F5F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FFBE123C"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE4E6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2394,11 +2504,121 @@
     <dxf>
       <font>
         <sz val="9"/>
+        <color rgb="FF047857"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD1FAE5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FFB45309"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FFC2410C"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEDD5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FF0E7490"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCFFAFE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FF4338CA"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE0E7FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
         <color rgb="FF6D28D9"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFEDE9FE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FF1D4ED8"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDBEAFE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FF475569"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1F5F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FFBE123C"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE4E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FF0F766E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCCFBF1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FFBE185D"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE7F3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2427,17 +2647,6 @@
     <dxf>
       <font>
         <sz val="9"/>
-        <color rgb="FF4338CA"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE0E7FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
         <color rgb="FFC2410C"/>
       </font>
       <fill>
@@ -2460,44 +2669,11 @@
     <dxf>
       <font>
         <sz val="9"/>
-        <color rgb="FF475569"/>
+        <color rgb="FF4338CA"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF1F5F9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF1D4ED8"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDBEAFE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FFBE123C"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE4E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF0F766E"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCCFBF1"/>
+          <fgColor rgb="FFE0E7FF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2515,187 +2691,11 @@
     <dxf>
       <font>
         <sz val="9"/>
-        <color rgb="FFBE185D"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE7F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF047857"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD1FAE5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF4338CA"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE0E7FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF0E7490"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFFAFE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FFC2410C"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEDD5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FFB45309"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF3C7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FFB45309"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF3C7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF0E7490"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFFAFE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
         <color rgb="FF1D4ED8"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFDBEAFE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF047857"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD1FAE5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF4338CA"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE0E7FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FFBE185D"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE7F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF0F766E"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCCFBF1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF6D28D9"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEDE9FE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FFBE123C"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE4E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF475569"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1F5F9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FFC2410C"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEDD5"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3351,13 +3351,13 @@
         <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C14" t="s">
         <v>225</v>
       </c>
       <c r="D14" t="s">
-        <v>226</v>
+        <v>159</v>
       </c>
       <c r="E14" t="s">
         <v>227</v>
@@ -3366,10 +3366,10 @@
         <v>228</v>
       </c>
       <c r="G14" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="H14" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -3377,13 +3377,13 @@
         <v>65</v>
       </c>
       <c r="B15" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C15" t="s">
         <v>232</v>
       </c>
       <c r="D15" t="s">
-        <v>159</v>
+        <v>239</v>
       </c>
       <c r="E15" t="s">
         <v>233</v>
@@ -3392,10 +3392,10 @@
         <v>234</v>
       </c>
       <c r="G15" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="H15" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -3403,13 +3403,13 @@
         <v>137</v>
       </c>
       <c r="B16" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="C16" t="s">
         <v>238</v>
       </c>
       <c r="D16" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="E16" t="s">
         <v>240</v>
@@ -3418,10 +3418,10 @@
         <v>228</v>
       </c>
       <c r="G16" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="H16" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -3559,25 +3559,25 @@
         <v>55</v>
       </c>
       <c r="B22" t="s">
+        <v>705</v>
+      </c>
+      <c r="C22" t="s">
         <v>270</v>
-      </c>
-      <c r="C22" t="s">
-        <v>271</v>
       </c>
       <c r="D22" t="s">
         <v>159</v>
       </c>
       <c r="E22" t="s">
+        <v>271</v>
+      </c>
+      <c r="F22" t="s">
         <v>272</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>273</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>274</v>
-      </c>
-      <c r="H22" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -3585,7 +3585,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C23" t="s">
         <v>183</v>
@@ -3594,16 +3594,16 @@
         <v>159</v>
       </c>
       <c r="E23" t="s">
+        <v>276</v>
+      </c>
+      <c r="F23" t="s">
         <v>277</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>278</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>279</v>
-      </c>
-      <c r="H23" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
@@ -3611,7 +3611,7 @@
         <v>77</v>
       </c>
       <c r="B24" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C24" t="s">
         <v>232</v>
@@ -3620,16 +3620,16 @@
         <v>239</v>
       </c>
       <c r="E24" t="s">
+        <v>281</v>
+      </c>
+      <c r="F24" t="s">
         <v>282</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>283</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>284</v>
-      </c>
-      <c r="H24" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -3637,25 +3637,25 @@
         <v>96</v>
       </c>
       <c r="B25" t="s">
+        <v>285</v>
+      </c>
+      <c r="C25" t="s">
         <v>286</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>287</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>288</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>289</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>290</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>291</v>
-      </c>
-      <c r="H25" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
@@ -3663,25 +3663,25 @@
         <v>87</v>
       </c>
       <c r="B26" t="s">
+        <v>292</v>
+      </c>
+      <c r="C26" t="s">
         <v>293</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>294</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>295</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>296</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>297</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>298</v>
-      </c>
-      <c r="H26" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -3689,25 +3689,25 @@
         <v>70</v>
       </c>
       <c r="B27" t="s">
+        <v>299</v>
+      </c>
+      <c r="C27" t="s">
         <v>300</v>
-      </c>
-      <c r="C27" t="s">
-        <v>301</v>
       </c>
       <c r="D27" t="s">
         <v>152</v>
       </c>
       <c r="E27" t="s">
+        <v>301</v>
+      </c>
+      <c r="F27" t="s">
         <v>302</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>303</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
         <v>304</v>
-      </c>
-      <c r="H27" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -3715,25 +3715,25 @@
         <v>119</v>
       </c>
       <c r="B28" t="s">
+        <v>311</v>
+      </c>
+      <c r="C28" t="s">
         <v>306</v>
-      </c>
-      <c r="C28" t="s">
-        <v>307</v>
       </c>
       <c r="D28" t="s">
         <v>212</v>
       </c>
       <c r="E28" t="s">
+        <v>307</v>
+      </c>
+      <c r="F28" t="s">
         <v>308</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>309</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>310</v>
-      </c>
-      <c r="H28" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -3741,25 +3741,25 @@
         <v>122</v>
       </c>
       <c r="B29" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="C29" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D29" t="s">
         <v>212</v>
       </c>
       <c r="E29" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F29" t="s">
         <v>228</v>
       </c>
       <c r="G29" t="s">
+        <v>312</v>
+      </c>
+      <c r="H29" t="s">
         <v>313</v>
-      </c>
-      <c r="H29" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -3767,7 +3767,7 @@
         <v>139</v>
       </c>
       <c r="B30" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C30" t="s">
         <v>211</v>
@@ -3776,16 +3776,16 @@
         <v>212</v>
       </c>
       <c r="E30" t="s">
+        <v>315</v>
+      </c>
+      <c r="F30" t="s">
         <v>316</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>317</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>318</v>
-      </c>
-      <c r="H30" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -3793,25 +3793,25 @@
         <v>99</v>
       </c>
       <c r="B31" t="s">
+        <v>319</v>
+      </c>
+      <c r="C31" t="s">
         <v>320</v>
-      </c>
-      <c r="C31" t="s">
-        <v>321</v>
       </c>
       <c r="D31" t="s">
         <v>226</v>
       </c>
       <c r="E31" t="s">
+        <v>321</v>
+      </c>
+      <c r="F31" t="s">
         <v>322</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>323</v>
       </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
         <v>324</v>
-      </c>
-      <c r="H31" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -3819,25 +3819,25 @@
         <v>116</v>
       </c>
       <c r="B32" t="s">
+        <v>325</v>
+      </c>
+      <c r="C32" t="s">
         <v>326</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>327</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>328</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>329</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>330</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>331</v>
-      </c>
-      <c r="H32" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -3845,25 +3845,25 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
+        <v>332</v>
+      </c>
+      <c r="C33" t="s">
         <v>333</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
+        <v>287</v>
+      </c>
+      <c r="E33" t="s">
         <v>334</v>
       </c>
-      <c r="D33" t="s">
-        <v>288</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>335</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>336</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
         <v>337</v>
-      </c>
-      <c r="H33" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
@@ -3871,7 +3871,7 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C34" t="s">
         <v>177</v>
@@ -3880,16 +3880,16 @@
         <v>152</v>
       </c>
       <c r="E34" t="s">
+        <v>339</v>
+      </c>
+      <c r="F34" t="s">
         <v>340</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>341</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>342</v>
-      </c>
-      <c r="H34" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -3897,7 +3897,7 @@
         <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C35" t="s">
         <v>171</v>
@@ -3906,16 +3906,16 @@
         <v>152</v>
       </c>
       <c r="E35" t="s">
+        <v>344</v>
+      </c>
+      <c r="F35" t="s">
         <v>345</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>346</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
         <v>347</v>
-      </c>
-      <c r="H35" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -3923,25 +3923,25 @@
         <v>75</v>
       </c>
       <c r="B36" t="s">
+        <v>348</v>
+      </c>
+      <c r="C36" t="s">
         <v>349</v>
-      </c>
-      <c r="C36" t="s">
-        <v>350</v>
       </c>
       <c r="D36" t="s">
         <v>159</v>
       </c>
       <c r="E36" t="s">
+        <v>350</v>
+      </c>
+      <c r="F36" t="s">
         <v>351</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>352</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>353</v>
-      </c>
-      <c r="H36" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -3949,7 +3949,7 @@
         <v>19</v>
       </c>
       <c r="B37" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C37" t="s">
         <v>218</v>
@@ -3958,16 +3958,16 @@
         <v>219</v>
       </c>
       <c r="E37" t="s">
+        <v>355</v>
+      </c>
+      <c r="F37" t="s">
         <v>356</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>357</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>358</v>
-      </c>
-      <c r="H37" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
@@ -3975,7 +3975,7 @@
         <v>126</v>
       </c>
       <c r="B38" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C38" t="s">
         <v>189</v>
@@ -3984,16 +3984,16 @@
         <v>159</v>
       </c>
       <c r="E38" t="s">
+        <v>360</v>
+      </c>
+      <c r="F38" t="s">
         <v>361</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>362</v>
       </c>
-      <c r="G38" t="s">
+      <c r="H38" t="s">
         <v>363</v>
-      </c>
-      <c r="H38" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -4001,25 +4001,25 @@
         <v>131</v>
       </c>
       <c r="B39" t="s">
+        <v>364</v>
+      </c>
+      <c r="C39" t="s">
         <v>365</v>
-      </c>
-      <c r="C39" t="s">
-        <v>366</v>
       </c>
       <c r="D39" t="s">
         <v>159</v>
       </c>
       <c r="E39" t="s">
+        <v>366</v>
+      </c>
+      <c r="F39" t="s">
         <v>367</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>368</v>
       </c>
-      <c r="G39" t="s">
+      <c r="H39" t="s">
         <v>369</v>
-      </c>
-      <c r="H39" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -4027,7 +4027,7 @@
         <v>105</v>
       </c>
       <c r="B40" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C40" t="s">
         <v>183</v>
@@ -4036,16 +4036,16 @@
         <v>212</v>
       </c>
       <c r="E40" t="s">
+        <v>371</v>
+      </c>
+      <c r="F40" t="s">
         <v>372</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>373</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
         <v>374</v>
-      </c>
-      <c r="H40" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -4053,25 +4053,25 @@
         <v>124</v>
       </c>
       <c r="B41" t="s">
+        <v>375</v>
+      </c>
+      <c r="C41" t="s">
         <v>376</v>
-      </c>
-      <c r="C41" t="s">
-        <v>377</v>
       </c>
       <c r="D41" t="s">
         <v>159</v>
       </c>
       <c r="E41" t="s">
+        <v>377</v>
+      </c>
+      <c r="F41" t="s">
         <v>378</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>379</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41" t="s">
         <v>380</v>
-      </c>
-      <c r="H41" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
@@ -4079,25 +4079,25 @@
         <v>53</v>
       </c>
       <c r="B42" t="s">
+        <v>387</v>
+      </c>
+      <c r="C42" t="s">
         <v>382</v>
-      </c>
-      <c r="C42" t="s">
-        <v>383</v>
       </c>
       <c r="D42" t="s">
         <v>219</v>
       </c>
       <c r="E42" t="s">
+        <v>383</v>
+      </c>
+      <c r="F42" t="s">
         <v>384</v>
       </c>
-      <c r="F42" t="s">
-        <v>385</v>
-      </c>
       <c r="G42" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="H42" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -4105,7 +4105,7 @@
         <v>111</v>
       </c>
       <c r="B43" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="C43" t="s">
         <v>151</v>
@@ -4114,16 +4114,16 @@
         <v>219</v>
       </c>
       <c r="E43" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F43" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G43" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="H43" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -4131,25 +4131,25 @@
         <v>108</v>
       </c>
       <c r="B44" t="s">
+        <v>391</v>
+      </c>
+      <c r="C44" t="s">
         <v>392</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
+        <v>294</v>
+      </c>
+      <c r="E44" t="s">
         <v>393</v>
       </c>
-      <c r="D44" t="s">
-        <v>295</v>
-      </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>394</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>395</v>
       </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
         <v>396</v>
-      </c>
-      <c r="H44" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -4157,25 +4157,25 @@
         <v>33</v>
       </c>
       <c r="B45" t="s">
+        <v>397</v>
+      </c>
+      <c r="C45" t="s">
         <v>398</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
+        <v>287</v>
+      </c>
+      <c r="E45" t="s">
         <v>399</v>
       </c>
-      <c r="D45" t="s">
-        <v>288</v>
-      </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>400</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>401</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>402</v>
-      </c>
-      <c r="H45" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
@@ -4183,25 +4183,25 @@
         <v>127</v>
       </c>
       <c r="B46" t="s">
+        <v>403</v>
+      </c>
+      <c r="C46" t="s">
         <v>404</v>
-      </c>
-      <c r="C46" t="s">
-        <v>405</v>
       </c>
       <c r="D46" t="s">
         <v>159</v>
       </c>
       <c r="E46" t="s">
+        <v>405</v>
+      </c>
+      <c r="F46" t="s">
         <v>406</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>407</v>
       </c>
-      <c r="G46" t="s">
+      <c r="H46" t="s">
         <v>408</v>
-      </c>
-      <c r="H46" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
@@ -4209,25 +4209,25 @@
         <v>142</v>
       </c>
       <c r="B47" t="s">
+        <v>409</v>
+      </c>
+      <c r="C47" t="s">
         <v>410</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>411</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>412</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>413</v>
       </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>414</v>
       </c>
-      <c r="G47" t="s">
+      <c r="H47" t="s">
         <v>415</v>
-      </c>
-      <c r="H47" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
@@ -4235,25 +4235,25 @@
         <v>23</v>
       </c>
       <c r="B48" t="s">
+        <v>416</v>
+      </c>
+      <c r="C48" t="s">
         <v>417</v>
-      </c>
-      <c r="C48" t="s">
-        <v>418</v>
       </c>
       <c r="D48" t="s">
         <v>219</v>
       </c>
       <c r="E48" t="s">
+        <v>418</v>
+      </c>
+      <c r="F48" t="s">
         <v>419</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>420</v>
       </c>
-      <c r="G48" t="s">
+      <c r="H48" t="s">
         <v>421</v>
-      </c>
-      <c r="H48" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
@@ -4261,25 +4261,25 @@
         <v>104</v>
       </c>
       <c r="B49" t="s">
+        <v>422</v>
+      </c>
+      <c r="C49" t="s">
         <v>423</v>
-      </c>
-      <c r="C49" t="s">
-        <v>424</v>
       </c>
       <c r="D49" t="s">
         <v>159</v>
       </c>
       <c r="E49" t="s">
+        <v>424</v>
+      </c>
+      <c r="F49" t="s">
         <v>425</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>426</v>
       </c>
-      <c r="G49" t="s">
+      <c r="H49" t="s">
         <v>427</v>
-      </c>
-      <c r="H49" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
@@ -4287,7 +4287,7 @@
         <v>29</v>
       </c>
       <c r="B50" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C50" t="s">
         <v>177</v>
@@ -4296,16 +4296,16 @@
         <v>152</v>
       </c>
       <c r="E50" t="s">
+        <v>429</v>
+      </c>
+      <c r="F50" t="s">
         <v>430</v>
       </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>431</v>
       </c>
-      <c r="G50" t="s">
+      <c r="H50" t="s">
         <v>432</v>
-      </c>
-      <c r="H50" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
@@ -4313,25 +4313,25 @@
         <v>74</v>
       </c>
       <c r="B51" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C51" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D51" t="s">
         <v>152</v>
       </c>
       <c r="E51" t="s">
+        <v>434</v>
+      </c>
+      <c r="F51" t="s">
         <v>435</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>436</v>
       </c>
-      <c r="G51" t="s">
+      <c r="H51" t="s">
         <v>437</v>
-      </c>
-      <c r="H51" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
@@ -4339,25 +4339,25 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C52" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D52" t="s">
         <v>219</v>
       </c>
       <c r="E52" t="s">
+        <v>439</v>
+      </c>
+      <c r="F52" t="s">
         <v>440</v>
       </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>441</v>
       </c>
-      <c r="G52" t="s">
+      <c r="H52" t="s">
         <v>442</v>
-      </c>
-      <c r="H52" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
@@ -4365,25 +4365,25 @@
         <v>100</v>
       </c>
       <c r="B53" t="s">
+        <v>443</v>
+      </c>
+      <c r="C53" t="s">
+        <v>286</v>
+      </c>
+      <c r="D53" t="s">
+        <v>287</v>
+      </c>
+      <c r="E53" t="s">
         <v>444</v>
       </c>
-      <c r="C53" t="s">
-        <v>287</v>
-      </c>
-      <c r="D53" t="s">
-        <v>288</v>
-      </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
+        <v>345</v>
+      </c>
+      <c r="G53" t="s">
         <v>445</v>
       </c>
-      <c r="F53" t="s">
-        <v>346</v>
-      </c>
-      <c r="G53" t="s">
+      <c r="H53" t="s">
         <v>446</v>
-      </c>
-      <c r="H53" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
@@ -4391,25 +4391,25 @@
         <v>27</v>
       </c>
       <c r="B54" t="s">
+        <v>447</v>
+      </c>
+      <c r="C54" t="s">
         <v>448</v>
-      </c>
-      <c r="C54" t="s">
-        <v>449</v>
       </c>
       <c r="D54" t="s">
         <v>219</v>
       </c>
       <c r="E54" t="s">
+        <v>449</v>
+      </c>
+      <c r="F54" t="s">
+        <v>419</v>
+      </c>
+      <c r="G54" t="s">
         <v>450</v>
       </c>
-      <c r="F54" t="s">
-        <v>420</v>
-      </c>
-      <c r="G54" t="s">
+      <c r="H54" t="s">
         <v>451</v>
-      </c>
-      <c r="H54" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
@@ -4417,25 +4417,25 @@
         <v>40</v>
       </c>
       <c r="B55" t="s">
+        <v>452</v>
+      </c>
+      <c r="C55" t="s">
         <v>453</v>
-      </c>
-      <c r="C55" t="s">
-        <v>454</v>
       </c>
       <c r="D55" t="s">
         <v>226</v>
       </c>
       <c r="E55" t="s">
+        <v>454</v>
+      </c>
+      <c r="F55" t="s">
         <v>455</v>
       </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>456</v>
       </c>
-      <c r="G55" t="s">
+      <c r="H55" t="s">
         <v>457</v>
-      </c>
-      <c r="H55" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
@@ -4443,25 +4443,25 @@
         <v>129</v>
       </c>
       <c r="B56" t="s">
+        <v>458</v>
+      </c>
+      <c r="C56" t="s">
         <v>459</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
+        <v>294</v>
+      </c>
+      <c r="E56" t="s">
         <v>460</v>
       </c>
-      <c r="D56" t="s">
-        <v>295</v>
-      </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>461</v>
       </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
         <v>462</v>
       </c>
-      <c r="G56" t="s">
+      <c r="H56" t="s">
         <v>463</v>
-      </c>
-      <c r="H56" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
@@ -4469,25 +4469,25 @@
         <v>130</v>
       </c>
       <c r="B57" t="s">
+        <v>464</v>
+      </c>
+      <c r="C57" t="s">
         <v>465</v>
-      </c>
-      <c r="C57" t="s">
-        <v>466</v>
       </c>
       <c r="D57" t="s">
         <v>159</v>
       </c>
       <c r="E57" t="s">
+        <v>466</v>
+      </c>
+      <c r="F57" t="s">
         <v>467</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>468</v>
       </c>
-      <c r="G57" t="s">
+      <c r="H57" t="s">
         <v>469</v>
-      </c>
-      <c r="H57" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -4495,7 +4495,7 @@
         <v>120</v>
       </c>
       <c r="B58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C58" t="s">
         <v>158</v>
@@ -4504,16 +4504,16 @@
         <v>159</v>
       </c>
       <c r="E58" t="s">
+        <v>471</v>
+      </c>
+      <c r="F58" t="s">
         <v>472</v>
       </c>
-      <c r="F58" t="s">
+      <c r="G58" t="s">
         <v>473</v>
       </c>
-      <c r="G58" t="s">
+      <c r="H58" t="s">
         <v>474</v>
-      </c>
-      <c r="H58" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
@@ -4521,7 +4521,7 @@
         <v>14</v>
       </c>
       <c r="B59" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C59" t="s">
         <v>171</v>
@@ -4530,16 +4530,16 @@
         <v>159</v>
       </c>
       <c r="E59" t="s">
+        <v>476</v>
+      </c>
+      <c r="F59" t="s">
         <v>477</v>
       </c>
-      <c r="F59" t="s">
+      <c r="G59" t="s">
         <v>478</v>
       </c>
-      <c r="G59" t="s">
+      <c r="H59" t="s">
         <v>479</v>
-      </c>
-      <c r="H59" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
@@ -4547,25 +4547,25 @@
         <v>92</v>
       </c>
       <c r="B60" t="s">
+        <v>480</v>
+      </c>
+      <c r="C60" t="s">
         <v>481</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
+        <v>327</v>
+      </c>
+      <c r="E60" t="s">
         <v>482</v>
       </c>
-      <c r="D60" t="s">
-        <v>328</v>
-      </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>483</v>
       </c>
-      <c r="F60" t="s">
+      <c r="G60" t="s">
         <v>484</v>
       </c>
-      <c r="G60" t="s">
+      <c r="H60" t="s">
         <v>485</v>
-      </c>
-      <c r="H60" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
@@ -4573,7 +4573,7 @@
         <v>81</v>
       </c>
       <c r="B61" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C61" t="s">
         <v>232</v>
@@ -4582,16 +4582,16 @@
         <v>239</v>
       </c>
       <c r="E61" t="s">
+        <v>487</v>
+      </c>
+      <c r="F61" t="s">
         <v>488</v>
       </c>
-      <c r="F61" t="s">
+      <c r="G61" t="s">
         <v>489</v>
       </c>
-      <c r="G61" t="s">
+      <c r="H61" t="s">
         <v>490</v>
-      </c>
-      <c r="H61" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
@@ -4599,7 +4599,7 @@
         <v>30</v>
       </c>
       <c r="B62" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C62" t="s">
         <v>255</v>
@@ -4608,16 +4608,16 @@
         <v>152</v>
       </c>
       <c r="E62" t="s">
+        <v>492</v>
+      </c>
+      <c r="F62" t="s">
         <v>493</v>
       </c>
-      <c r="F62" t="s">
+      <c r="G62" t="s">
         <v>494</v>
       </c>
-      <c r="G62" t="s">
+      <c r="H62" t="s">
         <v>495</v>
-      </c>
-      <c r="H62" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
@@ -4625,25 +4625,25 @@
         <v>138</v>
       </c>
       <c r="B63" t="s">
+        <v>496</v>
+      </c>
+      <c r="C63" t="s">
         <v>497</v>
-      </c>
-      <c r="C63" t="s">
-        <v>498</v>
       </c>
       <c r="D63" t="s">
         <v>159</v>
       </c>
       <c r="E63" t="s">
+        <v>498</v>
+      </c>
+      <c r="F63" t="s">
         <v>499</v>
       </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
         <v>500</v>
       </c>
-      <c r="G63" t="s">
+      <c r="H63" t="s">
         <v>501</v>
-      </c>
-      <c r="H63" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
@@ -4651,25 +4651,25 @@
         <v>35</v>
       </c>
       <c r="B64" t="s">
+        <v>502</v>
+      </c>
+      <c r="C64" t="s">
         <v>503</v>
-      </c>
-      <c r="C64" t="s">
-        <v>504</v>
       </c>
       <c r="D64" t="s">
         <v>219</v>
       </c>
       <c r="E64" t="s">
+        <v>504</v>
+      </c>
+      <c r="F64" t="s">
         <v>505</v>
       </c>
-      <c r="F64" t="s">
+      <c r="G64" t="s">
         <v>506</v>
       </c>
-      <c r="G64" t="s">
+      <c r="H64" t="s">
         <v>507</v>
-      </c>
-      <c r="H64" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
@@ -4677,25 +4677,25 @@
         <v>43</v>
       </c>
       <c r="B65" t="s">
+        <v>508</v>
+      </c>
+      <c r="C65" t="s">
         <v>509</v>
-      </c>
-      <c r="C65" t="s">
-        <v>510</v>
       </c>
       <c r="D65" t="s">
         <v>226</v>
       </c>
       <c r="E65" t="s">
+        <v>510</v>
+      </c>
+      <c r="F65" t="s">
         <v>511</v>
       </c>
-      <c r="F65" t="s">
+      <c r="G65" t="s">
         <v>512</v>
       </c>
-      <c r="G65" t="s">
+      <c r="H65" t="s">
         <v>513</v>
-      </c>
-      <c r="H65" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
@@ -4703,25 +4703,25 @@
         <v>44</v>
       </c>
       <c r="B66" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C66" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D66" t="s">
         <v>226</v>
       </c>
       <c r="E66" t="s">
+        <v>515</v>
+      </c>
+      <c r="F66" t="s">
         <v>516</v>
       </c>
-      <c r="F66" t="s">
+      <c r="G66" t="s">
         <v>517</v>
       </c>
-      <c r="G66" t="s">
+      <c r="H66" t="s">
         <v>518</v>
-      </c>
-      <c r="H66" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
@@ -4729,25 +4729,25 @@
         <v>13</v>
       </c>
       <c r="B67" t="s">
+        <v>519</v>
+      </c>
+      <c r="C67" t="s">
         <v>520</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
+        <v>411</v>
+      </c>
+      <c r="E67" t="s">
         <v>521</v>
       </c>
-      <c r="D67" t="s">
-        <v>412</v>
-      </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>522</v>
       </c>
-      <c r="F67" t="s">
+      <c r="G67" t="s">
         <v>523</v>
       </c>
-      <c r="G67" t="s">
+      <c r="H67" t="s">
         <v>524</v>
-      </c>
-      <c r="H67" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
@@ -4755,25 +4755,25 @@
         <v>48</v>
       </c>
       <c r="B68" t="s">
+        <v>525</v>
+      </c>
+      <c r="C68" t="s">
         <v>526</v>
       </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
+        <v>294</v>
+      </c>
+      <c r="E68" t="s">
         <v>527</v>
       </c>
-      <c r="D68" t="s">
-        <v>295</v>
-      </c>
-      <c r="E68" t="s">
+      <c r="F68" t="s">
         <v>528</v>
       </c>
-      <c r="F68" t="s">
+      <c r="G68" t="s">
         <v>529</v>
       </c>
-      <c r="G68" t="s">
+      <c r="H68" t="s">
         <v>530</v>
-      </c>
-      <c r="H68" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
@@ -4781,25 +4781,25 @@
         <v>86</v>
       </c>
       <c r="B69" t="s">
+        <v>531</v>
+      </c>
+      <c r="C69" t="s">
         <v>532</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
+        <v>411</v>
+      </c>
+      <c r="E69" t="s">
         <v>533</v>
       </c>
-      <c r="D69" t="s">
-        <v>412</v>
-      </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>534</v>
       </c>
-      <c r="F69" t="s">
+      <c r="G69" t="s">
         <v>535</v>
       </c>
-      <c r="G69" t="s">
+      <c r="H69" t="s">
         <v>536</v>
-      </c>
-      <c r="H69" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
@@ -4807,25 +4807,25 @@
         <v>78</v>
       </c>
       <c r="B70" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C70" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D70" t="s">
         <v>152</v>
       </c>
       <c r="E70" t="s">
+        <v>538</v>
+      </c>
+      <c r="F70" t="s">
         <v>539</v>
       </c>
-      <c r="F70" t="s">
+      <c r="G70" t="s">
         <v>540</v>
       </c>
-      <c r="G70" t="s">
+      <c r="H70" t="s">
         <v>541</v>
-      </c>
-      <c r="H70" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
@@ -4833,7 +4833,7 @@
         <v>140</v>
       </c>
       <c r="B71" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C71" t="s">
         <v>238</v>
@@ -4842,16 +4842,16 @@
         <v>226</v>
       </c>
       <c r="E71" t="s">
+        <v>543</v>
+      </c>
+      <c r="F71" t="s">
         <v>544</v>
       </c>
-      <c r="F71" t="s">
+      <c r="G71" t="s">
         <v>545</v>
       </c>
-      <c r="G71" t="s">
+      <c r="H71" t="s">
         <v>546</v>
-      </c>
-      <c r="H71" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
@@ -4859,25 +4859,25 @@
         <v>45</v>
       </c>
       <c r="B72" t="s">
+        <v>547</v>
+      </c>
+      <c r="C72" t="s">
         <v>548</v>
-      </c>
-      <c r="C72" t="s">
-        <v>549</v>
       </c>
       <c r="D72" t="s">
         <v>219</v>
       </c>
       <c r="E72" t="s">
+        <v>549</v>
+      </c>
+      <c r="F72" t="s">
         <v>550</v>
       </c>
-      <c r="F72" t="s">
+      <c r="G72" t="s">
         <v>551</v>
       </c>
-      <c r="G72" t="s">
+      <c r="H72" t="s">
         <v>552</v>
-      </c>
-      <c r="H72" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
@@ -4885,25 +4885,25 @@
         <v>51</v>
       </c>
       <c r="B73" t="s">
+        <v>553</v>
+      </c>
+      <c r="C73" t="s">
         <v>554</v>
-      </c>
-      <c r="C73" t="s">
-        <v>555</v>
       </c>
       <c r="D73" t="s">
         <v>212</v>
       </c>
       <c r="E73" t="s">
+        <v>555</v>
+      </c>
+      <c r="F73" t="s">
         <v>556</v>
       </c>
-      <c r="F73" t="s">
+      <c r="G73" t="s">
         <v>557</v>
       </c>
-      <c r="G73" t="s">
+      <c r="H73" t="s">
         <v>558</v>
-      </c>
-      <c r="H73" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
@@ -4911,25 +4911,25 @@
         <v>135</v>
       </c>
       <c r="B74" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C74" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D74" t="s">
         <v>159</v>
       </c>
       <c r="E74" t="s">
+        <v>560</v>
+      </c>
+      <c r="F74" t="s">
         <v>561</v>
       </c>
-      <c r="F74" t="s">
+      <c r="G74" t="s">
         <v>562</v>
       </c>
-      <c r="G74" t="s">
+      <c r="H74" t="s">
         <v>563</v>
-      </c>
-      <c r="H74" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
@@ -4937,25 +4937,25 @@
         <v>56</v>
       </c>
       <c r="B75" t="s">
+        <v>564</v>
+      </c>
+      <c r="C75" t="s">
+        <v>703</v>
+      </c>
+      <c r="D75" t="s">
+        <v>411</v>
+      </c>
+      <c r="E75" t="s">
         <v>565</v>
       </c>
-      <c r="C75" t="s">
-        <v>705</v>
-      </c>
-      <c r="D75" t="s">
-        <v>412</v>
-      </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>566</v>
       </c>
-      <c r="F75" t="s">
+      <c r="G75" t="s">
         <v>567</v>
       </c>
-      <c r="G75" t="s">
+      <c r="H75" t="s">
         <v>568</v>
-      </c>
-      <c r="H75" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
@@ -4963,25 +4963,25 @@
         <v>61</v>
       </c>
       <c r="B76" t="s">
+        <v>569</v>
+      </c>
+      <c r="C76" t="s">
         <v>570</v>
-      </c>
-      <c r="C76" t="s">
-        <v>571</v>
       </c>
       <c r="D76" t="s">
         <v>219</v>
       </c>
       <c r="E76" t="s">
+        <v>571</v>
+      </c>
+      <c r="F76" t="s">
         <v>572</v>
       </c>
-      <c r="F76" t="s">
+      <c r="G76" t="s">
         <v>573</v>
       </c>
-      <c r="G76" t="s">
+      <c r="H76" t="s">
         <v>574</v>
-      </c>
-      <c r="H76" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
@@ -4989,25 +4989,25 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C77" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D77" t="s">
         <v>152</v>
       </c>
       <c r="E77" t="s">
+        <v>576</v>
+      </c>
+      <c r="F77" t="s">
         <v>577</v>
       </c>
-      <c r="F77" t="s">
+      <c r="G77" t="s">
         <v>578</v>
       </c>
-      <c r="G77" t="s">
+      <c r="H77" t="s">
         <v>579</v>
-      </c>
-      <c r="H77" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
@@ -5015,25 +5015,25 @@
         <v>143</v>
       </c>
       <c r="B78" t="s">
+        <v>580</v>
+      </c>
+      <c r="C78" t="s">
         <v>581</v>
-      </c>
-      <c r="C78" t="s">
-        <v>582</v>
       </c>
       <c r="D78" t="s">
         <v>159</v>
       </c>
       <c r="E78" t="s">
+        <v>582</v>
+      </c>
+      <c r="F78" t="s">
         <v>583</v>
       </c>
-      <c r="F78" t="s">
+      <c r="G78" t="s">
         <v>584</v>
       </c>
-      <c r="G78" t="s">
+      <c r="H78" t="s">
         <v>585</v>
-      </c>
-      <c r="H78" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
@@ -5041,25 +5041,25 @@
         <v>59</v>
       </c>
       <c r="B79" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C79" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D79" t="s">
         <v>159</v>
       </c>
       <c r="E79" t="s">
+        <v>587</v>
+      </c>
+      <c r="F79" t="s">
         <v>588</v>
       </c>
-      <c r="F79" t="s">
+      <c r="G79" t="s">
         <v>589</v>
       </c>
-      <c r="G79" t="s">
+      <c r="H79" t="s">
         <v>590</v>
-      </c>
-      <c r="H79" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
@@ -5067,25 +5067,25 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
+        <v>591</v>
+      </c>
+      <c r="C80" t="s">
         <v>592</v>
-      </c>
-      <c r="C80" t="s">
-        <v>593</v>
       </c>
       <c r="D80" t="s">
         <v>159</v>
       </c>
       <c r="E80" t="s">
+        <v>593</v>
+      </c>
+      <c r="F80" t="s">
         <v>594</v>
       </c>
-      <c r="F80" t="s">
+      <c r="G80" t="s">
         <v>595</v>
       </c>
-      <c r="G80" t="s">
+      <c r="H80" t="s">
         <v>596</v>
-      </c>
-      <c r="H80" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
@@ -5093,25 +5093,25 @@
         <v>141</v>
       </c>
       <c r="B81" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C81" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D81" t="s">
         <v>159</v>
       </c>
       <c r="E81" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F81" t="s">
+        <v>598</v>
+      </c>
+      <c r="G81" t="s">
         <v>599</v>
       </c>
-      <c r="G81" t="s">
+      <c r="H81" t="s">
         <v>600</v>
-      </c>
-      <c r="H81" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
@@ -5119,25 +5119,25 @@
         <v>144</v>
       </c>
       <c r="B82" t="s">
+        <v>601</v>
+      </c>
+      <c r="C82" t="s">
+        <v>410</v>
+      </c>
+      <c r="D82" t="s">
+        <v>411</v>
+      </c>
+      <c r="E82" t="s">
         <v>602</v>
       </c>
-      <c r="C82" t="s">
-        <v>411</v>
-      </c>
-      <c r="D82" t="s">
-        <v>412</v>
-      </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
         <v>603</v>
       </c>
-      <c r="F82" t="s">
+      <c r="G82" t="s">
         <v>604</v>
       </c>
-      <c r="G82" t="s">
+      <c r="H82" t="s">
         <v>605</v>
-      </c>
-      <c r="H82" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
@@ -5145,25 +5145,25 @@
         <v>60</v>
       </c>
       <c r="B83" t="s">
+        <v>606</v>
+      </c>
+      <c r="C83" t="s">
         <v>607</v>
-      </c>
-      <c r="C83" t="s">
-        <v>608</v>
       </c>
       <c r="D83" t="s">
         <v>159</v>
       </c>
       <c r="E83" t="s">
+        <v>608</v>
+      </c>
+      <c r="F83" t="s">
         <v>609</v>
       </c>
-      <c r="F83" t="s">
+      <c r="G83" t="s">
         <v>610</v>
       </c>
-      <c r="G83" t="s">
+      <c r="H83" t="s">
         <v>611</v>
-      </c>
-      <c r="H83" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
@@ -5171,25 +5171,25 @@
         <v>66</v>
       </c>
       <c r="B84" t="s">
+        <v>612</v>
+      </c>
+      <c r="C84" t="s">
         <v>613</v>
       </c>
-      <c r="C84" t="s">
+      <c r="D84" t="s">
+        <v>411</v>
+      </c>
+      <c r="E84" t="s">
         <v>614</v>
       </c>
-      <c r="D84" t="s">
-        <v>412</v>
-      </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>615</v>
       </c>
-      <c r="F84" t="s">
+      <c r="G84" t="s">
         <v>616</v>
       </c>
-      <c r="G84" t="s">
+      <c r="H84" t="s">
         <v>617</v>
-      </c>
-      <c r="H84" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
@@ -5197,25 +5197,25 @@
         <v>34</v>
       </c>
       <c r="B85" t="s">
+        <v>618</v>
+      </c>
+      <c r="C85" t="s">
         <v>619</v>
       </c>
-      <c r="C85" t="s">
+      <c r="D85" t="s">
+        <v>287</v>
+      </c>
+      <c r="E85" t="s">
         <v>620</v>
       </c>
-      <c r="D85" t="s">
-        <v>288</v>
-      </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
         <v>621</v>
       </c>
-      <c r="F85" t="s">
+      <c r="G85" t="s">
         <v>622</v>
       </c>
-      <c r="G85" t="s">
+      <c r="H85" t="s">
         <v>623</v>
-      </c>
-      <c r="H85" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
@@ -5223,25 +5223,25 @@
         <v>41</v>
       </c>
       <c r="B86" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C86" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D86" t="s">
         <v>219</v>
       </c>
       <c r="E86" t="s">
+        <v>625</v>
+      </c>
+      <c r="F86" t="s">
         <v>626</v>
       </c>
-      <c r="F86" t="s">
+      <c r="G86" t="s">
         <v>627</v>
       </c>
-      <c r="G86" t="s">
+      <c r="H86" t="s">
         <v>628</v>
-      </c>
-      <c r="H86" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
@@ -5249,25 +5249,25 @@
         <v>79</v>
       </c>
       <c r="B87" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C87" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D87" t="s">
         <v>159</v>
       </c>
       <c r="E87" t="s">
+        <v>630</v>
+      </c>
+      <c r="F87" t="s">
         <v>631</v>
       </c>
-      <c r="F87" t="s">
+      <c r="G87" t="s">
         <v>632</v>
       </c>
-      <c r="G87" t="s">
+      <c r="H87" t="s">
         <v>633</v>
-      </c>
-      <c r="H87" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
@@ -5275,7 +5275,7 @@
         <v>91</v>
       </c>
       <c r="B88" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C88" t="s">
         <v>232</v>
@@ -5284,16 +5284,16 @@
         <v>239</v>
       </c>
       <c r="E88" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="F88" t="s">
+        <v>635</v>
+      </c>
+      <c r="G88" t="s">
         <v>636</v>
       </c>
-      <c r="G88" t="s">
+      <c r="H88" t="s">
         <v>637</v>
-      </c>
-      <c r="H88" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
@@ -5301,25 +5301,25 @@
         <v>118</v>
       </c>
       <c r="B89" t="s">
+        <v>638</v>
+      </c>
+      <c r="C89" t="s">
         <v>639</v>
-      </c>
-      <c r="C89" t="s">
-        <v>640</v>
       </c>
       <c r="D89" t="s">
         <v>152</v>
       </c>
       <c r="E89" t="s">
+        <v>640</v>
+      </c>
+      <c r="F89" t="s">
         <v>641</v>
       </c>
-      <c r="F89" t="s">
+      <c r="G89" t="s">
         <v>642</v>
       </c>
-      <c r="G89" t="s">
+      <c r="H89" t="s">
         <v>643</v>
-      </c>
-      <c r="H89" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
@@ -5327,25 +5327,25 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C90" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D90" t="s">
         <v>226</v>
       </c>
       <c r="E90" t="s">
+        <v>645</v>
+      </c>
+      <c r="F90" t="s">
+        <v>345</v>
+      </c>
+      <c r="G90" t="s">
         <v>646</v>
       </c>
-      <c r="F90" t="s">
-        <v>346</v>
-      </c>
-      <c r="G90" t="s">
+      <c r="H90" t="s">
         <v>647</v>
-      </c>
-      <c r="H90" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
@@ -5353,25 +5353,25 @@
         <v>121</v>
       </c>
       <c r="B91" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C91" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D91" t="s">
         <v>152</v>
       </c>
       <c r="E91" t="s">
+        <v>649</v>
+      </c>
+      <c r="F91" t="s">
         <v>650</v>
       </c>
-      <c r="F91" t="s">
+      <c r="G91" t="s">
         <v>651</v>
       </c>
-      <c r="G91" t="s">
+      <c r="H91" t="s">
         <v>652</v>
-      </c>
-      <c r="H91" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
@@ -5379,25 +5379,25 @@
         <v>67</v>
       </c>
       <c r="B92" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C92" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D92" t="s">
         <v>219</v>
       </c>
       <c r="E92" t="s">
+        <v>654</v>
+      </c>
+      <c r="F92" t="s">
         <v>655</v>
       </c>
-      <c r="F92" t="s">
+      <c r="G92" t="s">
         <v>656</v>
       </c>
-      <c r="G92" t="s">
+      <c r="H92" t="s">
         <v>657</v>
-      </c>
-      <c r="H92" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
@@ -5405,25 +5405,25 @@
         <v>49</v>
       </c>
       <c r="B93" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C93" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D93" t="s">
         <v>219</v>
       </c>
       <c r="E93" t="s">
+        <v>659</v>
+      </c>
+      <c r="F93" t="s">
+        <v>467</v>
+      </c>
+      <c r="G93" t="s">
         <v>660</v>
       </c>
-      <c r="F93" t="s">
-        <v>468</v>
-      </c>
-      <c r="G93" t="s">
+      <c r="H93" t="s">
         <v>661</v>
-      </c>
-      <c r="H93" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
@@ -5431,25 +5431,25 @@
         <v>31</v>
       </c>
       <c r="B94" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C94" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D94" t="s">
         <v>219</v>
       </c>
       <c r="E94" t="s">
+        <v>663</v>
+      </c>
+      <c r="F94" t="s">
         <v>664</v>
       </c>
-      <c r="F94" t="s">
+      <c r="G94" t="s">
         <v>665</v>
       </c>
-      <c r="G94" t="s">
+      <c r="H94" t="s">
         <v>666</v>
-      </c>
-      <c r="H94" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
@@ -5457,7 +5457,7 @@
         <v>109</v>
       </c>
       <c r="B95" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C95" t="s">
         <v>183</v>
@@ -5466,16 +5466,16 @@
         <v>159</v>
       </c>
       <c r="E95" t="s">
+        <v>668</v>
+      </c>
+      <c r="F95" t="s">
+        <v>626</v>
+      </c>
+      <c r="G95" t="s">
         <v>669</v>
       </c>
-      <c r="F95" t="s">
-        <v>627</v>
-      </c>
-      <c r="G95" t="s">
+      <c r="H95" t="s">
         <v>670</v>
-      </c>
-      <c r="H95" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
@@ -5483,25 +5483,25 @@
         <v>71</v>
       </c>
       <c r="B96" t="s">
-        <v>672</v>
+        <v>704</v>
       </c>
       <c r="C96" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D96" t="s">
         <v>219</v>
       </c>
       <c r="E96" t="s">
+        <v>671</v>
+      </c>
+      <c r="F96" t="s">
+        <v>505</v>
+      </c>
+      <c r="G96" t="s">
+        <v>672</v>
+      </c>
+      <c r="H96" t="s">
         <v>673</v>
-      </c>
-      <c r="F96" t="s">
-        <v>506</v>
-      </c>
-      <c r="G96" t="s">
-        <v>674</v>
-      </c>
-      <c r="H96" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
@@ -5509,25 +5509,25 @@
         <v>128</v>
       </c>
       <c r="B97" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C97" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D97" t="s">
         <v>226</v>
       </c>
       <c r="E97" t="s">
+        <v>676</v>
+      </c>
+      <c r="F97" t="s">
+        <v>677</v>
+      </c>
+      <c r="G97" t="s">
         <v>678</v>
       </c>
-      <c r="F97" t="s">
+      <c r="H97" t="s">
         <v>679</v>
-      </c>
-      <c r="G97" t="s">
-        <v>680</v>
-      </c>
-      <c r="H97" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
@@ -5535,7 +5535,7 @@
         <v>95</v>
       </c>
       <c r="B98" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C98" t="s">
         <v>232</v>
@@ -5544,16 +5544,16 @@
         <v>239</v>
       </c>
       <c r="E98" t="s">
+        <v>681</v>
+      </c>
+      <c r="F98" t="s">
+        <v>682</v>
+      </c>
+      <c r="G98" t="s">
         <v>683</v>
       </c>
-      <c r="F98" t="s">
+      <c r="H98" t="s">
         <v>684</v>
-      </c>
-      <c r="G98" t="s">
-        <v>685</v>
-      </c>
-      <c r="H98" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
@@ -5561,25 +5561,25 @@
         <v>133</v>
       </c>
       <c r="B99" t="s">
+        <v>685</v>
+      </c>
+      <c r="C99" t="s">
+        <v>686</v>
+      </c>
+      <c r="D99" t="s">
+        <v>411</v>
+      </c>
+      <c r="E99" t="s">
         <v>687</v>
       </c>
-      <c r="C99" t="s">
+      <c r="F99" t="s">
         <v>688</v>
       </c>
-      <c r="D99" t="s">
-        <v>412</v>
-      </c>
-      <c r="E99" t="s">
+      <c r="G99" t="s">
         <v>689</v>
       </c>
-      <c r="F99" t="s">
+      <c r="H99" t="s">
         <v>690</v>
-      </c>
-      <c r="G99" t="s">
-        <v>691</v>
-      </c>
-      <c r="H99" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
@@ -5587,25 +5587,25 @@
         <v>17</v>
       </c>
       <c r="B100" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C100" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="D100" t="s">
         <v>239</v>
       </c>
       <c r="E100" t="s">
+        <v>693</v>
+      </c>
+      <c r="F100" t="s">
+        <v>694</v>
+      </c>
+      <c r="G100" t="s">
         <v>695</v>
       </c>
-      <c r="F100" t="s">
+      <c r="H100" t="s">
         <v>696</v>
-      </c>
-      <c r="G100" t="s">
-        <v>697</v>
-      </c>
-      <c r="H100" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
@@ -5613,7 +5613,7 @@
         <v>113</v>
       </c>
       <c r="B101" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C101" t="s">
         <v>183</v>
@@ -5622,16 +5622,16 @@
         <v>152</v>
       </c>
       <c r="E101" t="s">
+        <v>698</v>
+      </c>
+      <c r="F101" t="s">
+        <v>699</v>
+      </c>
+      <c r="G101" t="s">
         <v>700</v>
       </c>
-      <c r="F101" t="s">
+      <c r="H101" t="s">
         <v>701</v>
-      </c>
-      <c r="G101" t="s">
-        <v>702</v>
-      </c>
-      <c r="H101" t="s">
-        <v>703</v>
       </c>
     </row>
   </sheetData>
@@ -6356,11 +6356,11 @@
       </c>
       <c r="G22" s="6" t="str">
         <f>IFERROR(VLOOKUP($F22,Data!$A:$D,4,FALSE),"")</f>
-        <v>Physics</v>
+        <v>Biology &amp; Medicine</v>
       </c>
       <c r="H22" s="6" t="str">
         <f>IFERROR(VLOOKUP($F22,Data!$A:$D,2,FALSE),"")</f>
-        <v>Sinusoidal Representation Networks for Neural Renormalization-Group Flows on the1D and 2D Ising Models</v>
+        <v>Temporal Mapping of Doxorubicin-Induced Alterations in Autophagic Flux in hiPSC-Derived Cardiomyocytes</v>
       </c>
       <c r="I22" s="6" t="str">
         <f>IFERROR(VLOOKUP($F22,Data!$A:$D,3,FALSE),"")</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="L22" s="6" t="str">
         <f>IFERROR(VLOOKUP($J22,Data!$A:$D,2,FALSE),"")</f>
-        <v>DC-MTNN: A Drug-Conditioned Multi-Task Neural Network for Predicting Drug Resistance in Mycobacterium tuberculosis Using Genomic Data</v>
+        <v>Effective Computation of Free Resolutions and Cohomology for Quotients of Braid Groups</v>
       </c>
       <c r="M22" s="6" t="str">
         <f>IFERROR(VLOOKUP($J22,Data!$A:$D,3,FALSE),"")</f>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="D23" s="6" t="str">
         <f>IFERROR(VLOOKUP($B23,Data!$A:$D,2,FALSE),"")</f>
-        <v>Effect of ZAP70 Mutations on CAR T-Cell Effectiveness Targeting GD2 in Brain Tumors</v>
+        <v>Effect of ZAP70 Mutations on CAR T-Cell Effectiveness Targeting GD2 in Brain Tumors and N6 Leukemia Cells</v>
       </c>
       <c r="E23" s="6" t="str">
         <f>IFERROR(VLOOKUP($B23,Data!$A:$D,3,FALSE),"")</f>
@@ -6586,11 +6586,11 @@
       </c>
       <c r="C29" s="6" t="str">
         <f>IFERROR(VLOOKUP($B29,Data!$A:$D,4,FALSE),"")</f>
-        <v>Biology &amp; Medicine</v>
+        <v>Earth, Ocean &amp; Climate</v>
       </c>
       <c r="D29" s="6" t="str">
         <f>IFERROR(VLOOKUP($B29,Data!$A:$D,2,FALSE),"")</f>
-        <v>Temporal Mapping of Doxorubicin-Induced Alterations in Autophagic Flux in hiPSC-Derived Cardiomyocytes</v>
+        <v>Navier–Stokes Characteristic Boundary Conditions for Limited-Area Numerical Weather Prediction</v>
       </c>
       <c r="E29" s="6" t="str">
         <f>IFERROR(VLOOKUP($B29,Data!$A:$D,3,FALSE),"")</f>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="L30" s="6" t="str">
         <f>IFERROR(VLOOKUP($J30,Data!$A:$D,2,FALSE),"")</f>
-        <v>Triangular Taxicabs</v>
+        <v>A Taxicab Journey to Triangle Centres</v>
       </c>
       <c r="M30" s="6" t="str">
         <f>IFERROR(VLOOKUP($J30,Data!$A:$D,3,FALSE),"")</f>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="D44" s="6" t="str">
         <f>IFERROR(VLOOKUP($B44,Data!$A:$D,2,FALSE),"")</f>
-        <v>Effective Computation of Free Resolutions and Cohomology for Quotients of Braid Groups</v>
+        <v>DC-MTNN: A Drug-Conditioned Multi-Task Neural Network for Predicting Drug Resistance in Mycobacterium tuberculosis Using Genomic Data</v>
       </c>
       <c r="E44" s="6" t="str">
         <f>IFERROR(VLOOKUP($B44,Data!$A:$D,3,FALSE),"")</f>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="D52" s="6" t="str">
         <f>IFERROR(VLOOKUP($B52,Data!$A:$D,2,FALSE),"")</f>
-        <v>The Grammar of Natural Systems: Compositional Material Design Across Scales</v>
+        <v>Predicting Peptide Self-Assembly Phase from LLM Extracted Experimental Conditions</v>
       </c>
       <c r="E52" s="6" t="str">
         <f>IFERROR(VLOOKUP($B52,Data!$A:$D,3,FALSE),"")</f>
@@ -7480,7 +7480,7 @@
       </c>
       <c r="D53" s="6" t="str">
         <f>IFERROR(VLOOKUP($B53,Data!$A:$D,2,FALSE),"")</f>
-        <v>Predicting Peptide Self-Assembly Phase from LLM Extracted Experimental Conditions</v>
+        <v>The Grammar of Natural Systems: Compositional Material Design Across Scales</v>
       </c>
       <c r="E53" s="6" t="str">
         <f>IFERROR(VLOOKUP($B53,Data!$A:$D,3,FALSE),"")</f>
@@ -7801,11 +7801,11 @@
       </c>
       <c r="K61" s="6" t="str">
         <f>IFERROR(VLOOKUP($J61,Data!$A:$D,4,FALSE),"")</f>
-        <v>Earth, Ocean &amp; Climate</v>
+        <v>Physics</v>
       </c>
       <c r="L61" s="6" t="str">
         <f>IFERROR(VLOOKUP($J61,Data!$A:$D,2,FALSE),"")</f>
-        <v>Navier–Stokes Characteristic Boundary Conditions for Limited-Area Numerical Weather Prediction</v>
+        <v>Sinusoidal Representation Networks for Neural Renormalization-Group Flows on the1D and 2D Ising Models</v>
       </c>
       <c r="M61" s="6" t="str">
         <f>IFERROR(VLOOKUP($J61,Data!$A:$D,3,FALSE),"")</f>
@@ -7994,102 +7994,102 @@
     <mergeCell ref="A47:M47"/>
   </mergeCells>
   <conditionalFormatting sqref="C4:C71">
-    <cfRule type="cellIs" dxfId="32" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
+      <formula>"Math"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="4" operator="equal">
+      <formula>"Physics"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="7" operator="equal">
+      <formula>"Astronomy &amp; Planetary Science"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="29" priority="10" operator="equal">
+      <formula>"Computer Science &amp; AI"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="13" operator="equal">
       <formula>"Engineering"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="31" operator="equal">
-      <formula>"Other"</formula>
+    <cfRule type="cellIs" dxfId="27" priority="16" operator="equal">
+      <formula>"Chemistry &amp; Materials"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="19" operator="equal">
+      <formula>"Biology &amp; Medicine"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="22" operator="equal">
+      <formula>"Neuroscience &amp; Psychology"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="25" operator="equal">
+      <formula>"Earth, Ocean &amp; Climate"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="23" priority="28" operator="equal">
       <formula>"Economics &amp; Policy"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="4" operator="equal">
-      <formula>"Physics"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="25" operator="equal">
-      <formula>"Earth, Ocean &amp; Climate"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="22" operator="equal">
-      <formula>"Neuroscience &amp; Psychology"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="7" operator="equal">
-      <formula>"Astronomy &amp; Planetary Science"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="19" operator="equal">
-      <formula>"Biology &amp; Medicine"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
-      <formula>"Math"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="10" operator="equal">
-      <formula>"Computer Science &amp; AI"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="16" operator="equal">
-      <formula>"Chemistry &amp; Materials"</formula>
+    <cfRule type="cellIs" dxfId="22" priority="31" operator="equal">
+      <formula>"Other"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G71">
-    <cfRule type="cellIs" dxfId="21" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
+      <formula>"Math"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="20" priority="5" operator="equal">
+      <formula>"Physics"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="8" operator="equal">
+      <formula>"Astronomy &amp; Planetary Science"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="11" operator="equal">
+      <formula>"Computer Science &amp; AI"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="14" operator="equal">
+      <formula>"Engineering"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
       <formula>"Chemistry &amp; Materials"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="14" operator="equal">
-      <formula>"Engineering"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="11" operator="equal">
-      <formula>"Computer Science &amp; AI"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="8" operator="equal">
-      <formula>"Astronomy &amp; Planetary Science"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="20" operator="equal">
       <formula>"Biology &amp; Medicine"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="23" operator="equal">
       <formula>"Neuroscience &amp; Psychology"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
-      <formula>"Physics"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="26" operator="equal">
       <formula>"Earth, Ocean &amp; Climate"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="29" operator="equal">
       <formula>"Economics &amp; Policy"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
-      <formula>"Math"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="11" priority="32" operator="equal">
       <formula>"Other"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4:K71">
-    <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
-      <formula>"Computer Science &amp; AI"</formula>
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
+      <formula>"Math"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="15" operator="equal">
-      <formula>"Engineering"</formula>
+    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
+      <formula>"Physics"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
       <formula>"Astronomy &amp; Planetary Science"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="12" operator="equal">
+      <formula>"Computer Science &amp; AI"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="15" operator="equal">
+      <formula>"Engineering"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="18" operator="equal">
       <formula>"Chemistry &amp; Materials"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="21" operator="equal">
       <formula>"Biology &amp; Medicine"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
-      <formula>"Physics"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="24" operator="equal">
       <formula>"Neuroscience &amp; Psychology"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="27" operator="equal">
       <formula>"Earth, Ocean &amp; Climate"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"Math"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="1" priority="30" operator="equal">
       <formula>"Economics &amp; Policy"</formula>

--- a/RSI_2026_Schedule.xlsx
+++ b/RSI_2026_Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/evanlim/Documents/rsi-symposium/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F4999B-D936-F546-BC67-D41FFE4EF26E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7629648-54C8-5E46-A4CF-216DE6E77D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="705">
   <si>
     <t>RSI 2026 Symposium Schedule</t>
   </si>
@@ -585,9 +585,6 @@
     <t>alej0</t>
   </si>
   <si>
-    <t>Investigating cognitive decline in HIV</t>
-  </si>
-  <si>
     <t>Prof. Manolis Kellis</t>
   </si>
   <si>
@@ -786,9 +783,6 @@
     <t>Observing Landau Levels in Simulated Strained Graphene</t>
   </si>
   <si>
-    <t>Prof. Jenny Hoffman, Sarah Ziegler</t>
-  </si>
-  <si>
     <t>ah-ZAR-ee-ah</t>
   </si>
   <si>
@@ -831,9 +825,6 @@
     <t>cho0707</t>
   </si>
   <si>
-    <t>Schrodinger Bridges for Graph Interpolations</t>
-  </si>
-  <si>
     <t>Prof. Justin Solomon</t>
   </si>
   <si>
@@ -1053,9 +1044,6 @@
     <t>eason</t>
   </si>
   <si>
-    <t>Teaching a Medical Vision-Language Model with Automatic Feedback</t>
-  </si>
-  <si>
     <t>EH-rik</t>
   </si>
   <si>
@@ -1998,9 +1986,6 @@
     <t>tarora</t>
   </si>
   <si>
-    <t>Enumerating Index-Two and Index-Three Nilpotent Matrices in Symplectic Lie Algebras</t>
-  </si>
-  <si>
     <t>TAH-rah</t>
   </si>
   <si>
@@ -2155,6 +2140,18 @@
   </si>
   <si>
     <t>Effect of ZAP70 Mutations on CAR T-Cell Effectiveness Targeting GD2 in Brain Tumors and N6 Leukemia Cells</t>
+  </si>
+  <si>
+    <t>Enumerating Nilpotent Matrices over Finite Fields</t>
+  </si>
+  <si>
+    <t>Sinkhorn Schrödinger Bridges for Graph Interpolations</t>
+  </si>
+  <si>
+    <t>Using Cell-Projected Phenotypes to study HIV induced cognitive decline</t>
+  </si>
+  <si>
+    <t>Two-Stage Outcome-Based Reinforcement Learning for a Compact Medical Vision-Language Model</t>
   </si>
 </sst>
 </file>
@@ -2311,6 +2308,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2330,7 +2328,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2361,11 +2358,154 @@
     <dxf>
       <font>
         <sz val="9"/>
+        <color rgb="FF1D4ED8"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDBEAFE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
         <color rgb="FF0F766E"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFCCFBF1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FFBE185D"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE7F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FF6D28D9"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEDE9FE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FF047857"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD1FAE5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FFB45309"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FF4338CA"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE0E7FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FFC2410C"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEDD5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FF0E7490"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCFFAFE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FF475569"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1F5F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FF1D4ED8"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDBEAFE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FFBE123C"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE4E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FF0F766E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCCFBF1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FF6D28D9"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEDE9FE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2394,11 +2534,22 @@
     <dxf>
       <font>
         <sz val="9"/>
-        <color rgb="FFB45309"/>
+        <color rgb="FF4338CA"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFEF3C7"/>
+          <fgColor rgb="FFE0E7FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FF0E7490"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCFFAFE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2416,11 +2567,55 @@
     <dxf>
       <font>
         <sz val="9"/>
+        <color rgb="FFB45309"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FFB45309"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
         <color rgb="FF0E7490"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFCFFAFE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FF1D4ED8"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDBEAFE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FF047857"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD1FAE5"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2438,6 +2633,28 @@
     <dxf>
       <font>
         <sz val="9"/>
+        <color rgb="FFBE185D"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE7F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+        <color rgb="FF0F766E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCCFBF1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
         <color rgb="FF6D28D9"/>
       </font>
       <fill>
@@ -2449,11 +2666,11 @@
     <dxf>
       <font>
         <sz val="9"/>
-        <color rgb="FF1D4ED8"/>
+        <color rgb="FFBE123C"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFDBEAFE"/>
+          <fgColor rgb="FFFFE4E6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2471,231 +2688,11 @@
     <dxf>
       <font>
         <sz val="9"/>
-        <color rgb="FFBE123C"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE4E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF0F766E"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCCFBF1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FFBE185D"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE7F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF047857"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD1FAE5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FFB45309"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF3C7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
         <color rgb="FFC2410C"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFEDD5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF0E7490"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFFAFE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF4338CA"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE0E7FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF6D28D9"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEDE9FE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF1D4ED8"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDBEAFE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF475569"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1F5F9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FFBE123C"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE4E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF0F766E"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCCFBF1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FFBE185D"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE7F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF047857"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD1FAE5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FFB45309"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF3C7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FFC2410C"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEDD5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF0E7490"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFFAFE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF4338CA"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE0E7FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF6D28D9"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEDE9FE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-        <color rgb="FF1D4ED8"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDBEAFE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3169,25 +3166,25 @@
         <v>93</v>
       </c>
       <c r="B7" t="s">
+        <v>703</v>
+      </c>
+      <c r="C7" t="s">
         <v>182</v>
-      </c>
-      <c r="C7" t="s">
-        <v>183</v>
       </c>
       <c r="D7" t="s">
         <v>159</v>
       </c>
       <c r="E7" t="s">
+        <v>183</v>
+      </c>
+      <c r="F7" t="s">
         <v>184</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>185</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>186</v>
-      </c>
-      <c r="H7" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -3195,25 +3192,25 @@
         <v>123</v>
       </c>
       <c r="B8" t="s">
+        <v>187</v>
+      </c>
+      <c r="C8" t="s">
         <v>188</v>
-      </c>
-      <c r="C8" t="s">
-        <v>189</v>
       </c>
       <c r="D8" t="s">
         <v>159</v>
       </c>
       <c r="E8" t="s">
+        <v>189</v>
+      </c>
+      <c r="F8" t="s">
         <v>190</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>191</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>192</v>
-      </c>
-      <c r="H8" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -3221,25 +3218,25 @@
         <v>97</v>
       </c>
       <c r="B9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D9" t="s">
         <v>159</v>
       </c>
       <c r="E9" t="s">
+        <v>194</v>
+      </c>
+      <c r="F9" t="s">
         <v>195</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>196</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>197</v>
-      </c>
-      <c r="H9" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -3247,25 +3244,25 @@
         <v>112</v>
       </c>
       <c r="B10" t="s">
+        <v>198</v>
+      </c>
+      <c r="C10" t="s">
         <v>199</v>
-      </c>
-      <c r="C10" t="s">
-        <v>200</v>
       </c>
       <c r="D10" t="s">
         <v>159</v>
       </c>
       <c r="E10" t="s">
+        <v>200</v>
+      </c>
+      <c r="F10" t="s">
         <v>201</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>202</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>203</v>
-      </c>
-      <c r="H10" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -3273,7 +3270,7 @@
         <v>107</v>
       </c>
       <c r="B11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C11" t="s">
         <v>151</v>
@@ -3282,16 +3279,16 @@
         <v>159</v>
       </c>
       <c r="E11" t="s">
+        <v>205</v>
+      </c>
+      <c r="F11" t="s">
         <v>206</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>207</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>208</v>
-      </c>
-      <c r="H11" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -3299,25 +3296,25 @@
         <v>136</v>
       </c>
       <c r="B12" t="s">
+        <v>209</v>
+      </c>
+      <c r="C12" t="s">
         <v>210</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>211</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>212</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>213</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>214</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>215</v>
-      </c>
-      <c r="H12" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -3325,25 +3322,25 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
+        <v>216</v>
+      </c>
+      <c r="C13" t="s">
         <v>217</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>218</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>219</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>220</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>221</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>222</v>
-      </c>
-      <c r="H13" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -3351,25 +3348,25 @@
         <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C14" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D14" t="s">
         <v>159</v>
       </c>
       <c r="E14" t="s">
+        <v>226</v>
+      </c>
+      <c r="F14" t="s">
         <v>227</v>
       </c>
-      <c r="F14" t="s">
-        <v>228</v>
-      </c>
       <c r="G14" t="s">
+        <v>234</v>
+      </c>
+      <c r="H14" t="s">
         <v>235</v>
-      </c>
-      <c r="H14" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -3377,25 +3374,25 @@
         <v>65</v>
       </c>
       <c r="B15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C15" t="s">
+        <v>231</v>
+      </c>
+      <c r="D15" t="s">
+        <v>238</v>
+      </c>
+      <c r="E15" t="s">
         <v>232</v>
       </c>
-      <c r="D15" t="s">
-        <v>239</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>233</v>
       </c>
-      <c r="F15" t="s">
-        <v>234</v>
-      </c>
       <c r="G15" t="s">
+        <v>240</v>
+      </c>
+      <c r="H15" t="s">
         <v>241</v>
-      </c>
-      <c r="H15" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -3403,25 +3400,25 @@
         <v>137</v>
       </c>
       <c r="B16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C16" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F16" t="s">
+        <v>227</v>
+      </c>
+      <c r="G16" t="s">
         <v>228</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>229</v>
-      </c>
-      <c r="H16" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -3429,25 +3426,25 @@
         <v>69</v>
       </c>
       <c r="B17" t="s">
+        <v>242</v>
+      </c>
+      <c r="C17" t="s">
+        <v>231</v>
+      </c>
+      <c r="D17" t="s">
+        <v>238</v>
+      </c>
+      <c r="E17" t="s">
         <v>243</v>
       </c>
-      <c r="C17" t="s">
-        <v>232</v>
-      </c>
-      <c r="D17" t="s">
-        <v>239</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>244</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>245</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>246</v>
-      </c>
-      <c r="H17" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -3455,25 +3452,25 @@
         <v>125</v>
       </c>
       <c r="B18" t="s">
+        <v>247</v>
+      </c>
+      <c r="C18" t="s">
+        <v>670</v>
+      </c>
+      <c r="D18" t="s">
+        <v>225</v>
+      </c>
+      <c r="E18" t="s">
         <v>248</v>
       </c>
-      <c r="C18" t="s">
+      <c r="F18" t="s">
         <v>249</v>
       </c>
-      <c r="D18" t="s">
-        <v>226</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="G18" t="s">
         <v>250</v>
       </c>
-      <c r="F18" t="s">
+      <c r="H18" t="s">
         <v>251</v>
-      </c>
-      <c r="G18" t="s">
-        <v>252</v>
-      </c>
-      <c r="H18" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -3481,25 +3478,25 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C19" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D19" t="s">
         <v>152</v>
       </c>
       <c r="E19" t="s">
+        <v>254</v>
+      </c>
+      <c r="F19" t="s">
+        <v>255</v>
+      </c>
+      <c r="G19" t="s">
         <v>256</v>
       </c>
-      <c r="F19" t="s">
+      <c r="H19" t="s">
         <v>257</v>
-      </c>
-      <c r="G19" t="s">
-        <v>258</v>
-      </c>
-      <c r="H19" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -3507,25 +3504,25 @@
         <v>73</v>
       </c>
       <c r="B20" t="s">
+        <v>258</v>
+      </c>
+      <c r="C20" t="s">
+        <v>231</v>
+      </c>
+      <c r="D20" t="s">
+        <v>238</v>
+      </c>
+      <c r="E20" t="s">
+        <v>259</v>
+      </c>
+      <c r="F20" t="s">
+        <v>190</v>
+      </c>
+      <c r="G20" t="s">
         <v>260</v>
       </c>
-      <c r="C20" t="s">
-        <v>232</v>
-      </c>
-      <c r="D20" t="s">
-        <v>239</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="H20" t="s">
         <v>261</v>
-      </c>
-      <c r="F20" t="s">
-        <v>191</v>
-      </c>
-      <c r="G20" t="s">
-        <v>262</v>
-      </c>
-      <c r="H20" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -3533,25 +3530,25 @@
         <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>264</v>
+        <v>702</v>
       </c>
       <c r="C21" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>152</v>
       </c>
       <c r="E21" t="s">
+        <v>263</v>
+      </c>
+      <c r="F21" t="s">
+        <v>264</v>
+      </c>
+      <c r="G21" t="s">
+        <v>265</v>
+      </c>
+      <c r="H21" t="s">
         <v>266</v>
-      </c>
-      <c r="F21" t="s">
-        <v>267</v>
-      </c>
-      <c r="G21" t="s">
-        <v>268</v>
-      </c>
-      <c r="H21" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -3559,25 +3556,25 @@
         <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="C22" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D22" t="s">
         <v>159</v>
       </c>
       <c r="E22" t="s">
+        <v>268</v>
+      </c>
+      <c r="F22" t="s">
+        <v>269</v>
+      </c>
+      <c r="G22" t="s">
+        <v>270</v>
+      </c>
+      <c r="H22" t="s">
         <v>271</v>
-      </c>
-      <c r="F22" t="s">
-        <v>272</v>
-      </c>
-      <c r="G22" t="s">
-        <v>273</v>
-      </c>
-      <c r="H22" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -3585,25 +3582,25 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D23" t="s">
         <v>159</v>
       </c>
       <c r="E23" t="s">
+        <v>273</v>
+      </c>
+      <c r="F23" t="s">
+        <v>274</v>
+      </c>
+      <c r="G23" t="s">
+        <v>275</v>
+      </c>
+      <c r="H23" t="s">
         <v>276</v>
-      </c>
-      <c r="F23" t="s">
-        <v>277</v>
-      </c>
-      <c r="G23" t="s">
-        <v>278</v>
-      </c>
-      <c r="H23" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
@@ -3611,25 +3608,25 @@
         <v>77</v>
       </c>
       <c r="B24" t="s">
+        <v>277</v>
+      </c>
+      <c r="C24" t="s">
+        <v>231</v>
+      </c>
+      <c r="D24" t="s">
+        <v>238</v>
+      </c>
+      <c r="E24" t="s">
+        <v>278</v>
+      </c>
+      <c r="F24" t="s">
+        <v>279</v>
+      </c>
+      <c r="G24" t="s">
         <v>280</v>
       </c>
-      <c r="C24" t="s">
-        <v>232</v>
-      </c>
-      <c r="D24" t="s">
-        <v>239</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="H24" t="s">
         <v>281</v>
-      </c>
-      <c r="F24" t="s">
-        <v>282</v>
-      </c>
-      <c r="G24" t="s">
-        <v>283</v>
-      </c>
-      <c r="H24" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -3637,25 +3634,25 @@
         <v>96</v>
       </c>
       <c r="B25" t="s">
+        <v>282</v>
+      </c>
+      <c r="C25" t="s">
+        <v>283</v>
+      </c>
+      <c r="D25" t="s">
+        <v>284</v>
+      </c>
+      <c r="E25" t="s">
         <v>285</v>
       </c>
-      <c r="C25" t="s">
+      <c r="F25" t="s">
         <v>286</v>
       </c>
-      <c r="D25" t="s">
+      <c r="G25" t="s">
         <v>287</v>
       </c>
-      <c r="E25" t="s">
+      <c r="H25" t="s">
         <v>288</v>
-      </c>
-      <c r="F25" t="s">
-        <v>289</v>
-      </c>
-      <c r="G25" t="s">
-        <v>290</v>
-      </c>
-      <c r="H25" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
@@ -3663,25 +3660,25 @@
         <v>87</v>
       </c>
       <c r="B26" t="s">
+        <v>289</v>
+      </c>
+      <c r="C26" t="s">
+        <v>290</v>
+      </c>
+      <c r="D26" t="s">
+        <v>291</v>
+      </c>
+      <c r="E26" t="s">
         <v>292</v>
       </c>
-      <c r="C26" t="s">
+      <c r="F26" t="s">
         <v>293</v>
       </c>
-      <c r="D26" t="s">
+      <c r="G26" t="s">
         <v>294</v>
       </c>
-      <c r="E26" t="s">
+      <c r="H26" t="s">
         <v>295</v>
-      </c>
-      <c r="F26" t="s">
-        <v>296</v>
-      </c>
-      <c r="G26" t="s">
-        <v>297</v>
-      </c>
-      <c r="H26" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -3689,25 +3686,25 @@
         <v>70</v>
       </c>
       <c r="B27" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C27" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D27" t="s">
         <v>152</v>
       </c>
       <c r="E27" t="s">
+        <v>298</v>
+      </c>
+      <c r="F27" t="s">
+        <v>299</v>
+      </c>
+      <c r="G27" t="s">
+        <v>300</v>
+      </c>
+      <c r="H27" t="s">
         <v>301</v>
-      </c>
-      <c r="F27" t="s">
-        <v>302</v>
-      </c>
-      <c r="G27" t="s">
-        <v>303</v>
-      </c>
-      <c r="H27" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -3715,25 +3712,25 @@
         <v>119</v>
       </c>
       <c r="B28" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C28" t="s">
+        <v>303</v>
+      </c>
+      <c r="D28" t="s">
+        <v>211</v>
+      </c>
+      <c r="E28" t="s">
+        <v>304</v>
+      </c>
+      <c r="F28" t="s">
+        <v>305</v>
+      </c>
+      <c r="G28" t="s">
         <v>306</v>
       </c>
-      <c r="D28" t="s">
-        <v>212</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="H28" t="s">
         <v>307</v>
-      </c>
-      <c r="F28" t="s">
-        <v>308</v>
-      </c>
-      <c r="G28" t="s">
-        <v>309</v>
-      </c>
-      <c r="H28" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -3741,25 +3738,25 @@
         <v>122</v>
       </c>
       <c r="B29" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C29" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D29" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E29" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="F29" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G29" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="H29" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -3767,25 +3764,25 @@
         <v>139</v>
       </c>
       <c r="B30" t="s">
+        <v>311</v>
+      </c>
+      <c r="C30" t="s">
+        <v>210</v>
+      </c>
+      <c r="D30" t="s">
+        <v>211</v>
+      </c>
+      <c r="E30" t="s">
+        <v>312</v>
+      </c>
+      <c r="F30" t="s">
+        <v>313</v>
+      </c>
+      <c r="G30" t="s">
         <v>314</v>
       </c>
-      <c r="C30" t="s">
-        <v>211</v>
-      </c>
-      <c r="D30" t="s">
-        <v>212</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="H30" t="s">
         <v>315</v>
-      </c>
-      <c r="F30" t="s">
-        <v>316</v>
-      </c>
-      <c r="G30" t="s">
-        <v>317</v>
-      </c>
-      <c r="H30" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -3793,25 +3790,25 @@
         <v>99</v>
       </c>
       <c r="B31" t="s">
+        <v>316</v>
+      </c>
+      <c r="C31" t="s">
+        <v>317</v>
+      </c>
+      <c r="D31" t="s">
+        <v>225</v>
+      </c>
+      <c r="E31" t="s">
+        <v>318</v>
+      </c>
+      <c r="F31" t="s">
         <v>319</v>
       </c>
-      <c r="C31" t="s">
+      <c r="G31" t="s">
         <v>320</v>
       </c>
-      <c r="D31" t="s">
-        <v>226</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="H31" t="s">
         <v>321</v>
-      </c>
-      <c r="F31" t="s">
-        <v>322</v>
-      </c>
-      <c r="G31" t="s">
-        <v>323</v>
-      </c>
-      <c r="H31" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -3819,25 +3816,25 @@
         <v>116</v>
       </c>
       <c r="B32" t="s">
+        <v>322</v>
+      </c>
+      <c r="C32" t="s">
+        <v>323</v>
+      </c>
+      <c r="D32" t="s">
+        <v>324</v>
+      </c>
+      <c r="E32" t="s">
         <v>325</v>
       </c>
-      <c r="C32" t="s">
+      <c r="F32" t="s">
         <v>326</v>
       </c>
-      <c r="D32" t="s">
+      <c r="G32" t="s">
         <v>327</v>
       </c>
-      <c r="E32" t="s">
+      <c r="H32" t="s">
         <v>328</v>
-      </c>
-      <c r="F32" t="s">
-        <v>329</v>
-      </c>
-      <c r="G32" t="s">
-        <v>330</v>
-      </c>
-      <c r="H32" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -3845,25 +3842,25 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
+        <v>329</v>
+      </c>
+      <c r="C33" t="s">
+        <v>330</v>
+      </c>
+      <c r="D33" t="s">
+        <v>284</v>
+      </c>
+      <c r="E33" t="s">
+        <v>331</v>
+      </c>
+      <c r="F33" t="s">
         <v>332</v>
       </c>
-      <c r="C33" t="s">
+      <c r="G33" t="s">
         <v>333</v>
       </c>
-      <c r="D33" t="s">
-        <v>287</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="H33" t="s">
         <v>334</v>
-      </c>
-      <c r="F33" t="s">
-        <v>335</v>
-      </c>
-      <c r="G33" t="s">
-        <v>336</v>
-      </c>
-      <c r="H33" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
@@ -3871,7 +3868,7 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>338</v>
+        <v>704</v>
       </c>
       <c r="C34" t="s">
         <v>177</v>
@@ -3880,16 +3877,16 @@
         <v>152</v>
       </c>
       <c r="E34" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="F34" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G34" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="H34" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -3897,7 +3894,7 @@
         <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C35" t="s">
         <v>171</v>
@@ -3906,16 +3903,16 @@
         <v>152</v>
       </c>
       <c r="E35" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F35" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G35" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="H35" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -3923,25 +3920,25 @@
         <v>75</v>
       </c>
       <c r="B36" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C36" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D36" t="s">
         <v>159</v>
       </c>
       <c r="E36" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="F36" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="G36" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="H36" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -3949,25 +3946,25 @@
         <v>19</v>
       </c>
       <c r="B37" t="s">
+        <v>350</v>
+      </c>
+      <c r="C37" t="s">
+        <v>217</v>
+      </c>
+      <c r="D37" t="s">
+        <v>218</v>
+      </c>
+      <c r="E37" t="s">
+        <v>351</v>
+      </c>
+      <c r="F37" t="s">
+        <v>352</v>
+      </c>
+      <c r="G37" t="s">
+        <v>353</v>
+      </c>
+      <c r="H37" t="s">
         <v>354</v>
-      </c>
-      <c r="C37" t="s">
-        <v>218</v>
-      </c>
-      <c r="D37" t="s">
-        <v>219</v>
-      </c>
-      <c r="E37" t="s">
-        <v>355</v>
-      </c>
-      <c r="F37" t="s">
-        <v>356</v>
-      </c>
-      <c r="G37" t="s">
-        <v>357</v>
-      </c>
-      <c r="H37" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
@@ -3975,25 +3972,25 @@
         <v>126</v>
       </c>
       <c r="B38" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C38" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D38" t="s">
         <v>159</v>
       </c>
       <c r="E38" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="F38" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="G38" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="H38" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -4001,25 +3998,25 @@
         <v>131</v>
       </c>
       <c r="B39" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C39" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="D39" t="s">
         <v>159</v>
       </c>
       <c r="E39" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="F39" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="G39" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="H39" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -4027,25 +4024,25 @@
         <v>105</v>
       </c>
       <c r="B40" t="s">
+        <v>366</v>
+      </c>
+      <c r="C40" t="s">
+        <v>182</v>
+      </c>
+      <c r="D40" t="s">
+        <v>211</v>
+      </c>
+      <c r="E40" t="s">
+        <v>367</v>
+      </c>
+      <c r="F40" t="s">
+        <v>368</v>
+      </c>
+      <c r="G40" t="s">
+        <v>369</v>
+      </c>
+      <c r="H40" t="s">
         <v>370</v>
-      </c>
-      <c r="C40" t="s">
-        <v>183</v>
-      </c>
-      <c r="D40" t="s">
-        <v>212</v>
-      </c>
-      <c r="E40" t="s">
-        <v>371</v>
-      </c>
-      <c r="F40" t="s">
-        <v>372</v>
-      </c>
-      <c r="G40" t="s">
-        <v>373</v>
-      </c>
-      <c r="H40" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -4053,25 +4050,25 @@
         <v>124</v>
       </c>
       <c r="B41" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C41" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D41" t="s">
         <v>159</v>
       </c>
       <c r="E41" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="F41" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="G41" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="H41" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
@@ -4079,25 +4076,25 @@
         <v>53</v>
       </c>
       <c r="B42" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C42" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D42" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E42" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="F42" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="G42" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="H42" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -4105,25 +4102,25 @@
         <v>111</v>
       </c>
       <c r="B43" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C43" t="s">
         <v>151</v>
       </c>
       <c r="D43" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E43" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="F43" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="G43" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="H43" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -4131,25 +4128,25 @@
         <v>108</v>
       </c>
       <c r="B44" t="s">
+        <v>387</v>
+      </c>
+      <c r="C44" t="s">
+        <v>388</v>
+      </c>
+      <c r="D44" t="s">
+        <v>291</v>
+      </c>
+      <c r="E44" t="s">
+        <v>389</v>
+      </c>
+      <c r="F44" t="s">
+        <v>390</v>
+      </c>
+      <c r="G44" t="s">
         <v>391</v>
       </c>
-      <c r="C44" t="s">
+      <c r="H44" t="s">
         <v>392</v>
-      </c>
-      <c r="D44" t="s">
-        <v>294</v>
-      </c>
-      <c r="E44" t="s">
-        <v>393</v>
-      </c>
-      <c r="F44" t="s">
-        <v>394</v>
-      </c>
-      <c r="G44" t="s">
-        <v>395</v>
-      </c>
-      <c r="H44" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -4157,25 +4154,25 @@
         <v>33</v>
       </c>
       <c r="B45" t="s">
+        <v>393</v>
+      </c>
+      <c r="C45" t="s">
+        <v>394</v>
+      </c>
+      <c r="D45" t="s">
+        <v>284</v>
+      </c>
+      <c r="E45" t="s">
+        <v>395</v>
+      </c>
+      <c r="F45" t="s">
+        <v>396</v>
+      </c>
+      <c r="G45" t="s">
         <v>397</v>
       </c>
-      <c r="C45" t="s">
+      <c r="H45" t="s">
         <v>398</v>
-      </c>
-      <c r="D45" t="s">
-        <v>287</v>
-      </c>
-      <c r="E45" t="s">
-        <v>399</v>
-      </c>
-      <c r="F45" t="s">
-        <v>400</v>
-      </c>
-      <c r="G45" t="s">
-        <v>401</v>
-      </c>
-      <c r="H45" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
@@ -4183,25 +4180,25 @@
         <v>127</v>
       </c>
       <c r="B46" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C46" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="D46" t="s">
         <v>159</v>
       </c>
       <c r="E46" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="F46" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="G46" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="H46" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
@@ -4209,25 +4206,25 @@
         <v>142</v>
       </c>
       <c r="B47" t="s">
+        <v>405</v>
+      </c>
+      <c r="C47" t="s">
+        <v>406</v>
+      </c>
+      <c r="D47" t="s">
+        <v>407</v>
+      </c>
+      <c r="E47" t="s">
+        <v>408</v>
+      </c>
+      <c r="F47" t="s">
         <v>409</v>
       </c>
-      <c r="C47" t="s">
+      <c r="G47" t="s">
         <v>410</v>
       </c>
-      <c r="D47" t="s">
+      <c r="H47" t="s">
         <v>411</v>
-      </c>
-      <c r="E47" t="s">
-        <v>412</v>
-      </c>
-      <c r="F47" t="s">
-        <v>413</v>
-      </c>
-      <c r="G47" t="s">
-        <v>414</v>
-      </c>
-      <c r="H47" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
@@ -4235,25 +4232,25 @@
         <v>23</v>
       </c>
       <c r="B48" t="s">
+        <v>412</v>
+      </c>
+      <c r="C48" t="s">
+        <v>413</v>
+      </c>
+      <c r="D48" t="s">
+        <v>218</v>
+      </c>
+      <c r="E48" t="s">
+        <v>414</v>
+      </c>
+      <c r="F48" t="s">
+        <v>415</v>
+      </c>
+      <c r="G48" t="s">
         <v>416</v>
       </c>
-      <c r="C48" t="s">
+      <c r="H48" t="s">
         <v>417</v>
-      </c>
-      <c r="D48" t="s">
-        <v>219</v>
-      </c>
-      <c r="E48" t="s">
-        <v>418</v>
-      </c>
-      <c r="F48" t="s">
-        <v>419</v>
-      </c>
-      <c r="G48" t="s">
-        <v>420</v>
-      </c>
-      <c r="H48" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
@@ -4261,25 +4258,25 @@
         <v>104</v>
       </c>
       <c r="B49" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C49" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="D49" t="s">
         <v>159</v>
       </c>
       <c r="E49" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="F49" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="G49" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="H49" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
@@ -4287,7 +4284,7 @@
         <v>29</v>
       </c>
       <c r="B50" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C50" t="s">
         <v>177</v>
@@ -4296,16 +4293,16 @@
         <v>152</v>
       </c>
       <c r="E50" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="F50" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="G50" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="H50" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
@@ -4313,25 +4310,25 @@
         <v>74</v>
       </c>
       <c r="B51" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C51" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D51" t="s">
         <v>152</v>
       </c>
       <c r="E51" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="F51" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="G51" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="H51" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
@@ -4339,25 +4336,25 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
+        <v>434</v>
+      </c>
+      <c r="C52" t="s">
+        <v>378</v>
+      </c>
+      <c r="D52" t="s">
+        <v>218</v>
+      </c>
+      <c r="E52" t="s">
+        <v>435</v>
+      </c>
+      <c r="F52" t="s">
+        <v>436</v>
+      </c>
+      <c r="G52" t="s">
+        <v>437</v>
+      </c>
+      <c r="H52" t="s">
         <v>438</v>
-      </c>
-      <c r="C52" t="s">
-        <v>382</v>
-      </c>
-      <c r="D52" t="s">
-        <v>219</v>
-      </c>
-      <c r="E52" t="s">
-        <v>439</v>
-      </c>
-      <c r="F52" t="s">
-        <v>440</v>
-      </c>
-      <c r="G52" t="s">
-        <v>441</v>
-      </c>
-      <c r="H52" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
@@ -4365,25 +4362,25 @@
         <v>100</v>
       </c>
       <c r="B53" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C53" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D53" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E53" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="F53" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G53" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="H53" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
@@ -4391,25 +4388,25 @@
         <v>27</v>
       </c>
       <c r="B54" t="s">
+        <v>443</v>
+      </c>
+      <c r="C54" t="s">
+        <v>444</v>
+      </c>
+      <c r="D54" t="s">
+        <v>218</v>
+      </c>
+      <c r="E54" t="s">
+        <v>445</v>
+      </c>
+      <c r="F54" t="s">
+        <v>415</v>
+      </c>
+      <c r="G54" t="s">
+        <v>446</v>
+      </c>
+      <c r="H54" t="s">
         <v>447</v>
-      </c>
-      <c r="C54" t="s">
-        <v>448</v>
-      </c>
-      <c r="D54" t="s">
-        <v>219</v>
-      </c>
-      <c r="E54" t="s">
-        <v>449</v>
-      </c>
-      <c r="F54" t="s">
-        <v>419</v>
-      </c>
-      <c r="G54" t="s">
-        <v>450</v>
-      </c>
-      <c r="H54" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
@@ -4417,25 +4414,25 @@
         <v>40</v>
       </c>
       <c r="B55" t="s">
+        <v>448</v>
+      </c>
+      <c r="C55" t="s">
+        <v>449</v>
+      </c>
+      <c r="D55" t="s">
+        <v>225</v>
+      </c>
+      <c r="E55" t="s">
+        <v>450</v>
+      </c>
+      <c r="F55" t="s">
+        <v>451</v>
+      </c>
+      <c r="G55" t="s">
         <v>452</v>
       </c>
-      <c r="C55" t="s">
+      <c r="H55" t="s">
         <v>453</v>
-      </c>
-      <c r="D55" t="s">
-        <v>226</v>
-      </c>
-      <c r="E55" t="s">
-        <v>454</v>
-      </c>
-      <c r="F55" t="s">
-        <v>455</v>
-      </c>
-      <c r="G55" t="s">
-        <v>456</v>
-      </c>
-      <c r="H55" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
@@ -4443,25 +4440,25 @@
         <v>129</v>
       </c>
       <c r="B56" t="s">
+        <v>454</v>
+      </c>
+      <c r="C56" t="s">
+        <v>455</v>
+      </c>
+      <c r="D56" t="s">
+        <v>291</v>
+      </c>
+      <c r="E56" t="s">
+        <v>456</v>
+      </c>
+      <c r="F56" t="s">
+        <v>457</v>
+      </c>
+      <c r="G56" t="s">
         <v>458</v>
       </c>
-      <c r="C56" t="s">
+      <c r="H56" t="s">
         <v>459</v>
-      </c>
-      <c r="D56" t="s">
-        <v>294</v>
-      </c>
-      <c r="E56" t="s">
-        <v>460</v>
-      </c>
-      <c r="F56" t="s">
-        <v>461</v>
-      </c>
-      <c r="G56" t="s">
-        <v>462</v>
-      </c>
-      <c r="H56" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
@@ -4469,25 +4466,25 @@
         <v>130</v>
       </c>
       <c r="B57" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C57" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="D57" t="s">
         <v>159</v>
       </c>
       <c r="E57" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="F57" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="G57" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="H57" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -4495,7 +4492,7 @@
         <v>120</v>
       </c>
       <c r="B58" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C58" t="s">
         <v>158</v>
@@ -4504,16 +4501,16 @@
         <v>159</v>
       </c>
       <c r="E58" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="F58" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="G58" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="H58" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
@@ -4521,7 +4518,7 @@
         <v>14</v>
       </c>
       <c r="B59" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="C59" t="s">
         <v>171</v>
@@ -4530,16 +4527,16 @@
         <v>159</v>
       </c>
       <c r="E59" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="F59" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="G59" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="H59" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
@@ -4547,25 +4544,25 @@
         <v>92</v>
       </c>
       <c r="B60" t="s">
+        <v>476</v>
+      </c>
+      <c r="C60" t="s">
+        <v>477</v>
+      </c>
+      <c r="D60" t="s">
+        <v>324</v>
+      </c>
+      <c r="E60" t="s">
+        <v>478</v>
+      </c>
+      <c r="F60" t="s">
+        <v>479</v>
+      </c>
+      <c r="G60" t="s">
         <v>480</v>
       </c>
-      <c r="C60" t="s">
+      <c r="H60" t="s">
         <v>481</v>
-      </c>
-      <c r="D60" t="s">
-        <v>327</v>
-      </c>
-      <c r="E60" t="s">
-        <v>482</v>
-      </c>
-      <c r="F60" t="s">
-        <v>483</v>
-      </c>
-      <c r="G60" t="s">
-        <v>484</v>
-      </c>
-      <c r="H60" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
@@ -4573,25 +4570,25 @@
         <v>81</v>
       </c>
       <c r="B61" t="s">
+        <v>482</v>
+      </c>
+      <c r="C61" t="s">
+        <v>231</v>
+      </c>
+      <c r="D61" t="s">
+        <v>238</v>
+      </c>
+      <c r="E61" t="s">
+        <v>483</v>
+      </c>
+      <c r="F61" t="s">
+        <v>484</v>
+      </c>
+      <c r="G61" t="s">
+        <v>485</v>
+      </c>
+      <c r="H61" t="s">
         <v>486</v>
-      </c>
-      <c r="C61" t="s">
-        <v>232</v>
-      </c>
-      <c r="D61" t="s">
-        <v>239</v>
-      </c>
-      <c r="E61" t="s">
-        <v>487</v>
-      </c>
-      <c r="F61" t="s">
-        <v>488</v>
-      </c>
-      <c r="G61" t="s">
-        <v>489</v>
-      </c>
-      <c r="H61" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
@@ -4599,25 +4596,25 @@
         <v>30</v>
       </c>
       <c r="B62" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C62" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D62" t="s">
         <v>152</v>
       </c>
       <c r="E62" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="F62" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="G62" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="H62" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
@@ -4625,25 +4622,25 @@
         <v>138</v>
       </c>
       <c r="B63" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="C63" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="D63" t="s">
         <v>159</v>
       </c>
       <c r="E63" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="F63" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="G63" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="H63" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
@@ -4651,25 +4648,25 @@
         <v>35</v>
       </c>
       <c r="B64" t="s">
+        <v>498</v>
+      </c>
+      <c r="C64" t="s">
+        <v>499</v>
+      </c>
+      <c r="D64" t="s">
+        <v>218</v>
+      </c>
+      <c r="E64" t="s">
+        <v>500</v>
+      </c>
+      <c r="F64" t="s">
+        <v>501</v>
+      </c>
+      <c r="G64" t="s">
         <v>502</v>
       </c>
-      <c r="C64" t="s">
+      <c r="H64" t="s">
         <v>503</v>
-      </c>
-      <c r="D64" t="s">
-        <v>219</v>
-      </c>
-      <c r="E64" t="s">
-        <v>504</v>
-      </c>
-      <c r="F64" t="s">
-        <v>505</v>
-      </c>
-      <c r="G64" t="s">
-        <v>506</v>
-      </c>
-      <c r="H64" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
@@ -4677,25 +4674,25 @@
         <v>43</v>
       </c>
       <c r="B65" t="s">
+        <v>504</v>
+      </c>
+      <c r="C65" t="s">
+        <v>505</v>
+      </c>
+      <c r="D65" t="s">
+        <v>225</v>
+      </c>
+      <c r="E65" t="s">
+        <v>506</v>
+      </c>
+      <c r="F65" t="s">
+        <v>507</v>
+      </c>
+      <c r="G65" t="s">
         <v>508</v>
       </c>
-      <c r="C65" t="s">
+      <c r="H65" t="s">
         <v>509</v>
-      </c>
-      <c r="D65" t="s">
-        <v>226</v>
-      </c>
-      <c r="E65" t="s">
-        <v>510</v>
-      </c>
-      <c r="F65" t="s">
-        <v>511</v>
-      </c>
-      <c r="G65" t="s">
-        <v>512</v>
-      </c>
-      <c r="H65" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
@@ -4703,25 +4700,25 @@
         <v>44</v>
       </c>
       <c r="B66" t="s">
+        <v>510</v>
+      </c>
+      <c r="C66" t="s">
+        <v>449</v>
+      </c>
+      <c r="D66" t="s">
+        <v>225</v>
+      </c>
+      <c r="E66" t="s">
+        <v>511</v>
+      </c>
+      <c r="F66" t="s">
+        <v>512</v>
+      </c>
+      <c r="G66" t="s">
+        <v>513</v>
+      </c>
+      <c r="H66" t="s">
         <v>514</v>
-      </c>
-      <c r="C66" t="s">
-        <v>453</v>
-      </c>
-      <c r="D66" t="s">
-        <v>226</v>
-      </c>
-      <c r="E66" t="s">
-        <v>515</v>
-      </c>
-      <c r="F66" t="s">
-        <v>516</v>
-      </c>
-      <c r="G66" t="s">
-        <v>517</v>
-      </c>
-      <c r="H66" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
@@ -4729,25 +4726,25 @@
         <v>13</v>
       </c>
       <c r="B67" t="s">
+        <v>515</v>
+      </c>
+      <c r="C67" t="s">
+        <v>516</v>
+      </c>
+      <c r="D67" t="s">
+        <v>407</v>
+      </c>
+      <c r="E67" t="s">
+        <v>517</v>
+      </c>
+      <c r="F67" t="s">
+        <v>518</v>
+      </c>
+      <c r="G67" t="s">
         <v>519</v>
       </c>
-      <c r="C67" t="s">
+      <c r="H67" t="s">
         <v>520</v>
-      </c>
-      <c r="D67" t="s">
-        <v>411</v>
-      </c>
-      <c r="E67" t="s">
-        <v>521</v>
-      </c>
-      <c r="F67" t="s">
-        <v>522</v>
-      </c>
-      <c r="G67" t="s">
-        <v>523</v>
-      </c>
-      <c r="H67" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
@@ -4755,25 +4752,25 @@
         <v>48</v>
       </c>
       <c r="B68" t="s">
+        <v>521</v>
+      </c>
+      <c r="C68" t="s">
+        <v>522</v>
+      </c>
+      <c r="D68" t="s">
+        <v>291</v>
+      </c>
+      <c r="E68" t="s">
+        <v>523</v>
+      </c>
+      <c r="F68" t="s">
+        <v>524</v>
+      </c>
+      <c r="G68" t="s">
         <v>525</v>
       </c>
-      <c r="C68" t="s">
+      <c r="H68" t="s">
         <v>526</v>
-      </c>
-      <c r="D68" t="s">
-        <v>294</v>
-      </c>
-      <c r="E68" t="s">
-        <v>527</v>
-      </c>
-      <c r="F68" t="s">
-        <v>528</v>
-      </c>
-      <c r="G68" t="s">
-        <v>529</v>
-      </c>
-      <c r="H68" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
@@ -4781,25 +4778,25 @@
         <v>86</v>
       </c>
       <c r="B69" t="s">
+        <v>527</v>
+      </c>
+      <c r="C69" t="s">
+        <v>528</v>
+      </c>
+      <c r="D69" t="s">
+        <v>407</v>
+      </c>
+      <c r="E69" t="s">
+        <v>529</v>
+      </c>
+      <c r="F69" t="s">
+        <v>530</v>
+      </c>
+      <c r="G69" t="s">
         <v>531</v>
       </c>
-      <c r="C69" t="s">
+      <c r="H69" t="s">
         <v>532</v>
-      </c>
-      <c r="D69" t="s">
-        <v>411</v>
-      </c>
-      <c r="E69" t="s">
-        <v>533</v>
-      </c>
-      <c r="F69" t="s">
-        <v>534</v>
-      </c>
-      <c r="G69" t="s">
-        <v>535</v>
-      </c>
-      <c r="H69" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
@@ -4807,25 +4804,25 @@
         <v>78</v>
       </c>
       <c r="B70" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="C70" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D70" t="s">
         <v>152</v>
       </c>
       <c r="E70" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="F70" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="G70" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="H70" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
@@ -4833,25 +4830,25 @@
         <v>140</v>
       </c>
       <c r="B71" t="s">
+        <v>538</v>
+      </c>
+      <c r="C71" t="s">
+        <v>237</v>
+      </c>
+      <c r="D71" t="s">
+        <v>225</v>
+      </c>
+      <c r="E71" t="s">
+        <v>539</v>
+      </c>
+      <c r="F71" t="s">
+        <v>540</v>
+      </c>
+      <c r="G71" t="s">
+        <v>541</v>
+      </c>
+      <c r="H71" t="s">
         <v>542</v>
-      </c>
-      <c r="C71" t="s">
-        <v>238</v>
-      </c>
-      <c r="D71" t="s">
-        <v>226</v>
-      </c>
-      <c r="E71" t="s">
-        <v>543</v>
-      </c>
-      <c r="F71" t="s">
-        <v>544</v>
-      </c>
-      <c r="G71" t="s">
-        <v>545</v>
-      </c>
-      <c r="H71" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
@@ -4859,25 +4856,25 @@
         <v>45</v>
       </c>
       <c r="B72" t="s">
+        <v>543</v>
+      </c>
+      <c r="C72" t="s">
+        <v>544</v>
+      </c>
+      <c r="D72" t="s">
+        <v>218</v>
+      </c>
+      <c r="E72" t="s">
+        <v>545</v>
+      </c>
+      <c r="F72" t="s">
+        <v>546</v>
+      </c>
+      <c r="G72" t="s">
         <v>547</v>
       </c>
-      <c r="C72" t="s">
+      <c r="H72" t="s">
         <v>548</v>
-      </c>
-      <c r="D72" t="s">
-        <v>219</v>
-      </c>
-      <c r="E72" t="s">
-        <v>549</v>
-      </c>
-      <c r="F72" t="s">
-        <v>550</v>
-      </c>
-      <c r="G72" t="s">
-        <v>551</v>
-      </c>
-      <c r="H72" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
@@ -4885,25 +4882,25 @@
         <v>51</v>
       </c>
       <c r="B73" t="s">
+        <v>549</v>
+      </c>
+      <c r="C73" t="s">
+        <v>550</v>
+      </c>
+      <c r="D73" t="s">
+        <v>211</v>
+      </c>
+      <c r="E73" t="s">
+        <v>551</v>
+      </c>
+      <c r="F73" t="s">
+        <v>552</v>
+      </c>
+      <c r="G73" t="s">
         <v>553</v>
       </c>
-      <c r="C73" t="s">
+      <c r="H73" t="s">
         <v>554</v>
-      </c>
-      <c r="D73" t="s">
-        <v>212</v>
-      </c>
-      <c r="E73" t="s">
-        <v>555</v>
-      </c>
-      <c r="F73" t="s">
-        <v>556</v>
-      </c>
-      <c r="G73" t="s">
-        <v>557</v>
-      </c>
-      <c r="H73" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
@@ -4911,25 +4908,25 @@
         <v>135</v>
       </c>
       <c r="B74" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="C74" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="D74" t="s">
         <v>159</v>
       </c>
       <c r="E74" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="F74" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="G74" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="H74" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
@@ -4937,25 +4934,25 @@
         <v>56</v>
       </c>
       <c r="B75" t="s">
+        <v>560</v>
+      </c>
+      <c r="C75" t="s">
+        <v>698</v>
+      </c>
+      <c r="D75" t="s">
+        <v>407</v>
+      </c>
+      <c r="E75" t="s">
+        <v>561</v>
+      </c>
+      <c r="F75" t="s">
+        <v>562</v>
+      </c>
+      <c r="G75" t="s">
+        <v>563</v>
+      </c>
+      <c r="H75" t="s">
         <v>564</v>
-      </c>
-      <c r="C75" t="s">
-        <v>703</v>
-      </c>
-      <c r="D75" t="s">
-        <v>411</v>
-      </c>
-      <c r="E75" t="s">
-        <v>565</v>
-      </c>
-      <c r="F75" t="s">
-        <v>566</v>
-      </c>
-      <c r="G75" t="s">
-        <v>567</v>
-      </c>
-      <c r="H75" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
@@ -4963,25 +4960,25 @@
         <v>61</v>
       </c>
       <c r="B76" t="s">
+        <v>565</v>
+      </c>
+      <c r="C76" t="s">
+        <v>566</v>
+      </c>
+      <c r="D76" t="s">
+        <v>218</v>
+      </c>
+      <c r="E76" t="s">
+        <v>567</v>
+      </c>
+      <c r="F76" t="s">
+        <v>568</v>
+      </c>
+      <c r="G76" t="s">
         <v>569</v>
       </c>
-      <c r="C76" t="s">
+      <c r="H76" t="s">
         <v>570</v>
-      </c>
-      <c r="D76" t="s">
-        <v>219</v>
-      </c>
-      <c r="E76" t="s">
-        <v>571</v>
-      </c>
-      <c r="F76" t="s">
-        <v>572</v>
-      </c>
-      <c r="G76" t="s">
-        <v>573</v>
-      </c>
-      <c r="H76" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
@@ -4989,25 +4986,25 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="C77" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D77" t="s">
         <v>152</v>
       </c>
       <c r="E77" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="F77" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="G77" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="H77" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
@@ -5015,25 +5012,25 @@
         <v>143</v>
       </c>
       <c r="B78" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C78" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="D78" t="s">
         <v>159</v>
       </c>
       <c r="E78" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="F78" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="G78" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="H78" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
@@ -5041,25 +5038,25 @@
         <v>59</v>
       </c>
       <c r="B79" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C79" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D79" t="s">
         <v>159</v>
       </c>
       <c r="E79" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="F79" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="G79" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="H79" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
@@ -5067,25 +5064,25 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C80" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="D80" t="s">
         <v>159</v>
       </c>
       <c r="E80" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="F80" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="G80" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="H80" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
@@ -5093,25 +5090,25 @@
         <v>141</v>
       </c>
       <c r="B81" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="C81" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="D81" t="s">
         <v>159</v>
       </c>
       <c r="E81" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="F81" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="G81" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="H81" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
@@ -5119,25 +5116,25 @@
         <v>144</v>
       </c>
       <c r="B82" t="s">
+        <v>597</v>
+      </c>
+      <c r="C82" t="s">
+        <v>406</v>
+      </c>
+      <c r="D82" t="s">
+        <v>407</v>
+      </c>
+      <c r="E82" t="s">
+        <v>598</v>
+      </c>
+      <c r="F82" t="s">
+        <v>599</v>
+      </c>
+      <c r="G82" t="s">
+        <v>600</v>
+      </c>
+      <c r="H82" t="s">
         <v>601</v>
-      </c>
-      <c r="C82" t="s">
-        <v>410</v>
-      </c>
-      <c r="D82" t="s">
-        <v>411</v>
-      </c>
-      <c r="E82" t="s">
-        <v>602</v>
-      </c>
-      <c r="F82" t="s">
-        <v>603</v>
-      </c>
-      <c r="G82" t="s">
-        <v>604</v>
-      </c>
-      <c r="H82" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
@@ -5145,25 +5142,25 @@
         <v>60</v>
       </c>
       <c r="B83" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="C83" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="D83" t="s">
         <v>159</v>
       </c>
       <c r="E83" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="F83" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="G83" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="H83" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
@@ -5171,25 +5168,25 @@
         <v>66</v>
       </c>
       <c r="B84" t="s">
+        <v>608</v>
+      </c>
+      <c r="C84" t="s">
+        <v>609</v>
+      </c>
+      <c r="D84" t="s">
+        <v>407</v>
+      </c>
+      <c r="E84" t="s">
+        <v>610</v>
+      </c>
+      <c r="F84" t="s">
+        <v>611</v>
+      </c>
+      <c r="G84" t="s">
         <v>612</v>
       </c>
-      <c r="C84" t="s">
+      <c r="H84" t="s">
         <v>613</v>
-      </c>
-      <c r="D84" t="s">
-        <v>411</v>
-      </c>
-      <c r="E84" t="s">
-        <v>614</v>
-      </c>
-      <c r="F84" t="s">
-        <v>615</v>
-      </c>
-      <c r="G84" t="s">
-        <v>616</v>
-      </c>
-      <c r="H84" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
@@ -5197,25 +5194,25 @@
         <v>34</v>
       </c>
       <c r="B85" t="s">
+        <v>614</v>
+      </c>
+      <c r="C85" t="s">
+        <v>615</v>
+      </c>
+      <c r="D85" t="s">
+        <v>284</v>
+      </c>
+      <c r="E85" t="s">
+        <v>616</v>
+      </c>
+      <c r="F85" t="s">
+        <v>617</v>
+      </c>
+      <c r="G85" t="s">
         <v>618</v>
       </c>
-      <c r="C85" t="s">
+      <c r="H85" t="s">
         <v>619</v>
-      </c>
-      <c r="D85" t="s">
-        <v>287</v>
-      </c>
-      <c r="E85" t="s">
-        <v>620</v>
-      </c>
-      <c r="F85" t="s">
-        <v>621</v>
-      </c>
-      <c r="G85" t="s">
-        <v>622</v>
-      </c>
-      <c r="H85" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
@@ -5223,25 +5220,25 @@
         <v>41</v>
       </c>
       <c r="B86" t="s">
+        <v>620</v>
+      </c>
+      <c r="C86" t="s">
+        <v>499</v>
+      </c>
+      <c r="D86" t="s">
+        <v>218</v>
+      </c>
+      <c r="E86" t="s">
+        <v>621</v>
+      </c>
+      <c r="F86" t="s">
+        <v>622</v>
+      </c>
+      <c r="G86" t="s">
+        <v>623</v>
+      </c>
+      <c r="H86" t="s">
         <v>624</v>
-      </c>
-      <c r="C86" t="s">
-        <v>503</v>
-      </c>
-      <c r="D86" t="s">
-        <v>219</v>
-      </c>
-      <c r="E86" t="s">
-        <v>625</v>
-      </c>
-      <c r="F86" t="s">
-        <v>626</v>
-      </c>
-      <c r="G86" t="s">
-        <v>627</v>
-      </c>
-      <c r="H86" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
@@ -5249,25 +5246,25 @@
         <v>79</v>
       </c>
       <c r="B87" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="C87" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D87" t="s">
         <v>159</v>
       </c>
       <c r="E87" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="F87" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="G87" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="H87" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
@@ -5275,25 +5272,25 @@
         <v>91</v>
       </c>
       <c r="B88" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="C88" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D88" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E88" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="F88" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="G88" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="H88" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
@@ -5301,25 +5298,25 @@
         <v>118</v>
       </c>
       <c r="B89" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="C89" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="D89" t="s">
         <v>152</v>
       </c>
       <c r="E89" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="F89" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="G89" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="H89" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
@@ -5327,25 +5324,25 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="C90" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="D90" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E90" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="F90" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G90" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="H90" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
@@ -5353,25 +5350,25 @@
         <v>121</v>
       </c>
       <c r="B91" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="C91" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="D91" t="s">
         <v>152</v>
       </c>
       <c r="E91" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="F91" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="G91" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H91" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
@@ -5379,25 +5376,25 @@
         <v>67</v>
       </c>
       <c r="B92" t="s">
-        <v>653</v>
+        <v>701</v>
       </c>
       <c r="C92" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="D92" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E92" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="F92" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="G92" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="H92" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
@@ -5405,25 +5402,25 @@
         <v>49</v>
       </c>
       <c r="B93" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="C93" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="D93" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E93" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="F93" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="G93" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="H93" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
@@ -5431,25 +5428,25 @@
         <v>31</v>
       </c>
       <c r="B94" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="C94" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="D94" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E94" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="F94" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="G94" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="H94" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
@@ -5457,25 +5454,25 @@
         <v>109</v>
       </c>
       <c r="B95" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="C95" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D95" t="s">
         <v>159</v>
       </c>
       <c r="E95" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="F95" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="G95" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="H95" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
@@ -5483,25 +5480,25 @@
         <v>71</v>
       </c>
       <c r="B96" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="C96" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="D96" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E96" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="F96" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="G96" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="H96" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
@@ -5509,25 +5506,25 @@
         <v>128</v>
       </c>
       <c r="B97" t="s">
+        <v>669</v>
+      </c>
+      <c r="C97" t="s">
+        <v>670</v>
+      </c>
+      <c r="D97" t="s">
+        <v>225</v>
+      </c>
+      <c r="E97" t="s">
+        <v>671</v>
+      </c>
+      <c r="F97" t="s">
+        <v>672</v>
+      </c>
+      <c r="G97" t="s">
+        <v>673</v>
+      </c>
+      <c r="H97" t="s">
         <v>674</v>
-      </c>
-      <c r="C97" t="s">
-        <v>675</v>
-      </c>
-      <c r="D97" t="s">
-        <v>226</v>
-      </c>
-      <c r="E97" t="s">
-        <v>676</v>
-      </c>
-      <c r="F97" t="s">
-        <v>677</v>
-      </c>
-      <c r="G97" t="s">
-        <v>678</v>
-      </c>
-      <c r="H97" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
@@ -5535,25 +5532,25 @@
         <v>95</v>
       </c>
       <c r="B98" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="C98" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D98" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E98" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="F98" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="G98" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="H98" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
@@ -5561,25 +5558,25 @@
         <v>133</v>
       </c>
       <c r="B99" t="s">
+        <v>680</v>
+      </c>
+      <c r="C99" t="s">
+        <v>681</v>
+      </c>
+      <c r="D99" t="s">
+        <v>407</v>
+      </c>
+      <c r="E99" t="s">
+        <v>682</v>
+      </c>
+      <c r="F99" t="s">
+        <v>683</v>
+      </c>
+      <c r="G99" t="s">
+        <v>684</v>
+      </c>
+      <c r="H99" t="s">
         <v>685</v>
-      </c>
-      <c r="C99" t="s">
-        <v>686</v>
-      </c>
-      <c r="D99" t="s">
-        <v>411</v>
-      </c>
-      <c r="E99" t="s">
-        <v>687</v>
-      </c>
-      <c r="F99" t="s">
-        <v>688</v>
-      </c>
-      <c r="G99" t="s">
-        <v>689</v>
-      </c>
-      <c r="H99" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
@@ -5587,25 +5584,25 @@
         <v>17</v>
       </c>
       <c r="B100" t="s">
+        <v>686</v>
+      </c>
+      <c r="C100" t="s">
+        <v>687</v>
+      </c>
+      <c r="D100" t="s">
+        <v>238</v>
+      </c>
+      <c r="E100" t="s">
+        <v>688</v>
+      </c>
+      <c r="F100" t="s">
+        <v>689</v>
+      </c>
+      <c r="G100" t="s">
+        <v>690</v>
+      </c>
+      <c r="H100" t="s">
         <v>691</v>
-      </c>
-      <c r="C100" t="s">
-        <v>692</v>
-      </c>
-      <c r="D100" t="s">
-        <v>239</v>
-      </c>
-      <c r="E100" t="s">
-        <v>693</v>
-      </c>
-      <c r="F100" t="s">
-        <v>694</v>
-      </c>
-      <c r="G100" t="s">
-        <v>695</v>
-      </c>
-      <c r="H100" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
@@ -5613,30 +5610,31 @@
         <v>113</v>
       </c>
       <c r="B101" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="C101" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D101" t="s">
         <v>152</v>
       </c>
       <c r="E101" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="F101" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="G101" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="H101" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H101" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -5659,95 +5657,95 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
     </row>
     <row r="5" spans="1:13" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="9" t="s">
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="9" t="s">
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
@@ -5950,7 +5948,7 @@
       </c>
       <c r="D12" s="6" t="str">
         <f>IFERROR(VLOOKUP($B12,Data!$A:$D,2,FALSE),"")</f>
-        <v>Teaching a Medical Vision-Language Model with Automatic Feedback</v>
+        <v>Two-Stage Outcome-Based Reinforcement Learning for a Compact Medical Vision-Language Model</v>
       </c>
       <c r="E12" s="6" t="str">
         <f>IFERROR(VLOOKUP($B12,Data!$A:$D,3,FALSE),"")</f>
@@ -5971,7 +5969,7 @@
         <f>IFERROR(VLOOKUP($F12,Data!$A:$D,3,FALSE),"")</f>
         <v>Timothy Gomez</v>
       </c>
-      <c r="J12" s="14" t="s">
+      <c r="J12" s="7" t="s">
         <v>35</v>
       </c>
       <c r="K12" s="6" t="str">
@@ -6088,61 +6086,61 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="9" t="s">
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="9" t="s">
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B18" s="3" t="s">
@@ -6332,7 +6330,7 @@
         <v>Ayan Nath</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="39" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>50</v>
       </c>
@@ -6483,61 +6481,61 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="9" t="s">
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="9" t="s">
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B28" s="3" t="s">
@@ -6620,7 +6618,7 @@
       </c>
       <c r="L29" s="6" t="str">
         <f>IFERROR(VLOOKUP($J29,Data!$A:$D,2,FALSE),"")</f>
-        <v>Enumerating Index-Two and Index-Three Nilpotent Matrices in Symplectic Lie Algebras</v>
+        <v>Enumerating Nilpotent Matrices over Finite Fields</v>
       </c>
       <c r="M29" s="6" t="str">
         <f>IFERROR(VLOOKUP($J29,Data!$A:$D,3,FALSE),"")</f>
@@ -6820,7 +6818,7 @@
       </c>
       <c r="L33" s="6" t="str">
         <f>IFERROR(VLOOKUP($J33,Data!$A:$D,2,FALSE),"")</f>
-        <v>Schrodinger Bridges for Graph Interpolations</v>
+        <v>Sinkhorn Schrödinger Bridges for Graph Interpolations</v>
       </c>
       <c r="M33" s="6" t="str">
         <f>IFERROR(VLOOKUP($J33,Data!$A:$D,3,FALSE),"")</f>
@@ -6878,61 +6876,61 @@
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
-      <c r="J35" s="8"/>
-      <c r="K35" s="8"/>
-      <c r="L35" s="8"/>
-      <c r="M35" s="8"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="9"/>
+      <c r="M35" s="9"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8"/>
-      <c r="M36" s="8"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="9"/>
+      <c r="M36" s="9"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9" t="s">
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="8"/>
-      <c r="J37" s="9" t="s">
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="K37" s="8"/>
-      <c r="L37" s="8"/>
-      <c r="M37" s="8"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B38" s="3" t="s">
@@ -7015,7 +7013,7 @@
       </c>
       <c r="L39" s="6" t="str">
         <f>IFERROR(VLOOKUP($J39,Data!$A:$D,2,FALSE),"")</f>
-        <v>Investigating cognitive decline in HIV</v>
+        <v>Using Cell-Projected Phenotypes to study HIV induced cognitive decline</v>
       </c>
       <c r="M39" s="6" t="str">
         <f>IFERROR(VLOOKUP($J39,Data!$A:$D,3,FALSE),"")</f>
@@ -7122,7 +7120,7 @@
         <v>Prof. Manolis Kellis</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="39" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>102</v>
       </c>
@@ -7222,7 +7220,7 @@
         <v>Prof. Manolis Kellis</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="26" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13" ht="39" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>110</v>
       </c>
@@ -7273,61 +7271,61 @@
       </c>
     </row>
     <row r="47" spans="1:13" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="13" t="s">
+      <c r="A47" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
-      <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="8"/>
-      <c r="M47" s="8"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="9"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="9"/>
+      <c r="K47" s="9"/>
+      <c r="L47" s="9"/>
+      <c r="M47" s="9"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A48" s="10" t="s">
+      <c r="A48" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8"/>
-      <c r="H48" s="8"/>
-      <c r="I48" s="8"/>
-      <c r="J48" s="8"/>
-      <c r="K48" s="8"/>
-      <c r="L48" s="8"/>
-      <c r="M48" s="8"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="9"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="9"/>
+      <c r="M48" s="9"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="9" t="s">
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G49" s="8"/>
-      <c r="H49" s="8"/>
-      <c r="I49" s="8"/>
-      <c r="J49" s="9" t="s">
+      <c r="G49" s="9"/>
+      <c r="H49" s="9"/>
+      <c r="I49" s="9"/>
+      <c r="J49" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="K49" s="8"/>
-      <c r="L49" s="8"/>
-      <c r="M49" s="8"/>
+      <c r="K49" s="9"/>
+      <c r="L49" s="9"/>
+      <c r="M49" s="9"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B50" s="3" t="s">
@@ -7534,7 +7532,7 @@
       </c>
       <c r="E54" s="6" t="str">
         <f>IFERROR(VLOOKUP($B54,Data!$A:$D,3,FALSE),"")</f>
-        <v>Prof. Jenny Hoffman, Sarah Ziegler</v>
+        <v>Prof. Jenny Hoffman</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>126</v>
@@ -7668,61 +7666,61 @@
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A57" s="11" t="s">
+      <c r="A57" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B57" s="8"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8"/>
-      <c r="G57" s="8"/>
-      <c r="H57" s="8"/>
-      <c r="I57" s="8"/>
-      <c r="J57" s="8"/>
-      <c r="K57" s="8"/>
-      <c r="L57" s="8"/>
-      <c r="M57" s="8"/>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
+      <c r="I57" s="9"/>
+      <c r="J57" s="9"/>
+      <c r="K57" s="9"/>
+      <c r="L57" s="9"/>
+      <c r="M57" s="9"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A58" s="10" t="s">
+      <c r="A58" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="8"/>
-      <c r="I58" s="8"/>
-      <c r="J58" s="8"/>
-      <c r="K58" s="8"/>
-      <c r="L58" s="8"/>
-      <c r="M58" s="8"/>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9"/>
+      <c r="K58" s="9"/>
+      <c r="L58" s="9"/>
+      <c r="M58" s="9"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="9" t="s">
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G59" s="8"/>
-      <c r="H59" s="8"/>
-      <c r="I59" s="8"/>
-      <c r="J59" s="9" t="s">
+      <c r="G59" s="9"/>
+      <c r="H59" s="9"/>
+      <c r="I59" s="9"/>
+      <c r="J59" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="K59" s="8"/>
-      <c r="L59" s="8"/>
-      <c r="M59" s="8"/>
+      <c r="K59" s="9"/>
+      <c r="L59" s="9"/>
+      <c r="M59" s="9"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B60" s="3" t="s">
@@ -7994,102 +7992,102 @@
     <mergeCell ref="A47:M47"/>
   </mergeCells>
   <conditionalFormatting sqref="C4:C71">
-    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="13" operator="equal">
+      <formula>"Engineering"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="31" operator="equal">
+      <formula>"Other"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="28" operator="equal">
+      <formula>"Economics &amp; Policy"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="29" priority="4" operator="equal">
+      <formula>"Physics"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="25" operator="equal">
+      <formula>"Earth, Ocean &amp; Climate"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="27" priority="22" operator="equal">
+      <formula>"Neuroscience &amp; Psychology"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="26" priority="7" operator="equal">
+      <formula>"Astronomy &amp; Planetary Science"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="19" operator="equal">
+      <formula>"Biology &amp; Medicine"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
       <formula>"Math"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="4" operator="equal">
-      <formula>"Physics"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="7" operator="equal">
-      <formula>"Astronomy &amp; Planetary Science"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="10" operator="equal">
       <formula>"Computer Science &amp; AI"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="13" operator="equal">
-      <formula>"Engineering"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="16" operator="equal">
       <formula>"Chemistry &amp; Materials"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="19" operator="equal">
-      <formula>"Biology &amp; Medicine"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="22" operator="equal">
-      <formula>"Neuroscience &amp; Psychology"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="25" operator="equal">
-      <formula>"Earth, Ocean &amp; Climate"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="28" operator="equal">
-      <formula>"Economics &amp; Policy"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="31" operator="equal">
-      <formula>"Other"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G71">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
-      <formula>"Math"</formula>
+    <cfRule type="cellIs" dxfId="21" priority="17" operator="equal">
+      <formula>"Chemistry &amp; Materials"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="14" operator="equal">
+      <formula>"Engineering"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="11" operator="equal">
+      <formula>"Computer Science &amp; AI"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="8" operator="equal">
+      <formula>"Astronomy &amp; Planetary Science"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="20" operator="equal">
+      <formula>"Biology &amp; Medicine"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="23" operator="equal">
+      <formula>"Neuroscience &amp; Psychology"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
       <formula>"Physics"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="8" operator="equal">
-      <formula>"Astronomy &amp; Planetary Science"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="11" operator="equal">
-      <formula>"Computer Science &amp; AI"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="14" operator="equal">
-      <formula>"Engineering"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
-      <formula>"Chemistry &amp; Materials"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="20" operator="equal">
-      <formula>"Biology &amp; Medicine"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="23" operator="equal">
-      <formula>"Neuroscience &amp; Psychology"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="26" operator="equal">
       <formula>"Earth, Ocean &amp; Climate"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="29" operator="equal">
       <formula>"Economics &amp; Policy"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+      <formula>"Math"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="11" priority="32" operator="equal">
       <formula>"Other"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4:K71">
-    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
-      <formula>"Math"</formula>
+    <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
+      <formula>"Computer Science &amp; AI"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
-      <formula>"Physics"</formula>
+    <cfRule type="cellIs" dxfId="9" priority="15" operator="equal">
+      <formula>"Engineering"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
       <formula>"Astronomy &amp; Planetary Science"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="12" operator="equal">
-      <formula>"Computer Science &amp; AI"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="15" operator="equal">
-      <formula>"Engineering"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="18" operator="equal">
       <formula>"Chemistry &amp; Materials"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="21" operator="equal">
       <formula>"Biology &amp; Medicine"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"Physics"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="24" operator="equal">
       <formula>"Neuroscience &amp; Psychology"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="27" operator="equal">
       <formula>"Earth, Ocean &amp; Climate"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"Math"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="1" priority="30" operator="equal">
       <formula>"Economics &amp; Policy"</formula>

--- a/RSI_2026_Schedule.xlsx
+++ b/RSI_2026_Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/evanlim/Documents/rsi-symposium/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7629648-54C8-5E46-A4CF-216DE6E77D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF002864-FB68-9B4F-A397-79EACC97E35D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -813,9 +813,6 @@
     <t>bensonh</t>
   </si>
   <si>
-    <t>Parametric study of regime transitions in quasi-turbulence</t>
-  </si>
-  <si>
     <t>BRY-un</t>
   </si>
   <si>
@@ -2152,6 +2149,9 @@
   </si>
   <si>
     <t>Two-Stage Outcome-Based Reinforcement Learning for a Compact Medical Vision-Language Model</t>
+  </si>
+  <si>
+    <t>Parametric Study of Regime Transition in Quasi-Geostrophic Turbulence</t>
   </si>
 </sst>
 </file>
@@ -3166,7 +3166,7 @@
         <v>93</v>
       </c>
       <c r="B7" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C7" t="s">
         <v>182</v>
@@ -3455,7 +3455,7 @@
         <v>247</v>
       </c>
       <c r="C18" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D18" t="s">
         <v>225</v>
@@ -3504,7 +3504,7 @@
         <v>73</v>
       </c>
       <c r="B20" t="s">
-        <v>258</v>
+        <v>704</v>
       </c>
       <c r="C20" t="s">
         <v>231</v>
@@ -3513,16 +3513,16 @@
         <v>238</v>
       </c>
       <c r="E20" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F20" t="s">
         <v>190</v>
       </c>
       <c r="G20" t="s">
+        <v>259</v>
+      </c>
+      <c r="H20" t="s">
         <v>260</v>
-      </c>
-      <c r="H20" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -3530,25 +3530,25 @@
         <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D21" t="s">
         <v>152</v>
       </c>
       <c r="E21" t="s">
+        <v>262</v>
+      </c>
+      <c r="F21" t="s">
         <v>263</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>264</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>265</v>
-      </c>
-      <c r="H21" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -3556,25 +3556,25 @@
         <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C22" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D22" t="s">
         <v>159</v>
       </c>
       <c r="E22" t="s">
+        <v>267</v>
+      </c>
+      <c r="F22" t="s">
         <v>268</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>269</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>270</v>
-      </c>
-      <c r="H22" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -3582,7 +3582,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C23" t="s">
         <v>182</v>
@@ -3591,16 +3591,16 @@
         <v>159</v>
       </c>
       <c r="E23" t="s">
+        <v>272</v>
+      </c>
+      <c r="F23" t="s">
         <v>273</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>274</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>275</v>
-      </c>
-      <c r="H23" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
@@ -3608,7 +3608,7 @@
         <v>77</v>
       </c>
       <c r="B24" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C24" t="s">
         <v>231</v>
@@ -3617,16 +3617,16 @@
         <v>238</v>
       </c>
       <c r="E24" t="s">
+        <v>277</v>
+      </c>
+      <c r="F24" t="s">
         <v>278</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>279</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>280</v>
-      </c>
-      <c r="H24" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -3634,25 +3634,25 @@
         <v>96</v>
       </c>
       <c r="B25" t="s">
+        <v>281</v>
+      </c>
+      <c r="C25" t="s">
         <v>282</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>283</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>284</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>285</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>286</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>287</v>
-      </c>
-      <c r="H25" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
@@ -3660,25 +3660,25 @@
         <v>87</v>
       </c>
       <c r="B26" t="s">
+        <v>288</v>
+      </c>
+      <c r="C26" t="s">
         <v>289</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>290</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>291</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>292</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>293</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>294</v>
-      </c>
-      <c r="H26" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -3686,25 +3686,25 @@
         <v>70</v>
       </c>
       <c r="B27" t="s">
+        <v>295</v>
+      </c>
+      <c r="C27" t="s">
         <v>296</v>
-      </c>
-      <c r="C27" t="s">
-        <v>297</v>
       </c>
       <c r="D27" t="s">
         <v>152</v>
       </c>
       <c r="E27" t="s">
+        <v>297</v>
+      </c>
+      <c r="F27" t="s">
         <v>298</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>299</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
         <v>300</v>
-      </c>
-      <c r="H27" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -3712,25 +3712,25 @@
         <v>119</v>
       </c>
       <c r="B28" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C28" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D28" t="s">
         <v>211</v>
       </c>
       <c r="E28" t="s">
+        <v>303</v>
+      </c>
+      <c r="F28" t="s">
         <v>304</v>
       </c>
-      <c r="F28" t="s">
-        <v>305</v>
-      </c>
       <c r="G28" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H28" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -3738,25 +3738,25 @@
         <v>122</v>
       </c>
       <c r="B29" t="s">
+        <v>301</v>
+      </c>
+      <c r="C29" t="s">
         <v>302</v>
-      </c>
-      <c r="C29" t="s">
-        <v>303</v>
       </c>
       <c r="D29" t="s">
         <v>211</v>
       </c>
       <c r="E29" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F29" t="s">
         <v>227</v>
       </c>
       <c r="G29" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="H29" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -3764,7 +3764,7 @@
         <v>139</v>
       </c>
       <c r="B30" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C30" t="s">
         <v>210</v>
@@ -3773,16 +3773,16 @@
         <v>211</v>
       </c>
       <c r="E30" t="s">
+        <v>311</v>
+      </c>
+      <c r="F30" t="s">
         <v>312</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>313</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>314</v>
-      </c>
-      <c r="H30" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -3790,25 +3790,25 @@
         <v>99</v>
       </c>
       <c r="B31" t="s">
+        <v>315</v>
+      </c>
+      <c r="C31" t="s">
         <v>316</v>
-      </c>
-      <c r="C31" t="s">
-        <v>317</v>
       </c>
       <c r="D31" t="s">
         <v>225</v>
       </c>
       <c r="E31" t="s">
+        <v>317</v>
+      </c>
+      <c r="F31" t="s">
         <v>318</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>319</v>
       </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
         <v>320</v>
-      </c>
-      <c r="H31" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -3816,25 +3816,25 @@
         <v>116</v>
       </c>
       <c r="B32" t="s">
+        <v>321</v>
+      </c>
+      <c r="C32" t="s">
         <v>322</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>323</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>324</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>325</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>326</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>327</v>
-      </c>
-      <c r="H32" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -3842,25 +3842,25 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
+        <v>328</v>
+      </c>
+      <c r="C33" t="s">
         <v>329</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
+        <v>283</v>
+      </c>
+      <c r="E33" t="s">
         <v>330</v>
       </c>
-      <c r="D33" t="s">
-        <v>284</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>331</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>332</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
         <v>333</v>
-      </c>
-      <c r="H33" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
@@ -3868,7 +3868,7 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C34" t="s">
         <v>177</v>
@@ -3877,16 +3877,16 @@
         <v>152</v>
       </c>
       <c r="E34" t="s">
+        <v>334</v>
+      </c>
+      <c r="F34" t="s">
         <v>335</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>336</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>337</v>
-      </c>
-      <c r="H34" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -3894,7 +3894,7 @@
         <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C35" t="s">
         <v>171</v>
@@ -3903,16 +3903,16 @@
         <v>152</v>
       </c>
       <c r="E35" t="s">
+        <v>339</v>
+      </c>
+      <c r="F35" t="s">
         <v>340</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>341</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
         <v>342</v>
-      </c>
-      <c r="H35" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -3920,25 +3920,25 @@
         <v>75</v>
       </c>
       <c r="B36" t="s">
+        <v>343</v>
+      </c>
+      <c r="C36" t="s">
         <v>344</v>
-      </c>
-      <c r="C36" t="s">
-        <v>345</v>
       </c>
       <c r="D36" t="s">
         <v>159</v>
       </c>
       <c r="E36" t="s">
+        <v>345</v>
+      </c>
+      <c r="F36" t="s">
         <v>346</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>347</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>348</v>
-      </c>
-      <c r="H36" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -3946,7 +3946,7 @@
         <v>19</v>
       </c>
       <c r="B37" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C37" t="s">
         <v>217</v>
@@ -3955,16 +3955,16 @@
         <v>218</v>
       </c>
       <c r="E37" t="s">
+        <v>350</v>
+      </c>
+      <c r="F37" t="s">
         <v>351</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>352</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>353</v>
-      </c>
-      <c r="H37" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
@@ -3972,7 +3972,7 @@
         <v>126</v>
       </c>
       <c r="B38" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C38" t="s">
         <v>188</v>
@@ -3981,16 +3981,16 @@
         <v>159</v>
       </c>
       <c r="E38" t="s">
+        <v>355</v>
+      </c>
+      <c r="F38" t="s">
         <v>356</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>357</v>
       </c>
-      <c r="G38" t="s">
+      <c r="H38" t="s">
         <v>358</v>
-      </c>
-      <c r="H38" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -3998,25 +3998,25 @@
         <v>131</v>
       </c>
       <c r="B39" t="s">
+        <v>359</v>
+      </c>
+      <c r="C39" t="s">
         <v>360</v>
-      </c>
-      <c r="C39" t="s">
-        <v>361</v>
       </c>
       <c r="D39" t="s">
         <v>159</v>
       </c>
       <c r="E39" t="s">
+        <v>361</v>
+      </c>
+      <c r="F39" t="s">
         <v>362</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>363</v>
       </c>
-      <c r="G39" t="s">
+      <c r="H39" t="s">
         <v>364</v>
-      </c>
-      <c r="H39" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -4024,7 +4024,7 @@
         <v>105</v>
       </c>
       <c r="B40" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C40" t="s">
         <v>182</v>
@@ -4033,16 +4033,16 @@
         <v>211</v>
       </c>
       <c r="E40" t="s">
+        <v>366</v>
+      </c>
+      <c r="F40" t="s">
         <v>367</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>368</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
         <v>369</v>
-      </c>
-      <c r="H40" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -4050,25 +4050,25 @@
         <v>124</v>
       </c>
       <c r="B41" t="s">
+        <v>370</v>
+      </c>
+      <c r="C41" t="s">
         <v>371</v>
-      </c>
-      <c r="C41" t="s">
-        <v>372</v>
       </c>
       <c r="D41" t="s">
         <v>159</v>
       </c>
       <c r="E41" t="s">
+        <v>372</v>
+      </c>
+      <c r="F41" t="s">
         <v>373</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>374</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41" t="s">
         <v>375</v>
-      </c>
-      <c r="H41" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
@@ -4076,25 +4076,25 @@
         <v>53</v>
       </c>
       <c r="B42" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C42" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D42" t="s">
         <v>218</v>
       </c>
       <c r="E42" t="s">
+        <v>378</v>
+      </c>
+      <c r="F42" t="s">
         <v>379</v>
       </c>
-      <c r="F42" t="s">
-        <v>380</v>
-      </c>
       <c r="G42" t="s">
+        <v>384</v>
+      </c>
+      <c r="H42" t="s">
         <v>385</v>
-      </c>
-      <c r="H42" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -4102,7 +4102,7 @@
         <v>111</v>
       </c>
       <c r="B43" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C43" t="s">
         <v>151</v>
@@ -4111,16 +4111,16 @@
         <v>218</v>
       </c>
       <c r="E43" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F43" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G43" t="s">
+        <v>380</v>
+      </c>
+      <c r="H43" t="s">
         <v>381</v>
-      </c>
-      <c r="H43" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -4128,25 +4128,25 @@
         <v>108</v>
       </c>
       <c r="B44" t="s">
+        <v>386</v>
+      </c>
+      <c r="C44" t="s">
         <v>387</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
+        <v>290</v>
+      </c>
+      <c r="E44" t="s">
         <v>388</v>
       </c>
-      <c r="D44" t="s">
-        <v>291</v>
-      </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>389</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>390</v>
       </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
         <v>391</v>
-      </c>
-      <c r="H44" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -4154,25 +4154,25 @@
         <v>33</v>
       </c>
       <c r="B45" t="s">
+        <v>392</v>
+      </c>
+      <c r="C45" t="s">
         <v>393</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
+        <v>283</v>
+      </c>
+      <c r="E45" t="s">
         <v>394</v>
       </c>
-      <c r="D45" t="s">
-        <v>284</v>
-      </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>395</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>396</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>397</v>
-      </c>
-      <c r="H45" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
@@ -4180,25 +4180,25 @@
         <v>127</v>
       </c>
       <c r="B46" t="s">
+        <v>398</v>
+      </c>
+      <c r="C46" t="s">
         <v>399</v>
-      </c>
-      <c r="C46" t="s">
-        <v>400</v>
       </c>
       <c r="D46" t="s">
         <v>159</v>
       </c>
       <c r="E46" t="s">
+        <v>400</v>
+      </c>
+      <c r="F46" t="s">
         <v>401</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>402</v>
       </c>
-      <c r="G46" t="s">
+      <c r="H46" t="s">
         <v>403</v>
-      </c>
-      <c r="H46" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
@@ -4206,25 +4206,25 @@
         <v>142</v>
       </c>
       <c r="B47" t="s">
+        <v>404</v>
+      </c>
+      <c r="C47" t="s">
         <v>405</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>406</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>407</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>408</v>
       </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>409</v>
       </c>
-      <c r="G47" t="s">
+      <c r="H47" t="s">
         <v>410</v>
-      </c>
-      <c r="H47" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
@@ -4232,25 +4232,25 @@
         <v>23</v>
       </c>
       <c r="B48" t="s">
+        <v>411</v>
+      </c>
+      <c r="C48" t="s">
         <v>412</v>
-      </c>
-      <c r="C48" t="s">
-        <v>413</v>
       </c>
       <c r="D48" t="s">
         <v>218</v>
       </c>
       <c r="E48" t="s">
+        <v>413</v>
+      </c>
+      <c r="F48" t="s">
         <v>414</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>415</v>
       </c>
-      <c r="G48" t="s">
+      <c r="H48" t="s">
         <v>416</v>
-      </c>
-      <c r="H48" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
@@ -4258,25 +4258,25 @@
         <v>104</v>
       </c>
       <c r="B49" t="s">
+        <v>417</v>
+      </c>
+      <c r="C49" t="s">
         <v>418</v>
-      </c>
-      <c r="C49" t="s">
-        <v>419</v>
       </c>
       <c r="D49" t="s">
         <v>159</v>
       </c>
       <c r="E49" t="s">
+        <v>419</v>
+      </c>
+      <c r="F49" t="s">
         <v>420</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>421</v>
       </c>
-      <c r="G49" t="s">
+      <c r="H49" t="s">
         <v>422</v>
-      </c>
-      <c r="H49" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
@@ -4284,7 +4284,7 @@
         <v>29</v>
       </c>
       <c r="B50" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C50" t="s">
         <v>177</v>
@@ -4293,16 +4293,16 @@
         <v>152</v>
       </c>
       <c r="E50" t="s">
+        <v>424</v>
+      </c>
+      <c r="F50" t="s">
         <v>425</v>
       </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>426</v>
       </c>
-      <c r="G50" t="s">
+      <c r="H50" t="s">
         <v>427</v>
-      </c>
-      <c r="H50" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
@@ -4310,25 +4310,25 @@
         <v>74</v>
       </c>
       <c r="B51" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C51" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D51" t="s">
         <v>152</v>
       </c>
       <c r="E51" t="s">
+        <v>429</v>
+      </c>
+      <c r="F51" t="s">
         <v>430</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>431</v>
       </c>
-      <c r="G51" t="s">
+      <c r="H51" t="s">
         <v>432</v>
-      </c>
-      <c r="H51" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
@@ -4336,25 +4336,25 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C52" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D52" t="s">
         <v>218</v>
       </c>
       <c r="E52" t="s">
+        <v>434</v>
+      </c>
+      <c r="F52" t="s">
         <v>435</v>
       </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>436</v>
       </c>
-      <c r="G52" t="s">
+      <c r="H52" t="s">
         <v>437</v>
-      </c>
-      <c r="H52" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
@@ -4362,25 +4362,25 @@
         <v>100</v>
       </c>
       <c r="B53" t="s">
+        <v>438</v>
+      </c>
+      <c r="C53" t="s">
+        <v>282</v>
+      </c>
+      <c r="D53" t="s">
+        <v>283</v>
+      </c>
+      <c r="E53" t="s">
         <v>439</v>
       </c>
-      <c r="C53" t="s">
-        <v>283</v>
-      </c>
-      <c r="D53" t="s">
-        <v>284</v>
-      </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
+        <v>340</v>
+      </c>
+      <c r="G53" t="s">
         <v>440</v>
       </c>
-      <c r="F53" t="s">
-        <v>341</v>
-      </c>
-      <c r="G53" t="s">
+      <c r="H53" t="s">
         <v>441</v>
-      </c>
-      <c r="H53" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
@@ -4388,25 +4388,25 @@
         <v>27</v>
       </c>
       <c r="B54" t="s">
+        <v>442</v>
+      </c>
+      <c r="C54" t="s">
         <v>443</v>
-      </c>
-      <c r="C54" t="s">
-        <v>444</v>
       </c>
       <c r="D54" t="s">
         <v>218</v>
       </c>
       <c r="E54" t="s">
+        <v>444</v>
+      </c>
+      <c r="F54" t="s">
+        <v>414</v>
+      </c>
+      <c r="G54" t="s">
         <v>445</v>
       </c>
-      <c r="F54" t="s">
-        <v>415</v>
-      </c>
-      <c r="G54" t="s">
+      <c r="H54" t="s">
         <v>446</v>
-      </c>
-      <c r="H54" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
@@ -4414,25 +4414,25 @@
         <v>40</v>
       </c>
       <c r="B55" t="s">
+        <v>447</v>
+      </c>
+      <c r="C55" t="s">
         <v>448</v>
-      </c>
-      <c r="C55" t="s">
-        <v>449</v>
       </c>
       <c r="D55" t="s">
         <v>225</v>
       </c>
       <c r="E55" t="s">
+        <v>449</v>
+      </c>
+      <c r="F55" t="s">
         <v>450</v>
       </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>451</v>
       </c>
-      <c r="G55" t="s">
+      <c r="H55" t="s">
         <v>452</v>
-      </c>
-      <c r="H55" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
@@ -4440,25 +4440,25 @@
         <v>129</v>
       </c>
       <c r="B56" t="s">
+        <v>453</v>
+      </c>
+      <c r="C56" t="s">
         <v>454</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
+        <v>290</v>
+      </c>
+      <c r="E56" t="s">
         <v>455</v>
       </c>
-      <c r="D56" t="s">
-        <v>291</v>
-      </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>456</v>
       </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
         <v>457</v>
       </c>
-      <c r="G56" t="s">
+      <c r="H56" t="s">
         <v>458</v>
-      </c>
-      <c r="H56" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
@@ -4466,25 +4466,25 @@
         <v>130</v>
       </c>
       <c r="B57" t="s">
+        <v>459</v>
+      </c>
+      <c r="C57" t="s">
         <v>460</v>
-      </c>
-      <c r="C57" t="s">
-        <v>461</v>
       </c>
       <c r="D57" t="s">
         <v>159</v>
       </c>
       <c r="E57" t="s">
+        <v>461</v>
+      </c>
+      <c r="F57" t="s">
         <v>462</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>463</v>
       </c>
-      <c r="G57" t="s">
+      <c r="H57" t="s">
         <v>464</v>
-      </c>
-      <c r="H57" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -4492,7 +4492,7 @@
         <v>120</v>
       </c>
       <c r="B58" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C58" t="s">
         <v>158</v>
@@ -4501,16 +4501,16 @@
         <v>159</v>
       </c>
       <c r="E58" t="s">
+        <v>466</v>
+      </c>
+      <c r="F58" t="s">
         <v>467</v>
       </c>
-      <c r="F58" t="s">
+      <c r="G58" t="s">
         <v>468</v>
       </c>
-      <c r="G58" t="s">
+      <c r="H58" t="s">
         <v>469</v>
-      </c>
-      <c r="H58" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
@@ -4518,7 +4518,7 @@
         <v>14</v>
       </c>
       <c r="B59" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C59" t="s">
         <v>171</v>
@@ -4527,16 +4527,16 @@
         <v>159</v>
       </c>
       <c r="E59" t="s">
+        <v>471</v>
+      </c>
+      <c r="F59" t="s">
         <v>472</v>
       </c>
-      <c r="F59" t="s">
+      <c r="G59" t="s">
         <v>473</v>
       </c>
-      <c r="G59" t="s">
+      <c r="H59" t="s">
         <v>474</v>
-      </c>
-      <c r="H59" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
@@ -4544,25 +4544,25 @@
         <v>92</v>
       </c>
       <c r="B60" t="s">
+        <v>475</v>
+      </c>
+      <c r="C60" t="s">
         <v>476</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
+        <v>323</v>
+      </c>
+      <c r="E60" t="s">
         <v>477</v>
       </c>
-      <c r="D60" t="s">
-        <v>324</v>
-      </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>478</v>
       </c>
-      <c r="F60" t="s">
+      <c r="G60" t="s">
         <v>479</v>
       </c>
-      <c r="G60" t="s">
+      <c r="H60" t="s">
         <v>480</v>
-      </c>
-      <c r="H60" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
@@ -4570,7 +4570,7 @@
         <v>81</v>
       </c>
       <c r="B61" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C61" t="s">
         <v>231</v>
@@ -4579,16 +4579,16 @@
         <v>238</v>
       </c>
       <c r="E61" t="s">
+        <v>482</v>
+      </c>
+      <c r="F61" t="s">
         <v>483</v>
       </c>
-      <c r="F61" t="s">
+      <c r="G61" t="s">
         <v>484</v>
       </c>
-      <c r="G61" t="s">
+      <c r="H61" t="s">
         <v>485</v>
-      </c>
-      <c r="H61" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
@@ -4596,7 +4596,7 @@
         <v>30</v>
       </c>
       <c r="B62" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C62" t="s">
         <v>253</v>
@@ -4605,16 +4605,16 @@
         <v>152</v>
       </c>
       <c r="E62" t="s">
+        <v>487</v>
+      </c>
+      <c r="F62" t="s">
         <v>488</v>
       </c>
-      <c r="F62" t="s">
+      <c r="G62" t="s">
         <v>489</v>
       </c>
-      <c r="G62" t="s">
+      <c r="H62" t="s">
         <v>490</v>
-      </c>
-      <c r="H62" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
@@ -4622,25 +4622,25 @@
         <v>138</v>
       </c>
       <c r="B63" t="s">
+        <v>491</v>
+      </c>
+      <c r="C63" t="s">
         <v>492</v>
-      </c>
-      <c r="C63" t="s">
-        <v>493</v>
       </c>
       <c r="D63" t="s">
         <v>159</v>
       </c>
       <c r="E63" t="s">
+        <v>493</v>
+      </c>
+      <c r="F63" t="s">
         <v>494</v>
       </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
         <v>495</v>
       </c>
-      <c r="G63" t="s">
+      <c r="H63" t="s">
         <v>496</v>
-      </c>
-      <c r="H63" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
@@ -4648,25 +4648,25 @@
         <v>35</v>
       </c>
       <c r="B64" t="s">
+        <v>497</v>
+      </c>
+      <c r="C64" t="s">
         <v>498</v>
-      </c>
-      <c r="C64" t="s">
-        <v>499</v>
       </c>
       <c r="D64" t="s">
         <v>218</v>
       </c>
       <c r="E64" t="s">
+        <v>499</v>
+      </c>
+      <c r="F64" t="s">
         <v>500</v>
       </c>
-      <c r="F64" t="s">
+      <c r="G64" t="s">
         <v>501</v>
       </c>
-      <c r="G64" t="s">
+      <c r="H64" t="s">
         <v>502</v>
-      </c>
-      <c r="H64" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
@@ -4674,25 +4674,25 @@
         <v>43</v>
       </c>
       <c r="B65" t="s">
+        <v>503</v>
+      </c>
+      <c r="C65" t="s">
         <v>504</v>
-      </c>
-      <c r="C65" t="s">
-        <v>505</v>
       </c>
       <c r="D65" t="s">
         <v>225</v>
       </c>
       <c r="E65" t="s">
+        <v>505</v>
+      </c>
+      <c r="F65" t="s">
         <v>506</v>
       </c>
-      <c r="F65" t="s">
+      <c r="G65" t="s">
         <v>507</v>
       </c>
-      <c r="G65" t="s">
+      <c r="H65" t="s">
         <v>508</v>
-      </c>
-      <c r="H65" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
@@ -4700,25 +4700,25 @@
         <v>44</v>
       </c>
       <c r="B66" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C66" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D66" t="s">
         <v>225</v>
       </c>
       <c r="E66" t="s">
+        <v>510</v>
+      </c>
+      <c r="F66" t="s">
         <v>511</v>
       </c>
-      <c r="F66" t="s">
+      <c r="G66" t="s">
         <v>512</v>
       </c>
-      <c r="G66" t="s">
+      <c r="H66" t="s">
         <v>513</v>
-      </c>
-      <c r="H66" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
@@ -4726,25 +4726,25 @@
         <v>13</v>
       </c>
       <c r="B67" t="s">
+        <v>514</v>
+      </c>
+      <c r="C67" t="s">
         <v>515</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
+        <v>406</v>
+      </c>
+      <c r="E67" t="s">
         <v>516</v>
       </c>
-      <c r="D67" t="s">
-        <v>407</v>
-      </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>517</v>
       </c>
-      <c r="F67" t="s">
+      <c r="G67" t="s">
         <v>518</v>
       </c>
-      <c r="G67" t="s">
+      <c r="H67" t="s">
         <v>519</v>
-      </c>
-      <c r="H67" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
@@ -4752,25 +4752,25 @@
         <v>48</v>
       </c>
       <c r="B68" t="s">
+        <v>520</v>
+      </c>
+      <c r="C68" t="s">
         <v>521</v>
       </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
+        <v>290</v>
+      </c>
+      <c r="E68" t="s">
         <v>522</v>
       </c>
-      <c r="D68" t="s">
-        <v>291</v>
-      </c>
-      <c r="E68" t="s">
+      <c r="F68" t="s">
         <v>523</v>
       </c>
-      <c r="F68" t="s">
+      <c r="G68" t="s">
         <v>524</v>
       </c>
-      <c r="G68" t="s">
+      <c r="H68" t="s">
         <v>525</v>
-      </c>
-      <c r="H68" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
@@ -4778,25 +4778,25 @@
         <v>86</v>
       </c>
       <c r="B69" t="s">
+        <v>526</v>
+      </c>
+      <c r="C69" t="s">
         <v>527</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
+        <v>406</v>
+      </c>
+      <c r="E69" t="s">
         <v>528</v>
       </c>
-      <c r="D69" t="s">
-        <v>407</v>
-      </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>529</v>
       </c>
-      <c r="F69" t="s">
+      <c r="G69" t="s">
         <v>530</v>
       </c>
-      <c r="G69" t="s">
+      <c r="H69" t="s">
         <v>531</v>
-      </c>
-      <c r="H69" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
@@ -4804,25 +4804,25 @@
         <v>78</v>
       </c>
       <c r="B70" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C70" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D70" t="s">
         <v>152</v>
       </c>
       <c r="E70" t="s">
+        <v>533</v>
+      </c>
+      <c r="F70" t="s">
         <v>534</v>
       </c>
-      <c r="F70" t="s">
+      <c r="G70" t="s">
         <v>535</v>
       </c>
-      <c r="G70" t="s">
+      <c r="H70" t="s">
         <v>536</v>
-      </c>
-      <c r="H70" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
@@ -4830,7 +4830,7 @@
         <v>140</v>
       </c>
       <c r="B71" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C71" t="s">
         <v>237</v>
@@ -4839,16 +4839,16 @@
         <v>225</v>
       </c>
       <c r="E71" t="s">
+        <v>538</v>
+      </c>
+      <c r="F71" t="s">
         <v>539</v>
       </c>
-      <c r="F71" t="s">
+      <c r="G71" t="s">
         <v>540</v>
       </c>
-      <c r="G71" t="s">
+      <c r="H71" t="s">
         <v>541</v>
-      </c>
-      <c r="H71" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
@@ -4856,25 +4856,25 @@
         <v>45</v>
       </c>
       <c r="B72" t="s">
+        <v>542</v>
+      </c>
+      <c r="C72" t="s">
         <v>543</v>
-      </c>
-      <c r="C72" t="s">
-        <v>544</v>
       </c>
       <c r="D72" t="s">
         <v>218</v>
       </c>
       <c r="E72" t="s">
+        <v>544</v>
+      </c>
+      <c r="F72" t="s">
         <v>545</v>
       </c>
-      <c r="F72" t="s">
+      <c r="G72" t="s">
         <v>546</v>
       </c>
-      <c r="G72" t="s">
+      <c r="H72" t="s">
         <v>547</v>
-      </c>
-      <c r="H72" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
@@ -4882,25 +4882,25 @@
         <v>51</v>
       </c>
       <c r="B73" t="s">
+        <v>548</v>
+      </c>
+      <c r="C73" t="s">
         <v>549</v>
-      </c>
-      <c r="C73" t="s">
-        <v>550</v>
       </c>
       <c r="D73" t="s">
         <v>211</v>
       </c>
       <c r="E73" t="s">
+        <v>550</v>
+      </c>
+      <c r="F73" t="s">
         <v>551</v>
       </c>
-      <c r="F73" t="s">
+      <c r="G73" t="s">
         <v>552</v>
       </c>
-      <c r="G73" t="s">
+      <c r="H73" t="s">
         <v>553</v>
-      </c>
-      <c r="H73" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
@@ -4908,25 +4908,25 @@
         <v>135</v>
       </c>
       <c r="B74" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C74" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D74" t="s">
         <v>159</v>
       </c>
       <c r="E74" t="s">
+        <v>555</v>
+      </c>
+      <c r="F74" t="s">
         <v>556</v>
       </c>
-      <c r="F74" t="s">
+      <c r="G74" t="s">
         <v>557</v>
       </c>
-      <c r="G74" t="s">
+      <c r="H74" t="s">
         <v>558</v>
-      </c>
-      <c r="H74" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
@@ -4934,25 +4934,25 @@
         <v>56</v>
       </c>
       <c r="B75" t="s">
+        <v>559</v>
+      </c>
+      <c r="C75" t="s">
+        <v>697</v>
+      </c>
+      <c r="D75" t="s">
+        <v>406</v>
+      </c>
+      <c r="E75" t="s">
         <v>560</v>
       </c>
-      <c r="C75" t="s">
-        <v>698</v>
-      </c>
-      <c r="D75" t="s">
-        <v>407</v>
-      </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>561</v>
       </c>
-      <c r="F75" t="s">
+      <c r="G75" t="s">
         <v>562</v>
       </c>
-      <c r="G75" t="s">
+      <c r="H75" t="s">
         <v>563</v>
-      </c>
-      <c r="H75" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
@@ -4960,25 +4960,25 @@
         <v>61</v>
       </c>
       <c r="B76" t="s">
+        <v>564</v>
+      </c>
+      <c r="C76" t="s">
         <v>565</v>
-      </c>
-      <c r="C76" t="s">
-        <v>566</v>
       </c>
       <c r="D76" t="s">
         <v>218</v>
       </c>
       <c r="E76" t="s">
+        <v>566</v>
+      </c>
+      <c r="F76" t="s">
         <v>567</v>
       </c>
-      <c r="F76" t="s">
+      <c r="G76" t="s">
         <v>568</v>
       </c>
-      <c r="G76" t="s">
+      <c r="H76" t="s">
         <v>569</v>
-      </c>
-      <c r="H76" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
@@ -4986,25 +4986,25 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C77" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D77" t="s">
         <v>152</v>
       </c>
       <c r="E77" t="s">
+        <v>571</v>
+      </c>
+      <c r="F77" t="s">
         <v>572</v>
       </c>
-      <c r="F77" t="s">
+      <c r="G77" t="s">
         <v>573</v>
       </c>
-      <c r="G77" t="s">
+      <c r="H77" t="s">
         <v>574</v>
-      </c>
-      <c r="H77" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
@@ -5012,25 +5012,25 @@
         <v>143</v>
       </c>
       <c r="B78" t="s">
+        <v>575</v>
+      </c>
+      <c r="C78" t="s">
         <v>576</v>
-      </c>
-      <c r="C78" t="s">
-        <v>577</v>
       </c>
       <c r="D78" t="s">
         <v>159</v>
       </c>
       <c r="E78" t="s">
+        <v>577</v>
+      </c>
+      <c r="F78" t="s">
         <v>578</v>
       </c>
-      <c r="F78" t="s">
+      <c r="G78" t="s">
         <v>579</v>
       </c>
-      <c r="G78" t="s">
+      <c r="H78" t="s">
         <v>580</v>
-      </c>
-      <c r="H78" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
@@ -5038,25 +5038,25 @@
         <v>59</v>
       </c>
       <c r="B79" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C79" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D79" t="s">
         <v>159</v>
       </c>
       <c r="E79" t="s">
+        <v>582</v>
+      </c>
+      <c r="F79" t="s">
         <v>583</v>
       </c>
-      <c r="F79" t="s">
+      <c r="G79" t="s">
         <v>584</v>
       </c>
-      <c r="G79" t="s">
+      <c r="H79" t="s">
         <v>585</v>
-      </c>
-      <c r="H79" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
@@ -5064,25 +5064,25 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
+        <v>586</v>
+      </c>
+      <c r="C80" t="s">
         <v>587</v>
-      </c>
-      <c r="C80" t="s">
-        <v>588</v>
       </c>
       <c r="D80" t="s">
         <v>159</v>
       </c>
       <c r="E80" t="s">
+        <v>588</v>
+      </c>
+      <c r="F80" t="s">
         <v>589</v>
       </c>
-      <c r="F80" t="s">
+      <c r="G80" t="s">
         <v>590</v>
       </c>
-      <c r="G80" t="s">
+      <c r="H80" t="s">
         <v>591</v>
-      </c>
-      <c r="H80" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
@@ -5090,25 +5090,25 @@
         <v>141</v>
       </c>
       <c r="B81" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C81" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D81" t="s">
         <v>159</v>
       </c>
       <c r="E81" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="F81" t="s">
+        <v>593</v>
+      </c>
+      <c r="G81" t="s">
         <v>594</v>
       </c>
-      <c r="G81" t="s">
+      <c r="H81" t="s">
         <v>595</v>
-      </c>
-      <c r="H81" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
@@ -5116,25 +5116,25 @@
         <v>144</v>
       </c>
       <c r="B82" t="s">
+        <v>596</v>
+      </c>
+      <c r="C82" t="s">
+        <v>405</v>
+      </c>
+      <c r="D82" t="s">
+        <v>406</v>
+      </c>
+      <c r="E82" t="s">
         <v>597</v>
       </c>
-      <c r="C82" t="s">
-        <v>406</v>
-      </c>
-      <c r="D82" t="s">
-        <v>407</v>
-      </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
         <v>598</v>
       </c>
-      <c r="F82" t="s">
+      <c r="G82" t="s">
         <v>599</v>
       </c>
-      <c r="G82" t="s">
+      <c r="H82" t="s">
         <v>600</v>
-      </c>
-      <c r="H82" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
@@ -5142,25 +5142,25 @@
         <v>60</v>
       </c>
       <c r="B83" t="s">
+        <v>601</v>
+      </c>
+      <c r="C83" t="s">
         <v>602</v>
-      </c>
-      <c r="C83" t="s">
-        <v>603</v>
       </c>
       <c r="D83" t="s">
         <v>159</v>
       </c>
       <c r="E83" t="s">
+        <v>603</v>
+      </c>
+      <c r="F83" t="s">
         <v>604</v>
       </c>
-      <c r="F83" t="s">
+      <c r="G83" t="s">
         <v>605</v>
       </c>
-      <c r="G83" t="s">
+      <c r="H83" t="s">
         <v>606</v>
-      </c>
-      <c r="H83" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
@@ -5168,25 +5168,25 @@
         <v>66</v>
       </c>
       <c r="B84" t="s">
+        <v>607</v>
+      </c>
+      <c r="C84" t="s">
         <v>608</v>
       </c>
-      <c r="C84" t="s">
+      <c r="D84" t="s">
+        <v>406</v>
+      </c>
+      <c r="E84" t="s">
         <v>609</v>
       </c>
-      <c r="D84" t="s">
-        <v>407</v>
-      </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>610</v>
       </c>
-      <c r="F84" t="s">
+      <c r="G84" t="s">
         <v>611</v>
       </c>
-      <c r="G84" t="s">
+      <c r="H84" t="s">
         <v>612</v>
-      </c>
-      <c r="H84" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
@@ -5194,25 +5194,25 @@
         <v>34</v>
       </c>
       <c r="B85" t="s">
+        <v>613</v>
+      </c>
+      <c r="C85" t="s">
         <v>614</v>
       </c>
-      <c r="C85" t="s">
+      <c r="D85" t="s">
+        <v>283</v>
+      </c>
+      <c r="E85" t="s">
         <v>615</v>
       </c>
-      <c r="D85" t="s">
-        <v>284</v>
-      </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
         <v>616</v>
       </c>
-      <c r="F85" t="s">
+      <c r="G85" t="s">
         <v>617</v>
       </c>
-      <c r="G85" t="s">
+      <c r="H85" t="s">
         <v>618</v>
-      </c>
-      <c r="H85" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
@@ -5220,25 +5220,25 @@
         <v>41</v>
       </c>
       <c r="B86" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C86" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D86" t="s">
         <v>218</v>
       </c>
       <c r="E86" t="s">
+        <v>620</v>
+      </c>
+      <c r="F86" t="s">
         <v>621</v>
       </c>
-      <c r="F86" t="s">
+      <c r="G86" t="s">
         <v>622</v>
       </c>
-      <c r="G86" t="s">
+      <c r="H86" t="s">
         <v>623</v>
-      </c>
-      <c r="H86" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
@@ -5246,25 +5246,25 @@
         <v>79</v>
       </c>
       <c r="B87" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C87" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D87" t="s">
         <v>159</v>
       </c>
       <c r="E87" t="s">
+        <v>625</v>
+      </c>
+      <c r="F87" t="s">
         <v>626</v>
       </c>
-      <c r="F87" t="s">
+      <c r="G87" t="s">
         <v>627</v>
       </c>
-      <c r="G87" t="s">
+      <c r="H87" t="s">
         <v>628</v>
-      </c>
-      <c r="H87" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
@@ -5272,7 +5272,7 @@
         <v>91</v>
       </c>
       <c r="B88" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C88" t="s">
         <v>231</v>
@@ -5281,16 +5281,16 @@
         <v>238</v>
       </c>
       <c r="E88" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F88" t="s">
+        <v>630</v>
+      </c>
+      <c r="G88" t="s">
         <v>631</v>
       </c>
-      <c r="G88" t="s">
+      <c r="H88" t="s">
         <v>632</v>
-      </c>
-      <c r="H88" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
@@ -5298,25 +5298,25 @@
         <v>118</v>
       </c>
       <c r="B89" t="s">
+        <v>633</v>
+      </c>
+      <c r="C89" t="s">
         <v>634</v>
-      </c>
-      <c r="C89" t="s">
-        <v>635</v>
       </c>
       <c r="D89" t="s">
         <v>152</v>
       </c>
       <c r="E89" t="s">
+        <v>635</v>
+      </c>
+      <c r="F89" t="s">
         <v>636</v>
       </c>
-      <c r="F89" t="s">
+      <c r="G89" t="s">
         <v>637</v>
       </c>
-      <c r="G89" t="s">
+      <c r="H89" t="s">
         <v>638</v>
-      </c>
-      <c r="H89" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
@@ -5324,25 +5324,25 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C90" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D90" t="s">
         <v>225</v>
       </c>
       <c r="E90" t="s">
+        <v>640</v>
+      </c>
+      <c r="F90" t="s">
+        <v>340</v>
+      </c>
+      <c r="G90" t="s">
         <v>641</v>
       </c>
-      <c r="F90" t="s">
-        <v>341</v>
-      </c>
-      <c r="G90" t="s">
+      <c r="H90" t="s">
         <v>642</v>
-      </c>
-      <c r="H90" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
@@ -5350,25 +5350,25 @@
         <v>121</v>
       </c>
       <c r="B91" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C91" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D91" t="s">
         <v>152</v>
       </c>
       <c r="E91" t="s">
+        <v>644</v>
+      </c>
+      <c r="F91" t="s">
         <v>645</v>
       </c>
-      <c r="F91" t="s">
+      <c r="G91" t="s">
         <v>646</v>
       </c>
-      <c r="G91" t="s">
+      <c r="H91" t="s">
         <v>647</v>
-      </c>
-      <c r="H91" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
@@ -5376,25 +5376,25 @@
         <v>67</v>
       </c>
       <c r="B92" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C92" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D92" t="s">
         <v>218</v>
       </c>
       <c r="E92" t="s">
+        <v>648</v>
+      </c>
+      <c r="F92" t="s">
         <v>649</v>
       </c>
-      <c r="F92" t="s">
+      <c r="G92" t="s">
         <v>650</v>
       </c>
-      <c r="G92" t="s">
+      <c r="H92" t="s">
         <v>651</v>
-      </c>
-      <c r="H92" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
@@ -5402,25 +5402,25 @@
         <v>49</v>
       </c>
       <c r="B93" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C93" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D93" t="s">
         <v>218</v>
       </c>
       <c r="E93" t="s">
+        <v>653</v>
+      </c>
+      <c r="F93" t="s">
+        <v>462</v>
+      </c>
+      <c r="G93" t="s">
         <v>654</v>
       </c>
-      <c r="F93" t="s">
-        <v>463</v>
-      </c>
-      <c r="G93" t="s">
+      <c r="H93" t="s">
         <v>655</v>
-      </c>
-      <c r="H93" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
@@ -5428,25 +5428,25 @@
         <v>31</v>
       </c>
       <c r="B94" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C94" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D94" t="s">
         <v>218</v>
       </c>
       <c r="E94" t="s">
+        <v>657</v>
+      </c>
+      <c r="F94" t="s">
         <v>658</v>
       </c>
-      <c r="F94" t="s">
+      <c r="G94" t="s">
         <v>659</v>
       </c>
-      <c r="G94" t="s">
+      <c r="H94" t="s">
         <v>660</v>
-      </c>
-      <c r="H94" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
@@ -5454,7 +5454,7 @@
         <v>109</v>
       </c>
       <c r="B95" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C95" t="s">
         <v>182</v>
@@ -5463,16 +5463,16 @@
         <v>159</v>
       </c>
       <c r="E95" t="s">
+        <v>662</v>
+      </c>
+      <c r="F95" t="s">
+        <v>621</v>
+      </c>
+      <c r="G95" t="s">
         <v>663</v>
       </c>
-      <c r="F95" t="s">
-        <v>622</v>
-      </c>
-      <c r="G95" t="s">
+      <c r="H95" t="s">
         <v>664</v>
-      </c>
-      <c r="H95" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
@@ -5480,25 +5480,25 @@
         <v>71</v>
       </c>
       <c r="B96" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D96" t="s">
         <v>218</v>
       </c>
       <c r="E96" t="s">
+        <v>665</v>
+      </c>
+      <c r="F96" t="s">
+        <v>500</v>
+      </c>
+      <c r="G96" t="s">
         <v>666</v>
       </c>
-      <c r="F96" t="s">
-        <v>501</v>
-      </c>
-      <c r="G96" t="s">
+      <c r="H96" t="s">
         <v>667</v>
-      </c>
-      <c r="H96" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
@@ -5506,25 +5506,25 @@
         <v>128</v>
       </c>
       <c r="B97" t="s">
+        <v>668</v>
+      </c>
+      <c r="C97" t="s">
         <v>669</v>
-      </c>
-      <c r="C97" t="s">
-        <v>670</v>
       </c>
       <c r="D97" t="s">
         <v>225</v>
       </c>
       <c r="E97" t="s">
+        <v>670</v>
+      </c>
+      <c r="F97" t="s">
         <v>671</v>
       </c>
-      <c r="F97" t="s">
+      <c r="G97" t="s">
         <v>672</v>
       </c>
-      <c r="G97" t="s">
+      <c r="H97" t="s">
         <v>673</v>
-      </c>
-      <c r="H97" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
@@ -5532,7 +5532,7 @@
         <v>95</v>
       </c>
       <c r="B98" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C98" t="s">
         <v>231</v>
@@ -5541,16 +5541,16 @@
         <v>238</v>
       </c>
       <c r="E98" t="s">
+        <v>675</v>
+      </c>
+      <c r="F98" t="s">
         <v>676</v>
       </c>
-      <c r="F98" t="s">
+      <c r="G98" t="s">
         <v>677</v>
       </c>
-      <c r="G98" t="s">
+      <c r="H98" t="s">
         <v>678</v>
-      </c>
-      <c r="H98" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
@@ -5558,25 +5558,25 @@
         <v>133</v>
       </c>
       <c r="B99" t="s">
+        <v>679</v>
+      </c>
+      <c r="C99" t="s">
         <v>680</v>
       </c>
-      <c r="C99" t="s">
+      <c r="D99" t="s">
+        <v>406</v>
+      </c>
+      <c r="E99" t="s">
         <v>681</v>
       </c>
-      <c r="D99" t="s">
-        <v>407</v>
-      </c>
-      <c r="E99" t="s">
+      <c r="F99" t="s">
         <v>682</v>
       </c>
-      <c r="F99" t="s">
+      <c r="G99" t="s">
         <v>683</v>
       </c>
-      <c r="G99" t="s">
+      <c r="H99" t="s">
         <v>684</v>
-      </c>
-      <c r="H99" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
@@ -5584,25 +5584,25 @@
         <v>17</v>
       </c>
       <c r="B100" t="s">
+        <v>685</v>
+      </c>
+      <c r="C100" t="s">
         <v>686</v>
-      </c>
-      <c r="C100" t="s">
-        <v>687</v>
       </c>
       <c r="D100" t="s">
         <v>238</v>
       </c>
       <c r="E100" t="s">
+        <v>687</v>
+      </c>
+      <c r="F100" t="s">
         <v>688</v>
       </c>
-      <c r="F100" t="s">
+      <c r="G100" t="s">
         <v>689</v>
       </c>
-      <c r="G100" t="s">
+      <c r="H100" t="s">
         <v>690</v>
-      </c>
-      <c r="H100" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
@@ -5610,7 +5610,7 @@
         <v>113</v>
       </c>
       <c r="B101" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C101" t="s">
         <v>182</v>
@@ -5619,16 +5619,16 @@
         <v>152</v>
       </c>
       <c r="E101" t="s">
+        <v>692</v>
+      </c>
+      <c r="F101" t="s">
         <v>693</v>
       </c>
-      <c r="F101" t="s">
+      <c r="G101" t="s">
         <v>694</v>
       </c>
-      <c r="G101" t="s">
+      <c r="H101" t="s">
         <v>695</v>
-      </c>
-      <c r="H101" t="s">
-        <v>696</v>
       </c>
     </row>
   </sheetData>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="D31" s="6" t="str">
         <f>IFERROR(VLOOKUP($B31,Data!$A:$D,2,FALSE),"")</f>
-        <v>Parametric study of regime transitions in quasi-turbulence</v>
+        <v>Parametric Study of Regime Transition in Quasi-Geostrophic Turbulence</v>
       </c>
       <c r="E31" s="6" t="str">
         <f>IFERROR(VLOOKUP($B31,Data!$A:$D,3,FALSE),"")</f>

--- a/RSI_2026_Schedule.xlsx
+++ b/RSI_2026_Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/evanlim/Documents/rsi-symposium/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF002864-FB68-9B4F-A397-79EACC97E35D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4635FA73-AEBF-1E42-933D-B32D9927B414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="706">
   <si>
     <t>RSI 2026 Symposium Schedule</t>
   </si>
@@ -1053,9 +1053,6 @@
     <t>ebuehler</t>
   </si>
   <si>
-    <t>Building a Machine Learning Model to Track Many C. elegans Worms Simultaneously and Resolve Collisions</t>
-  </si>
-  <si>
     <t>FAIR-is</t>
   </si>
   <si>
@@ -1926,9 +1923,6 @@
     <t>sofia937</t>
   </si>
   <si>
-    <t>Reachability-Based Path Planning Across Autonomous Ocean Vehicles Platforms</t>
-  </si>
-  <si>
     <t>JOW</t>
   </si>
   <si>
@@ -2152,6 +2146,15 @@
   </si>
   <si>
     <t>Parametric Study of Regime Transition in Quasi-Geostrophic Turbulence</t>
+  </si>
+  <si>
+    <t>Prof. Peter Lu, Mateusz Zubrzycki</t>
+  </si>
+  <si>
+    <t>Reachability-Based Path Planning Across Autonomous Ocean Vehicle Platforms</t>
+  </si>
+  <si>
+    <t>Building a Machine Learning Model to Resolve C. elegans Collisions</t>
   </si>
 </sst>
 </file>
@@ -2309,23 +2312,23 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3166,7 +3169,7 @@
         <v>93</v>
       </c>
       <c r="B7" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C7" t="s">
         <v>182</v>
@@ -3455,7 +3458,7 @@
         <v>247</v>
       </c>
       <c r="C18" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D18" t="s">
         <v>225</v>
@@ -3504,7 +3507,7 @@
         <v>73</v>
       </c>
       <c r="B20" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C20" t="s">
         <v>231</v>
@@ -3530,7 +3533,7 @@
         <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C21" t="s">
         <v>261</v>
@@ -3556,7 +3559,7 @@
         <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C22" t="s">
         <v>266</v>
@@ -3868,7 +3871,7 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C34" t="s">
         <v>177</v>
@@ -3894,7 +3897,7 @@
         <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>338</v>
+        <v>705</v>
       </c>
       <c r="C35" t="s">
         <v>171</v>
@@ -3903,16 +3906,16 @@
         <v>152</v>
       </c>
       <c r="E35" t="s">
+        <v>338</v>
+      </c>
+      <c r="F35" t="s">
         <v>339</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>340</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
         <v>341</v>
-      </c>
-      <c r="H35" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -3920,25 +3923,25 @@
         <v>75</v>
       </c>
       <c r="B36" t="s">
+        <v>342</v>
+      </c>
+      <c r="C36" t="s">
         <v>343</v>
-      </c>
-      <c r="C36" t="s">
-        <v>344</v>
       </c>
       <c r="D36" t="s">
         <v>159</v>
       </c>
       <c r="E36" t="s">
+        <v>344</v>
+      </c>
+      <c r="F36" t="s">
         <v>345</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>346</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>347</v>
-      </c>
-      <c r="H36" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -3946,7 +3949,7 @@
         <v>19</v>
       </c>
       <c r="B37" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C37" t="s">
         <v>217</v>
@@ -3955,16 +3958,16 @@
         <v>218</v>
       </c>
       <c r="E37" t="s">
+        <v>349</v>
+      </c>
+      <c r="F37" t="s">
         <v>350</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>351</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>352</v>
-      </c>
-      <c r="H37" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
@@ -3972,7 +3975,7 @@
         <v>126</v>
       </c>
       <c r="B38" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C38" t="s">
         <v>188</v>
@@ -3981,16 +3984,16 @@
         <v>159</v>
       </c>
       <c r="E38" t="s">
+        <v>354</v>
+      </c>
+      <c r="F38" t="s">
         <v>355</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>356</v>
       </c>
-      <c r="G38" t="s">
+      <c r="H38" t="s">
         <v>357</v>
-      </c>
-      <c r="H38" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -3998,25 +4001,25 @@
         <v>131</v>
       </c>
       <c r="B39" t="s">
+        <v>358</v>
+      </c>
+      <c r="C39" t="s">
         <v>359</v>
-      </c>
-      <c r="C39" t="s">
-        <v>360</v>
       </c>
       <c r="D39" t="s">
         <v>159</v>
       </c>
       <c r="E39" t="s">
+        <v>360</v>
+      </c>
+      <c r="F39" t="s">
         <v>361</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>362</v>
       </c>
-      <c r="G39" t="s">
+      <c r="H39" t="s">
         <v>363</v>
-      </c>
-      <c r="H39" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -4024,7 +4027,7 @@
         <v>105</v>
       </c>
       <c r="B40" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C40" t="s">
         <v>182</v>
@@ -4033,16 +4036,16 @@
         <v>211</v>
       </c>
       <c r="E40" t="s">
+        <v>365</v>
+      </c>
+      <c r="F40" t="s">
         <v>366</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>367</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
         <v>368</v>
-      </c>
-      <c r="H40" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -4050,25 +4053,25 @@
         <v>124</v>
       </c>
       <c r="B41" t="s">
+        <v>369</v>
+      </c>
+      <c r="C41" t="s">
         <v>370</v>
-      </c>
-      <c r="C41" t="s">
-        <v>371</v>
       </c>
       <c r="D41" t="s">
         <v>159</v>
       </c>
       <c r="E41" t="s">
+        <v>371</v>
+      </c>
+      <c r="F41" t="s">
         <v>372</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>373</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41" t="s">
         <v>374</v>
-      </c>
-      <c r="H41" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
@@ -4076,25 +4079,25 @@
         <v>53</v>
       </c>
       <c r="B42" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C42" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D42" t="s">
         <v>218</v>
       </c>
       <c r="E42" t="s">
+        <v>377</v>
+      </c>
+      <c r="F42" t="s">
         <v>378</v>
       </c>
-      <c r="F42" t="s">
-        <v>379</v>
-      </c>
       <c r="G42" t="s">
+        <v>383</v>
+      </c>
+      <c r="H42" t="s">
         <v>384</v>
-      </c>
-      <c r="H42" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -4102,7 +4105,7 @@
         <v>111</v>
       </c>
       <c r="B43" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C43" t="s">
         <v>151</v>
@@ -4111,16 +4114,16 @@
         <v>218</v>
       </c>
       <c r="E43" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F43" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G43" t="s">
+        <v>379</v>
+      </c>
+      <c r="H43" t="s">
         <v>380</v>
-      </c>
-      <c r="H43" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -4128,25 +4131,25 @@
         <v>108</v>
       </c>
       <c r="B44" t="s">
+        <v>385</v>
+      </c>
+      <c r="C44" t="s">
         <v>386</v>
-      </c>
-      <c r="C44" t="s">
-        <v>387</v>
       </c>
       <c r="D44" t="s">
         <v>290</v>
       </c>
       <c r="E44" t="s">
+        <v>387</v>
+      </c>
+      <c r="F44" t="s">
         <v>388</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>389</v>
       </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
         <v>390</v>
-      </c>
-      <c r="H44" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -4154,25 +4157,25 @@
         <v>33</v>
       </c>
       <c r="B45" t="s">
+        <v>391</v>
+      </c>
+      <c r="C45" t="s">
         <v>392</v>
-      </c>
-      <c r="C45" t="s">
-        <v>393</v>
       </c>
       <c r="D45" t="s">
         <v>283</v>
       </c>
       <c r="E45" t="s">
+        <v>393</v>
+      </c>
+      <c r="F45" t="s">
         <v>394</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>395</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>396</v>
-      </c>
-      <c r="H45" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
@@ -4180,25 +4183,25 @@
         <v>127</v>
       </c>
       <c r="B46" t="s">
+        <v>397</v>
+      </c>
+      <c r="C46" t="s">
         <v>398</v>
-      </c>
-      <c r="C46" t="s">
-        <v>399</v>
       </c>
       <c r="D46" t="s">
         <v>159</v>
       </c>
       <c r="E46" t="s">
+        <v>399</v>
+      </c>
+      <c r="F46" t="s">
         <v>400</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>401</v>
       </c>
-      <c r="G46" t="s">
+      <c r="H46" t="s">
         <v>402</v>
-      </c>
-      <c r="H46" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
@@ -4206,25 +4209,25 @@
         <v>142</v>
       </c>
       <c r="B47" t="s">
+        <v>403</v>
+      </c>
+      <c r="C47" t="s">
         <v>404</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>405</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>406</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>407</v>
       </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>408</v>
       </c>
-      <c r="G47" t="s">
+      <c r="H47" t="s">
         <v>409</v>
-      </c>
-      <c r="H47" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
@@ -4232,25 +4235,25 @@
         <v>23</v>
       </c>
       <c r="B48" t="s">
+        <v>410</v>
+      </c>
+      <c r="C48" t="s">
         <v>411</v>
-      </c>
-      <c r="C48" t="s">
-        <v>412</v>
       </c>
       <c r="D48" t="s">
         <v>218</v>
       </c>
       <c r="E48" t="s">
+        <v>412</v>
+      </c>
+      <c r="F48" t="s">
         <v>413</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>414</v>
       </c>
-      <c r="G48" t="s">
+      <c r="H48" t="s">
         <v>415</v>
-      </c>
-      <c r="H48" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
@@ -4258,25 +4261,25 @@
         <v>104</v>
       </c>
       <c r="B49" t="s">
+        <v>416</v>
+      </c>
+      <c r="C49" t="s">
         <v>417</v>
-      </c>
-      <c r="C49" t="s">
-        <v>418</v>
       </c>
       <c r="D49" t="s">
         <v>159</v>
       </c>
       <c r="E49" t="s">
+        <v>418</v>
+      </c>
+      <c r="F49" t="s">
         <v>419</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>420</v>
       </c>
-      <c r="G49" t="s">
+      <c r="H49" t="s">
         <v>421</v>
-      </c>
-      <c r="H49" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
@@ -4284,7 +4287,7 @@
         <v>29</v>
       </c>
       <c r="B50" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C50" t="s">
         <v>177</v>
@@ -4293,16 +4296,16 @@
         <v>152</v>
       </c>
       <c r="E50" t="s">
+        <v>423</v>
+      </c>
+      <c r="F50" t="s">
         <v>424</v>
       </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>425</v>
       </c>
-      <c r="G50" t="s">
+      <c r="H50" t="s">
         <v>426</v>
-      </c>
-      <c r="H50" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
@@ -4310,7 +4313,7 @@
         <v>74</v>
       </c>
       <c r="B51" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C51" t="s">
         <v>296</v>
@@ -4319,16 +4322,16 @@
         <v>152</v>
       </c>
       <c r="E51" t="s">
+        <v>428</v>
+      </c>
+      <c r="F51" t="s">
         <v>429</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>430</v>
       </c>
-      <c r="G51" t="s">
+      <c r="H51" t="s">
         <v>431</v>
-      </c>
-      <c r="H51" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
@@ -4336,25 +4339,25 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C52" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D52" t="s">
         <v>218</v>
       </c>
       <c r="E52" t="s">
+        <v>433</v>
+      </c>
+      <c r="F52" t="s">
         <v>434</v>
       </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>435</v>
       </c>
-      <c r="G52" t="s">
+      <c r="H52" t="s">
         <v>436</v>
-      </c>
-      <c r="H52" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
@@ -4362,7 +4365,7 @@
         <v>100</v>
       </c>
       <c r="B53" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C53" t="s">
         <v>282</v>
@@ -4371,16 +4374,16 @@
         <v>283</v>
       </c>
       <c r="E53" t="s">
+        <v>438</v>
+      </c>
+      <c r="F53" t="s">
+        <v>339</v>
+      </c>
+      <c r="G53" t="s">
         <v>439</v>
       </c>
-      <c r="F53" t="s">
-        <v>340</v>
-      </c>
-      <c r="G53" t="s">
+      <c r="H53" t="s">
         <v>440</v>
-      </c>
-      <c r="H53" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
@@ -4388,25 +4391,25 @@
         <v>27</v>
       </c>
       <c r="B54" t="s">
+        <v>441</v>
+      </c>
+      <c r="C54" t="s">
         <v>442</v>
-      </c>
-      <c r="C54" t="s">
-        <v>443</v>
       </c>
       <c r="D54" t="s">
         <v>218</v>
       </c>
       <c r="E54" t="s">
+        <v>443</v>
+      </c>
+      <c r="F54" t="s">
+        <v>413</v>
+      </c>
+      <c r="G54" t="s">
         <v>444</v>
       </c>
-      <c r="F54" t="s">
-        <v>414</v>
-      </c>
-      <c r="G54" t="s">
+      <c r="H54" t="s">
         <v>445</v>
-      </c>
-      <c r="H54" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
@@ -4414,25 +4417,25 @@
         <v>40</v>
       </c>
       <c r="B55" t="s">
+        <v>446</v>
+      </c>
+      <c r="C55" t="s">
         <v>447</v>
-      </c>
-      <c r="C55" t="s">
-        <v>448</v>
       </c>
       <c r="D55" t="s">
         <v>225</v>
       </c>
       <c r="E55" t="s">
+        <v>448</v>
+      </c>
+      <c r="F55" t="s">
         <v>449</v>
       </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>450</v>
       </c>
-      <c r="G55" t="s">
+      <c r="H55" t="s">
         <v>451</v>
-      </c>
-      <c r="H55" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
@@ -4440,25 +4443,25 @@
         <v>129</v>
       </c>
       <c r="B56" t="s">
+        <v>452</v>
+      </c>
+      <c r="C56" t="s">
         <v>453</v>
-      </c>
-      <c r="C56" t="s">
-        <v>454</v>
       </c>
       <c r="D56" t="s">
         <v>290</v>
       </c>
       <c r="E56" t="s">
+        <v>454</v>
+      </c>
+      <c r="F56" t="s">
         <v>455</v>
       </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
         <v>456</v>
       </c>
-      <c r="G56" t="s">
+      <c r="H56" t="s">
         <v>457</v>
-      </c>
-      <c r="H56" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
@@ -4466,25 +4469,25 @@
         <v>130</v>
       </c>
       <c r="B57" t="s">
+        <v>458</v>
+      </c>
+      <c r="C57" t="s">
         <v>459</v>
-      </c>
-      <c r="C57" t="s">
-        <v>460</v>
       </c>
       <c r="D57" t="s">
         <v>159</v>
       </c>
       <c r="E57" t="s">
+        <v>460</v>
+      </c>
+      <c r="F57" t="s">
         <v>461</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>462</v>
       </c>
-      <c r="G57" t="s">
+      <c r="H57" t="s">
         <v>463</v>
-      </c>
-      <c r="H57" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -4492,7 +4495,7 @@
         <v>120</v>
       </c>
       <c r="B58" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C58" t="s">
         <v>158</v>
@@ -4501,16 +4504,16 @@
         <v>159</v>
       </c>
       <c r="E58" t="s">
+        <v>465</v>
+      </c>
+      <c r="F58" t="s">
         <v>466</v>
       </c>
-      <c r="F58" t="s">
+      <c r="G58" t="s">
         <v>467</v>
       </c>
-      <c r="G58" t="s">
+      <c r="H58" t="s">
         <v>468</v>
-      </c>
-      <c r="H58" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
@@ -4518,7 +4521,7 @@
         <v>14</v>
       </c>
       <c r="B59" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C59" t="s">
         <v>171</v>
@@ -4527,16 +4530,16 @@
         <v>159</v>
       </c>
       <c r="E59" t="s">
+        <v>470</v>
+      </c>
+      <c r="F59" t="s">
         <v>471</v>
       </c>
-      <c r="F59" t="s">
+      <c r="G59" t="s">
         <v>472</v>
       </c>
-      <c r="G59" t="s">
+      <c r="H59" t="s">
         <v>473</v>
-      </c>
-      <c r="H59" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
@@ -4544,25 +4547,25 @@
         <v>92</v>
       </c>
       <c r="B60" t="s">
+        <v>474</v>
+      </c>
+      <c r="C60" t="s">
         <v>475</v>
-      </c>
-      <c r="C60" t="s">
-        <v>476</v>
       </c>
       <c r="D60" t="s">
         <v>323</v>
       </c>
       <c r="E60" t="s">
+        <v>476</v>
+      </c>
+      <c r="F60" t="s">
         <v>477</v>
       </c>
-      <c r="F60" t="s">
+      <c r="G60" t="s">
         <v>478</v>
       </c>
-      <c r="G60" t="s">
+      <c r="H60" t="s">
         <v>479</v>
-      </c>
-      <c r="H60" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
@@ -4570,7 +4573,7 @@
         <v>81</v>
       </c>
       <c r="B61" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C61" t="s">
         <v>231</v>
@@ -4579,16 +4582,16 @@
         <v>238</v>
       </c>
       <c r="E61" t="s">
+        <v>481</v>
+      </c>
+      <c r="F61" t="s">
         <v>482</v>
       </c>
-      <c r="F61" t="s">
+      <c r="G61" t="s">
         <v>483</v>
       </c>
-      <c r="G61" t="s">
+      <c r="H61" t="s">
         <v>484</v>
-      </c>
-      <c r="H61" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
@@ -4596,7 +4599,7 @@
         <v>30</v>
       </c>
       <c r="B62" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C62" t="s">
         <v>253</v>
@@ -4605,16 +4608,16 @@
         <v>152</v>
       </c>
       <c r="E62" t="s">
+        <v>486</v>
+      </c>
+      <c r="F62" t="s">
         <v>487</v>
       </c>
-      <c r="F62" t="s">
+      <c r="G62" t="s">
         <v>488</v>
       </c>
-      <c r="G62" t="s">
+      <c r="H62" t="s">
         <v>489</v>
-      </c>
-      <c r="H62" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
@@ -4622,25 +4625,25 @@
         <v>138</v>
       </c>
       <c r="B63" t="s">
+        <v>490</v>
+      </c>
+      <c r="C63" t="s">
         <v>491</v>
-      </c>
-      <c r="C63" t="s">
-        <v>492</v>
       </c>
       <c r="D63" t="s">
         <v>159</v>
       </c>
       <c r="E63" t="s">
+        <v>492</v>
+      </c>
+      <c r="F63" t="s">
         <v>493</v>
       </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
         <v>494</v>
       </c>
-      <c r="G63" t="s">
+      <c r="H63" t="s">
         <v>495</v>
-      </c>
-      <c r="H63" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
@@ -4648,25 +4651,25 @@
         <v>35</v>
       </c>
       <c r="B64" t="s">
+        <v>496</v>
+      </c>
+      <c r="C64" t="s">
         <v>497</v>
-      </c>
-      <c r="C64" t="s">
-        <v>498</v>
       </c>
       <c r="D64" t="s">
         <v>218</v>
       </c>
       <c r="E64" t="s">
+        <v>498</v>
+      </c>
+      <c r="F64" t="s">
         <v>499</v>
       </c>
-      <c r="F64" t="s">
+      <c r="G64" t="s">
         <v>500</v>
       </c>
-      <c r="G64" t="s">
+      <c r="H64" t="s">
         <v>501</v>
-      </c>
-      <c r="H64" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
@@ -4674,25 +4677,25 @@
         <v>43</v>
       </c>
       <c r="B65" t="s">
+        <v>502</v>
+      </c>
+      <c r="C65" t="s">
         <v>503</v>
-      </c>
-      <c r="C65" t="s">
-        <v>504</v>
       </c>
       <c r="D65" t="s">
         <v>225</v>
       </c>
       <c r="E65" t="s">
+        <v>504</v>
+      </c>
+      <c r="F65" t="s">
         <v>505</v>
       </c>
-      <c r="F65" t="s">
+      <c r="G65" t="s">
         <v>506</v>
       </c>
-      <c r="G65" t="s">
+      <c r="H65" t="s">
         <v>507</v>
-      </c>
-      <c r="H65" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
@@ -4700,25 +4703,25 @@
         <v>44</v>
       </c>
       <c r="B66" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C66" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D66" t="s">
         <v>225</v>
       </c>
       <c r="E66" t="s">
+        <v>509</v>
+      </c>
+      <c r="F66" t="s">
         <v>510</v>
       </c>
-      <c r="F66" t="s">
+      <c r="G66" t="s">
         <v>511</v>
       </c>
-      <c r="G66" t="s">
+      <c r="H66" t="s">
         <v>512</v>
-      </c>
-      <c r="H66" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
@@ -4726,25 +4729,25 @@
         <v>13</v>
       </c>
       <c r="B67" t="s">
+        <v>513</v>
+      </c>
+      <c r="C67" t="s">
         <v>514</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
+        <v>405</v>
+      </c>
+      <c r="E67" t="s">
         <v>515</v>
       </c>
-      <c r="D67" t="s">
-        <v>406</v>
-      </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>516</v>
       </c>
-      <c r="F67" t="s">
+      <c r="G67" t="s">
         <v>517</v>
       </c>
-      <c r="G67" t="s">
+      <c r="H67" t="s">
         <v>518</v>
-      </c>
-      <c r="H67" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
@@ -4752,25 +4755,25 @@
         <v>48</v>
       </c>
       <c r="B68" t="s">
+        <v>519</v>
+      </c>
+      <c r="C68" t="s">
         <v>520</v>
-      </c>
-      <c r="C68" t="s">
-        <v>521</v>
       </c>
       <c r="D68" t="s">
         <v>290</v>
       </c>
       <c r="E68" t="s">
+        <v>521</v>
+      </c>
+      <c r="F68" t="s">
         <v>522</v>
       </c>
-      <c r="F68" t="s">
+      <c r="G68" t="s">
         <v>523</v>
       </c>
-      <c r="G68" t="s">
+      <c r="H68" t="s">
         <v>524</v>
-      </c>
-      <c r="H68" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
@@ -4778,25 +4781,25 @@
         <v>86</v>
       </c>
       <c r="B69" t="s">
+        <v>525</v>
+      </c>
+      <c r="C69" t="s">
         <v>526</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
+        <v>405</v>
+      </c>
+      <c r="E69" t="s">
         <v>527</v>
       </c>
-      <c r="D69" t="s">
-        <v>406</v>
-      </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>528</v>
       </c>
-      <c r="F69" t="s">
+      <c r="G69" t="s">
         <v>529</v>
       </c>
-      <c r="G69" t="s">
+      <c r="H69" t="s">
         <v>530</v>
-      </c>
-      <c r="H69" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
@@ -4804,7 +4807,7 @@
         <v>78</v>
       </c>
       <c r="B70" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C70" t="s">
         <v>296</v>
@@ -4813,16 +4816,16 @@
         <v>152</v>
       </c>
       <c r="E70" t="s">
+        <v>532</v>
+      </c>
+      <c r="F70" t="s">
         <v>533</v>
       </c>
-      <c r="F70" t="s">
+      <c r="G70" t="s">
         <v>534</v>
       </c>
-      <c r="G70" t="s">
+      <c r="H70" t="s">
         <v>535</v>
-      </c>
-      <c r="H70" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
@@ -4830,25 +4833,25 @@
         <v>140</v>
       </c>
       <c r="B71" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C71" t="s">
-        <v>237</v>
+        <v>703</v>
       </c>
       <c r="D71" t="s">
         <v>225</v>
       </c>
       <c r="E71" t="s">
+        <v>537</v>
+      </c>
+      <c r="F71" t="s">
         <v>538</v>
       </c>
-      <c r="F71" t="s">
+      <c r="G71" t="s">
         <v>539</v>
       </c>
-      <c r="G71" t="s">
+      <c r="H71" t="s">
         <v>540</v>
-      </c>
-      <c r="H71" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
@@ -4856,25 +4859,25 @@
         <v>45</v>
       </c>
       <c r="B72" t="s">
+        <v>541</v>
+      </c>
+      <c r="C72" t="s">
         <v>542</v>
-      </c>
-      <c r="C72" t="s">
-        <v>543</v>
       </c>
       <c r="D72" t="s">
         <v>218</v>
       </c>
       <c r="E72" t="s">
+        <v>543</v>
+      </c>
+      <c r="F72" t="s">
         <v>544</v>
       </c>
-      <c r="F72" t="s">
+      <c r="G72" t="s">
         <v>545</v>
       </c>
-      <c r="G72" t="s">
+      <c r="H72" t="s">
         <v>546</v>
-      </c>
-      <c r="H72" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
@@ -4882,25 +4885,25 @@
         <v>51</v>
       </c>
       <c r="B73" t="s">
+        <v>547</v>
+      </c>
+      <c r="C73" t="s">
         <v>548</v>
-      </c>
-      <c r="C73" t="s">
-        <v>549</v>
       </c>
       <c r="D73" t="s">
         <v>211</v>
       </c>
       <c r="E73" t="s">
+        <v>549</v>
+      </c>
+      <c r="F73" t="s">
         <v>550</v>
       </c>
-      <c r="F73" t="s">
+      <c r="G73" t="s">
         <v>551</v>
       </c>
-      <c r="G73" t="s">
+      <c r="H73" t="s">
         <v>552</v>
-      </c>
-      <c r="H73" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
@@ -4908,25 +4911,25 @@
         <v>135</v>
       </c>
       <c r="B74" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C74" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D74" t="s">
         <v>159</v>
       </c>
       <c r="E74" t="s">
+        <v>554</v>
+      </c>
+      <c r="F74" t="s">
         <v>555</v>
       </c>
-      <c r="F74" t="s">
+      <c r="G74" t="s">
         <v>556</v>
       </c>
-      <c r="G74" t="s">
+      <c r="H74" t="s">
         <v>557</v>
-      </c>
-      <c r="H74" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
@@ -4934,25 +4937,25 @@
         <v>56</v>
       </c>
       <c r="B75" t="s">
+        <v>558</v>
+      </c>
+      <c r="C75" t="s">
+        <v>695</v>
+      </c>
+      <c r="D75" t="s">
+        <v>405</v>
+      </c>
+      <c r="E75" t="s">
         <v>559</v>
       </c>
-      <c r="C75" t="s">
-        <v>697</v>
-      </c>
-      <c r="D75" t="s">
-        <v>406</v>
-      </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>560</v>
       </c>
-      <c r="F75" t="s">
+      <c r="G75" t="s">
         <v>561</v>
       </c>
-      <c r="G75" t="s">
+      <c r="H75" t="s">
         <v>562</v>
-      </c>
-      <c r="H75" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
@@ -4960,25 +4963,25 @@
         <v>61</v>
       </c>
       <c r="B76" t="s">
+        <v>563</v>
+      </c>
+      <c r="C76" t="s">
         <v>564</v>
-      </c>
-      <c r="C76" t="s">
-        <v>565</v>
       </c>
       <c r="D76" t="s">
         <v>218</v>
       </c>
       <c r="E76" t="s">
+        <v>565</v>
+      </c>
+      <c r="F76" t="s">
         <v>566</v>
       </c>
-      <c r="F76" t="s">
+      <c r="G76" t="s">
         <v>567</v>
       </c>
-      <c r="G76" t="s">
+      <c r="H76" t="s">
         <v>568</v>
-      </c>
-      <c r="H76" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
@@ -4986,7 +4989,7 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C77" t="s">
         <v>296</v>
@@ -4995,16 +4998,16 @@
         <v>152</v>
       </c>
       <c r="E77" t="s">
+        <v>570</v>
+      </c>
+      <c r="F77" t="s">
         <v>571</v>
       </c>
-      <c r="F77" t="s">
+      <c r="G77" t="s">
         <v>572</v>
       </c>
-      <c r="G77" t="s">
+      <c r="H77" t="s">
         <v>573</v>
-      </c>
-      <c r="H77" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
@@ -5012,25 +5015,25 @@
         <v>143</v>
       </c>
       <c r="B78" t="s">
+        <v>574</v>
+      </c>
+      <c r="C78" t="s">
         <v>575</v>
-      </c>
-      <c r="C78" t="s">
-        <v>576</v>
       </c>
       <c r="D78" t="s">
         <v>159</v>
       </c>
       <c r="E78" t="s">
+        <v>576</v>
+      </c>
+      <c r="F78" t="s">
         <v>577</v>
       </c>
-      <c r="F78" t="s">
+      <c r="G78" t="s">
         <v>578</v>
       </c>
-      <c r="G78" t="s">
+      <c r="H78" t="s">
         <v>579</v>
-      </c>
-      <c r="H78" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
@@ -5038,7 +5041,7 @@
         <v>59</v>
       </c>
       <c r="B79" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C79" t="s">
         <v>266</v>
@@ -5047,16 +5050,16 @@
         <v>159</v>
       </c>
       <c r="E79" t="s">
+        <v>581</v>
+      </c>
+      <c r="F79" t="s">
         <v>582</v>
       </c>
-      <c r="F79" t="s">
+      <c r="G79" t="s">
         <v>583</v>
       </c>
-      <c r="G79" t="s">
+      <c r="H79" t="s">
         <v>584</v>
-      </c>
-      <c r="H79" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
@@ -5064,25 +5067,25 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
+        <v>585</v>
+      </c>
+      <c r="C80" t="s">
         <v>586</v>
-      </c>
-      <c r="C80" t="s">
-        <v>587</v>
       </c>
       <c r="D80" t="s">
         <v>159</v>
       </c>
       <c r="E80" t="s">
+        <v>587</v>
+      </c>
+      <c r="F80" t="s">
         <v>588</v>
       </c>
-      <c r="F80" t="s">
+      <c r="G80" t="s">
         <v>589</v>
       </c>
-      <c r="G80" t="s">
+      <c r="H80" t="s">
         <v>590</v>
-      </c>
-      <c r="H80" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
@@ -5090,25 +5093,25 @@
         <v>141</v>
       </c>
       <c r="B81" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C81" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D81" t="s">
         <v>159</v>
       </c>
       <c r="E81" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="F81" t="s">
+        <v>592</v>
+      </c>
+      <c r="G81" t="s">
         <v>593</v>
       </c>
-      <c r="G81" t="s">
+      <c r="H81" t="s">
         <v>594</v>
-      </c>
-      <c r="H81" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
@@ -5116,25 +5119,25 @@
         <v>144</v>
       </c>
       <c r="B82" t="s">
+        <v>595</v>
+      </c>
+      <c r="C82" t="s">
+        <v>404</v>
+      </c>
+      <c r="D82" t="s">
+        <v>405</v>
+      </c>
+      <c r="E82" t="s">
         <v>596</v>
       </c>
-      <c r="C82" t="s">
-        <v>405</v>
-      </c>
-      <c r="D82" t="s">
-        <v>406</v>
-      </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
         <v>597</v>
       </c>
-      <c r="F82" t="s">
+      <c r="G82" t="s">
         <v>598</v>
       </c>
-      <c r="G82" t="s">
+      <c r="H82" t="s">
         <v>599</v>
-      </c>
-      <c r="H82" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
@@ -5142,25 +5145,25 @@
         <v>60</v>
       </c>
       <c r="B83" t="s">
+        <v>600</v>
+      </c>
+      <c r="C83" t="s">
         <v>601</v>
-      </c>
-      <c r="C83" t="s">
-        <v>602</v>
       </c>
       <c r="D83" t="s">
         <v>159</v>
       </c>
       <c r="E83" t="s">
+        <v>602</v>
+      </c>
+      <c r="F83" t="s">
         <v>603</v>
       </c>
-      <c r="F83" t="s">
+      <c r="G83" t="s">
         <v>604</v>
       </c>
-      <c r="G83" t="s">
+      <c r="H83" t="s">
         <v>605</v>
-      </c>
-      <c r="H83" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
@@ -5168,25 +5171,25 @@
         <v>66</v>
       </c>
       <c r="B84" t="s">
+        <v>606</v>
+      </c>
+      <c r="C84" t="s">
         <v>607</v>
       </c>
-      <c r="C84" t="s">
+      <c r="D84" t="s">
+        <v>405</v>
+      </c>
+      <c r="E84" t="s">
         <v>608</v>
       </c>
-      <c r="D84" t="s">
-        <v>406</v>
-      </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>609</v>
       </c>
-      <c r="F84" t="s">
+      <c r="G84" t="s">
         <v>610</v>
       </c>
-      <c r="G84" t="s">
+      <c r="H84" t="s">
         <v>611</v>
-      </c>
-      <c r="H84" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
@@ -5194,25 +5197,25 @@
         <v>34</v>
       </c>
       <c r="B85" t="s">
+        <v>612</v>
+      </c>
+      <c r="C85" t="s">
         <v>613</v>
-      </c>
-      <c r="C85" t="s">
-        <v>614</v>
       </c>
       <c r="D85" t="s">
         <v>283</v>
       </c>
       <c r="E85" t="s">
+        <v>614</v>
+      </c>
+      <c r="F85" t="s">
         <v>615</v>
       </c>
-      <c r="F85" t="s">
+      <c r="G85" t="s">
         <v>616</v>
       </c>
-      <c r="G85" t="s">
+      <c r="H85" t="s">
         <v>617</v>
-      </c>
-      <c r="H85" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
@@ -5220,25 +5223,25 @@
         <v>41</v>
       </c>
       <c r="B86" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C86" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D86" t="s">
         <v>218</v>
       </c>
       <c r="E86" t="s">
+        <v>619</v>
+      </c>
+      <c r="F86" t="s">
         <v>620</v>
       </c>
-      <c r="F86" t="s">
+      <c r="G86" t="s">
         <v>621</v>
       </c>
-      <c r="G86" t="s">
+      <c r="H86" t="s">
         <v>622</v>
-      </c>
-      <c r="H86" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
@@ -5246,25 +5249,25 @@
         <v>79</v>
       </c>
       <c r="B87" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C87" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D87" t="s">
         <v>159</v>
       </c>
       <c r="E87" t="s">
+        <v>624</v>
+      </c>
+      <c r="F87" t="s">
         <v>625</v>
       </c>
-      <c r="F87" t="s">
+      <c r="G87" t="s">
         <v>626</v>
       </c>
-      <c r="G87" t="s">
+      <c r="H87" t="s">
         <v>627</v>
-      </c>
-      <c r="H87" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
@@ -5272,7 +5275,7 @@
         <v>91</v>
       </c>
       <c r="B88" t="s">
-        <v>629</v>
+        <v>704</v>
       </c>
       <c r="C88" t="s">
         <v>231</v>
@@ -5281,16 +5284,16 @@
         <v>238</v>
       </c>
       <c r="E88" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F88" t="s">
+        <v>628</v>
+      </c>
+      <c r="G88" t="s">
+        <v>629</v>
+      </c>
+      <c r="H88" t="s">
         <v>630</v>
-      </c>
-      <c r="G88" t="s">
-        <v>631</v>
-      </c>
-      <c r="H88" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
@@ -5298,25 +5301,25 @@
         <v>118</v>
       </c>
       <c r="B89" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C89" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="D89" t="s">
         <v>152</v>
       </c>
       <c r="E89" t="s">
+        <v>633</v>
+      </c>
+      <c r="F89" t="s">
+        <v>634</v>
+      </c>
+      <c r="G89" t="s">
         <v>635</v>
       </c>
-      <c r="F89" t="s">
+      <c r="H89" t="s">
         <v>636</v>
-      </c>
-      <c r="G89" t="s">
-        <v>637</v>
-      </c>
-      <c r="H89" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
@@ -5324,25 +5327,25 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C90" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D90" t="s">
         <v>225</v>
       </c>
       <c r="E90" t="s">
+        <v>638</v>
+      </c>
+      <c r="F90" t="s">
+        <v>339</v>
+      </c>
+      <c r="G90" t="s">
+        <v>639</v>
+      </c>
+      <c r="H90" t="s">
         <v>640</v>
-      </c>
-      <c r="F90" t="s">
-        <v>340</v>
-      </c>
-      <c r="G90" t="s">
-        <v>641</v>
-      </c>
-      <c r="H90" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
@@ -5350,25 +5353,25 @@
         <v>121</v>
       </c>
       <c r="B91" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C91" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="D91" t="s">
         <v>152</v>
       </c>
       <c r="E91" t="s">
+        <v>642</v>
+      </c>
+      <c r="F91" t="s">
+        <v>643</v>
+      </c>
+      <c r="G91" t="s">
         <v>644</v>
       </c>
-      <c r="F91" t="s">
+      <c r="H91" t="s">
         <v>645</v>
-      </c>
-      <c r="G91" t="s">
-        <v>646</v>
-      </c>
-      <c r="H91" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
@@ -5376,25 +5379,25 @@
         <v>67</v>
       </c>
       <c r="B92" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C92" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D92" t="s">
         <v>218</v>
       </c>
       <c r="E92" t="s">
+        <v>646</v>
+      </c>
+      <c r="F92" t="s">
+        <v>647</v>
+      </c>
+      <c r="G92" t="s">
         <v>648</v>
       </c>
-      <c r="F92" t="s">
+      <c r="H92" t="s">
         <v>649</v>
-      </c>
-      <c r="G92" t="s">
-        <v>650</v>
-      </c>
-      <c r="H92" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
@@ -5402,25 +5405,25 @@
         <v>49</v>
       </c>
       <c r="B93" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C93" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D93" t="s">
         <v>218</v>
       </c>
       <c r="E93" t="s">
+        <v>651</v>
+      </c>
+      <c r="F93" t="s">
+        <v>461</v>
+      </c>
+      <c r="G93" t="s">
+        <v>652</v>
+      </c>
+      <c r="H93" t="s">
         <v>653</v>
-      </c>
-      <c r="F93" t="s">
-        <v>462</v>
-      </c>
-      <c r="G93" t="s">
-        <v>654</v>
-      </c>
-      <c r="H93" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
@@ -5428,25 +5431,25 @@
         <v>31</v>
       </c>
       <c r="B94" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C94" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D94" t="s">
         <v>218</v>
       </c>
       <c r="E94" t="s">
+        <v>655</v>
+      </c>
+      <c r="F94" t="s">
+        <v>656</v>
+      </c>
+      <c r="G94" t="s">
         <v>657</v>
       </c>
-      <c r="F94" t="s">
+      <c r="H94" t="s">
         <v>658</v>
-      </c>
-      <c r="G94" t="s">
-        <v>659</v>
-      </c>
-      <c r="H94" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
@@ -5454,7 +5457,7 @@
         <v>109</v>
       </c>
       <c r="B95" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C95" t="s">
         <v>182</v>
@@ -5463,16 +5466,16 @@
         <v>159</v>
       </c>
       <c r="E95" t="s">
+        <v>660</v>
+      </c>
+      <c r="F95" t="s">
+        <v>620</v>
+      </c>
+      <c r="G95" t="s">
+        <v>661</v>
+      </c>
+      <c r="H95" t="s">
         <v>662</v>
-      </c>
-      <c r="F95" t="s">
-        <v>621</v>
-      </c>
-      <c r="G95" t="s">
-        <v>663</v>
-      </c>
-      <c r="H95" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
@@ -5480,25 +5483,25 @@
         <v>71</v>
       </c>
       <c r="B96" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C96" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D96" t="s">
         <v>218</v>
       </c>
       <c r="E96" t="s">
+        <v>663</v>
+      </c>
+      <c r="F96" t="s">
+        <v>499</v>
+      </c>
+      <c r="G96" t="s">
+        <v>664</v>
+      </c>
+      <c r="H96" t="s">
         <v>665</v>
-      </c>
-      <c r="F96" t="s">
-        <v>500</v>
-      </c>
-      <c r="G96" t="s">
-        <v>666</v>
-      </c>
-      <c r="H96" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
@@ -5506,25 +5509,25 @@
         <v>128</v>
       </c>
       <c r="B97" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C97" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D97" t="s">
         <v>225</v>
       </c>
       <c r="E97" t="s">
+        <v>668</v>
+      </c>
+      <c r="F97" t="s">
+        <v>669</v>
+      </c>
+      <c r="G97" t="s">
         <v>670</v>
       </c>
-      <c r="F97" t="s">
+      <c r="H97" t="s">
         <v>671</v>
-      </c>
-      <c r="G97" t="s">
-        <v>672</v>
-      </c>
-      <c r="H97" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
@@ -5532,7 +5535,7 @@
         <v>95</v>
       </c>
       <c r="B98" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C98" t="s">
         <v>231</v>
@@ -5541,16 +5544,16 @@
         <v>238</v>
       </c>
       <c r="E98" t="s">
+        <v>673</v>
+      </c>
+      <c r="F98" t="s">
+        <v>674</v>
+      </c>
+      <c r="G98" t="s">
         <v>675</v>
       </c>
-      <c r="F98" t="s">
+      <c r="H98" t="s">
         <v>676</v>
-      </c>
-      <c r="G98" t="s">
-        <v>677</v>
-      </c>
-      <c r="H98" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
@@ -5558,25 +5561,25 @@
         <v>133</v>
       </c>
       <c r="B99" t="s">
+        <v>677</v>
+      </c>
+      <c r="C99" t="s">
+        <v>678</v>
+      </c>
+      <c r="D99" t="s">
+        <v>405</v>
+      </c>
+      <c r="E99" t="s">
         <v>679</v>
       </c>
-      <c r="C99" t="s">
+      <c r="F99" t="s">
         <v>680</v>
       </c>
-      <c r="D99" t="s">
-        <v>406</v>
-      </c>
-      <c r="E99" t="s">
+      <c r="G99" t="s">
         <v>681</v>
       </c>
-      <c r="F99" t="s">
+      <c r="H99" t="s">
         <v>682</v>
-      </c>
-      <c r="G99" t="s">
-        <v>683</v>
-      </c>
-      <c r="H99" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
@@ -5584,25 +5587,25 @@
         <v>17</v>
       </c>
       <c r="B100" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C100" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="D100" t="s">
         <v>238</v>
       </c>
       <c r="E100" t="s">
+        <v>685</v>
+      </c>
+      <c r="F100" t="s">
+        <v>686</v>
+      </c>
+      <c r="G100" t="s">
         <v>687</v>
       </c>
-      <c r="F100" t="s">
+      <c r="H100" t="s">
         <v>688</v>
-      </c>
-      <c r="G100" t="s">
-        <v>689</v>
-      </c>
-      <c r="H100" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
@@ -5610,7 +5613,7 @@
         <v>113</v>
       </c>
       <c r="B101" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C101" t="s">
         <v>182</v>
@@ -5619,16 +5622,16 @@
         <v>152</v>
       </c>
       <c r="E101" t="s">
+        <v>690</v>
+      </c>
+      <c r="F101" t="s">
+        <v>691</v>
+      </c>
+      <c r="G101" t="s">
         <v>692</v>
       </c>
-      <c r="F101" t="s">
+      <c r="H101" t="s">
         <v>693</v>
-      </c>
-      <c r="G101" t="s">
-        <v>694</v>
-      </c>
-      <c r="H101" t="s">
-        <v>695</v>
       </c>
     </row>
   </sheetData>
@@ -5657,7 +5660,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="9"/>
@@ -5674,7 +5677,7 @@
       <c r="M1" s="9"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="9"/>
@@ -5691,7 +5694,7 @@
       <c r="M2" s="9"/>
     </row>
     <row r="5" spans="1:13" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="9"/>
@@ -5708,7 +5711,7 @@
       <c r="M5" s="9"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="9"/>
@@ -5728,19 +5731,19 @@
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="11" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="11" t="s">
         <v>6</v>
       </c>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
-      <c r="J7" s="10" t="s">
+      <c r="J7" s="11" t="s">
         <v>7</v>
       </c>
       <c r="K7" s="9"/>
@@ -5913,7 +5916,7 @@
       </c>
       <c r="H11" s="6" t="str">
         <f>IFERROR(VLOOKUP($F11,Data!$A:$D,2,FALSE),"")</f>
-        <v>Building a Machine Learning Model to Track Many C. elegans Worms Simultaneously and Resolve Collisions</v>
+        <v>Building a Machine Learning Model to Resolve C. elegans Collisions</v>
       </c>
       <c r="I11" s="6" t="str">
         <f>IFERROR(VLOOKUP($F11,Data!$A:$D,3,FALSE),"")</f>
@@ -6086,7 +6089,7 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="10" t="s">
         <v>36</v>
       </c>
       <c r="B15" s="9"/>
@@ -6103,7 +6106,7 @@
       <c r="M15" s="9"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="12" t="s">
         <v>37</v>
       </c>
       <c r="B16" s="9"/>
@@ -6123,19 +6126,19 @@
       <c r="A17" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="11" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="11" t="s">
         <v>6</v>
       </c>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
-      <c r="J17" s="10" t="s">
+      <c r="J17" s="11" t="s">
         <v>7</v>
       </c>
       <c r="K17" s="9"/>
@@ -6481,7 +6484,7 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="10" t="s">
         <v>62</v>
       </c>
       <c r="B25" s="9"/>
@@ -6498,7 +6501,7 @@
       <c r="M25" s="9"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="12" t="s">
         <v>63</v>
       </c>
       <c r="B26" s="9"/>
@@ -6518,19 +6521,19 @@
       <c r="A27" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="11" t="s">
         <v>5</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
-      <c r="F27" s="10" t="s">
+      <c r="F27" s="11" t="s">
         <v>6</v>
       </c>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
-      <c r="J27" s="10" t="s">
+      <c r="J27" s="11" t="s">
         <v>7</v>
       </c>
       <c r="K27" s="9"/>
@@ -6876,7 +6879,7 @@
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A35" s="12" t="s">
+      <c r="A35" s="10" t="s">
         <v>88</v>
       </c>
       <c r="B35" s="9"/>
@@ -6893,7 +6896,7 @@
       <c r="M35" s="9"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="12" t="s">
         <v>89</v>
       </c>
       <c r="B36" s="9"/>
@@ -6913,19 +6916,19 @@
       <c r="A37" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="11" t="s">
         <v>5</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
-      <c r="F37" s="10" t="s">
+      <c r="F37" s="11" t="s">
         <v>6</v>
       </c>
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
-      <c r="J37" s="10" t="s">
+      <c r="J37" s="11" t="s">
         <v>7</v>
       </c>
       <c r="K37" s="9"/>
@@ -6983,7 +6986,7 @@
       </c>
       <c r="D39" s="6" t="str">
         <f>IFERROR(VLOOKUP($B39,Data!$A:$D,2,FALSE),"")</f>
-        <v>Reachability-Based Path Planning Across Autonomous Ocean Vehicles Platforms</v>
+        <v>Reachability-Based Path Planning Across Autonomous Ocean Vehicle Platforms</v>
       </c>
       <c r="E39" s="6" t="str">
         <f>IFERROR(VLOOKUP($B39,Data!$A:$D,3,FALSE),"")</f>
@@ -7271,7 +7274,7 @@
       </c>
     </row>
     <row r="47" spans="1:13" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="14" t="s">
+      <c r="A47" s="8" t="s">
         <v>114</v>
       </c>
       <c r="B47" s="9"/>
@@ -7288,7 +7291,7 @@
       <c r="M47" s="9"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A48" s="11" t="s">
+      <c r="A48" s="12" t="s">
         <v>115</v>
       </c>
       <c r="B48" s="9"/>
@@ -7308,19 +7311,19 @@
       <c r="A49" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B49" s="11" t="s">
         <v>5</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
-      <c r="F49" s="10" t="s">
+      <c r="F49" s="11" t="s">
         <v>6</v>
       </c>
       <c r="G49" s="9"/>
       <c r="H49" s="9"/>
       <c r="I49" s="9"/>
-      <c r="J49" s="10" t="s">
+      <c r="J49" s="11" t="s">
         <v>7</v>
       </c>
       <c r="K49" s="9"/>
@@ -7666,7 +7669,7 @@
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A57" s="12" t="s">
+      <c r="A57" s="10" t="s">
         <v>36</v>
       </c>
       <c r="B57" s="9"/>
@@ -7683,7 +7686,7 @@
       <c r="M57" s="9"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A58" s="11" t="s">
+      <c r="A58" s="12" t="s">
         <v>134</v>
       </c>
       <c r="B58" s="9"/>
@@ -7703,19 +7706,19 @@
       <c r="A59" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="B59" s="11" t="s">
         <v>5</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
-      <c r="F59" s="10" t="s">
+      <c r="F59" s="11" t="s">
         <v>6</v>
       </c>
       <c r="G59" s="9"/>
       <c r="H59" s="9"/>
       <c r="I59" s="9"/>
-      <c r="J59" s="10" t="s">
+      <c r="J59" s="11" t="s">
         <v>7</v>
       </c>
       <c r="K59" s="9"/>
@@ -7857,7 +7860,7 @@
       </c>
       <c r="M62" s="6" t="str">
         <f>IFERROR(VLOOKUP($J62,Data!$A:$D,3,FALSE),"")</f>
-        <v>Prof. Peter Lu, Oreoluwa Alao</v>
+        <v>Prof. Peter Lu, Mateusz Zubrzycki</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
@@ -7958,22 +7961,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A5:M5"/>
-    <mergeCell ref="A35:M35"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="F49:I49"/>
-    <mergeCell ref="J17:M17"/>
-    <mergeCell ref="A58:M58"/>
-    <mergeCell ref="A48:M48"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="J59:M59"/>
-    <mergeCell ref="A36:M36"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="B49:E49"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="F7:I7"/>
     <mergeCell ref="A6:M6"/>
@@ -7990,6 +7977,22 @@
     <mergeCell ref="A57:M57"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A47:M47"/>
+    <mergeCell ref="A58:M58"/>
+    <mergeCell ref="A48:M48"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="J59:M59"/>
+    <mergeCell ref="A36:M36"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A35:M35"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="F49:I49"/>
+    <mergeCell ref="J17:M17"/>
   </mergeCells>
   <conditionalFormatting sqref="C4:C71">
     <cfRule type="cellIs" dxfId="32" priority="13" operator="equal">

--- a/RSI_2026_Schedule.xlsx
+++ b/RSI_2026_Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/evanlim/Documents/rsi-symposium/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4635FA73-AEBF-1E42-933D-B32D9927B414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAAEAD33-A5A2-D34E-983B-7B69F5608DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1431,9 +1431,6 @@
     <t>lucichen</t>
   </si>
   <si>
-    <t>Yeast-Based High-Throughput Screening for _Plasmodium falciparum_ PDEα Inhibitor Discovery</t>
-  </si>
-  <si>
     <t>LOOK</t>
   </si>
   <si>
@@ -1596,9 +1593,6 @@
     <t>mira_c36</t>
   </si>
   <si>
-    <t>Patient-Specific Modeling of Brain and Cerebrospinal Fluid Response to Rapid Head Acceleration in Chiari I Malformation</t>
-  </si>
-  <si>
     <t>Prof. Francis Loth and Hannah Higgins</t>
   </si>
   <si>
@@ -2155,6 +2149,12 @@
   </si>
   <si>
     <t>Building a Machine Learning Model to Resolve C. elegans Collisions</t>
+  </si>
+  <si>
+    <t>Patient-Specific Modeling of Cerebrospinal Fluid Flow in Chiari I Malformation</t>
+  </si>
+  <si>
+    <t>A Fission Yeast High-Throughput Screen Identifies Candidate Small-Molecule Inhibitors of Plasmodium falciparum PDEα</t>
   </si>
 </sst>
 </file>
@@ -2312,23 +2312,23 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3169,7 +3169,7 @@
         <v>93</v>
       </c>
       <c r="B7" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C7" t="s">
         <v>182</v>
@@ -3458,7 +3458,7 @@
         <v>247</v>
       </c>
       <c r="C18" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D18" t="s">
         <v>225</v>
@@ -3507,7 +3507,7 @@
         <v>73</v>
       </c>
       <c r="B20" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C20" t="s">
         <v>231</v>
@@ -3533,7 +3533,7 @@
         <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C21" t="s">
         <v>261</v>
@@ -3559,7 +3559,7 @@
         <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C22" t="s">
         <v>266</v>
@@ -3871,7 +3871,7 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C34" t="s">
         <v>177</v>
@@ -3897,7 +3897,7 @@
         <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C35" t="s">
         <v>171</v>
@@ -4495,7 +4495,7 @@
         <v>120</v>
       </c>
       <c r="B58" t="s">
-        <v>464</v>
+        <v>705</v>
       </c>
       <c r="C58" t="s">
         <v>158</v>
@@ -4504,16 +4504,16 @@
         <v>159</v>
       </c>
       <c r="E58" t="s">
+        <v>464</v>
+      </c>
+      <c r="F58" t="s">
         <v>465</v>
       </c>
-      <c r="F58" t="s">
+      <c r="G58" t="s">
         <v>466</v>
       </c>
-      <c r="G58" t="s">
+      <c r="H58" t="s">
         <v>467</v>
-      </c>
-      <c r="H58" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
@@ -4521,7 +4521,7 @@
         <v>14</v>
       </c>
       <c r="B59" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C59" t="s">
         <v>171</v>
@@ -4530,16 +4530,16 @@
         <v>159</v>
       </c>
       <c r="E59" t="s">
+        <v>469</v>
+      </c>
+      <c r="F59" t="s">
         <v>470</v>
       </c>
-      <c r="F59" t="s">
+      <c r="G59" t="s">
         <v>471</v>
       </c>
-      <c r="G59" t="s">
+      <c r="H59" t="s">
         <v>472</v>
-      </c>
-      <c r="H59" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
@@ -4547,25 +4547,25 @@
         <v>92</v>
       </c>
       <c r="B60" t="s">
+        <v>473</v>
+      </c>
+      <c r="C60" t="s">
         <v>474</v>
-      </c>
-      <c r="C60" t="s">
-        <v>475</v>
       </c>
       <c r="D60" t="s">
         <v>323</v>
       </c>
       <c r="E60" t="s">
+        <v>475</v>
+      </c>
+      <c r="F60" t="s">
         <v>476</v>
       </c>
-      <c r="F60" t="s">
+      <c r="G60" t="s">
         <v>477</v>
       </c>
-      <c r="G60" t="s">
+      <c r="H60" t="s">
         <v>478</v>
-      </c>
-      <c r="H60" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
@@ -4573,7 +4573,7 @@
         <v>81</v>
       </c>
       <c r="B61" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C61" t="s">
         <v>231</v>
@@ -4582,16 +4582,16 @@
         <v>238</v>
       </c>
       <c r="E61" t="s">
+        <v>480</v>
+      </c>
+      <c r="F61" t="s">
         <v>481</v>
       </c>
-      <c r="F61" t="s">
+      <c r="G61" t="s">
         <v>482</v>
       </c>
-      <c r="G61" t="s">
+      <c r="H61" t="s">
         <v>483</v>
-      </c>
-      <c r="H61" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
@@ -4599,7 +4599,7 @@
         <v>30</v>
       </c>
       <c r="B62" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C62" t="s">
         <v>253</v>
@@ -4608,16 +4608,16 @@
         <v>152</v>
       </c>
       <c r="E62" t="s">
+        <v>485</v>
+      </c>
+      <c r="F62" t="s">
         <v>486</v>
       </c>
-      <c r="F62" t="s">
+      <c r="G62" t="s">
         <v>487</v>
       </c>
-      <c r="G62" t="s">
+      <c r="H62" t="s">
         <v>488</v>
-      </c>
-      <c r="H62" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
@@ -4625,25 +4625,25 @@
         <v>138</v>
       </c>
       <c r="B63" t="s">
+        <v>489</v>
+      </c>
+      <c r="C63" t="s">
         <v>490</v>
-      </c>
-      <c r="C63" t="s">
-        <v>491</v>
       </c>
       <c r="D63" t="s">
         <v>159</v>
       </c>
       <c r="E63" t="s">
+        <v>491</v>
+      </c>
+      <c r="F63" t="s">
         <v>492</v>
       </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
         <v>493</v>
       </c>
-      <c r="G63" t="s">
+      <c r="H63" t="s">
         <v>494</v>
-      </c>
-      <c r="H63" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
@@ -4651,25 +4651,25 @@
         <v>35</v>
       </c>
       <c r="B64" t="s">
+        <v>495</v>
+      </c>
+      <c r="C64" t="s">
         <v>496</v>
-      </c>
-      <c r="C64" t="s">
-        <v>497</v>
       </c>
       <c r="D64" t="s">
         <v>218</v>
       </c>
       <c r="E64" t="s">
+        <v>497</v>
+      </c>
+      <c r="F64" t="s">
         <v>498</v>
       </c>
-      <c r="F64" t="s">
+      <c r="G64" t="s">
         <v>499</v>
       </c>
-      <c r="G64" t="s">
+      <c r="H64" t="s">
         <v>500</v>
-      </c>
-      <c r="H64" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
@@ -4677,25 +4677,25 @@
         <v>43</v>
       </c>
       <c r="B65" t="s">
+        <v>501</v>
+      </c>
+      <c r="C65" t="s">
         <v>502</v>
-      </c>
-      <c r="C65" t="s">
-        <v>503</v>
       </c>
       <c r="D65" t="s">
         <v>225</v>
       </c>
       <c r="E65" t="s">
+        <v>503</v>
+      </c>
+      <c r="F65" t="s">
         <v>504</v>
       </c>
-      <c r="F65" t="s">
+      <c r="G65" t="s">
         <v>505</v>
       </c>
-      <c r="G65" t="s">
+      <c r="H65" t="s">
         <v>506</v>
-      </c>
-      <c r="H65" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
@@ -4703,7 +4703,7 @@
         <v>44</v>
       </c>
       <c r="B66" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C66" t="s">
         <v>447</v>
@@ -4712,16 +4712,16 @@
         <v>225</v>
       </c>
       <c r="E66" t="s">
+        <v>508</v>
+      </c>
+      <c r="F66" t="s">
         <v>509</v>
       </c>
-      <c r="F66" t="s">
+      <c r="G66" t="s">
         <v>510</v>
       </c>
-      <c r="G66" t="s">
+      <c r="H66" t="s">
         <v>511</v>
-      </c>
-      <c r="H66" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
@@ -4729,25 +4729,25 @@
         <v>13</v>
       </c>
       <c r="B67" t="s">
+        <v>512</v>
+      </c>
+      <c r="C67" t="s">
         <v>513</v>
-      </c>
-      <c r="C67" t="s">
-        <v>514</v>
       </c>
       <c r="D67" t="s">
         <v>405</v>
       </c>
       <c r="E67" t="s">
+        <v>514</v>
+      </c>
+      <c r="F67" t="s">
         <v>515</v>
       </c>
-      <c r="F67" t="s">
+      <c r="G67" t="s">
         <v>516</v>
       </c>
-      <c r="G67" t="s">
+      <c r="H67" t="s">
         <v>517</v>
-      </c>
-      <c r="H67" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
@@ -4755,25 +4755,25 @@
         <v>48</v>
       </c>
       <c r="B68" t="s">
-        <v>519</v>
+        <v>704</v>
       </c>
       <c r="C68" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D68" t="s">
         <v>290</v>
       </c>
       <c r="E68" t="s">
+        <v>519</v>
+      </c>
+      <c r="F68" t="s">
+        <v>520</v>
+      </c>
+      <c r="G68" t="s">
         <v>521</v>
       </c>
-      <c r="F68" t="s">
+      <c r="H68" t="s">
         <v>522</v>
-      </c>
-      <c r="G68" t="s">
-        <v>523</v>
-      </c>
-      <c r="H68" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
@@ -4781,25 +4781,25 @@
         <v>86</v>
       </c>
       <c r="B69" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C69" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D69" t="s">
         <v>405</v>
       </c>
       <c r="E69" t="s">
+        <v>525</v>
+      </c>
+      <c r="F69" t="s">
+        <v>526</v>
+      </c>
+      <c r="G69" t="s">
         <v>527</v>
       </c>
-      <c r="F69" t="s">
+      <c r="H69" t="s">
         <v>528</v>
-      </c>
-      <c r="G69" t="s">
-        <v>529</v>
-      </c>
-      <c r="H69" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
@@ -4807,7 +4807,7 @@
         <v>78</v>
       </c>
       <c r="B70" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C70" t="s">
         <v>296</v>
@@ -4816,16 +4816,16 @@
         <v>152</v>
       </c>
       <c r="E70" t="s">
+        <v>530</v>
+      </c>
+      <c r="F70" t="s">
+        <v>531</v>
+      </c>
+      <c r="G70" t="s">
         <v>532</v>
       </c>
-      <c r="F70" t="s">
+      <c r="H70" t="s">
         <v>533</v>
-      </c>
-      <c r="G70" t="s">
-        <v>534</v>
-      </c>
-      <c r="H70" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
@@ -4833,25 +4833,25 @@
         <v>140</v>
       </c>
       <c r="B71" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C71" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="D71" t="s">
         <v>225</v>
       </c>
       <c r="E71" t="s">
+        <v>535</v>
+      </c>
+      <c r="F71" t="s">
+        <v>536</v>
+      </c>
+      <c r="G71" t="s">
         <v>537</v>
       </c>
-      <c r="F71" t="s">
+      <c r="H71" t="s">
         <v>538</v>
-      </c>
-      <c r="G71" t="s">
-        <v>539</v>
-      </c>
-      <c r="H71" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
@@ -4859,25 +4859,25 @@
         <v>45</v>
       </c>
       <c r="B72" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C72" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="D72" t="s">
         <v>218</v>
       </c>
       <c r="E72" t="s">
+        <v>541</v>
+      </c>
+      <c r="F72" t="s">
+        <v>542</v>
+      </c>
+      <c r="G72" t="s">
         <v>543</v>
       </c>
-      <c r="F72" t="s">
+      <c r="H72" t="s">
         <v>544</v>
-      </c>
-      <c r="G72" t="s">
-        <v>545</v>
-      </c>
-      <c r="H72" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
@@ -4885,25 +4885,25 @@
         <v>51</v>
       </c>
       <c r="B73" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C73" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D73" t="s">
         <v>211</v>
       </c>
       <c r="E73" t="s">
+        <v>547</v>
+      </c>
+      <c r="F73" t="s">
+        <v>548</v>
+      </c>
+      <c r="G73" t="s">
         <v>549</v>
       </c>
-      <c r="F73" t="s">
+      <c r="H73" t="s">
         <v>550</v>
-      </c>
-      <c r="G73" t="s">
-        <v>551</v>
-      </c>
-      <c r="H73" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
@@ -4911,25 +4911,25 @@
         <v>135</v>
       </c>
       <c r="B74" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C74" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="D74" t="s">
         <v>159</v>
       </c>
       <c r="E74" t="s">
+        <v>552</v>
+      </c>
+      <c r="F74" t="s">
+        <v>553</v>
+      </c>
+      <c r="G74" t="s">
         <v>554</v>
       </c>
-      <c r="F74" t="s">
+      <c r="H74" t="s">
         <v>555</v>
-      </c>
-      <c r="G74" t="s">
-        <v>556</v>
-      </c>
-      <c r="H74" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
@@ -4937,25 +4937,25 @@
         <v>56</v>
       </c>
       <c r="B75" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C75" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="D75" t="s">
         <v>405</v>
       </c>
       <c r="E75" t="s">
+        <v>557</v>
+      </c>
+      <c r="F75" t="s">
+        <v>558</v>
+      </c>
+      <c r="G75" t="s">
         <v>559</v>
       </c>
-      <c r="F75" t="s">
+      <c r="H75" t="s">
         <v>560</v>
-      </c>
-      <c r="G75" t="s">
-        <v>561</v>
-      </c>
-      <c r="H75" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
@@ -4963,25 +4963,25 @@
         <v>61</v>
       </c>
       <c r="B76" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C76" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D76" t="s">
         <v>218</v>
       </c>
       <c r="E76" t="s">
+        <v>563</v>
+      </c>
+      <c r="F76" t="s">
+        <v>564</v>
+      </c>
+      <c r="G76" t="s">
         <v>565</v>
       </c>
-      <c r="F76" t="s">
+      <c r="H76" t="s">
         <v>566</v>
-      </c>
-      <c r="G76" t="s">
-        <v>567</v>
-      </c>
-      <c r="H76" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
@@ -4989,7 +4989,7 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C77" t="s">
         <v>296</v>
@@ -4998,16 +4998,16 @@
         <v>152</v>
       </c>
       <c r="E77" t="s">
+        <v>568</v>
+      </c>
+      <c r="F77" t="s">
+        <v>569</v>
+      </c>
+      <c r="G77" t="s">
         <v>570</v>
       </c>
-      <c r="F77" t="s">
+      <c r="H77" t="s">
         <v>571</v>
-      </c>
-      <c r="G77" t="s">
-        <v>572</v>
-      </c>
-      <c r="H77" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
@@ -5015,25 +5015,25 @@
         <v>143</v>
       </c>
       <c r="B78" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C78" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="D78" t="s">
         <v>159</v>
       </c>
       <c r="E78" t="s">
+        <v>574</v>
+      </c>
+      <c r="F78" t="s">
+        <v>575</v>
+      </c>
+      <c r="G78" t="s">
         <v>576</v>
       </c>
-      <c r="F78" t="s">
+      <c r="H78" t="s">
         <v>577</v>
-      </c>
-      <c r="G78" t="s">
-        <v>578</v>
-      </c>
-      <c r="H78" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
@@ -5041,7 +5041,7 @@
         <v>59</v>
       </c>
       <c r="B79" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C79" t="s">
         <v>266</v>
@@ -5050,16 +5050,16 @@
         <v>159</v>
       </c>
       <c r="E79" t="s">
+        <v>579</v>
+      </c>
+      <c r="F79" t="s">
+        <v>580</v>
+      </c>
+      <c r="G79" t="s">
         <v>581</v>
       </c>
-      <c r="F79" t="s">
+      <c r="H79" t="s">
         <v>582</v>
-      </c>
-      <c r="G79" t="s">
-        <v>583</v>
-      </c>
-      <c r="H79" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
@@ -5067,25 +5067,25 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C80" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D80" t="s">
         <v>159</v>
       </c>
       <c r="E80" t="s">
+        <v>585</v>
+      </c>
+      <c r="F80" t="s">
+        <v>586</v>
+      </c>
+      <c r="G80" t="s">
         <v>587</v>
       </c>
-      <c r="F80" t="s">
+      <c r="H80" t="s">
         <v>588</v>
-      </c>
-      <c r="G80" t="s">
-        <v>589</v>
-      </c>
-      <c r="H80" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
@@ -5093,25 +5093,25 @@
         <v>141</v>
       </c>
       <c r="B81" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C81" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D81" t="s">
         <v>159</v>
       </c>
       <c r="E81" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="F81" t="s">
+        <v>590</v>
+      </c>
+      <c r="G81" t="s">
+        <v>591</v>
+      </c>
+      <c r="H81" t="s">
         <v>592</v>
-      </c>
-      <c r="G81" t="s">
-        <v>593</v>
-      </c>
-      <c r="H81" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
@@ -5119,7 +5119,7 @@
         <v>144</v>
       </c>
       <c r="B82" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C82" t="s">
         <v>404</v>
@@ -5128,16 +5128,16 @@
         <v>405</v>
       </c>
       <c r="E82" t="s">
+        <v>594</v>
+      </c>
+      <c r="F82" t="s">
+        <v>595</v>
+      </c>
+      <c r="G82" t="s">
         <v>596</v>
       </c>
-      <c r="F82" t="s">
+      <c r="H82" t="s">
         <v>597</v>
-      </c>
-      <c r="G82" t="s">
-        <v>598</v>
-      </c>
-      <c r="H82" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
@@ -5145,25 +5145,25 @@
         <v>60</v>
       </c>
       <c r="B83" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C83" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="D83" t="s">
         <v>159</v>
       </c>
       <c r="E83" t="s">
+        <v>600</v>
+      </c>
+      <c r="F83" t="s">
+        <v>601</v>
+      </c>
+      <c r="G83" t="s">
         <v>602</v>
       </c>
-      <c r="F83" t="s">
+      <c r="H83" t="s">
         <v>603</v>
-      </c>
-      <c r="G83" t="s">
-        <v>604</v>
-      </c>
-      <c r="H83" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
@@ -5171,25 +5171,25 @@
         <v>66</v>
       </c>
       <c r="B84" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C84" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="D84" t="s">
         <v>405</v>
       </c>
       <c r="E84" t="s">
+        <v>606</v>
+      </c>
+      <c r="F84" t="s">
+        <v>607</v>
+      </c>
+      <c r="G84" t="s">
         <v>608</v>
       </c>
-      <c r="F84" t="s">
+      <c r="H84" t="s">
         <v>609</v>
-      </c>
-      <c r="G84" t="s">
-        <v>610</v>
-      </c>
-      <c r="H84" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
@@ -5197,25 +5197,25 @@
         <v>34</v>
       </c>
       <c r="B85" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C85" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D85" t="s">
         <v>283</v>
       </c>
       <c r="E85" t="s">
+        <v>612</v>
+      </c>
+      <c r="F85" t="s">
+        <v>613</v>
+      </c>
+      <c r="G85" t="s">
         <v>614</v>
       </c>
-      <c r="F85" t="s">
+      <c r="H85" t="s">
         <v>615</v>
-      </c>
-      <c r="G85" t="s">
-        <v>616</v>
-      </c>
-      <c r="H85" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
@@ -5223,25 +5223,25 @@
         <v>41</v>
       </c>
       <c r="B86" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C86" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D86" t="s">
         <v>218</v>
       </c>
       <c r="E86" t="s">
+        <v>617</v>
+      </c>
+      <c r="F86" t="s">
+        <v>618</v>
+      </c>
+      <c r="G86" t="s">
         <v>619</v>
       </c>
-      <c r="F86" t="s">
+      <c r="H86" t="s">
         <v>620</v>
-      </c>
-      <c r="G86" t="s">
-        <v>621</v>
-      </c>
-      <c r="H86" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
@@ -5249,7 +5249,7 @@
         <v>79</v>
       </c>
       <c r="B87" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C87" t="s">
         <v>343</v>
@@ -5258,16 +5258,16 @@
         <v>159</v>
       </c>
       <c r="E87" t="s">
+        <v>622</v>
+      </c>
+      <c r="F87" t="s">
+        <v>623</v>
+      </c>
+      <c r="G87" t="s">
         <v>624</v>
       </c>
-      <c r="F87" t="s">
+      <c r="H87" t="s">
         <v>625</v>
-      </c>
-      <c r="G87" t="s">
-        <v>626</v>
-      </c>
-      <c r="H87" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
@@ -5275,7 +5275,7 @@
         <v>91</v>
       </c>
       <c r="B88" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C88" t="s">
         <v>231</v>
@@ -5284,16 +5284,16 @@
         <v>238</v>
       </c>
       <c r="E88" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="F88" t="s">
+        <v>626</v>
+      </c>
+      <c r="G88" t="s">
+        <v>627</v>
+      </c>
+      <c r="H88" t="s">
         <v>628</v>
-      </c>
-      <c r="G88" t="s">
-        <v>629</v>
-      </c>
-      <c r="H88" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
@@ -5301,25 +5301,25 @@
         <v>118</v>
       </c>
       <c r="B89" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C89" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D89" t="s">
         <v>152</v>
       </c>
       <c r="E89" t="s">
+        <v>631</v>
+      </c>
+      <c r="F89" t="s">
+        <v>632</v>
+      </c>
+      <c r="G89" t="s">
         <v>633</v>
       </c>
-      <c r="F89" t="s">
+      <c r="H89" t="s">
         <v>634</v>
-      </c>
-      <c r="G89" t="s">
-        <v>635</v>
-      </c>
-      <c r="H89" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
@@ -5327,25 +5327,25 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C90" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D90" t="s">
         <v>225</v>
       </c>
       <c r="E90" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="F90" t="s">
         <v>339</v>
       </c>
       <c r="G90" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="H90" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
@@ -5353,25 +5353,25 @@
         <v>121</v>
       </c>
       <c r="B91" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C91" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D91" t="s">
         <v>152</v>
       </c>
       <c r="E91" t="s">
+        <v>640</v>
+      </c>
+      <c r="F91" t="s">
+        <v>641</v>
+      </c>
+      <c r="G91" t="s">
         <v>642</v>
       </c>
-      <c r="F91" t="s">
+      <c r="H91" t="s">
         <v>643</v>
-      </c>
-      <c r="G91" t="s">
-        <v>644</v>
-      </c>
-      <c r="H91" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
@@ -5379,25 +5379,25 @@
         <v>67</v>
       </c>
       <c r="B92" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C92" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D92" t="s">
         <v>218</v>
       </c>
       <c r="E92" t="s">
+        <v>644</v>
+      </c>
+      <c r="F92" t="s">
+        <v>645</v>
+      </c>
+      <c r="G92" t="s">
         <v>646</v>
       </c>
-      <c r="F92" t="s">
+      <c r="H92" t="s">
         <v>647</v>
-      </c>
-      <c r="G92" t="s">
-        <v>648</v>
-      </c>
-      <c r="H92" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
@@ -5405,25 +5405,25 @@
         <v>49</v>
       </c>
       <c r="B93" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C93" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="D93" t="s">
         <v>218</v>
       </c>
       <c r="E93" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="F93" t="s">
         <v>461</v>
       </c>
       <c r="G93" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="H93" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
@@ -5431,7 +5431,7 @@
         <v>31</v>
       </c>
       <c r="B94" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C94" t="s">
         <v>442</v>
@@ -5440,16 +5440,16 @@
         <v>218</v>
       </c>
       <c r="E94" t="s">
+        <v>653</v>
+      </c>
+      <c r="F94" t="s">
+        <v>654</v>
+      </c>
+      <c r="G94" t="s">
         <v>655</v>
       </c>
-      <c r="F94" t="s">
+      <c r="H94" t="s">
         <v>656</v>
-      </c>
-      <c r="G94" t="s">
-        <v>657</v>
-      </c>
-      <c r="H94" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
@@ -5457,7 +5457,7 @@
         <v>109</v>
       </c>
       <c r="B95" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C95" t="s">
         <v>182</v>
@@ -5466,16 +5466,16 @@
         <v>159</v>
       </c>
       <c r="E95" t="s">
+        <v>658</v>
+      </c>
+      <c r="F95" t="s">
+        <v>618</v>
+      </c>
+      <c r="G95" t="s">
+        <v>659</v>
+      </c>
+      <c r="H95" t="s">
         <v>660</v>
-      </c>
-      <c r="F95" t="s">
-        <v>620</v>
-      </c>
-      <c r="G95" t="s">
-        <v>661</v>
-      </c>
-      <c r="H95" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
@@ -5483,25 +5483,25 @@
         <v>71</v>
       </c>
       <c r="B96" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C96" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D96" t="s">
         <v>218</v>
       </c>
       <c r="E96" t="s">
+        <v>661</v>
+      </c>
+      <c r="F96" t="s">
+        <v>498</v>
+      </c>
+      <c r="G96" t="s">
+        <v>662</v>
+      </c>
+      <c r="H96" t="s">
         <v>663</v>
-      </c>
-      <c r="F96" t="s">
-        <v>499</v>
-      </c>
-      <c r="G96" t="s">
-        <v>664</v>
-      </c>
-      <c r="H96" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
@@ -5509,25 +5509,25 @@
         <v>128</v>
       </c>
       <c r="B97" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C97" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D97" t="s">
         <v>225</v>
       </c>
       <c r="E97" t="s">
+        <v>666</v>
+      </c>
+      <c r="F97" t="s">
+        <v>667</v>
+      </c>
+      <c r="G97" t="s">
         <v>668</v>
       </c>
-      <c r="F97" t="s">
+      <c r="H97" t="s">
         <v>669</v>
-      </c>
-      <c r="G97" t="s">
-        <v>670</v>
-      </c>
-      <c r="H97" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
@@ -5535,7 +5535,7 @@
         <v>95</v>
       </c>
       <c r="B98" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C98" t="s">
         <v>231</v>
@@ -5544,16 +5544,16 @@
         <v>238</v>
       </c>
       <c r="E98" t="s">
+        <v>671</v>
+      </c>
+      <c r="F98" t="s">
+        <v>672</v>
+      </c>
+      <c r="G98" t="s">
         <v>673</v>
       </c>
-      <c r="F98" t="s">
+      <c r="H98" t="s">
         <v>674</v>
-      </c>
-      <c r="G98" t="s">
-        <v>675</v>
-      </c>
-      <c r="H98" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
@@ -5561,25 +5561,25 @@
         <v>133</v>
       </c>
       <c r="B99" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C99" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D99" t="s">
         <v>405</v>
       </c>
       <c r="E99" t="s">
+        <v>677</v>
+      </c>
+      <c r="F99" t="s">
+        <v>678</v>
+      </c>
+      <c r="G99" t="s">
         <v>679</v>
       </c>
-      <c r="F99" t="s">
+      <c r="H99" t="s">
         <v>680</v>
-      </c>
-      <c r="G99" t="s">
-        <v>681</v>
-      </c>
-      <c r="H99" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
@@ -5587,25 +5587,25 @@
         <v>17</v>
       </c>
       <c r="B100" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C100" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D100" t="s">
         <v>238</v>
       </c>
       <c r="E100" t="s">
+        <v>683</v>
+      </c>
+      <c r="F100" t="s">
+        <v>684</v>
+      </c>
+      <c r="G100" t="s">
         <v>685</v>
       </c>
-      <c r="F100" t="s">
+      <c r="H100" t="s">
         <v>686</v>
-      </c>
-      <c r="G100" t="s">
-        <v>687</v>
-      </c>
-      <c r="H100" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
@@ -5613,7 +5613,7 @@
         <v>113</v>
       </c>
       <c r="B101" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C101" t="s">
         <v>182</v>
@@ -5622,16 +5622,16 @@
         <v>152</v>
       </c>
       <c r="E101" t="s">
+        <v>688</v>
+      </c>
+      <c r="F101" t="s">
+        <v>689</v>
+      </c>
+      <c r="G101" t="s">
         <v>690</v>
       </c>
-      <c r="F101" t="s">
+      <c r="H101" t="s">
         <v>691</v>
-      </c>
-      <c r="G101" t="s">
-        <v>692</v>
-      </c>
-      <c r="H101" t="s">
-        <v>693</v>
       </c>
     </row>
   </sheetData>
@@ -5660,7 +5660,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="9"/>
@@ -5677,7 +5677,7 @@
       <c r="M1" s="9"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="13" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="9"/>
@@ -5694,7 +5694,7 @@
       <c r="M2" s="9"/>
     </row>
     <row r="5" spans="1:13" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="14" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="9"/>
@@ -5711,7 +5711,7 @@
       <c r="M5" s="9"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="9"/>
@@ -5731,19 +5731,19 @@
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="10" t="s">
         <v>6</v>
       </c>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="10" t="s">
         <v>7</v>
       </c>
       <c r="K7" s="9"/>
@@ -6089,7 +6089,7 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="12" t="s">
         <v>36</v>
       </c>
       <c r="B15" s="9"/>
@@ -6106,7 +6106,7 @@
       <c r="M15" s="9"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="11" t="s">
         <v>37</v>
       </c>
       <c r="B16" s="9"/>
@@ -6126,19 +6126,19 @@
       <c r="A17" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="10" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="10" t="s">
         <v>6</v>
       </c>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
-      <c r="J17" s="11" t="s">
+      <c r="J17" s="10" t="s">
         <v>7</v>
       </c>
       <c r="K17" s="9"/>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="H21" s="6" t="str">
         <f>IFERROR(VLOOKUP($F21,Data!$A:$D,2,FALSE),"")</f>
-        <v>Patient-Specific Modeling of Brain and Cerebrospinal Fluid Response to Rapid Head Acceleration in Chiari I Malformation</v>
+        <v>Patient-Specific Modeling of Cerebrospinal Fluid Flow in Chiari I Malformation</v>
       </c>
       <c r="I21" s="6" t="str">
         <f>IFERROR(VLOOKUP($F21,Data!$A:$D,3,FALSE),"")</f>
@@ -6484,7 +6484,7 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="12" t="s">
         <v>62</v>
       </c>
       <c r="B25" s="9"/>
@@ -6501,7 +6501,7 @@
       <c r="M25" s="9"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="11" t="s">
         <v>63</v>
       </c>
       <c r="B26" s="9"/>
@@ -6521,19 +6521,19 @@
       <c r="A27" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="10" t="s">
         <v>5</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
-      <c r="F27" s="11" t="s">
+      <c r="F27" s="10" t="s">
         <v>6</v>
       </c>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
-      <c r="J27" s="11" t="s">
+      <c r="J27" s="10" t="s">
         <v>7</v>
       </c>
       <c r="K27" s="9"/>
@@ -6879,7 +6879,7 @@
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="12" t="s">
         <v>88</v>
       </c>
       <c r="B35" s="9"/>
@@ -6896,7 +6896,7 @@
       <c r="M35" s="9"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A36" s="12" t="s">
+      <c r="A36" s="11" t="s">
         <v>89</v>
       </c>
       <c r="B36" s="9"/>
@@ -6916,19 +6916,19 @@
       <c r="A37" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="10" t="s">
         <v>5</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
-      <c r="F37" s="11" t="s">
+      <c r="F37" s="10" t="s">
         <v>6</v>
       </c>
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
-      <c r="J37" s="11" t="s">
+      <c r="J37" s="10" t="s">
         <v>7</v>
       </c>
       <c r="K37" s="9"/>
@@ -7274,7 +7274,7 @@
       </c>
     </row>
     <row r="47" spans="1:13" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="14" t="s">
         <v>114</v>
       </c>
       <c r="B47" s="9"/>
@@ -7291,7 +7291,7 @@
       <c r="M47" s="9"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A48" s="12" t="s">
+      <c r="A48" s="11" t="s">
         <v>115</v>
       </c>
       <c r="B48" s="9"/>
@@ -7311,19 +7311,19 @@
       <c r="A49" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="B49" s="10" t="s">
         <v>5</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
-      <c r="F49" s="11" t="s">
+      <c r="F49" s="10" t="s">
         <v>6</v>
       </c>
       <c r="G49" s="9"/>
       <c r="H49" s="9"/>
       <c r="I49" s="9"/>
-      <c r="J49" s="11" t="s">
+      <c r="J49" s="10" t="s">
         <v>7</v>
       </c>
       <c r="K49" s="9"/>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="H52" s="6" t="str">
         <f>IFERROR(VLOOKUP($F52,Data!$A:$D,2,FALSE),"")</f>
-        <v>Yeast-Based High-Throughput Screening for _Plasmodium falciparum_ PDEα Inhibitor Discovery</v>
+        <v>A Fission Yeast High-Throughput Screen Identifies Candidate Small-Molecule Inhibitors of Plasmodium falciparum PDEα</v>
       </c>
       <c r="I52" s="6" t="str">
         <f>IFERROR(VLOOKUP($F52,Data!$A:$D,3,FALSE),"")</f>
@@ -7669,7 +7669,7 @@
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A57" s="10" t="s">
+      <c r="A57" s="12" t="s">
         <v>36</v>
       </c>
       <c r="B57" s="9"/>
@@ -7686,7 +7686,7 @@
       <c r="M57" s="9"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A58" s="12" t="s">
+      <c r="A58" s="11" t="s">
         <v>134</v>
       </c>
       <c r="B58" s="9"/>
@@ -7706,19 +7706,19 @@
       <c r="A59" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B59" s="11" t="s">
+      <c r="B59" s="10" t="s">
         <v>5</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
-      <c r="F59" s="11" t="s">
+      <c r="F59" s="10" t="s">
         <v>6</v>
       </c>
       <c r="G59" s="9"/>
       <c r="H59" s="9"/>
       <c r="I59" s="9"/>
-      <c r="J59" s="11" t="s">
+      <c r="J59" s="10" t="s">
         <v>7</v>
       </c>
       <c r="K59" s="9"/>
@@ -7961,6 +7961,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A35:M35"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="F49:I49"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="A58:M58"/>
+    <mergeCell ref="A48:M48"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="J59:M59"/>
+    <mergeCell ref="A36:M36"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="B49:E49"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="F7:I7"/>
     <mergeCell ref="A6:M6"/>
@@ -7977,22 +7993,6 @@
     <mergeCell ref="A57:M57"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A47:M47"/>
-    <mergeCell ref="A58:M58"/>
-    <mergeCell ref="A48:M48"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="J59:M59"/>
-    <mergeCell ref="A36:M36"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="A5:M5"/>
-    <mergeCell ref="A35:M35"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="F49:I49"/>
-    <mergeCell ref="J17:M17"/>
   </mergeCells>
   <conditionalFormatting sqref="C4:C71">
     <cfRule type="cellIs" dxfId="32" priority="13" operator="equal">

--- a/RSI_2026_Schedule.xlsx
+++ b/RSI_2026_Schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/evanlim/Documents/rsi-symposium/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAAEAD33-A5A2-D34E-983B-7B69F5608DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59407157-8428-F64D-B470-68EA287FDB36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="716">
   <si>
     <t>RSI 2026 Symposium Schedule</t>
   </si>
@@ -531,9 +531,6 @@
     <t>abihqi</t>
   </si>
   <si>
-    <t>Characterizing Myo15-Cre Recombination in Cochlear Hair Cells to Validate Disease Models for Usher Syndrome Type 1F Gene Therapy</t>
-  </si>
-  <si>
     <t>Dr. Artur A. Indzhykulian</t>
   </si>
   <si>
@@ -903,9 +900,6 @@
     <t>cyh</t>
   </si>
   <si>
-    <t>Improving the Reliability of Hypersonic Airplane Engines Through Bleed Configurations</t>
-  </si>
-  <si>
     <t>Prof. Wesley L. Harris</t>
   </si>
   <si>
@@ -984,9 +978,6 @@
     <t>dtheisen</t>
   </si>
   <si>
-    <t>Structure Analysis using Partial Grotrian Diagram Construction and Isotope-Shift Systematics of Pa I,II,IV,V and Statistical Synthesis of Comagnetometer Constants</t>
-  </si>
-  <si>
     <t>Dr. Prajwal T. Mohan Murthy</t>
   </si>
   <si>
@@ -1335,9 +1326,6 @@
     <t>leobart</t>
   </si>
   <si>
-    <t>Explicit Free Resolutions for Central Quotients of Cyclic Amalgams</t>
-  </si>
-  <si>
     <t>Lee-yoo</t>
   </si>
   <si>
@@ -2010,9 +1998,6 @@
     <t>tlu27</t>
   </si>
   <si>
-    <t>Comorbidity-shaped cell states in Alzheimer’s disease: a single-nucleus dissection of 15 clinical phenotypes</t>
-  </si>
-  <si>
     <t>TRIS-tun</t>
   </si>
   <si>
@@ -2049,9 +2034,6 @@
     <t>doskhan</t>
   </si>
   <si>
-    <t>Quantifying Information Propagation in Diffusion Posterior Sampling for Ocean Flows</t>
-  </si>
-  <si>
     <t>YONG</t>
   </si>
   <si>
@@ -2155,6 +2137,54 @@
   </si>
   <si>
     <t>A Fission Yeast High-Throughput Screen Identifies Candidate Small-Molecule Inhibitors of Plasmodium falciparum PDEα</t>
+  </si>
+  <si>
+    <t>Mapping Myo-15 Cre Activity in Cochleae to Validate Disease Models for​ Usher Syndrome Type 1F Gene Therapy</t>
+  </si>
+  <si>
+    <t>Single-Nucleus Dissection of Nine Alzheimer's Disease Comorbidities</t>
+  </si>
+  <si>
+    <t>Quantifying the Information Availability of Spatial Observations for Ocean Flow Field Reconstruction with Diffusion Posterior Sampling</t>
+  </si>
+  <si>
+    <t>Low-Reynolds-Number Porous Bleed for Separation Control on Hypersonic Airplanes</t>
+  </si>
+  <si>
+    <t>Resolutions for Quotients of One-Relator Groups</t>
+  </si>
+  <si>
+    <t>Gyromagnetic Ratio and Protactinium Isotope-Shift Mapping for Electric Dipole Moment Searches</t>
+  </si>
+  <si>
+    <t>9:00 AM – 9:15 AM</t>
+  </si>
+  <si>
+    <t>9:15 AM – 9:30 AM</t>
+  </si>
+  <si>
+    <t>9:30 AM – 9:45 AM</t>
+  </si>
+  <si>
+    <t>9:45 AM – 10:00 AM</t>
+  </si>
+  <si>
+    <t>10:00 AM – 10:30 AM</t>
+  </si>
+  <si>
+    <t>10:30 AM – 10:45 AM</t>
+  </si>
+  <si>
+    <t>11:00 AM – 11:15 AM</t>
+  </si>
+  <si>
+    <t>11:15 AM – 11:30 AM</t>
+  </si>
+  <si>
+    <t>11:30 AM – 11:45 AM</t>
+  </si>
+  <si>
+    <t>11:45 AM – 12:00 PM</t>
   </si>
 </sst>
 </file>
@@ -3091,25 +3121,25 @@
         <v>132</v>
       </c>
       <c r="B4" t="s">
+        <v>700</v>
+      </c>
+      <c r="C4" t="s">
         <v>164</v>
-      </c>
-      <c r="C4" t="s">
-        <v>165</v>
       </c>
       <c r="D4" t="s">
         <v>159</v>
       </c>
       <c r="E4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F4" t="s">
         <v>166</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>167</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>168</v>
-      </c>
-      <c r="H4" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -3117,25 +3147,25 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" t="s">
         <v>170</v>
-      </c>
-      <c r="C5" t="s">
-        <v>171</v>
       </c>
       <c r="D5" t="s">
         <v>159</v>
       </c>
       <c r="E5" t="s">
+        <v>171</v>
+      </c>
+      <c r="F5" t="s">
         <v>172</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>173</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>174</v>
-      </c>
-      <c r="H5" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -3143,25 +3173,25 @@
         <v>21</v>
       </c>
       <c r="B6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C6" t="s">
         <v>176</v>
-      </c>
-      <c r="C6" t="s">
-        <v>177</v>
       </c>
       <c r="D6" t="s">
         <v>152</v>
       </c>
       <c r="E6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F6" t="s">
         <v>178</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>179</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>180</v>
-      </c>
-      <c r="H6" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -3169,25 +3199,25 @@
         <v>93</v>
       </c>
       <c r="B7" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="C7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D7" t="s">
         <v>159</v>
       </c>
       <c r="E7" t="s">
+        <v>182</v>
+      </c>
+      <c r="F7" t="s">
         <v>183</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>184</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>185</v>
-      </c>
-      <c r="H7" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -3195,25 +3225,25 @@
         <v>123</v>
       </c>
       <c r="B8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C8" t="s">
         <v>187</v>
-      </c>
-      <c r="C8" t="s">
-        <v>188</v>
       </c>
       <c r="D8" t="s">
         <v>159</v>
       </c>
       <c r="E8" t="s">
+        <v>188</v>
+      </c>
+      <c r="F8" t="s">
         <v>189</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>190</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>191</v>
-      </c>
-      <c r="H8" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -3221,25 +3251,25 @@
         <v>97</v>
       </c>
       <c r="B9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D9" t="s">
         <v>159</v>
       </c>
       <c r="E9" t="s">
+        <v>193</v>
+      </c>
+      <c r="F9" t="s">
         <v>194</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>195</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>196</v>
-      </c>
-      <c r="H9" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -3247,25 +3277,25 @@
         <v>112</v>
       </c>
       <c r="B10" t="s">
+        <v>197</v>
+      </c>
+      <c r="C10" t="s">
         <v>198</v>
-      </c>
-      <c r="C10" t="s">
-        <v>199</v>
       </c>
       <c r="D10" t="s">
         <v>159</v>
       </c>
       <c r="E10" t="s">
+        <v>199</v>
+      </c>
+      <c r="F10" t="s">
         <v>200</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>201</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>202</v>
-      </c>
-      <c r="H10" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -3273,7 +3303,7 @@
         <v>107</v>
       </c>
       <c r="B11" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C11" t="s">
         <v>151</v>
@@ -3282,16 +3312,16 @@
         <v>159</v>
       </c>
       <c r="E11" t="s">
+        <v>204</v>
+      </c>
+      <c r="F11" t="s">
         <v>205</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>206</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>207</v>
-      </c>
-      <c r="H11" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -3299,25 +3329,25 @@
         <v>136</v>
       </c>
       <c r="B12" t="s">
+        <v>208</v>
+      </c>
+      <c r="C12" t="s">
         <v>209</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>210</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>211</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>212</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>213</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>214</v>
-      </c>
-      <c r="H12" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -3325,25 +3355,25 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
+        <v>215</v>
+      </c>
+      <c r="C13" t="s">
         <v>216</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>217</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>218</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>219</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>220</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>221</v>
-      </c>
-      <c r="H13" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -3351,25 +3381,25 @@
         <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C14" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D14" t="s">
         <v>159</v>
       </c>
       <c r="E14" t="s">
+        <v>225</v>
+      </c>
+      <c r="F14" t="s">
         <v>226</v>
       </c>
-      <c r="F14" t="s">
-        <v>227</v>
-      </c>
       <c r="G14" t="s">
+        <v>233</v>
+      </c>
+      <c r="H14" t="s">
         <v>234</v>
-      </c>
-      <c r="H14" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -3377,25 +3407,25 @@
         <v>65</v>
       </c>
       <c r="B15" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C15" t="s">
+        <v>230</v>
+      </c>
+      <c r="D15" t="s">
+        <v>237</v>
+      </c>
+      <c r="E15" t="s">
         <v>231</v>
       </c>
-      <c r="D15" t="s">
-        <v>238</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>232</v>
       </c>
-      <c r="F15" t="s">
-        <v>233</v>
-      </c>
       <c r="G15" t="s">
+        <v>239</v>
+      </c>
+      <c r="H15" t="s">
         <v>240</v>
-      </c>
-      <c r="H15" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -3403,25 +3433,25 @@
         <v>137</v>
       </c>
       <c r="B16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F16" t="s">
+        <v>226</v>
+      </c>
+      <c r="G16" t="s">
         <v>227</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>228</v>
-      </c>
-      <c r="H16" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -3429,25 +3459,25 @@
         <v>69</v>
       </c>
       <c r="B17" t="s">
+        <v>241</v>
+      </c>
+      <c r="C17" t="s">
+        <v>230</v>
+      </c>
+      <c r="D17" t="s">
+        <v>237</v>
+      </c>
+      <c r="E17" t="s">
         <v>242</v>
       </c>
-      <c r="C17" t="s">
-        <v>231</v>
-      </c>
-      <c r="D17" t="s">
-        <v>238</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>243</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>244</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>245</v>
-      </c>
-      <c r="H17" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -3455,25 +3485,25 @@
         <v>125</v>
       </c>
       <c r="B18" t="s">
+        <v>246</v>
+      </c>
+      <c r="C18" t="s">
+        <v>660</v>
+      </c>
+      <c r="D18" t="s">
+        <v>224</v>
+      </c>
+      <c r="E18" t="s">
         <v>247</v>
       </c>
-      <c r="C18" t="s">
-        <v>665</v>
-      </c>
-      <c r="D18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>248</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>249</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>250</v>
-      </c>
-      <c r="H18" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -3481,25 +3511,25 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
+        <v>251</v>
+      </c>
+      <c r="C19" t="s">
         <v>252</v>
-      </c>
-      <c r="C19" t="s">
-        <v>253</v>
       </c>
       <c r="D19" t="s">
         <v>152</v>
       </c>
       <c r="E19" t="s">
+        <v>253</v>
+      </c>
+      <c r="F19" t="s">
         <v>254</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>255</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>256</v>
-      </c>
-      <c r="H19" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -3507,25 +3537,25 @@
         <v>73</v>
       </c>
       <c r="B20" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="C20" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D20" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E20" t="s">
+        <v>257</v>
+      </c>
+      <c r="F20" t="s">
+        <v>189</v>
+      </c>
+      <c r="G20" t="s">
         <v>258</v>
       </c>
-      <c r="F20" t="s">
-        <v>190</v>
-      </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>259</v>
-      </c>
-      <c r="H20" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -3533,25 +3563,25 @@
         <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="C21" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D21" t="s">
         <v>152</v>
       </c>
       <c r="E21" t="s">
+        <v>261</v>
+      </c>
+      <c r="F21" t="s">
         <v>262</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>263</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>264</v>
-      </c>
-      <c r="H21" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -3559,25 +3589,25 @@
         <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="C22" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D22" t="s">
         <v>159</v>
       </c>
       <c r="E22" t="s">
+        <v>266</v>
+      </c>
+      <c r="F22" t="s">
         <v>267</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>268</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>269</v>
-      </c>
-      <c r="H22" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -3585,25 +3615,25 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D23" t="s">
         <v>159</v>
       </c>
       <c r="E23" t="s">
+        <v>271</v>
+      </c>
+      <c r="F23" t="s">
         <v>272</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>273</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>274</v>
-      </c>
-      <c r="H23" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
@@ -3611,25 +3641,25 @@
         <v>77</v>
       </c>
       <c r="B24" t="s">
+        <v>275</v>
+      </c>
+      <c r="C24" t="s">
+        <v>230</v>
+      </c>
+      <c r="D24" t="s">
+        <v>237</v>
+      </c>
+      <c r="E24" t="s">
         <v>276</v>
       </c>
-      <c r="C24" t="s">
-        <v>231</v>
-      </c>
-      <c r="D24" t="s">
-        <v>238</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>277</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>278</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>279</v>
-      </c>
-      <c r="H24" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -3637,25 +3667,25 @@
         <v>96</v>
       </c>
       <c r="B25" t="s">
+        <v>280</v>
+      </c>
+      <c r="C25" t="s">
         <v>281</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>282</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>283</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>284</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>285</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>286</v>
-      </c>
-      <c r="H25" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
@@ -3663,25 +3693,25 @@
         <v>87</v>
       </c>
       <c r="B26" t="s">
+        <v>703</v>
+      </c>
+      <c r="C26" t="s">
+        <v>287</v>
+      </c>
+      <c r="D26" t="s">
         <v>288</v>
       </c>
-      <c r="C26" t="s">
+      <c r="E26" t="s">
         <v>289</v>
       </c>
-      <c r="D26" t="s">
+      <c r="F26" t="s">
         <v>290</v>
       </c>
-      <c r="E26" t="s">
+      <c r="G26" t="s">
         <v>291</v>
       </c>
-      <c r="F26" t="s">
+      <c r="H26" t="s">
         <v>292</v>
-      </c>
-      <c r="G26" t="s">
-        <v>293</v>
-      </c>
-      <c r="H26" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -3689,25 +3719,25 @@
         <v>70</v>
       </c>
       <c r="B27" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C27" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D27" t="s">
         <v>152</v>
       </c>
       <c r="E27" t="s">
+        <v>295</v>
+      </c>
+      <c r="F27" t="s">
+        <v>296</v>
+      </c>
+      <c r="G27" t="s">
         <v>297</v>
       </c>
-      <c r="F27" t="s">
+      <c r="H27" t="s">
         <v>298</v>
-      </c>
-      <c r="G27" t="s">
-        <v>299</v>
-      </c>
-      <c r="H27" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -3715,25 +3745,25 @@
         <v>119</v>
       </c>
       <c r="B28" t="s">
+        <v>305</v>
+      </c>
+      <c r="C28" t="s">
+        <v>300</v>
+      </c>
+      <c r="D28" t="s">
+        <v>210</v>
+      </c>
+      <c r="E28" t="s">
+        <v>301</v>
+      </c>
+      <c r="F28" t="s">
+        <v>302</v>
+      </c>
+      <c r="G28" t="s">
+        <v>306</v>
+      </c>
+      <c r="H28" t="s">
         <v>307</v>
-      </c>
-      <c r="C28" t="s">
-        <v>302</v>
-      </c>
-      <c r="D28" t="s">
-        <v>211</v>
-      </c>
-      <c r="E28" t="s">
-        <v>303</v>
-      </c>
-      <c r="F28" t="s">
-        <v>304</v>
-      </c>
-      <c r="G28" t="s">
-        <v>308</v>
-      </c>
-      <c r="H28" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -3741,25 +3771,25 @@
         <v>122</v>
       </c>
       <c r="B29" t="s">
+        <v>299</v>
+      </c>
+      <c r="C29" t="s">
+        <v>300</v>
+      </c>
+      <c r="D29" t="s">
+        <v>210</v>
+      </c>
+      <c r="E29" t="s">
         <v>301</v>
       </c>
-      <c r="C29" t="s">
-        <v>302</v>
-      </c>
-      <c r="D29" t="s">
-        <v>211</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
+        <v>226</v>
+      </c>
+      <c r="G29" t="s">
         <v>303</v>
       </c>
-      <c r="F29" t="s">
-        <v>227</v>
-      </c>
-      <c r="G29" t="s">
-        <v>305</v>
-      </c>
       <c r="H29" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -3767,25 +3797,25 @@
         <v>139</v>
       </c>
       <c r="B30" t="s">
+        <v>308</v>
+      </c>
+      <c r="C30" t="s">
+        <v>209</v>
+      </c>
+      <c r="D30" t="s">
+        <v>210</v>
+      </c>
+      <c r="E30" t="s">
+        <v>309</v>
+      </c>
+      <c r="F30" t="s">
         <v>310</v>
       </c>
-      <c r="C30" t="s">
-        <v>210</v>
-      </c>
-      <c r="D30" t="s">
-        <v>211</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="G30" t="s">
         <v>311</v>
       </c>
-      <c r="F30" t="s">
+      <c r="H30" t="s">
         <v>312</v>
-      </c>
-      <c r="G30" t="s">
-        <v>313</v>
-      </c>
-      <c r="H30" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -3793,25 +3823,25 @@
         <v>99</v>
       </c>
       <c r="B31" t="s">
+        <v>705</v>
+      </c>
+      <c r="C31" t="s">
+        <v>313</v>
+      </c>
+      <c r="D31" t="s">
+        <v>224</v>
+      </c>
+      <c r="E31" t="s">
+        <v>314</v>
+      </c>
+      <c r="F31" t="s">
         <v>315</v>
       </c>
-      <c r="C31" t="s">
+      <c r="G31" t="s">
         <v>316</v>
       </c>
-      <c r="D31" t="s">
-        <v>225</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="H31" t="s">
         <v>317</v>
-      </c>
-      <c r="F31" t="s">
-        <v>318</v>
-      </c>
-      <c r="G31" t="s">
-        <v>319</v>
-      </c>
-      <c r="H31" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -3819,25 +3849,25 @@
         <v>116</v>
       </c>
       <c r="B32" t="s">
+        <v>318</v>
+      </c>
+      <c r="C32" t="s">
+        <v>319</v>
+      </c>
+      <c r="D32" t="s">
+        <v>320</v>
+      </c>
+      <c r="E32" t="s">
         <v>321</v>
       </c>
-      <c r="C32" t="s">
+      <c r="F32" t="s">
         <v>322</v>
       </c>
-      <c r="D32" t="s">
+      <c r="G32" t="s">
         <v>323</v>
       </c>
-      <c r="E32" t="s">
+      <c r="H32" t="s">
         <v>324</v>
-      </c>
-      <c r="F32" t="s">
-        <v>325</v>
-      </c>
-      <c r="G32" t="s">
-        <v>326</v>
-      </c>
-      <c r="H32" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -3845,25 +3875,25 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
+        <v>325</v>
+      </c>
+      <c r="C33" t="s">
+        <v>326</v>
+      </c>
+      <c r="D33" t="s">
+        <v>282</v>
+      </c>
+      <c r="E33" t="s">
+        <v>327</v>
+      </c>
+      <c r="F33" t="s">
         <v>328</v>
       </c>
-      <c r="C33" t="s">
+      <c r="G33" t="s">
         <v>329</v>
       </c>
-      <c r="D33" t="s">
-        <v>283</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="H33" t="s">
         <v>330</v>
-      </c>
-      <c r="F33" t="s">
-        <v>331</v>
-      </c>
-      <c r="G33" t="s">
-        <v>332</v>
-      </c>
-      <c r="H33" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
@@ -3871,25 +3901,25 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="C34" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D34" t="s">
         <v>152</v>
       </c>
       <c r="E34" t="s">
+        <v>331</v>
+      </c>
+      <c r="F34" t="s">
+        <v>332</v>
+      </c>
+      <c r="G34" t="s">
+        <v>333</v>
+      </c>
+      <c r="H34" t="s">
         <v>334</v>
-      </c>
-      <c r="F34" t="s">
-        <v>335</v>
-      </c>
-      <c r="G34" t="s">
-        <v>336</v>
-      </c>
-      <c r="H34" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -3897,25 +3927,25 @@
         <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="C35" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D35" t="s">
         <v>152</v>
       </c>
       <c r="E35" t="s">
+        <v>335</v>
+      </c>
+      <c r="F35" t="s">
+        <v>336</v>
+      </c>
+      <c r="G35" t="s">
+        <v>337</v>
+      </c>
+      <c r="H35" t="s">
         <v>338</v>
-      </c>
-      <c r="F35" t="s">
-        <v>339</v>
-      </c>
-      <c r="G35" t="s">
-        <v>340</v>
-      </c>
-      <c r="H35" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -3923,25 +3953,25 @@
         <v>75</v>
       </c>
       <c r="B36" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C36" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D36" t="s">
         <v>159</v>
       </c>
       <c r="E36" t="s">
+        <v>341</v>
+      </c>
+      <c r="F36" t="s">
+        <v>342</v>
+      </c>
+      <c r="G36" t="s">
+        <v>343</v>
+      </c>
+      <c r="H36" t="s">
         <v>344</v>
-      </c>
-      <c r="F36" t="s">
-        <v>345</v>
-      </c>
-      <c r="G36" t="s">
-        <v>346</v>
-      </c>
-      <c r="H36" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -3949,25 +3979,25 @@
         <v>19</v>
       </c>
       <c r="B37" t="s">
+        <v>345</v>
+      </c>
+      <c r="C37" t="s">
+        <v>216</v>
+      </c>
+      <c r="D37" t="s">
+        <v>217</v>
+      </c>
+      <c r="E37" t="s">
+        <v>346</v>
+      </c>
+      <c r="F37" t="s">
+        <v>347</v>
+      </c>
+      <c r="G37" t="s">
         <v>348</v>
       </c>
-      <c r="C37" t="s">
-        <v>217</v>
-      </c>
-      <c r="D37" t="s">
-        <v>218</v>
-      </c>
-      <c r="E37" t="s">
+      <c r="H37" t="s">
         <v>349</v>
-      </c>
-      <c r="F37" t="s">
-        <v>350</v>
-      </c>
-      <c r="G37" t="s">
-        <v>351</v>
-      </c>
-      <c r="H37" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
@@ -3975,25 +4005,25 @@
         <v>126</v>
       </c>
       <c r="B38" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C38" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D38" t="s">
         <v>159</v>
       </c>
       <c r="E38" t="s">
+        <v>351</v>
+      </c>
+      <c r="F38" t="s">
+        <v>352</v>
+      </c>
+      <c r="G38" t="s">
+        <v>353</v>
+      </c>
+      <c r="H38" t="s">
         <v>354</v>
-      </c>
-      <c r="F38" t="s">
-        <v>355</v>
-      </c>
-      <c r="G38" t="s">
-        <v>356</v>
-      </c>
-      <c r="H38" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -4001,25 +4031,25 @@
         <v>131</v>
       </c>
       <c r="B39" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C39" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D39" t="s">
         <v>159</v>
       </c>
       <c r="E39" t="s">
+        <v>357</v>
+      </c>
+      <c r="F39" t="s">
+        <v>358</v>
+      </c>
+      <c r="G39" t="s">
+        <v>359</v>
+      </c>
+      <c r="H39" t="s">
         <v>360</v>
-      </c>
-      <c r="F39" t="s">
-        <v>361</v>
-      </c>
-      <c r="G39" t="s">
-        <v>362</v>
-      </c>
-      <c r="H39" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -4027,25 +4057,25 @@
         <v>105</v>
       </c>
       <c r="B40" t="s">
+        <v>361</v>
+      </c>
+      <c r="C40" t="s">
+        <v>181</v>
+      </c>
+      <c r="D40" t="s">
+        <v>210</v>
+      </c>
+      <c r="E40" t="s">
+        <v>362</v>
+      </c>
+      <c r="F40" t="s">
+        <v>363</v>
+      </c>
+      <c r="G40" t="s">
         <v>364</v>
       </c>
-      <c r="C40" t="s">
-        <v>182</v>
-      </c>
-      <c r="D40" t="s">
-        <v>211</v>
-      </c>
-      <c r="E40" t="s">
+      <c r="H40" t="s">
         <v>365</v>
-      </c>
-      <c r="F40" t="s">
-        <v>366</v>
-      </c>
-      <c r="G40" t="s">
-        <v>367</v>
-      </c>
-      <c r="H40" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -4053,25 +4083,25 @@
         <v>124</v>
       </c>
       <c r="B41" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C41" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="D41" t="s">
         <v>159</v>
       </c>
       <c r="E41" t="s">
+        <v>368</v>
+      </c>
+      <c r="F41" t="s">
+        <v>369</v>
+      </c>
+      <c r="G41" t="s">
+        <v>370</v>
+      </c>
+      <c r="H41" t="s">
         <v>371</v>
-      </c>
-      <c r="F41" t="s">
-        <v>372</v>
-      </c>
-      <c r="G41" t="s">
-        <v>373</v>
-      </c>
-      <c r="H41" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
@@ -4079,25 +4109,25 @@
         <v>53</v>
       </c>
       <c r="B42" t="s">
+        <v>378</v>
+      </c>
+      <c r="C42" t="s">
+        <v>373</v>
+      </c>
+      <c r="D42" t="s">
+        <v>217</v>
+      </c>
+      <c r="E42" t="s">
+        <v>374</v>
+      </c>
+      <c r="F42" t="s">
+        <v>375</v>
+      </c>
+      <c r="G42" t="s">
+        <v>380</v>
+      </c>
+      <c r="H42" t="s">
         <v>381</v>
-      </c>
-      <c r="C42" t="s">
-        <v>376</v>
-      </c>
-      <c r="D42" t="s">
-        <v>218</v>
-      </c>
-      <c r="E42" t="s">
-        <v>377</v>
-      </c>
-      <c r="F42" t="s">
-        <v>378</v>
-      </c>
-      <c r="G42" t="s">
-        <v>383</v>
-      </c>
-      <c r="H42" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -4105,25 +4135,25 @@
         <v>111</v>
       </c>
       <c r="B43" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C43" t="s">
         <v>151</v>
       </c>
       <c r="D43" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E43" t="s">
+        <v>374</v>
+      </c>
+      <c r="F43" t="s">
+        <v>379</v>
+      </c>
+      <c r="G43" t="s">
+        <v>376</v>
+      </c>
+      <c r="H43" t="s">
         <v>377</v>
-      </c>
-      <c r="F43" t="s">
-        <v>382</v>
-      </c>
-      <c r="G43" t="s">
-        <v>379</v>
-      </c>
-      <c r="H43" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -4131,25 +4161,25 @@
         <v>108</v>
       </c>
       <c r="B44" t="s">
+        <v>382</v>
+      </c>
+      <c r="C44" t="s">
+        <v>383</v>
+      </c>
+      <c r="D44" t="s">
+        <v>288</v>
+      </c>
+      <c r="E44" t="s">
+        <v>384</v>
+      </c>
+      <c r="F44" t="s">
         <v>385</v>
       </c>
-      <c r="C44" t="s">
+      <c r="G44" t="s">
         <v>386</v>
       </c>
-      <c r="D44" t="s">
-        <v>290</v>
-      </c>
-      <c r="E44" t="s">
+      <c r="H44" t="s">
         <v>387</v>
-      </c>
-      <c r="F44" t="s">
-        <v>388</v>
-      </c>
-      <c r="G44" t="s">
-        <v>389</v>
-      </c>
-      <c r="H44" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -4157,25 +4187,25 @@
         <v>33</v>
       </c>
       <c r="B45" t="s">
+        <v>388</v>
+      </c>
+      <c r="C45" t="s">
+        <v>389</v>
+      </c>
+      <c r="D45" t="s">
+        <v>282</v>
+      </c>
+      <c r="E45" t="s">
+        <v>390</v>
+      </c>
+      <c r="F45" t="s">
         <v>391</v>
       </c>
-      <c r="C45" t="s">
+      <c r="G45" t="s">
         <v>392</v>
       </c>
-      <c r="D45" t="s">
-        <v>283</v>
-      </c>
-      <c r="E45" t="s">
+      <c r="H45" t="s">
         <v>393</v>
-      </c>
-      <c r="F45" t="s">
-        <v>394</v>
-      </c>
-      <c r="G45" t="s">
-        <v>395</v>
-      </c>
-      <c r="H45" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
@@ -4183,25 +4213,25 @@
         <v>127</v>
       </c>
       <c r="B46" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C46" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D46" t="s">
         <v>159</v>
       </c>
       <c r="E46" t="s">
+        <v>396</v>
+      </c>
+      <c r="F46" t="s">
+        <v>397</v>
+      </c>
+      <c r="G46" t="s">
+        <v>398</v>
+      </c>
+      <c r="H46" t="s">
         <v>399</v>
-      </c>
-      <c r="F46" t="s">
-        <v>400</v>
-      </c>
-      <c r="G46" t="s">
-        <v>401</v>
-      </c>
-      <c r="H46" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
@@ -4209,25 +4239,25 @@
         <v>142</v>
       </c>
       <c r="B47" t="s">
+        <v>400</v>
+      </c>
+      <c r="C47" t="s">
+        <v>401</v>
+      </c>
+      <c r="D47" t="s">
+        <v>402</v>
+      </c>
+      <c r="E47" t="s">
         <v>403</v>
       </c>
-      <c r="C47" t="s">
+      <c r="F47" t="s">
         <v>404</v>
       </c>
-      <c r="D47" t="s">
+      <c r="G47" t="s">
         <v>405</v>
       </c>
-      <c r="E47" t="s">
+      <c r="H47" t="s">
         <v>406</v>
-      </c>
-      <c r="F47" t="s">
-        <v>407</v>
-      </c>
-      <c r="G47" t="s">
-        <v>408</v>
-      </c>
-      <c r="H47" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
@@ -4235,25 +4265,25 @@
         <v>23</v>
       </c>
       <c r="B48" t="s">
+        <v>407</v>
+      </c>
+      <c r="C48" t="s">
+        <v>408</v>
+      </c>
+      <c r="D48" t="s">
+        <v>217</v>
+      </c>
+      <c r="E48" t="s">
+        <v>409</v>
+      </c>
+      <c r="F48" t="s">
         <v>410</v>
       </c>
-      <c r="C48" t="s">
+      <c r="G48" t="s">
         <v>411</v>
       </c>
-      <c r="D48" t="s">
-        <v>218</v>
-      </c>
-      <c r="E48" t="s">
+      <c r="H48" t="s">
         <v>412</v>
-      </c>
-      <c r="F48" t="s">
-        <v>413</v>
-      </c>
-      <c r="G48" t="s">
-        <v>414</v>
-      </c>
-      <c r="H48" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
@@ -4261,25 +4291,25 @@
         <v>104</v>
       </c>
       <c r="B49" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C49" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D49" t="s">
         <v>159</v>
       </c>
       <c r="E49" t="s">
+        <v>415</v>
+      </c>
+      <c r="F49" t="s">
+        <v>416</v>
+      </c>
+      <c r="G49" t="s">
+        <v>417</v>
+      </c>
+      <c r="H49" t="s">
         <v>418</v>
-      </c>
-      <c r="F49" t="s">
-        <v>419</v>
-      </c>
-      <c r="G49" t="s">
-        <v>420</v>
-      </c>
-      <c r="H49" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
@@ -4287,25 +4317,25 @@
         <v>29</v>
       </c>
       <c r="B50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C50" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D50" t="s">
         <v>152</v>
       </c>
       <c r="E50" t="s">
+        <v>420</v>
+      </c>
+      <c r="F50" t="s">
+        <v>421</v>
+      </c>
+      <c r="G50" t="s">
+        <v>422</v>
+      </c>
+      <c r="H50" t="s">
         <v>423</v>
-      </c>
-      <c r="F50" t="s">
-        <v>424</v>
-      </c>
-      <c r="G50" t="s">
-        <v>425</v>
-      </c>
-      <c r="H50" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
@@ -4313,25 +4343,25 @@
         <v>74</v>
       </c>
       <c r="B51" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C51" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D51" t="s">
         <v>152</v>
       </c>
       <c r="E51" t="s">
+        <v>425</v>
+      </c>
+      <c r="F51" t="s">
+        <v>426</v>
+      </c>
+      <c r="G51" t="s">
+        <v>427</v>
+      </c>
+      <c r="H51" t="s">
         <v>428</v>
-      </c>
-      <c r="F51" t="s">
-        <v>429</v>
-      </c>
-      <c r="G51" t="s">
-        <v>430</v>
-      </c>
-      <c r="H51" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
@@ -4339,25 +4369,25 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
+        <v>704</v>
+      </c>
+      <c r="C52" t="s">
+        <v>373</v>
+      </c>
+      <c r="D52" t="s">
+        <v>217</v>
+      </c>
+      <c r="E52" t="s">
+        <v>429</v>
+      </c>
+      <c r="F52" t="s">
+        <v>430</v>
+      </c>
+      <c r="G52" t="s">
+        <v>431</v>
+      </c>
+      <c r="H52" t="s">
         <v>432</v>
-      </c>
-      <c r="C52" t="s">
-        <v>376</v>
-      </c>
-      <c r="D52" t="s">
-        <v>218</v>
-      </c>
-      <c r="E52" t="s">
-        <v>433</v>
-      </c>
-      <c r="F52" t="s">
-        <v>434</v>
-      </c>
-      <c r="G52" t="s">
-        <v>435</v>
-      </c>
-      <c r="H52" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
@@ -4365,25 +4395,25 @@
         <v>100</v>
       </c>
       <c r="B53" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C53" t="s">
+        <v>281</v>
+      </c>
+      <c r="D53" t="s">
         <v>282</v>
       </c>
-      <c r="D53" t="s">
-        <v>283</v>
-      </c>
       <c r="E53" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="F53" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G53" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="H53" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
@@ -4391,25 +4421,25 @@
         <v>27</v>
       </c>
       <c r="B54" t="s">
+        <v>437</v>
+      </c>
+      <c r="C54" t="s">
+        <v>438</v>
+      </c>
+      <c r="D54" t="s">
+        <v>217</v>
+      </c>
+      <c r="E54" t="s">
+        <v>439</v>
+      </c>
+      <c r="F54" t="s">
+        <v>410</v>
+      </c>
+      <c r="G54" t="s">
+        <v>440</v>
+      </c>
+      <c r="H54" t="s">
         <v>441</v>
-      </c>
-      <c r="C54" t="s">
-        <v>442</v>
-      </c>
-      <c r="D54" t="s">
-        <v>218</v>
-      </c>
-      <c r="E54" t="s">
-        <v>443</v>
-      </c>
-      <c r="F54" t="s">
-        <v>413</v>
-      </c>
-      <c r="G54" t="s">
-        <v>444</v>
-      </c>
-      <c r="H54" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
@@ -4417,25 +4447,25 @@
         <v>40</v>
       </c>
       <c r="B55" t="s">
+        <v>442</v>
+      </c>
+      <c r="C55" t="s">
+        <v>443</v>
+      </c>
+      <c r="D55" t="s">
+        <v>224</v>
+      </c>
+      <c r="E55" t="s">
+        <v>444</v>
+      </c>
+      <c r="F55" t="s">
+        <v>445</v>
+      </c>
+      <c r="G55" t="s">
         <v>446</v>
       </c>
-      <c r="C55" t="s">
+      <c r="H55" t="s">
         <v>447</v>
-      </c>
-      <c r="D55" t="s">
-        <v>225</v>
-      </c>
-      <c r="E55" t="s">
-        <v>448</v>
-      </c>
-      <c r="F55" t="s">
-        <v>449</v>
-      </c>
-      <c r="G55" t="s">
-        <v>450</v>
-      </c>
-      <c r="H55" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
@@ -4443,25 +4473,25 @@
         <v>129</v>
       </c>
       <c r="B56" t="s">
+        <v>448</v>
+      </c>
+      <c r="C56" t="s">
+        <v>449</v>
+      </c>
+      <c r="D56" t="s">
+        <v>288</v>
+      </c>
+      <c r="E56" t="s">
+        <v>450</v>
+      </c>
+      <c r="F56" t="s">
+        <v>451</v>
+      </c>
+      <c r="G56" t="s">
         <v>452</v>
       </c>
-      <c r="C56" t="s">
+      <c r="H56" t="s">
         <v>453</v>
-      </c>
-      <c r="D56" t="s">
-        <v>290</v>
-      </c>
-      <c r="E56" t="s">
-        <v>454</v>
-      </c>
-      <c r="F56" t="s">
-        <v>455</v>
-      </c>
-      <c r="G56" t="s">
-        <v>456</v>
-      </c>
-      <c r="H56" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
@@ -4469,25 +4499,25 @@
         <v>130</v>
       </c>
       <c r="B57" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C57" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="D57" t="s">
         <v>159</v>
       </c>
       <c r="E57" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="F57" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="G57" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="H57" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -4495,7 +4525,7 @@
         <v>120</v>
       </c>
       <c r="B58" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="C58" t="s">
         <v>158</v>
@@ -4504,16 +4534,16 @@
         <v>159</v>
       </c>
       <c r="E58" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="F58" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="G58" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="H58" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
@@ -4521,25 +4551,25 @@
         <v>14</v>
       </c>
       <c r="B59" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C59" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D59" t="s">
         <v>159</v>
       </c>
       <c r="E59" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="F59" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="G59" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="H59" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
@@ -4547,25 +4577,25 @@
         <v>92</v>
       </c>
       <c r="B60" t="s">
+        <v>469</v>
+      </c>
+      <c r="C60" t="s">
+        <v>470</v>
+      </c>
+      <c r="D60" t="s">
+        <v>320</v>
+      </c>
+      <c r="E60" t="s">
+        <v>471</v>
+      </c>
+      <c r="F60" t="s">
+        <v>472</v>
+      </c>
+      <c r="G60" t="s">
         <v>473</v>
       </c>
-      <c r="C60" t="s">
+      <c r="H60" t="s">
         <v>474</v>
-      </c>
-      <c r="D60" t="s">
-        <v>323</v>
-      </c>
-      <c r="E60" t="s">
-        <v>475</v>
-      </c>
-      <c r="F60" t="s">
-        <v>476</v>
-      </c>
-      <c r="G60" t="s">
-        <v>477</v>
-      </c>
-      <c r="H60" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
@@ -4573,25 +4603,25 @@
         <v>81</v>
       </c>
       <c r="B61" t="s">
+        <v>475</v>
+      </c>
+      <c r="C61" t="s">
+        <v>230</v>
+      </c>
+      <c r="D61" t="s">
+        <v>237</v>
+      </c>
+      <c r="E61" t="s">
+        <v>476</v>
+      </c>
+      <c r="F61" t="s">
+        <v>477</v>
+      </c>
+      <c r="G61" t="s">
+        <v>478</v>
+      </c>
+      <c r="H61" t="s">
         <v>479</v>
-      </c>
-      <c r="C61" t="s">
-        <v>231</v>
-      </c>
-      <c r="D61" t="s">
-        <v>238</v>
-      </c>
-      <c r="E61" t="s">
-        <v>480</v>
-      </c>
-      <c r="F61" t="s">
-        <v>481</v>
-      </c>
-      <c r="G61" t="s">
-        <v>482</v>
-      </c>
-      <c r="H61" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
@@ -4599,25 +4629,25 @@
         <v>30</v>
       </c>
       <c r="B62" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C62" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D62" t="s">
         <v>152</v>
       </c>
       <c r="E62" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="F62" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="G62" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="H62" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
@@ -4625,25 +4655,25 @@
         <v>138</v>
       </c>
       <c r="B63" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C63" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="D63" t="s">
         <v>159</v>
       </c>
       <c r="E63" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="F63" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="G63" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="H63" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
@@ -4651,25 +4681,25 @@
         <v>35</v>
       </c>
       <c r="B64" t="s">
+        <v>491</v>
+      </c>
+      <c r="C64" t="s">
+        <v>492</v>
+      </c>
+      <c r="D64" t="s">
+        <v>217</v>
+      </c>
+      <c r="E64" t="s">
+        <v>493</v>
+      </c>
+      <c r="F64" t="s">
+        <v>494</v>
+      </c>
+      <c r="G64" t="s">
         <v>495</v>
       </c>
-      <c r="C64" t="s">
+      <c r="H64" t="s">
         <v>496</v>
-      </c>
-      <c r="D64" t="s">
-        <v>218</v>
-      </c>
-      <c r="E64" t="s">
-        <v>497</v>
-      </c>
-      <c r="F64" t="s">
-        <v>498</v>
-      </c>
-      <c r="G64" t="s">
-        <v>499</v>
-      </c>
-      <c r="H64" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
@@ -4677,25 +4707,25 @@
         <v>43</v>
       </c>
       <c r="B65" t="s">
+        <v>497</v>
+      </c>
+      <c r="C65" t="s">
+        <v>498</v>
+      </c>
+      <c r="D65" t="s">
+        <v>224</v>
+      </c>
+      <c r="E65" t="s">
+        <v>499</v>
+      </c>
+      <c r="F65" t="s">
+        <v>500</v>
+      </c>
+      <c r="G65" t="s">
         <v>501</v>
       </c>
-      <c r="C65" t="s">
+      <c r="H65" t="s">
         <v>502</v>
-      </c>
-      <c r="D65" t="s">
-        <v>225</v>
-      </c>
-      <c r="E65" t="s">
-        <v>503</v>
-      </c>
-      <c r="F65" t="s">
-        <v>504</v>
-      </c>
-      <c r="G65" t="s">
-        <v>505</v>
-      </c>
-      <c r="H65" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
@@ -4703,25 +4733,25 @@
         <v>44</v>
       </c>
       <c r="B66" t="s">
+        <v>503</v>
+      </c>
+      <c r="C66" t="s">
+        <v>443</v>
+      </c>
+      <c r="D66" t="s">
+        <v>224</v>
+      </c>
+      <c r="E66" t="s">
+        <v>504</v>
+      </c>
+      <c r="F66" t="s">
+        <v>505</v>
+      </c>
+      <c r="G66" t="s">
+        <v>506</v>
+      </c>
+      <c r="H66" t="s">
         <v>507</v>
-      </c>
-      <c r="C66" t="s">
-        <v>447</v>
-      </c>
-      <c r="D66" t="s">
-        <v>225</v>
-      </c>
-      <c r="E66" t="s">
-        <v>508</v>
-      </c>
-      <c r="F66" t="s">
-        <v>509</v>
-      </c>
-      <c r="G66" t="s">
-        <v>510</v>
-      </c>
-      <c r="H66" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
@@ -4729,25 +4759,25 @@
         <v>13</v>
       </c>
       <c r="B67" t="s">
+        <v>508</v>
+      </c>
+      <c r="C67" t="s">
+        <v>509</v>
+      </c>
+      <c r="D67" t="s">
+        <v>402</v>
+      </c>
+      <c r="E67" t="s">
+        <v>510</v>
+      </c>
+      <c r="F67" t="s">
+        <v>511</v>
+      </c>
+      <c r="G67" t="s">
         <v>512</v>
       </c>
-      <c r="C67" t="s">
+      <c r="H67" t="s">
         <v>513</v>
-      </c>
-      <c r="D67" t="s">
-        <v>405</v>
-      </c>
-      <c r="E67" t="s">
-        <v>514</v>
-      </c>
-      <c r="F67" t="s">
-        <v>515</v>
-      </c>
-      <c r="G67" t="s">
-        <v>516</v>
-      </c>
-      <c r="H67" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
@@ -4755,25 +4785,25 @@
         <v>48</v>
       </c>
       <c r="B68" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="C68" t="s">
+        <v>514</v>
+      </c>
+      <c r="D68" t="s">
+        <v>288</v>
+      </c>
+      <c r="E68" t="s">
+        <v>515</v>
+      </c>
+      <c r="F68" t="s">
+        <v>516</v>
+      </c>
+      <c r="G68" t="s">
+        <v>517</v>
+      </c>
+      <c r="H68" t="s">
         <v>518</v>
-      </c>
-      <c r="D68" t="s">
-        <v>290</v>
-      </c>
-      <c r="E68" t="s">
-        <v>519</v>
-      </c>
-      <c r="F68" t="s">
-        <v>520</v>
-      </c>
-      <c r="G68" t="s">
-        <v>521</v>
-      </c>
-      <c r="H68" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
@@ -4781,25 +4811,25 @@
         <v>86</v>
       </c>
       <c r="B69" t="s">
+        <v>519</v>
+      </c>
+      <c r="C69" t="s">
+        <v>520</v>
+      </c>
+      <c r="D69" t="s">
+        <v>402</v>
+      </c>
+      <c r="E69" t="s">
+        <v>521</v>
+      </c>
+      <c r="F69" t="s">
+        <v>522</v>
+      </c>
+      <c r="G69" t="s">
         <v>523</v>
       </c>
-      <c r="C69" t="s">
+      <c r="H69" t="s">
         <v>524</v>
-      </c>
-      <c r="D69" t="s">
-        <v>405</v>
-      </c>
-      <c r="E69" t="s">
-        <v>525</v>
-      </c>
-      <c r="F69" t="s">
-        <v>526</v>
-      </c>
-      <c r="G69" t="s">
-        <v>527</v>
-      </c>
-      <c r="H69" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
@@ -4807,25 +4837,25 @@
         <v>78</v>
       </c>
       <c r="B70" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="C70" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D70" t="s">
         <v>152</v>
       </c>
       <c r="E70" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="F70" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="G70" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="H70" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
@@ -4833,25 +4863,25 @@
         <v>140</v>
       </c>
       <c r="B71" t="s">
+        <v>530</v>
+      </c>
+      <c r="C71" t="s">
+        <v>695</v>
+      </c>
+      <c r="D71" t="s">
+        <v>224</v>
+      </c>
+      <c r="E71" t="s">
+        <v>531</v>
+      </c>
+      <c r="F71" t="s">
+        <v>532</v>
+      </c>
+      <c r="G71" t="s">
+        <v>533</v>
+      </c>
+      <c r="H71" t="s">
         <v>534</v>
-      </c>
-      <c r="C71" t="s">
-        <v>701</v>
-      </c>
-      <c r="D71" t="s">
-        <v>225</v>
-      </c>
-      <c r="E71" t="s">
-        <v>535</v>
-      </c>
-      <c r="F71" t="s">
-        <v>536</v>
-      </c>
-      <c r="G71" t="s">
-        <v>537</v>
-      </c>
-      <c r="H71" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
@@ -4859,25 +4889,25 @@
         <v>45</v>
       </c>
       <c r="B72" t="s">
+        <v>535</v>
+      </c>
+      <c r="C72" t="s">
+        <v>536</v>
+      </c>
+      <c r="D72" t="s">
+        <v>217</v>
+      </c>
+      <c r="E72" t="s">
+        <v>537</v>
+      </c>
+      <c r="F72" t="s">
+        <v>538</v>
+      </c>
+      <c r="G72" t="s">
         <v>539</v>
       </c>
-      <c r="C72" t="s">
+      <c r="H72" t="s">
         <v>540</v>
-      </c>
-      <c r="D72" t="s">
-        <v>218</v>
-      </c>
-      <c r="E72" t="s">
-        <v>541</v>
-      </c>
-      <c r="F72" t="s">
-        <v>542</v>
-      </c>
-      <c r="G72" t="s">
-        <v>543</v>
-      </c>
-      <c r="H72" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
@@ -4885,25 +4915,25 @@
         <v>51</v>
       </c>
       <c r="B73" t="s">
+        <v>541</v>
+      </c>
+      <c r="C73" t="s">
+        <v>542</v>
+      </c>
+      <c r="D73" t="s">
+        <v>210</v>
+      </c>
+      <c r="E73" t="s">
+        <v>543</v>
+      </c>
+      <c r="F73" t="s">
+        <v>544</v>
+      </c>
+      <c r="G73" t="s">
         <v>545</v>
       </c>
-      <c r="C73" t="s">
+      <c r="H73" t="s">
         <v>546</v>
-      </c>
-      <c r="D73" t="s">
-        <v>211</v>
-      </c>
-      <c r="E73" t="s">
-        <v>547</v>
-      </c>
-      <c r="F73" t="s">
-        <v>548</v>
-      </c>
-      <c r="G73" t="s">
-        <v>549</v>
-      </c>
-      <c r="H73" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
@@ -4911,25 +4941,25 @@
         <v>135</v>
       </c>
       <c r="B74" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="C74" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="D74" t="s">
         <v>159</v>
       </c>
       <c r="E74" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="F74" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="G74" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="H74" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
@@ -4937,25 +4967,25 @@
         <v>56</v>
       </c>
       <c r="B75" t="s">
+        <v>552</v>
+      </c>
+      <c r="C75" t="s">
+        <v>687</v>
+      </c>
+      <c r="D75" t="s">
+        <v>402</v>
+      </c>
+      <c r="E75" t="s">
+        <v>553</v>
+      </c>
+      <c r="F75" t="s">
+        <v>554</v>
+      </c>
+      <c r="G75" t="s">
+        <v>555</v>
+      </c>
+      <c r="H75" t="s">
         <v>556</v>
-      </c>
-      <c r="C75" t="s">
-        <v>693</v>
-      </c>
-      <c r="D75" t="s">
-        <v>405</v>
-      </c>
-      <c r="E75" t="s">
-        <v>557</v>
-      </c>
-      <c r="F75" t="s">
-        <v>558</v>
-      </c>
-      <c r="G75" t="s">
-        <v>559</v>
-      </c>
-      <c r="H75" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
@@ -4963,25 +4993,25 @@
         <v>61</v>
       </c>
       <c r="B76" t="s">
+        <v>557</v>
+      </c>
+      <c r="C76" t="s">
+        <v>558</v>
+      </c>
+      <c r="D76" t="s">
+        <v>217</v>
+      </c>
+      <c r="E76" t="s">
+        <v>559</v>
+      </c>
+      <c r="F76" t="s">
+        <v>560</v>
+      </c>
+      <c r="G76" t="s">
         <v>561</v>
       </c>
-      <c r="C76" t="s">
+      <c r="H76" t="s">
         <v>562</v>
-      </c>
-      <c r="D76" t="s">
-        <v>218</v>
-      </c>
-      <c r="E76" t="s">
-        <v>563</v>
-      </c>
-      <c r="F76" t="s">
-        <v>564</v>
-      </c>
-      <c r="G76" t="s">
-        <v>565</v>
-      </c>
-      <c r="H76" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
@@ -4989,25 +5019,25 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="C77" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D77" t="s">
         <v>152</v>
       </c>
       <c r="E77" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="F77" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="G77" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="H77" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
@@ -5015,25 +5045,25 @@
         <v>143</v>
       </c>
       <c r="B78" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="C78" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="D78" t="s">
         <v>159</v>
       </c>
       <c r="E78" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="F78" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="G78" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="H78" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
@@ -5041,25 +5071,25 @@
         <v>59</v>
       </c>
       <c r="B79" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="C79" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D79" t="s">
         <v>159</v>
       </c>
       <c r="E79" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F79" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="G79" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="H79" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
@@ -5067,25 +5097,25 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C80" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="D80" t="s">
         <v>159</v>
       </c>
       <c r="E80" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="F80" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="G80" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="H80" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
@@ -5093,25 +5123,25 @@
         <v>141</v>
       </c>
       <c r="B81" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="C81" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="D81" t="s">
         <v>159</v>
       </c>
       <c r="E81" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="F81" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="G81" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="H81" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
@@ -5119,25 +5149,25 @@
         <v>144</v>
       </c>
       <c r="B82" t="s">
+        <v>589</v>
+      </c>
+      <c r="C82" t="s">
+        <v>401</v>
+      </c>
+      <c r="D82" t="s">
+        <v>402</v>
+      </c>
+      <c r="E82" t="s">
+        <v>590</v>
+      </c>
+      <c r="F82" t="s">
+        <v>591</v>
+      </c>
+      <c r="G82" t="s">
+        <v>592</v>
+      </c>
+      <c r="H82" t="s">
         <v>593</v>
-      </c>
-      <c r="C82" t="s">
-        <v>404</v>
-      </c>
-      <c r="D82" t="s">
-        <v>405</v>
-      </c>
-      <c r="E82" t="s">
-        <v>594</v>
-      </c>
-      <c r="F82" t="s">
-        <v>595</v>
-      </c>
-      <c r="G82" t="s">
-        <v>596</v>
-      </c>
-      <c r="H82" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
@@ -5145,25 +5175,25 @@
         <v>60</v>
       </c>
       <c r="B83" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="C83" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="D83" t="s">
         <v>159</v>
       </c>
       <c r="E83" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="F83" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="G83" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="H83" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
@@ -5171,25 +5201,25 @@
         <v>66</v>
       </c>
       <c r="B84" t="s">
+        <v>600</v>
+      </c>
+      <c r="C84" t="s">
+        <v>601</v>
+      </c>
+      <c r="D84" t="s">
+        <v>402</v>
+      </c>
+      <c r="E84" t="s">
+        <v>602</v>
+      </c>
+      <c r="F84" t="s">
+        <v>603</v>
+      </c>
+      <c r="G84" t="s">
         <v>604</v>
       </c>
-      <c r="C84" t="s">
+      <c r="H84" t="s">
         <v>605</v>
-      </c>
-      <c r="D84" t="s">
-        <v>405</v>
-      </c>
-      <c r="E84" t="s">
-        <v>606</v>
-      </c>
-      <c r="F84" t="s">
-        <v>607</v>
-      </c>
-      <c r="G84" t="s">
-        <v>608</v>
-      </c>
-      <c r="H84" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
@@ -5197,25 +5227,25 @@
         <v>34</v>
       </c>
       <c r="B85" t="s">
+        <v>606</v>
+      </c>
+      <c r="C85" t="s">
+        <v>607</v>
+      </c>
+      <c r="D85" t="s">
+        <v>282</v>
+      </c>
+      <c r="E85" t="s">
+        <v>608</v>
+      </c>
+      <c r="F85" t="s">
+        <v>609</v>
+      </c>
+      <c r="G85" t="s">
         <v>610</v>
       </c>
-      <c r="C85" t="s">
+      <c r="H85" t="s">
         <v>611</v>
-      </c>
-      <c r="D85" t="s">
-        <v>283</v>
-      </c>
-      <c r="E85" t="s">
-        <v>612</v>
-      </c>
-      <c r="F85" t="s">
-        <v>613</v>
-      </c>
-      <c r="G85" t="s">
-        <v>614</v>
-      </c>
-      <c r="H85" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
@@ -5223,25 +5253,25 @@
         <v>41</v>
       </c>
       <c r="B86" t="s">
+        <v>612</v>
+      </c>
+      <c r="C86" t="s">
+        <v>492</v>
+      </c>
+      <c r="D86" t="s">
+        <v>217</v>
+      </c>
+      <c r="E86" t="s">
+        <v>613</v>
+      </c>
+      <c r="F86" t="s">
+        <v>614</v>
+      </c>
+      <c r="G86" t="s">
+        <v>615</v>
+      </c>
+      <c r="H86" t="s">
         <v>616</v>
-      </c>
-      <c r="C86" t="s">
-        <v>496</v>
-      </c>
-      <c r="D86" t="s">
-        <v>218</v>
-      </c>
-      <c r="E86" t="s">
-        <v>617</v>
-      </c>
-      <c r="F86" t="s">
-        <v>618</v>
-      </c>
-      <c r="G86" t="s">
-        <v>619</v>
-      </c>
-      <c r="H86" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
@@ -5249,25 +5279,25 @@
         <v>79</v>
       </c>
       <c r="B87" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="C87" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D87" t="s">
         <v>159</v>
       </c>
       <c r="E87" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="F87" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="G87" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="H87" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
@@ -5275,25 +5305,25 @@
         <v>91</v>
       </c>
       <c r="B88" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C88" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D88" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E88" t="s">
+        <v>618</v>
+      </c>
+      <c r="F88" t="s">
         <v>622</v>
       </c>
-      <c r="F88" t="s">
-        <v>626</v>
-      </c>
       <c r="G88" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="H88" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
@@ -5301,25 +5331,25 @@
         <v>118</v>
       </c>
       <c r="B89" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="C89" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="D89" t="s">
         <v>152</v>
       </c>
       <c r="E89" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="F89" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="G89" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="H89" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
@@ -5327,25 +5357,25 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="C90" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="D90" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E90" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="F90" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G90" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="H90" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
@@ -5353,25 +5383,25 @@
         <v>121</v>
       </c>
       <c r="B91" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="C91" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="D91" t="s">
         <v>152</v>
       </c>
       <c r="E91" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="F91" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="G91" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="H91" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
@@ -5379,25 +5409,25 @@
         <v>67</v>
       </c>
       <c r="B92" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="C92" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="D92" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E92" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="F92" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="G92" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="H92" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
@@ -5405,25 +5435,25 @@
         <v>49</v>
       </c>
       <c r="B93" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="C93" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="D93" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E93" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="F93" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="G93" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="H93" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
@@ -5431,25 +5461,25 @@
         <v>31</v>
       </c>
       <c r="B94" t="s">
+        <v>648</v>
+      </c>
+      <c r="C94" t="s">
+        <v>438</v>
+      </c>
+      <c r="D94" t="s">
+        <v>217</v>
+      </c>
+      <c r="E94" t="s">
+        <v>649</v>
+      </c>
+      <c r="F94" t="s">
+        <v>650</v>
+      </c>
+      <c r="G94" t="s">
+        <v>651</v>
+      </c>
+      <c r="H94" t="s">
         <v>652</v>
-      </c>
-      <c r="C94" t="s">
-        <v>442</v>
-      </c>
-      <c r="D94" t="s">
-        <v>218</v>
-      </c>
-      <c r="E94" t="s">
-        <v>653</v>
-      </c>
-      <c r="F94" t="s">
-        <v>654</v>
-      </c>
-      <c r="G94" t="s">
-        <v>655</v>
-      </c>
-      <c r="H94" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
@@ -5457,25 +5487,25 @@
         <v>109</v>
       </c>
       <c r="B95" t="s">
-        <v>657</v>
+        <v>701</v>
       </c>
       <c r="C95" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D95" t="s">
         <v>159</v>
       </c>
       <c r="E95" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="F95" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="G95" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="H95" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
@@ -5483,25 +5513,25 @@
         <v>71</v>
       </c>
       <c r="B96" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="C96" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="D96" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E96" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="F96" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="G96" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="H96" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
@@ -5509,25 +5539,25 @@
         <v>128</v>
       </c>
       <c r="B97" t="s">
+        <v>659</v>
+      </c>
+      <c r="C97" t="s">
+        <v>660</v>
+      </c>
+      <c r="D97" t="s">
+        <v>224</v>
+      </c>
+      <c r="E97" t="s">
+        <v>661</v>
+      </c>
+      <c r="F97" t="s">
+        <v>662</v>
+      </c>
+      <c r="G97" t="s">
+        <v>663</v>
+      </c>
+      <c r="H97" t="s">
         <v>664</v>
-      </c>
-      <c r="C97" t="s">
-        <v>665</v>
-      </c>
-      <c r="D97" t="s">
-        <v>225</v>
-      </c>
-      <c r="E97" t="s">
-        <v>666</v>
-      </c>
-      <c r="F97" t="s">
-        <v>667</v>
-      </c>
-      <c r="G97" t="s">
-        <v>668</v>
-      </c>
-      <c r="H97" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
@@ -5535,25 +5565,25 @@
         <v>95</v>
       </c>
       <c r="B98" t="s">
-        <v>670</v>
+        <v>702</v>
       </c>
       <c r="C98" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D98" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E98" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="F98" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="G98" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="H98" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
@@ -5561,25 +5591,25 @@
         <v>133</v>
       </c>
       <c r="B99" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="C99" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="D99" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E99" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="F99" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="G99" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="H99" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
@@ -5587,25 +5617,25 @@
         <v>17</v>
       </c>
       <c r="B100" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="C100" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="D100" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E100" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="F100" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="G100" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="H100" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
@@ -5613,25 +5643,25 @@
         <v>113</v>
       </c>
       <c r="B101" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="C101" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D101" t="s">
         <v>152</v>
       </c>
       <c r="E101" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="F101" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="G101" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="H101" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
     </row>
   </sheetData>
@@ -6426,7 +6456,7 @@
       </c>
       <c r="L23" s="6" t="str">
         <f>IFERROR(VLOOKUP($J23,Data!$A:$D,2,FALSE),"")</f>
-        <v>Explicit Free Resolutions for Central Quotients of Cyclic Amalgams</v>
+        <v>Resolutions for Quotients of One-Relator Groups</v>
       </c>
       <c r="M23" s="6" t="str">
         <f>IFERROR(VLOOKUP($J23,Data!$A:$D,3,FALSE),"")</f>
@@ -6841,7 +6871,7 @@
       </c>
       <c r="D34" s="6" t="str">
         <f>IFERROR(VLOOKUP($B34,Data!$A:$D,2,FALSE),"")</f>
-        <v>Quantifying Information Propagation in Diffusion Posterior Sampling for Ocean Flows</v>
+        <v>Quantifying the Information Availability of Spatial Observations for Ocean Flow Field Reconstruction with Diffusion Posterior Sampling</v>
       </c>
       <c r="E34" s="6" t="str">
         <f>IFERROR(VLOOKUP($B34,Data!$A:$D,3,FALSE),"")</f>
@@ -6871,7 +6901,7 @@
       </c>
       <c r="L34" s="6" t="str">
         <f>IFERROR(VLOOKUP($J34,Data!$A:$D,2,FALSE),"")</f>
-        <v>Improving the Reliability of Hypersonic Airplane Engines Through Bleed Configurations</v>
+        <v>Low-Reynolds-Number Porous Bleed for Separation Control on Hypersonic Airplanes</v>
       </c>
       <c r="M34" s="6" t="str">
         <f>IFERROR(VLOOKUP($J34,Data!$A:$D,3,FALSE),"")</f>
@@ -7086,7 +7116,7 @@
       </c>
       <c r="D41" s="6" t="str">
         <f>IFERROR(VLOOKUP($B41,Data!$A:$D,2,FALSE),"")</f>
-        <v>Structure Analysis using Partial Grotrian Diagram Construction and Isotope-Shift Systematics of Pa I,II,IV,V and Statistical Synthesis of Comagnetometer Constants</v>
+        <v>Gyromagnetic Ratio and Protactinium Isotope-Shift Mapping for Electric Dipole Moment Searches</v>
       </c>
       <c r="E41" s="6" t="str">
         <f>IFERROR(VLOOKUP($B41,Data!$A:$D,3,FALSE),"")</f>
@@ -7216,7 +7246,7 @@
       </c>
       <c r="L43" s="6" t="str">
         <f>IFERROR(VLOOKUP($J43,Data!$A:$D,2,FALSE),"")</f>
-        <v>Comorbidity-shaped cell states in Alzheimer’s disease: a single-nucleus dissection of 15 clinical phenotypes</v>
+        <v>Single-Nucleus Dissection of Nine Alzheimer's Disease Comorbidities</v>
       </c>
       <c r="M43" s="6" t="str">
         <f>IFERROR(VLOOKUP($J43,Data!$A:$D,3,FALSE),"")</f>
@@ -7370,7 +7400,7 @@
     </row>
     <row r="51" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>12</v>
+        <v>706</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>116</v>
@@ -7420,7 +7450,7 @@
     </row>
     <row r="52" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>16</v>
+        <v>707</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>119</v>
@@ -7470,7 +7500,7 @@
     </row>
     <row r="53" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>20</v>
+        <v>708</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>122</v>
@@ -7520,7 +7550,7 @@
     </row>
     <row r="54" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>24</v>
+        <v>709</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>125</v>
@@ -7570,7 +7600,7 @@
     </row>
     <row r="55" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
-        <v>28</v>
+        <v>710</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>128</v>
@@ -7620,7 +7650,7 @@
     </row>
     <row r="56" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
-        <v>32</v>
+        <v>711</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>131</v>
@@ -7646,7 +7676,7 @@
       </c>
       <c r="H56" s="6" t="str">
         <f>IFERROR(VLOOKUP($F56,Data!$A:$D,2,FALSE),"")</f>
-        <v>Characterizing Myo15-Cre Recombination in Cochlear Hair Cells to Validate Disease Models for Usher Syndrome Type 1F Gene Therapy</v>
+        <v>Mapping Myo-15 Cre Activity in Cochleae to Validate Disease Models for​ Usher Syndrome Type 1F Gene Therapy</v>
       </c>
       <c r="I56" s="6" t="str">
         <f>IFERROR(VLOOKUP($F56,Data!$A:$D,3,FALSE),"")</f>
@@ -7765,7 +7795,7 @@
     </row>
     <row r="61" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
-        <v>38</v>
+        <v>712</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>135</v>
@@ -7815,7 +7845,7 @@
     </row>
     <row r="62" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
-        <v>42</v>
+        <v>713</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>138</v>
@@ -7865,7 +7895,7 @@
     </row>
     <row r="63" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>46</v>
+        <v>714</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>141</v>
@@ -7913,7 +7943,7 @@
     </row>
     <row r="64" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
-        <v>50</v>
+        <v>715</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>143</v>

--- a/RSI_2026_Schedule.xlsx
+++ b/RSI_2026_Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/evanlim/Documents/rsi-symposium/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59407157-8428-F64D-B470-68EA287FDB36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0CAC5F9-9860-5141-858E-CF225DE2A465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="706">
   <si>
     <t>RSI 2026 Symposium Schedule</t>
   </si>
@@ -75,9 +75,6 @@
     <t>Mentor</t>
   </si>
   <si>
-    <t>9:00 AM – 9:16 AM</t>
-  </si>
-  <si>
     <t>Mira Cakmak</t>
   </si>
   <si>
@@ -87,9 +84,6 @@
     <t>Anushka Tonapi</t>
   </si>
   <si>
-    <t>9:16 AM – 9:32 AM</t>
-  </si>
-  <si>
     <t>Zephyr Larson</t>
   </si>
   <si>
@@ -99,9 +93,6 @@
     <t>Grisham Paimagam</t>
   </si>
   <si>
-    <t>9:32 AM – 9:48 AM</t>
-  </si>
-  <si>
     <t>Alejandro Mayorga</t>
   </si>
   <si>
@@ -111,9 +102,6 @@
     <t>Katrina Liu</t>
   </si>
   <si>
-    <t>9:48 AM – 10:04 AM</t>
-  </si>
-  <si>
     <t>Eric Buehler</t>
   </si>
   <si>
@@ -123,9 +111,6 @@
     <t>Lincoln Liu</t>
   </si>
   <si>
-    <t>10:04 AM – 10:20 AM</t>
-  </si>
-  <si>
     <t>Layth Alzahrani</t>
   </si>
   <si>
@@ -135,9 +120,6 @@
     <t>Tony Lu</t>
   </si>
   <si>
-    <t>10:20 AM – 10:36 AM</t>
-  </si>
-  <si>
     <t>Kai Xuen Toh</t>
   </si>
   <si>
@@ -153,9 +135,6 @@
     <t>Block T2 (11:00 AM – 12:30 PM)</t>
   </si>
   <si>
-    <t>11:00 AM – 11:16 AM</t>
-  </si>
-  <si>
     <t>Eason Turner</t>
   </si>
   <si>
@@ -165,9 +144,6 @@
     <t>Sirius Sun</t>
   </si>
   <si>
-    <t>11:16 AM – 11:32 AM</t>
-  </si>
-  <si>
     <t>Miguel Shim</t>
   </si>
   <si>
@@ -177,9 +153,6 @@
     <t>Nikola Veselinov</t>
   </si>
   <si>
-    <t>11:32 AM – 11:48 AM</t>
-  </si>
-  <si>
     <t>Sylvia Lee</t>
   </si>
   <si>
@@ -189,9 +162,6 @@
     <t>Timothy Chen</t>
   </si>
   <si>
-    <t>11:48 AM – 12:04 PM</t>
-  </si>
-  <si>
     <t>Pavan Subramani</t>
   </si>
   <si>
@@ -201,9 +171,6 @@
     <t>Jay Athipatla</t>
   </si>
   <si>
-    <t>12:04 PM – 12:20 PM</t>
-  </si>
-  <si>
     <t>Cassidy Stocker</t>
   </si>
   <si>
@@ -213,9 +180,6 @@
     <t>Leyu Girma</t>
   </si>
   <si>
-    <t>12:20 PM – 12:36 PM</t>
-  </si>
-  <si>
     <t>Sara Mitchell</t>
   </si>
   <si>
@@ -231,9 +195,6 @@
     <t>Block T3 (1:15 PM – 2:45 PM)</t>
   </si>
   <si>
-    <t>1:15 PM – 1:31 PM</t>
-  </si>
-  <si>
     <t>Atharva Tyagi</t>
   </si>
   <si>
@@ -243,9 +204,6 @@
     <t>Tara Saini</t>
   </si>
   <si>
-    <t>1:31 PM – 1:47 PM</t>
-  </si>
-  <si>
     <t>Ayush Vispute</t>
   </si>
   <si>
@@ -255,9 +213,6 @@
     <t>Xindi Luo</t>
   </si>
   <si>
-    <t>1:47 PM – 2:03 PM</t>
-  </si>
-  <si>
     <t>Bryan Cho</t>
   </si>
   <si>
@@ -267,9 +222,6 @@
     <t>Greeshma Vinoy</t>
   </si>
   <si>
-    <t>2:03 PM – 2:19 PM</t>
-  </si>
-  <si>
     <t>Claire Zhan</t>
   </si>
   <si>
@@ -279,9 +231,6 @@
     <t>Sofia Passos</t>
   </si>
   <si>
-    <t>2:19 PM – 2:35 PM</t>
-  </si>
-  <si>
     <t>Malin Janna Vega</t>
   </si>
   <si>
@@ -291,9 +240,6 @@
     <t>Can Nalbantoglu</t>
   </si>
   <si>
-    <t>2:35 PM – 2:51 PM</t>
-  </si>
-  <si>
     <t>Sarah Dingli</t>
   </si>
   <si>
@@ -309,9 +255,6 @@
     <t>Block T4 (3:15 PM – 4:45 PM)</t>
   </si>
   <si>
-    <t>3:15 PM – 3:31 PM</t>
-  </si>
-  <si>
     <t>Sophia Zhao</t>
   </si>
   <si>
@@ -321,9 +264,6 @@
     <t>Alex Ren</t>
   </si>
   <si>
-    <t>3:31 PM – 3:47 PM</t>
-  </si>
-  <si>
     <t>Yong Ding</t>
   </si>
   <si>
@@ -333,9 +273,6 @@
     <t>Amogh Dattatri</t>
   </si>
   <si>
-    <t>3:47 PM – 4:03 PM</t>
-  </si>
-  <si>
     <t>Dhruv Jain</t>
   </si>
   <si>
@@ -345,9 +282,6 @@
     <t>Chloe Giglio</t>
   </si>
   <si>
-    <t>4:03 PM – 4:19 PM</t>
-  </si>
-  <si>
     <t>Aaryan Patel</t>
   </si>
   <si>
@@ -357,9 +291,6 @@
     <t>Ipek Zeynioğlu</t>
   </si>
   <si>
-    <t>4:19 PM – 4:35 PM</t>
-  </si>
-  <si>
     <t>Andy Jo</t>
   </si>
   <si>
@@ -369,9 +300,6 @@
     <t>Tristan Sun</t>
   </si>
   <si>
-    <t>4:35 PM – 4:51 PM</t>
-  </si>
-  <si>
     <t>Jay Desai</t>
   </si>
   <si>
@@ -879,9 +807,6 @@
     <t>cfyzhan</t>
   </si>
   <si>
-    <t>Detecting Long-Transit Exoplanets via Better Detrending TESS Light Curves</t>
-  </si>
-  <si>
     <t>Katharine Hesse</t>
   </si>
   <si>
@@ -2169,12 +2094,6 @@
     <t>9:45 AM – 10:00 AM</t>
   </si>
   <si>
-    <t>10:00 AM – 10:30 AM</t>
-  </si>
-  <si>
-    <t>10:30 AM – 10:45 AM</t>
-  </si>
-  <si>
     <t>11:00 AM – 11:15 AM</t>
   </si>
   <si>
@@ -2185,6 +2104,57 @@
   </si>
   <si>
     <t>11:45 AM – 12:00 PM</t>
+  </si>
+  <si>
+    <t>Recovering Long-Transit Planet Signals in TESS Light Curves with Improved KeplerSpline Detrending</t>
+  </si>
+  <si>
+    <t>12:00 PM – 12:15 PM</t>
+  </si>
+  <si>
+    <t>12:15 PM – 12:30 PM</t>
+  </si>
+  <si>
+    <t>10:00 AM – 10:15 AM</t>
+  </si>
+  <si>
+    <t>10:15 AM – 10:30 AM</t>
+  </si>
+  <si>
+    <t>1:15 PM – 1:30 PM</t>
+  </si>
+  <si>
+    <t>1:30 PM – 1:45 PM</t>
+  </si>
+  <si>
+    <t>1:45 PM – 2:00 PM</t>
+  </si>
+  <si>
+    <t>2:00 PM – 2:15 PM</t>
+  </si>
+  <si>
+    <t>2:15 PM – 2:30 PM</t>
+  </si>
+  <si>
+    <t>2:30 PM – 2:45 PM</t>
+  </si>
+  <si>
+    <t>3:15 PM – 3:30 PM</t>
+  </si>
+  <si>
+    <t>3:30 PM – 3:45 PM</t>
+  </si>
+  <si>
+    <t>3:45 PM – 4:00 PM</t>
+  </si>
+  <si>
+    <t>4:00 PM – 4:15 PM</t>
+  </si>
+  <si>
+    <t>4:15 PM – 4:30 PM</t>
+  </si>
+  <si>
+    <t>4:30 PM – 4:45 PM</t>
   </si>
 </sst>
 </file>
@@ -3040,7 +3010,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>10</v>
@@ -3052,2616 +3022,2616 @@
         <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="D2" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="E2" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="F2" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="G2" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="H2" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="B3" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="C3" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="D3" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E3" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="F3" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="G3" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="H3" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="B4" t="s">
-        <v>700</v>
+        <v>675</v>
       </c>
       <c r="C4" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="D4" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E4" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="F4" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="G4" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="H4" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="C5" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="D5" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E5" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="F5" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="G5" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="H5" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="C6" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="D6" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="E6" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="F6" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="G6" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="H6" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>692</v>
+        <v>667</v>
       </c>
       <c r="C7" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="D7" t="s">
+        <v>135</v>
+      </c>
+      <c r="E7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F7" t="s">
         <v>159</v>
       </c>
-      <c r="E7" t="s">
-        <v>182</v>
-      </c>
-      <c r="F7" t="s">
-        <v>183</v>
-      </c>
       <c r="G7" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="H7" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="B8" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="C8" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="D8" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E8" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="F8" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G8" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="H8" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="C9" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="D9" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E9" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="F9" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="G9" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="H9" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="B10" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="C10" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="D10" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E10" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="F10" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="G10" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="H10" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="C11" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="D11" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E11" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="F11" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="G11" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="H11" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="B12" t="s">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c r="C12" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="D12" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="E12" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="F12" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="G12" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="H12" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="C13" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="D13" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="E13" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="F13" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="G13" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="H13" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="C14" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="D14" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E14" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="F14" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="G14" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="H14" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="B15" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="C15" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="D15" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="E15" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="F15" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="G15" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="H15" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="B16" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="C16" t="s">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="D16" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="E16" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="F16" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="G16" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="H16" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="B17" t="s">
-        <v>241</v>
+        <v>217</v>
       </c>
       <c r="C17" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="D17" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="E17" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="F17" t="s">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="G17" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="H17" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="B18" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="C18" t="s">
-        <v>660</v>
+        <v>635</v>
       </c>
       <c r="D18" t="s">
+        <v>200</v>
+      </c>
+      <c r="E18" t="s">
+        <v>223</v>
+      </c>
+      <c r="F18" t="s">
         <v>224</v>
       </c>
-      <c r="E18" t="s">
-        <v>247</v>
-      </c>
-      <c r="F18" t="s">
-        <v>248</v>
-      </c>
       <c r="G18" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="H18" t="s">
-        <v>250</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>251</v>
+        <v>227</v>
       </c>
       <c r="C19" t="s">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="D19" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="E19" t="s">
-        <v>253</v>
+        <v>229</v>
       </c>
       <c r="F19" t="s">
-        <v>254</v>
+        <v>230</v>
       </c>
       <c r="G19" t="s">
-        <v>255</v>
+        <v>231</v>
       </c>
       <c r="H19" t="s">
-        <v>256</v>
+        <v>232</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="B20" t="s">
-        <v>694</v>
+        <v>669</v>
       </c>
       <c r="C20" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="D20" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="E20" t="s">
-        <v>257</v>
+        <v>233</v>
       </c>
       <c r="F20" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G20" t="s">
-        <v>258</v>
+        <v>234</v>
       </c>
       <c r="H20" t="s">
-        <v>259</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="B21" t="s">
-        <v>691</v>
+        <v>666</v>
       </c>
       <c r="C21" t="s">
-        <v>260</v>
+        <v>236</v>
       </c>
       <c r="D21" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="E21" t="s">
-        <v>261</v>
+        <v>237</v>
       </c>
       <c r="F21" t="s">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="G21" t="s">
-        <v>263</v>
+        <v>239</v>
       </c>
       <c r="H21" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B22" t="s">
-        <v>689</v>
+        <v>664</v>
       </c>
       <c r="C22" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
       <c r="D22" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E22" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="F22" t="s">
-        <v>267</v>
+        <v>243</v>
       </c>
       <c r="G22" t="s">
-        <v>268</v>
+        <v>244</v>
       </c>
       <c r="H22" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="B23" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="C23" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="D23" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E23" t="s">
-        <v>271</v>
+        <v>247</v>
       </c>
       <c r="F23" t="s">
-        <v>272</v>
+        <v>248</v>
       </c>
       <c r="G23" t="s">
-        <v>273</v>
+        <v>249</v>
       </c>
       <c r="H23" t="s">
-        <v>274</v>
+        <v>250</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="B24" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="C24" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="D24" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="E24" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="F24" t="s">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="G24" t="s">
-        <v>278</v>
+        <v>254</v>
       </c>
       <c r="H24" t="s">
-        <v>279</v>
+        <v>255</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s">
-        <v>280</v>
+        <v>689</v>
       </c>
       <c r="C25" t="s">
-        <v>281</v>
+        <v>256</v>
       </c>
       <c r="D25" t="s">
-        <v>282</v>
+        <v>257</v>
       </c>
       <c r="E25" t="s">
-        <v>283</v>
+        <v>258</v>
       </c>
       <c r="F25" t="s">
-        <v>284</v>
+        <v>259</v>
       </c>
       <c r="G25" t="s">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="H25" t="s">
-        <v>286</v>
+        <v>261</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="B26" t="s">
-        <v>703</v>
+        <v>678</v>
       </c>
       <c r="C26" t="s">
-        <v>287</v>
+        <v>262</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>263</v>
       </c>
       <c r="E26" t="s">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="F26" t="s">
-        <v>290</v>
+        <v>265</v>
       </c>
       <c r="G26" t="s">
-        <v>291</v>
+        <v>266</v>
       </c>
       <c r="H26" t="s">
-        <v>292</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="B27" t="s">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="C27" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="D27" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="E27" t="s">
-        <v>295</v>
+        <v>270</v>
       </c>
       <c r="F27" t="s">
-        <v>296</v>
+        <v>271</v>
       </c>
       <c r="G27" t="s">
-        <v>297</v>
+        <v>272</v>
       </c>
       <c r="H27" t="s">
-        <v>298</v>
+        <v>273</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="B28" t="s">
-        <v>305</v>
+        <v>280</v>
       </c>
       <c r="C28" t="s">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="D28" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="E28" t="s">
-        <v>301</v>
+        <v>276</v>
       </c>
       <c r="F28" t="s">
-        <v>302</v>
+        <v>277</v>
       </c>
       <c r="G28" t="s">
-        <v>306</v>
+        <v>281</v>
       </c>
       <c r="H28" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="B29" t="s">
-        <v>299</v>
+        <v>274</v>
       </c>
       <c r="C29" t="s">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="D29" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="E29" t="s">
-        <v>301</v>
+        <v>276</v>
       </c>
       <c r="F29" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="G29" t="s">
-        <v>303</v>
+        <v>278</v>
       </c>
       <c r="H29" t="s">
-        <v>304</v>
+        <v>279</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="B30" t="s">
-        <v>308</v>
+        <v>283</v>
       </c>
       <c r="C30" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="D30" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="E30" t="s">
-        <v>309</v>
+        <v>284</v>
       </c>
       <c r="F30" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="G30" t="s">
-        <v>311</v>
+        <v>286</v>
       </c>
       <c r="H30" t="s">
-        <v>312</v>
+        <v>287</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>705</v>
+        <v>680</v>
       </c>
       <c r="C31" t="s">
-        <v>313</v>
+        <v>288</v>
       </c>
       <c r="D31" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="E31" t="s">
-        <v>314</v>
+        <v>289</v>
       </c>
       <c r="F31" t="s">
-        <v>315</v>
+        <v>290</v>
       </c>
       <c r="G31" t="s">
-        <v>316</v>
+        <v>291</v>
       </c>
       <c r="H31" t="s">
-        <v>317</v>
+        <v>292</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="B32" t="s">
-        <v>318</v>
+        <v>293</v>
       </c>
       <c r="C32" t="s">
-        <v>319</v>
+        <v>294</v>
       </c>
       <c r="D32" t="s">
-        <v>320</v>
+        <v>295</v>
       </c>
       <c r="E32" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="F32" t="s">
-        <v>322</v>
+        <v>297</v>
       </c>
       <c r="G32" t="s">
-        <v>323</v>
+        <v>298</v>
       </c>
       <c r="H32" t="s">
-        <v>324</v>
+        <v>299</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="C33" t="s">
-        <v>326</v>
+        <v>301</v>
       </c>
       <c r="D33" t="s">
-        <v>282</v>
+        <v>257</v>
       </c>
       <c r="E33" t="s">
-        <v>327</v>
+        <v>302</v>
       </c>
       <c r="F33" t="s">
-        <v>328</v>
+        <v>303</v>
       </c>
       <c r="G33" t="s">
-        <v>329</v>
+        <v>304</v>
       </c>
       <c r="H33" t="s">
-        <v>330</v>
+        <v>305</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>693</v>
+        <v>668</v>
       </c>
       <c r="C34" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="D34" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="E34" t="s">
-        <v>331</v>
+        <v>306</v>
       </c>
       <c r="F34" t="s">
-        <v>332</v>
+        <v>307</v>
       </c>
       <c r="G34" t="s">
-        <v>333</v>
+        <v>308</v>
       </c>
       <c r="H34" t="s">
-        <v>334</v>
+        <v>309</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>697</v>
+        <v>672</v>
       </c>
       <c r="C35" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="D35" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="E35" t="s">
-        <v>335</v>
+        <v>310</v>
       </c>
       <c r="F35" t="s">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="G35" t="s">
-        <v>337</v>
+        <v>312</v>
       </c>
       <c r="H35" t="s">
-        <v>338</v>
+        <v>313</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="B36" t="s">
-        <v>339</v>
+        <v>314</v>
       </c>
       <c r="C36" t="s">
-        <v>340</v>
+        <v>315</v>
       </c>
       <c r="D36" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E36" t="s">
-        <v>341</v>
+        <v>316</v>
       </c>
       <c r="F36" t="s">
-        <v>342</v>
+        <v>317</v>
       </c>
       <c r="G36" t="s">
-        <v>343</v>
+        <v>318</v>
       </c>
       <c r="H36" t="s">
-        <v>344</v>
+        <v>319</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>345</v>
+        <v>320</v>
       </c>
       <c r="C37" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="D37" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="E37" t="s">
-        <v>346</v>
+        <v>321</v>
       </c>
       <c r="F37" t="s">
-        <v>347</v>
+        <v>322</v>
       </c>
       <c r="G37" t="s">
-        <v>348</v>
+        <v>323</v>
       </c>
       <c r="H37" t="s">
-        <v>349</v>
+        <v>324</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="B38" t="s">
-        <v>350</v>
+        <v>325</v>
       </c>
       <c r="C38" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="D38" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E38" t="s">
-        <v>351</v>
+        <v>326</v>
       </c>
       <c r="F38" t="s">
-        <v>352</v>
+        <v>327</v>
       </c>
       <c r="G38" t="s">
-        <v>353</v>
+        <v>328</v>
       </c>
       <c r="H38" t="s">
-        <v>354</v>
+        <v>329</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="B39" t="s">
-        <v>355</v>
+        <v>330</v>
       </c>
       <c r="C39" t="s">
-        <v>356</v>
+        <v>331</v>
       </c>
       <c r="D39" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E39" t="s">
-        <v>357</v>
+        <v>332</v>
       </c>
       <c r="F39" t="s">
-        <v>358</v>
+        <v>333</v>
       </c>
       <c r="G39" t="s">
-        <v>359</v>
+        <v>334</v>
       </c>
       <c r="H39" t="s">
-        <v>360</v>
+        <v>335</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="B40" t="s">
-        <v>361</v>
+        <v>336</v>
       </c>
       <c r="C40" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="D40" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="E40" t="s">
-        <v>362</v>
+        <v>337</v>
       </c>
       <c r="F40" t="s">
-        <v>363</v>
+        <v>338</v>
       </c>
       <c r="G40" t="s">
-        <v>364</v>
+        <v>339</v>
       </c>
       <c r="H40" t="s">
-        <v>365</v>
+        <v>340</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="B41" t="s">
-        <v>366</v>
+        <v>341</v>
       </c>
       <c r="C41" t="s">
-        <v>367</v>
+        <v>342</v>
       </c>
       <c r="D41" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E41" t="s">
-        <v>368</v>
+        <v>343</v>
       </c>
       <c r="F41" t="s">
-        <v>369</v>
+        <v>344</v>
       </c>
       <c r="G41" t="s">
-        <v>370</v>
+        <v>345</v>
       </c>
       <c r="H41" t="s">
-        <v>371</v>
+        <v>346</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>378</v>
+        <v>353</v>
       </c>
       <c r="C42" t="s">
-        <v>373</v>
+        <v>348</v>
       </c>
       <c r="D42" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="E42" t="s">
-        <v>374</v>
+        <v>349</v>
       </c>
       <c r="F42" t="s">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="G42" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
       <c r="H42" t="s">
-        <v>381</v>
+        <v>356</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="B43" t="s">
-        <v>372</v>
+        <v>347</v>
       </c>
       <c r="C43" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="D43" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="E43" t="s">
-        <v>374</v>
+        <v>349</v>
       </c>
       <c r="F43" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
       <c r="G43" t="s">
-        <v>376</v>
+        <v>351</v>
       </c>
       <c r="H43" t="s">
-        <v>377</v>
+        <v>352</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="B44" t="s">
-        <v>382</v>
+        <v>357</v>
       </c>
       <c r="C44" t="s">
-        <v>383</v>
+        <v>358</v>
       </c>
       <c r="D44" t="s">
-        <v>288</v>
+        <v>263</v>
       </c>
       <c r="E44" t="s">
-        <v>384</v>
+        <v>359</v>
       </c>
       <c r="F44" t="s">
-        <v>385</v>
+        <v>360</v>
       </c>
       <c r="G44" t="s">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="H44" t="s">
-        <v>387</v>
+        <v>362</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B45" t="s">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="C45" t="s">
-        <v>389</v>
+        <v>364</v>
       </c>
       <c r="D45" t="s">
-        <v>282</v>
+        <v>257</v>
       </c>
       <c r="E45" t="s">
-        <v>390</v>
+        <v>365</v>
       </c>
       <c r="F45" t="s">
-        <v>391</v>
+        <v>366</v>
       </c>
       <c r="G45" t="s">
-        <v>392</v>
+        <v>367</v>
       </c>
       <c r="H45" t="s">
-        <v>393</v>
+        <v>368</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="B46" t="s">
-        <v>394</v>
+        <v>369</v>
       </c>
       <c r="C46" t="s">
-        <v>395</v>
+        <v>370</v>
       </c>
       <c r="D46" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E46" t="s">
-        <v>396</v>
+        <v>371</v>
       </c>
       <c r="F46" t="s">
-        <v>397</v>
+        <v>372</v>
       </c>
       <c r="G46" t="s">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="H46" t="s">
-        <v>399</v>
+        <v>374</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="B47" t="s">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="C47" t="s">
-        <v>401</v>
+        <v>376</v>
       </c>
       <c r="D47" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="E47" t="s">
-        <v>403</v>
+        <v>378</v>
       </c>
       <c r="F47" t="s">
-        <v>404</v>
+        <v>379</v>
       </c>
       <c r="G47" t="s">
-        <v>405</v>
+        <v>380</v>
       </c>
       <c r="H47" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B48" t="s">
-        <v>407</v>
+        <v>382</v>
       </c>
       <c r="C48" t="s">
-        <v>408</v>
+        <v>383</v>
       </c>
       <c r="D48" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="E48" t="s">
-        <v>409</v>
+        <v>384</v>
       </c>
       <c r="F48" t="s">
-        <v>410</v>
+        <v>385</v>
       </c>
       <c r="G48" t="s">
-        <v>411</v>
+        <v>386</v>
       </c>
       <c r="H48" t="s">
-        <v>412</v>
+        <v>387</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="B49" t="s">
-        <v>413</v>
+        <v>388</v>
       </c>
       <c r="C49" t="s">
-        <v>414</v>
+        <v>389</v>
       </c>
       <c r="D49" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E49" t="s">
-        <v>415</v>
+        <v>390</v>
       </c>
       <c r="F49" t="s">
-        <v>416</v>
+        <v>391</v>
       </c>
       <c r="G49" t="s">
-        <v>417</v>
+        <v>392</v>
       </c>
       <c r="H49" t="s">
-        <v>418</v>
+        <v>393</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B50" t="s">
-        <v>419</v>
+        <v>394</v>
       </c>
       <c r="C50" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="D50" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="E50" t="s">
-        <v>420</v>
+        <v>395</v>
       </c>
       <c r="F50" t="s">
-        <v>421</v>
+        <v>396</v>
       </c>
       <c r="G50" t="s">
-        <v>422</v>
+        <v>397</v>
       </c>
       <c r="H50" t="s">
-        <v>423</v>
+        <v>398</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B51" t="s">
-        <v>424</v>
+        <v>399</v>
       </c>
       <c r="C51" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="D51" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="E51" t="s">
-        <v>425</v>
+        <v>400</v>
       </c>
       <c r="F51" t="s">
-        <v>426</v>
+        <v>401</v>
       </c>
       <c r="G51" t="s">
-        <v>427</v>
+        <v>402</v>
       </c>
       <c r="H51" t="s">
-        <v>428</v>
+        <v>403</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B52" t="s">
-        <v>704</v>
+        <v>679</v>
       </c>
       <c r="C52" t="s">
-        <v>373</v>
+        <v>348</v>
       </c>
       <c r="D52" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="E52" t="s">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="F52" t="s">
-        <v>430</v>
+        <v>405</v>
       </c>
       <c r="G52" t="s">
-        <v>431</v>
+        <v>406</v>
       </c>
       <c r="H52" t="s">
-        <v>432</v>
+        <v>407</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="B53" t="s">
-        <v>433</v>
+        <v>408</v>
       </c>
       <c r="C53" t="s">
-        <v>281</v>
+        <v>256</v>
       </c>
       <c r="D53" t="s">
-        <v>282</v>
+        <v>257</v>
       </c>
       <c r="E53" t="s">
-        <v>434</v>
+        <v>409</v>
       </c>
       <c r="F53" t="s">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="G53" t="s">
-        <v>435</v>
+        <v>410</v>
       </c>
       <c r="H53" t="s">
-        <v>436</v>
+        <v>411</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B54" t="s">
-        <v>437</v>
+        <v>412</v>
       </c>
       <c r="C54" t="s">
-        <v>438</v>
+        <v>413</v>
       </c>
       <c r="D54" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="E54" t="s">
-        <v>439</v>
+        <v>414</v>
       </c>
       <c r="F54" t="s">
-        <v>410</v>
+        <v>385</v>
       </c>
       <c r="G54" t="s">
-        <v>440</v>
+        <v>415</v>
       </c>
       <c r="H54" t="s">
-        <v>441</v>
+        <v>416</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B55" t="s">
-        <v>442</v>
+        <v>417</v>
       </c>
       <c r="C55" t="s">
-        <v>443</v>
+        <v>418</v>
       </c>
       <c r="D55" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="E55" t="s">
-        <v>444</v>
+        <v>419</v>
       </c>
       <c r="F55" t="s">
-        <v>445</v>
+        <v>420</v>
       </c>
       <c r="G55" t="s">
-        <v>446</v>
+        <v>421</v>
       </c>
       <c r="H55" t="s">
-        <v>447</v>
+        <v>422</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="B56" t="s">
-        <v>448</v>
+        <v>423</v>
       </c>
       <c r="C56" t="s">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="D56" t="s">
-        <v>288</v>
+        <v>263</v>
       </c>
       <c r="E56" t="s">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="F56" t="s">
-        <v>451</v>
+        <v>426</v>
       </c>
       <c r="G56" t="s">
-        <v>452</v>
+        <v>427</v>
       </c>
       <c r="H56" t="s">
-        <v>453</v>
+        <v>428</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="B57" t="s">
-        <v>454</v>
+        <v>429</v>
       </c>
       <c r="C57" t="s">
-        <v>455</v>
+        <v>430</v>
       </c>
       <c r="D57" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E57" t="s">
-        <v>456</v>
+        <v>431</v>
       </c>
       <c r="F57" t="s">
-        <v>457</v>
+        <v>432</v>
       </c>
       <c r="G57" t="s">
-        <v>458</v>
+        <v>433</v>
       </c>
       <c r="H57" t="s">
-        <v>459</v>
+        <v>434</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="B58" t="s">
-        <v>699</v>
+        <v>674</v>
       </c>
       <c r="C58" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="D58" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E58" t="s">
-        <v>460</v>
+        <v>435</v>
       </c>
       <c r="F58" t="s">
-        <v>461</v>
+        <v>436</v>
       </c>
       <c r="G58" t="s">
-        <v>462</v>
+        <v>437</v>
       </c>
       <c r="H58" t="s">
-        <v>463</v>
+        <v>438</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B59" t="s">
-        <v>464</v>
+        <v>439</v>
       </c>
       <c r="C59" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="D59" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E59" t="s">
-        <v>465</v>
+        <v>440</v>
       </c>
       <c r="F59" t="s">
-        <v>466</v>
+        <v>441</v>
       </c>
       <c r="G59" t="s">
-        <v>467</v>
+        <v>442</v>
       </c>
       <c r="H59" t="s">
-        <v>468</v>
+        <v>443</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="B60" t="s">
-        <v>469</v>
+        <v>444</v>
       </c>
       <c r="C60" t="s">
-        <v>470</v>
+        <v>445</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>295</v>
       </c>
       <c r="E60" t="s">
-        <v>471</v>
+        <v>446</v>
       </c>
       <c r="F60" t="s">
-        <v>472</v>
+        <v>447</v>
       </c>
       <c r="G60" t="s">
-        <v>473</v>
+        <v>448</v>
       </c>
       <c r="H60" t="s">
-        <v>474</v>
+        <v>449</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="B61" t="s">
-        <v>475</v>
+        <v>450</v>
       </c>
       <c r="C61" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="D61" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="E61" t="s">
-        <v>476</v>
+        <v>451</v>
       </c>
       <c r="F61" t="s">
-        <v>477</v>
+        <v>452</v>
       </c>
       <c r="G61" t="s">
-        <v>478</v>
+        <v>453</v>
       </c>
       <c r="H61" t="s">
-        <v>479</v>
+        <v>454</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B62" t="s">
-        <v>480</v>
+        <v>455</v>
       </c>
       <c r="C62" t="s">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="D62" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="E62" t="s">
-        <v>481</v>
+        <v>456</v>
       </c>
       <c r="F62" t="s">
-        <v>482</v>
+        <v>457</v>
       </c>
       <c r="G62" t="s">
-        <v>483</v>
+        <v>458</v>
       </c>
       <c r="H62" t="s">
-        <v>484</v>
+        <v>459</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="B63" t="s">
-        <v>485</v>
+        <v>460</v>
       </c>
       <c r="C63" t="s">
-        <v>486</v>
+        <v>461</v>
       </c>
       <c r="D63" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E63" t="s">
-        <v>487</v>
+        <v>462</v>
       </c>
       <c r="F63" t="s">
-        <v>488</v>
+        <v>463</v>
       </c>
       <c r="G63" t="s">
-        <v>489</v>
+        <v>464</v>
       </c>
       <c r="H63" t="s">
-        <v>490</v>
+        <v>465</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B64" t="s">
-        <v>491</v>
+        <v>466</v>
       </c>
       <c r="C64" t="s">
-        <v>492</v>
+        <v>467</v>
       </c>
       <c r="D64" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="E64" t="s">
-        <v>493</v>
+        <v>468</v>
       </c>
       <c r="F64" t="s">
-        <v>494</v>
+        <v>469</v>
       </c>
       <c r="G64" t="s">
-        <v>495</v>
+        <v>470</v>
       </c>
       <c r="H64" t="s">
-        <v>496</v>
+        <v>471</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B65" t="s">
-        <v>497</v>
+        <v>472</v>
       </c>
       <c r="C65" t="s">
-        <v>498</v>
+        <v>473</v>
       </c>
       <c r="D65" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="E65" t="s">
-        <v>499</v>
+        <v>474</v>
       </c>
       <c r="F65" t="s">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="G65" t="s">
-        <v>501</v>
+        <v>476</v>
       </c>
       <c r="H65" t="s">
-        <v>502</v>
+        <v>477</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B66" t="s">
-        <v>503</v>
+        <v>478</v>
       </c>
       <c r="C66" t="s">
-        <v>443</v>
+        <v>418</v>
       </c>
       <c r="D66" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="E66" t="s">
-        <v>504</v>
+        <v>479</v>
       </c>
       <c r="F66" t="s">
-        <v>505</v>
+        <v>480</v>
       </c>
       <c r="G66" t="s">
-        <v>506</v>
+        <v>481</v>
       </c>
       <c r="H66" t="s">
-        <v>507</v>
+        <v>482</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>508</v>
+        <v>483</v>
       </c>
       <c r="C67" t="s">
-        <v>509</v>
+        <v>484</v>
       </c>
       <c r="D67" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="E67" t="s">
-        <v>510</v>
+        <v>485</v>
       </c>
       <c r="F67" t="s">
-        <v>511</v>
+        <v>486</v>
       </c>
       <c r="G67" t="s">
-        <v>512</v>
+        <v>487</v>
       </c>
       <c r="H67" t="s">
-        <v>513</v>
+        <v>488</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B68" t="s">
-        <v>698</v>
+        <v>673</v>
       </c>
       <c r="C68" t="s">
-        <v>514</v>
+        <v>489</v>
       </c>
       <c r="D68" t="s">
-        <v>288</v>
+        <v>263</v>
       </c>
       <c r="E68" t="s">
-        <v>515</v>
+        <v>490</v>
       </c>
       <c r="F68" t="s">
-        <v>516</v>
+        <v>491</v>
       </c>
       <c r="G68" t="s">
-        <v>517</v>
+        <v>492</v>
       </c>
       <c r="H68" t="s">
-        <v>518</v>
+        <v>493</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>519</v>
+        <v>494</v>
       </c>
       <c r="C69" t="s">
-        <v>520</v>
+        <v>495</v>
       </c>
       <c r="D69" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="E69" t="s">
-        <v>521</v>
+        <v>496</v>
       </c>
       <c r="F69" t="s">
-        <v>522</v>
+        <v>497</v>
       </c>
       <c r="G69" t="s">
-        <v>523</v>
+        <v>498</v>
       </c>
       <c r="H69" t="s">
-        <v>524</v>
+        <v>499</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="B70" t="s">
-        <v>525</v>
+        <v>500</v>
       </c>
       <c r="C70" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="D70" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="E70" t="s">
-        <v>526</v>
+        <v>501</v>
       </c>
       <c r="F70" t="s">
-        <v>527</v>
+        <v>502</v>
       </c>
       <c r="G70" t="s">
-        <v>528</v>
+        <v>503</v>
       </c>
       <c r="H70" t="s">
-        <v>529</v>
+        <v>504</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="B71" t="s">
-        <v>530</v>
+        <v>505</v>
       </c>
       <c r="C71" t="s">
-        <v>695</v>
+        <v>670</v>
       </c>
       <c r="D71" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="E71" t="s">
-        <v>531</v>
+        <v>506</v>
       </c>
       <c r="F71" t="s">
-        <v>532</v>
+        <v>507</v>
       </c>
       <c r="G71" t="s">
-        <v>533</v>
+        <v>508</v>
       </c>
       <c r="H71" t="s">
-        <v>534</v>
+        <v>509</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B72" t="s">
-        <v>535</v>
+        <v>510</v>
       </c>
       <c r="C72" t="s">
-        <v>536</v>
+        <v>511</v>
       </c>
       <c r="D72" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="E72" t="s">
-        <v>537</v>
+        <v>512</v>
       </c>
       <c r="F72" t="s">
-        <v>538</v>
+        <v>513</v>
       </c>
       <c r="G72" t="s">
-        <v>539</v>
+        <v>514</v>
       </c>
       <c r="H72" t="s">
-        <v>540</v>
+        <v>515</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B73" t="s">
-        <v>541</v>
+        <v>516</v>
       </c>
       <c r="C73" t="s">
-        <v>542</v>
+        <v>517</v>
       </c>
       <c r="D73" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="E73" t="s">
-        <v>543</v>
+        <v>518</v>
       </c>
       <c r="F73" t="s">
-        <v>544</v>
+        <v>519</v>
       </c>
       <c r="G73" t="s">
-        <v>545</v>
+        <v>520</v>
       </c>
       <c r="H73" t="s">
-        <v>546</v>
+        <v>521</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
+        <v>111</v>
+      </c>
+      <c r="B74" t="s">
+        <v>661</v>
+      </c>
+      <c r="C74" t="s">
+        <v>522</v>
+      </c>
+      <c r="D74" t="s">
         <v>135</v>
       </c>
-      <c r="B74" t="s">
-        <v>686</v>
-      </c>
-      <c r="C74" t="s">
-        <v>547</v>
-      </c>
-      <c r="D74" t="s">
-        <v>159</v>
-      </c>
       <c r="E74" t="s">
-        <v>548</v>
+        <v>523</v>
       </c>
       <c r="F74" t="s">
-        <v>549</v>
+        <v>524</v>
       </c>
       <c r="G74" t="s">
-        <v>550</v>
+        <v>525</v>
       </c>
       <c r="H74" t="s">
-        <v>551</v>
+        <v>526</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B75" t="s">
-        <v>552</v>
+        <v>527</v>
       </c>
       <c r="C75" t="s">
-        <v>687</v>
+        <v>662</v>
       </c>
       <c r="D75" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="E75" t="s">
-        <v>553</v>
+        <v>528</v>
       </c>
       <c r="F75" t="s">
-        <v>554</v>
+        <v>529</v>
       </c>
       <c r="G75" t="s">
-        <v>555</v>
+        <v>530</v>
       </c>
       <c r="H75" t="s">
-        <v>556</v>
+        <v>531</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B76" t="s">
-        <v>557</v>
+        <v>532</v>
       </c>
       <c r="C76" t="s">
-        <v>558</v>
+        <v>533</v>
       </c>
       <c r="D76" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="E76" t="s">
-        <v>559</v>
+        <v>534</v>
       </c>
       <c r="F76" t="s">
-        <v>560</v>
+        <v>535</v>
       </c>
       <c r="G76" t="s">
-        <v>561</v>
+        <v>536</v>
       </c>
       <c r="H76" t="s">
-        <v>562</v>
+        <v>537</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="B77" t="s">
-        <v>563</v>
+        <v>538</v>
       </c>
       <c r="C77" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="D77" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="E77" t="s">
-        <v>564</v>
+        <v>539</v>
       </c>
       <c r="F77" t="s">
-        <v>565</v>
+        <v>540</v>
       </c>
       <c r="G77" t="s">
-        <v>566</v>
+        <v>541</v>
       </c>
       <c r="H77" t="s">
-        <v>567</v>
+        <v>542</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="B78" t="s">
-        <v>568</v>
+        <v>543</v>
       </c>
       <c r="C78" t="s">
-        <v>569</v>
+        <v>544</v>
       </c>
       <c r="D78" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E78" t="s">
-        <v>570</v>
+        <v>545</v>
       </c>
       <c r="F78" t="s">
-        <v>571</v>
+        <v>546</v>
       </c>
       <c r="G78" t="s">
-        <v>572</v>
+        <v>547</v>
       </c>
       <c r="H78" t="s">
-        <v>573</v>
+        <v>548</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="B79" t="s">
-        <v>574</v>
+        <v>549</v>
       </c>
       <c r="C79" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
       <c r="D79" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E79" t="s">
-        <v>575</v>
+        <v>550</v>
       </c>
       <c r="F79" t="s">
-        <v>576</v>
+        <v>551</v>
       </c>
       <c r="G79" t="s">
-        <v>577</v>
+        <v>552</v>
       </c>
       <c r="H79" t="s">
-        <v>578</v>
+        <v>553</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B80" t="s">
-        <v>579</v>
+        <v>554</v>
       </c>
       <c r="C80" t="s">
-        <v>580</v>
+        <v>555</v>
       </c>
       <c r="D80" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E80" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="F80" t="s">
-        <v>582</v>
+        <v>557</v>
       </c>
       <c r="G80" t="s">
-        <v>583</v>
+        <v>558</v>
       </c>
       <c r="H80" t="s">
-        <v>584</v>
+        <v>559</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="B81" t="s">
-        <v>585</v>
+        <v>560</v>
       </c>
       <c r="C81" t="s">
-        <v>486</v>
+        <v>461</v>
       </c>
       <c r="D81" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E81" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="F81" t="s">
-        <v>586</v>
+        <v>561</v>
       </c>
       <c r="G81" t="s">
-        <v>587</v>
+        <v>562</v>
       </c>
       <c r="H81" t="s">
-        <v>588</v>
+        <v>563</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="B82" t="s">
-        <v>589</v>
+        <v>564</v>
       </c>
       <c r="C82" t="s">
-        <v>401</v>
+        <v>376</v>
       </c>
       <c r="D82" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="E82" t="s">
-        <v>590</v>
+        <v>565</v>
       </c>
       <c r="F82" t="s">
-        <v>591</v>
+        <v>566</v>
       </c>
       <c r="G82" t="s">
-        <v>592</v>
+        <v>567</v>
       </c>
       <c r="H82" t="s">
-        <v>593</v>
+        <v>568</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B83" t="s">
-        <v>594</v>
+        <v>569</v>
       </c>
       <c r="C83" t="s">
-        <v>595</v>
+        <v>570</v>
       </c>
       <c r="D83" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E83" t="s">
-        <v>596</v>
+        <v>571</v>
       </c>
       <c r="F83" t="s">
-        <v>597</v>
+        <v>572</v>
       </c>
       <c r="G83" t="s">
-        <v>598</v>
+        <v>573</v>
       </c>
       <c r="H83" t="s">
-        <v>599</v>
+        <v>574</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="B84" t="s">
-        <v>600</v>
+        <v>575</v>
       </c>
       <c r="C84" t="s">
-        <v>601</v>
+        <v>576</v>
       </c>
       <c r="D84" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="E84" t="s">
-        <v>602</v>
+        <v>577</v>
       </c>
       <c r="F84" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="G84" t="s">
-        <v>604</v>
+        <v>579</v>
       </c>
       <c r="H84" t="s">
-        <v>605</v>
+        <v>580</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B85" t="s">
-        <v>606</v>
+        <v>581</v>
       </c>
       <c r="C85" t="s">
-        <v>607</v>
+        <v>582</v>
       </c>
       <c r="D85" t="s">
-        <v>282</v>
+        <v>257</v>
       </c>
       <c r="E85" t="s">
-        <v>608</v>
+        <v>583</v>
       </c>
       <c r="F85" t="s">
-        <v>609</v>
+        <v>584</v>
       </c>
       <c r="G85" t="s">
-        <v>610</v>
+        <v>585</v>
       </c>
       <c r="H85" t="s">
-        <v>611</v>
+        <v>586</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B86" t="s">
-        <v>612</v>
+        <v>587</v>
       </c>
       <c r="C86" t="s">
-        <v>492</v>
+        <v>467</v>
       </c>
       <c r="D86" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="E86" t="s">
-        <v>613</v>
+        <v>588</v>
       </c>
       <c r="F86" t="s">
-        <v>614</v>
+        <v>589</v>
       </c>
       <c r="G86" t="s">
-        <v>615</v>
+        <v>590</v>
       </c>
       <c r="H86" t="s">
-        <v>616</v>
+        <v>591</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="B87" t="s">
-        <v>617</v>
+        <v>592</v>
       </c>
       <c r="C87" t="s">
-        <v>340</v>
+        <v>315</v>
       </c>
       <c r="D87" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E87" t="s">
-        <v>618</v>
+        <v>593</v>
       </c>
       <c r="F87" t="s">
-        <v>619</v>
+        <v>594</v>
       </c>
       <c r="G87" t="s">
-        <v>620</v>
+        <v>595</v>
       </c>
       <c r="H87" t="s">
-        <v>621</v>
+        <v>596</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="B88" t="s">
-        <v>696</v>
+        <v>671</v>
       </c>
       <c r="C88" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="D88" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="E88" t="s">
-        <v>618</v>
+        <v>593</v>
       </c>
       <c r="F88" t="s">
-        <v>622</v>
+        <v>597</v>
       </c>
       <c r="G88" t="s">
-        <v>623</v>
+        <v>598</v>
       </c>
       <c r="H88" t="s">
-        <v>624</v>
+        <v>599</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>625</v>
+        <v>600</v>
       </c>
       <c r="C89" t="s">
-        <v>626</v>
+        <v>601</v>
       </c>
       <c r="D89" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="E89" t="s">
-        <v>627</v>
+        <v>602</v>
       </c>
       <c r="F89" t="s">
-        <v>628</v>
+        <v>603</v>
       </c>
       <c r="G89" t="s">
-        <v>629</v>
+        <v>604</v>
       </c>
       <c r="H89" t="s">
-        <v>630</v>
+        <v>605</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B90" t="s">
-        <v>631</v>
+        <v>606</v>
       </c>
       <c r="C90" t="s">
-        <v>498</v>
+        <v>473</v>
       </c>
       <c r="D90" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="E90" t="s">
-        <v>632</v>
+        <v>607</v>
       </c>
       <c r="F90" t="s">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="G90" t="s">
-        <v>633</v>
+        <v>608</v>
       </c>
       <c r="H90" t="s">
-        <v>634</v>
+        <v>609</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="B91" t="s">
-        <v>635</v>
+        <v>610</v>
       </c>
       <c r="C91" t="s">
-        <v>626</v>
+        <v>601</v>
       </c>
       <c r="D91" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="E91" t="s">
-        <v>636</v>
+        <v>611</v>
       </c>
       <c r="F91" t="s">
-        <v>637</v>
+        <v>612</v>
       </c>
       <c r="G91" t="s">
-        <v>638</v>
+        <v>613</v>
       </c>
       <c r="H91" t="s">
-        <v>639</v>
+        <v>614</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="B92" t="s">
-        <v>690</v>
+        <v>665</v>
       </c>
       <c r="C92" t="s">
-        <v>558</v>
+        <v>533</v>
       </c>
       <c r="D92" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="E92" t="s">
-        <v>640</v>
+        <v>615</v>
       </c>
       <c r="F92" t="s">
-        <v>641</v>
+        <v>616</v>
       </c>
       <c r="G92" t="s">
-        <v>642</v>
+        <v>617</v>
       </c>
       <c r="H92" t="s">
-        <v>643</v>
+        <v>618</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B93" t="s">
-        <v>644</v>
+        <v>619</v>
       </c>
       <c r="C93" t="s">
-        <v>536</v>
+        <v>511</v>
       </c>
       <c r="D93" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="E93" t="s">
-        <v>645</v>
+        <v>620</v>
       </c>
       <c r="F93" t="s">
-        <v>457</v>
+        <v>432</v>
       </c>
       <c r="G93" t="s">
-        <v>646</v>
+        <v>621</v>
       </c>
       <c r="H93" t="s">
-        <v>647</v>
+        <v>622</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B94" t="s">
-        <v>648</v>
+        <v>623</v>
       </c>
       <c r="C94" t="s">
-        <v>438</v>
+        <v>413</v>
       </c>
       <c r="D94" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="E94" t="s">
-        <v>649</v>
+        <v>624</v>
       </c>
       <c r="F94" t="s">
-        <v>650</v>
+        <v>625</v>
       </c>
       <c r="G94" t="s">
-        <v>651</v>
+        <v>626</v>
       </c>
       <c r="H94" t="s">
-        <v>652</v>
+        <v>627</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="B95" t="s">
-        <v>701</v>
+        <v>676</v>
       </c>
       <c r="C95" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="D95" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E95" t="s">
-        <v>653</v>
+        <v>628</v>
       </c>
       <c r="F95" t="s">
-        <v>614</v>
+        <v>589</v>
       </c>
       <c r="G95" t="s">
-        <v>654</v>
+        <v>629</v>
       </c>
       <c r="H95" t="s">
-        <v>655</v>
+        <v>630</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B96" t="s">
-        <v>688</v>
+        <v>663</v>
       </c>
       <c r="C96" t="s">
-        <v>558</v>
+        <v>533</v>
       </c>
       <c r="D96" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="E96" t="s">
-        <v>656</v>
+        <v>631</v>
       </c>
       <c r="F96" t="s">
-        <v>494</v>
+        <v>469</v>
       </c>
       <c r="G96" t="s">
-        <v>657</v>
+        <v>632</v>
       </c>
       <c r="H96" t="s">
-        <v>658</v>
+        <v>633</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="B97" t="s">
-        <v>659</v>
+        <v>634</v>
       </c>
       <c r="C97" t="s">
-        <v>660</v>
+        <v>635</v>
       </c>
       <c r="D97" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="E97" t="s">
-        <v>661</v>
+        <v>636</v>
       </c>
       <c r="F97" t="s">
-        <v>662</v>
+        <v>637</v>
       </c>
       <c r="G97" t="s">
-        <v>663</v>
+        <v>638</v>
       </c>
       <c r="H97" t="s">
-        <v>664</v>
+        <v>639</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="B98" t="s">
-        <v>702</v>
+        <v>677</v>
       </c>
       <c r="C98" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="D98" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="E98" t="s">
-        <v>665</v>
+        <v>640</v>
       </c>
       <c r="F98" t="s">
-        <v>666</v>
+        <v>641</v>
       </c>
       <c r="G98" t="s">
-        <v>667</v>
+        <v>642</v>
       </c>
       <c r="H98" t="s">
-        <v>668</v>
+        <v>643</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="B99" t="s">
-        <v>669</v>
+        <v>644</v>
       </c>
       <c r="C99" t="s">
-        <v>670</v>
+        <v>645</v>
       </c>
       <c r="D99" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="E99" t="s">
-        <v>671</v>
+        <v>646</v>
       </c>
       <c r="F99" t="s">
-        <v>672</v>
+        <v>647</v>
       </c>
       <c r="G99" t="s">
-        <v>673</v>
+        <v>648</v>
       </c>
       <c r="H99" t="s">
-        <v>674</v>
+        <v>649</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B100" t="s">
-        <v>675</v>
+        <v>650</v>
       </c>
       <c r="C100" t="s">
-        <v>676</v>
+        <v>651</v>
       </c>
       <c r="D100" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="E100" t="s">
-        <v>677</v>
+        <v>652</v>
       </c>
       <c r="F100" t="s">
-        <v>678</v>
+        <v>653</v>
       </c>
       <c r="G100" t="s">
-        <v>679</v>
+        <v>654</v>
       </c>
       <c r="H100" t="s">
-        <v>680</v>
+        <v>655</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="B101" t="s">
-        <v>681</v>
+        <v>656</v>
       </c>
       <c r="C101" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="D101" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="E101" t="s">
-        <v>682</v>
+        <v>657</v>
       </c>
       <c r="F101" t="s">
-        <v>683</v>
+        <v>658</v>
       </c>
       <c r="G101" t="s">
-        <v>684</v>
+        <v>659</v>
       </c>
       <c r="H101" t="s">
-        <v>685</v>
+        <v>660</v>
       </c>
     </row>
   </sheetData>
@@ -5820,10 +5790,10 @@
     </row>
     <row r="9" spans="1:13" ht="39" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>12</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>13</v>
       </c>
       <c r="C9" s="6" t="str">
         <f>IFERROR(VLOOKUP($B9,Data!$A:$D,4,FALSE),"")</f>
@@ -5838,7 +5808,7 @@
         <v>Dr. Daniel Press and Dr. Hsueh-Sheng Chiang</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G9" s="6" t="str">
         <f>IFERROR(VLOOKUP($F9,Data!$A:$D,4,FALSE),"")</f>
@@ -5853,7 +5823,7 @@
         <v>Prof. Vivek Venkatachalam</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K9" s="6" t="str">
         <f>IFERROR(VLOOKUP($J9,Data!$A:$D,4,FALSE),"")</f>
@@ -5870,10 +5840,10 @@
     </row>
     <row r="10" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>16</v>
+        <v>682</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10" s="6" t="str">
         <f>IFERROR(VLOOKUP($B10,Data!$A:$D,4,FALSE),"")</f>
@@ -5888,7 +5858,7 @@
         <v>Prof. Paul O'Gorman</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G10" s="6" t="str">
         <f>IFERROR(VLOOKUP($F10,Data!$A:$D,4,FALSE),"")</f>
@@ -5903,7 +5873,7 @@
         <v>Prof. Vivek Venkatachalam</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K10" s="6" t="str">
         <f>IFERROR(VLOOKUP($J10,Data!$A:$D,4,FALSE),"")</f>
@@ -5920,10 +5890,10 @@
     </row>
     <row r="11" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>20</v>
+        <v>683</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C11" s="6" t="str">
         <f>IFERROR(VLOOKUP($B11,Data!$A:$D,4,FALSE),"")</f>
@@ -5938,7 +5908,7 @@
         <v>Dr. Bo Wu</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G11" s="6" t="str">
         <f>IFERROR(VLOOKUP($F11,Data!$A:$D,4,FALSE),"")</f>
@@ -5953,7 +5923,7 @@
         <v>Prof. Vivek Venkatachalam</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="K11" s="6" t="str">
         <f>IFERROR(VLOOKUP($J11,Data!$A:$D,4,FALSE),"")</f>
@@ -5970,10 +5940,10 @@
     </row>
     <row r="12" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>24</v>
+        <v>684</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C12" s="6" t="str">
         <f>IFERROR(VLOOKUP($B12,Data!$A:$D,4,FALSE),"")</f>
@@ -5988,7 +5958,7 @@
         <v>Dr. Bo Wu</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G12" s="6" t="str">
         <f>IFERROR(VLOOKUP($F12,Data!$A:$D,4,FALSE),"")</f>
@@ -6003,7 +5973,7 @@
         <v>Timothy Gomez</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="K12" s="6" t="str">
         <f>IFERROR(VLOOKUP($J12,Data!$A:$D,4,FALSE),"")</f>
@@ -6020,10 +5990,10 @@
     </row>
     <row r="13" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>28</v>
+        <v>692</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C13" s="6" t="str">
         <f>IFERROR(VLOOKUP($B13,Data!$A:$D,4,FALSE),"")</f>
@@ -6038,7 +6008,7 @@
         <v>Dr. Bo Wu</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G13" s="6" t="str">
         <f>IFERROR(VLOOKUP($F13,Data!$A:$D,4,FALSE),"")</f>
@@ -6053,7 +6023,7 @@
         <v>Timothy Gomez</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="K13" s="6" t="str">
         <f>IFERROR(VLOOKUP($J13,Data!$A:$D,4,FALSE),"")</f>
@@ -6070,10 +6040,10 @@
     </row>
     <row r="14" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>32</v>
+        <v>693</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C14" s="6" t="str">
         <f>IFERROR(VLOOKUP($B14,Data!$A:$D,4,FALSE),"")</f>
@@ -6088,7 +6058,7 @@
         <v>Prof. Sara Seager</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G14" s="6" t="str">
         <f>IFERROR(VLOOKUP($F14,Data!$A:$D,4,FALSE),"")</f>
@@ -6103,7 +6073,7 @@
         <v>Dr. James Sullivan</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="K14" s="6" t="str">
         <f>IFERROR(VLOOKUP($J14,Data!$A:$D,4,FALSE),"")</f>
@@ -6120,7 +6090,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -6137,7 +6107,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -6215,10 +6185,10 @@
     </row>
     <row r="19" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>38</v>
+        <v>685</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C19" s="6" t="str">
         <f>IFERROR(VLOOKUP($B19,Data!$A:$D,4,FALSE),"")</f>
@@ -6233,7 +6203,7 @@
         <v>Dr. Rosanne Di Stefano</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G19" s="6" t="str">
         <f>IFERROR(VLOOKUP($F19,Data!$A:$D,4,FALSE),"")</f>
@@ -6248,7 +6218,7 @@
         <v>Prof. Vladan Vuletic</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K19" s="6" t="str">
         <f>IFERROR(VLOOKUP($J19,Data!$A:$D,4,FALSE),"")</f>
@@ -6265,10 +6235,10 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>42</v>
+        <v>686</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C20" s="6" t="str">
         <f>IFERROR(VLOOKUP($B20,Data!$A:$D,4,FALSE),"")</f>
@@ -6283,7 +6253,7 @@
         <v>Ashu Tripathi</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G20" s="6" t="str">
         <f>IFERROR(VLOOKUP($F20,Data!$A:$D,4,FALSE),"")</f>
@@ -6298,7 +6268,7 @@
         <v>Prof. Vladan Vuletic</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="K20" s="6" t="str">
         <f>IFERROR(VLOOKUP($J20,Data!$A:$D,4,FALSE),"")</f>
@@ -6315,10 +6285,10 @@
     </row>
     <row r="21" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>46</v>
+        <v>687</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C21" s="6" t="str">
         <f>IFERROR(VLOOKUP($B21,Data!$A:$D,4,FALSE),"")</f>
@@ -6333,7 +6303,7 @@
         <v>Ashu Tripathi</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="G21" s="6" t="str">
         <f>IFERROR(VLOOKUP($F21,Data!$A:$D,4,FALSE),"")</f>
@@ -6348,7 +6318,7 @@
         <v>Prof. Francis Loth and Hannah Higgins</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="K21" s="6" t="str">
         <f>IFERROR(VLOOKUP($J21,Data!$A:$D,4,FALSE),"")</f>
@@ -6365,10 +6335,10 @@
     </row>
     <row r="22" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>50</v>
+        <v>688</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C22" s="6" t="str">
         <f>IFERROR(VLOOKUP($B22,Data!$A:$D,4,FALSE),"")</f>
@@ -6383,7 +6353,7 @@
         <v>Dr. Mrinal Shekhar</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="G22" s="6" t="str">
         <f>IFERROR(VLOOKUP($F22,Data!$A:$D,4,FALSE),"")</f>
@@ -6398,7 +6368,7 @@
         <v>Dr. Howard Chen</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="K22" s="6" t="str">
         <f>IFERROR(VLOOKUP($J22,Data!$A:$D,4,FALSE),"")</f>
@@ -6415,10 +6385,10 @@
     </row>
     <row r="23" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>54</v>
+        <v>690</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C23" s="6" t="str">
         <f>IFERROR(VLOOKUP($B23,Data!$A:$D,4,FALSE),"")</f>
@@ -6433,7 +6403,7 @@
         <v>Dr. Robbie G. Majzner</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G23" s="6" t="str">
         <f>IFERROR(VLOOKUP($F23,Data!$A:$D,4,FALSE),"")</f>
@@ -6448,7 +6418,7 @@
         <v>Dr. Sarah Bricault</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="K23" s="6" t="str">
         <f>IFERROR(VLOOKUP($J23,Data!$A:$D,4,FALSE),"")</f>
@@ -6465,10 +6435,10 @@
     </row>
     <row r="24" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>58</v>
+        <v>691</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C24" s="6" t="str">
         <f>IFERROR(VLOOKUP($B24,Data!$A:$D,4,FALSE),"")</f>
@@ -6483,7 +6453,7 @@
         <v>Dr. Robbie G. Majzner</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G24" s="6" t="str">
         <f>IFERROR(VLOOKUP($F24,Data!$A:$D,4,FALSE),"")</f>
@@ -6498,7 +6468,7 @@
         <v>Dr. Ky Lowenhaupt</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="K24" s="6" t="str">
         <f>IFERROR(VLOOKUP($J24,Data!$A:$D,4,FALSE),"")</f>
@@ -6515,7 +6485,7 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -6532,7 +6502,7 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -6610,10 +6580,10 @@
     </row>
     <row r="29" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>64</v>
+        <v>694</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C29" s="6" t="str">
         <f>IFERROR(VLOOKUP($B29,Data!$A:$D,4,FALSE),"")</f>
@@ -6628,7 +6598,7 @@
         <v>Prof. Pierre F.J Lermusiaux</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="G29" s="6" t="str">
         <f>IFERROR(VLOOKUP($F29,Data!$A:$D,4,FALSE),"")</f>
@@ -6643,7 +6613,7 @@
         <v>Prof. John D. E. Gabrieli</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="K29" s="6" t="str">
         <f>IFERROR(VLOOKUP($J29,Data!$A:$D,4,FALSE),"")</f>
@@ -6660,10 +6630,10 @@
     </row>
     <row r="30" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>68</v>
+        <v>695</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="C30" s="6" t="str">
         <f>IFERROR(VLOOKUP($B30,Data!$A:$D,4,FALSE),"")</f>
@@ -6678,7 +6648,7 @@
         <v>Prof. Pierre F.J Lermusiaux</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="G30" s="6" t="str">
         <f>IFERROR(VLOOKUP($F30,Data!$A:$D,4,FALSE),"")</f>
@@ -6693,7 +6663,7 @@
         <v>Prof. Chuchu Fan</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="K30" s="6" t="str">
         <f>IFERROR(VLOOKUP($J30,Data!$A:$D,4,FALSE),"")</f>
@@ -6710,10 +6680,10 @@
     </row>
     <row r="31" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>72</v>
+        <v>696</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C31" s="6" t="str">
         <f>IFERROR(VLOOKUP($B31,Data!$A:$D,4,FALSE),"")</f>
@@ -6728,7 +6698,7 @@
         <v>Prof. Pierre F.J Lermusiaux</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="G31" s="6" t="str">
         <f>IFERROR(VLOOKUP($F31,Data!$A:$D,4,FALSE),"")</f>
@@ -6743,7 +6713,7 @@
         <v>Prof. Chuchu Fan</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="K31" s="6" t="str">
         <f>IFERROR(VLOOKUP($J31,Data!$A:$D,4,FALSE),"")</f>
@@ -6760,10 +6730,10 @@
     </row>
     <row r="32" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>76</v>
+        <v>697</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C32" s="6" t="str">
         <f>IFERROR(VLOOKUP($B32,Data!$A:$D,4,FALSE),"")</f>
@@ -6778,7 +6748,7 @@
         <v>Prof. Pierre F.J Lermusiaux</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="G32" s="6" t="str">
         <f>IFERROR(VLOOKUP($F32,Data!$A:$D,4,FALSE),"")</f>
@@ -6793,7 +6763,7 @@
         <v>Prof. Chuchu Fan</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="K32" s="6" t="str">
         <f>IFERROR(VLOOKUP($J32,Data!$A:$D,4,FALSE),"")</f>
@@ -6810,10 +6780,10 @@
     </row>
     <row r="33" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>80</v>
+        <v>698</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C33" s="6" t="str">
         <f>IFERROR(VLOOKUP($B33,Data!$A:$D,4,FALSE),"")</f>
@@ -6828,7 +6798,7 @@
         <v>Prof. Pierre F.J Lermusiaux</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="G33" s="6" t="str">
         <f>IFERROR(VLOOKUP($F33,Data!$A:$D,4,FALSE),"")</f>
@@ -6843,7 +6813,7 @@
         <v>Prof. Chuchu Fan</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="K33" s="6" t="str">
         <f>IFERROR(VLOOKUP($J33,Data!$A:$D,4,FALSE),"")</f>
@@ -6860,10 +6830,10 @@
     </row>
     <row r="34" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>84</v>
+        <v>699</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="C34" s="6" t="str">
         <f>IFERROR(VLOOKUP($B34,Data!$A:$D,4,FALSE),"")</f>
@@ -6878,7 +6848,7 @@
         <v>Prof. Pierre F.J Lermusiaux</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="G34" s="6" t="str">
         <f>IFERROR(VLOOKUP($F34,Data!$A:$D,4,FALSE),"")</f>
@@ -6893,7 +6863,7 @@
         <v>Dr. Yogesh Rathi, Dr. Sinead Marie Kelly, Dr. Lipeng Ning</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="K34" s="6" t="str">
         <f>IFERROR(VLOOKUP($J34,Data!$A:$D,4,FALSE),"")</f>
@@ -6910,7 +6880,7 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -6927,7 +6897,7 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -7005,10 +6975,10 @@
     </row>
     <row r="39" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>90</v>
+        <v>700</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="C39" s="6" t="str">
         <f>IFERROR(VLOOKUP($B39,Data!$A:$D,4,FALSE),"")</f>
@@ -7023,7 +6993,7 @@
         <v>Prof. Pierre F.J Lermusiaux</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="G39" s="6" t="str">
         <f>IFERROR(VLOOKUP($F39,Data!$A:$D,4,FALSE),"")</f>
@@ -7038,7 +7008,7 @@
         <v>Prof. Timothy Miller</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="K39" s="6" t="str">
         <f>IFERROR(VLOOKUP($J39,Data!$A:$D,4,FALSE),"")</f>
@@ -7055,10 +7025,10 @@
     </row>
     <row r="40" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>94</v>
+        <v>701</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="C40" s="6" t="str">
         <f>IFERROR(VLOOKUP($B40,Data!$A:$D,4,FALSE),"")</f>
@@ -7073,7 +7043,7 @@
         <v>Prof. Ron Weiss</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="G40" s="6" t="str">
         <f>IFERROR(VLOOKUP($F40,Data!$A:$D,4,FALSE),"")</f>
@@ -7081,14 +7051,14 @@
       </c>
       <c r="H40" s="6" t="str">
         <f>IFERROR(VLOOKUP($F40,Data!$A:$D,2,FALSE),"")</f>
-        <v>Detecting Long-Transit Exoplanets via Better Detrending TESS Light Curves</v>
+        <v>Recovering Long-Transit Planet Signals in TESS Light Curves with Improved KeplerSpline Detrending</v>
       </c>
       <c r="I40" s="6" t="str">
         <f>IFERROR(VLOOKUP($F40,Data!$A:$D,3,FALSE),"")</f>
         <v>Katharine Hesse</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="K40" s="6" t="str">
         <f>IFERROR(VLOOKUP($J40,Data!$A:$D,4,FALSE),"")</f>
@@ -7105,10 +7075,10 @@
     </row>
     <row r="41" spans="1:13" ht="39" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>98</v>
+        <v>702</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="C41" s="6" t="str">
         <f>IFERROR(VLOOKUP($B41,Data!$A:$D,4,FALSE),"")</f>
@@ -7123,7 +7093,7 @@
         <v>Dr. Prajwal T. Mohan Murthy</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="G41" s="6" t="str">
         <f>IFERROR(VLOOKUP($F41,Data!$A:$D,4,FALSE),"")</f>
@@ -7138,7 +7108,7 @@
         <v>Katharine Hesse</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="K41" s="6" t="str">
         <f>IFERROR(VLOOKUP($J41,Data!$A:$D,4,FALSE),"")</f>
@@ -7155,10 +7125,10 @@
     </row>
     <row r="42" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>102</v>
+        <v>703</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="C42" s="6" t="str">
         <f>IFERROR(VLOOKUP($B42,Data!$A:$D,4,FALSE),"")</f>
@@ -7173,7 +7143,7 @@
         <v>Prof. Gil Alterovitz</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="G42" s="6" t="str">
         <f>IFERROR(VLOOKUP($F42,Data!$A:$D,4,FALSE),"")</f>
@@ -7188,7 +7158,7 @@
         <v>Prof. Min Dong</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="K42" s="6" t="str">
         <f>IFERROR(VLOOKUP($J42,Data!$A:$D,4,FALSE),"")</f>
@@ -7205,10 +7175,10 @@
     </row>
     <row r="43" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
-        <v>106</v>
+        <v>704</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="C43" s="6" t="str">
         <f>IFERROR(VLOOKUP($B43,Data!$A:$D,4,FALSE),"")</f>
@@ -7223,7 +7193,7 @@
         <v>Prof. Gil Alterovitz</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="G43" s="6" t="str">
         <f>IFERROR(VLOOKUP($F43,Data!$A:$D,4,FALSE),"")</f>
@@ -7238,7 +7208,7 @@
         <v>Dr. Muhammad Fahad Ehsan</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="K43" s="6" t="str">
         <f>IFERROR(VLOOKUP($J43,Data!$A:$D,4,FALSE),"")</f>
@@ -7255,10 +7225,10 @@
     </row>
     <row r="44" spans="1:13" ht="39" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>110</v>
+        <v>705</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="C44" s="6" t="str">
         <f>IFERROR(VLOOKUP($B44,Data!$A:$D,4,FALSE),"")</f>
@@ -7273,7 +7243,7 @@
         <v>Prof. Gil Alterovitz</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="G44" s="6" t="str">
         <f>IFERROR(VLOOKUP($F44,Data!$A:$D,4,FALSE),"")</f>
@@ -7288,7 +7258,7 @@
         <v>Dr. Buu Truong</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="K44" s="6" t="str">
         <f>IFERROR(VLOOKUP($J44,Data!$A:$D,4,FALSE),"")</f>
@@ -7305,7 +7275,7 @@
     </row>
     <row r="47" spans="1:13" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="14" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -7322,7 +7292,7 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" s="11" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
@@ -7400,10 +7370,10 @@
     </row>
     <row r="51" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>706</v>
+        <v>681</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="C51" s="6" t="str">
         <f>IFERROR(VLOOKUP($B51,Data!$A:$D,4,FALSE),"")</f>
@@ -7418,7 +7388,7 @@
         <v>Dr. Aaron Kesselheim</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="G51" s="6" t="str">
         <f>IFERROR(VLOOKUP($F51,Data!$A:$D,4,FALSE),"")</f>
@@ -7433,7 +7403,7 @@
         <v>Prof. Charles Hoffman</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="K51" s="6" t="str">
         <f>IFERROR(VLOOKUP($J51,Data!$A:$D,4,FALSE),"")</f>
@@ -7450,10 +7420,10 @@
     </row>
     <row r="52" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>707</v>
+        <v>682</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="C52" s="6" t="str">
         <f>IFERROR(VLOOKUP($B52,Data!$A:$D,4,FALSE),"")</f>
@@ -7468,7 +7438,7 @@
         <v>Prof. Markus Buehler</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="G52" s="6" t="str">
         <f>IFERROR(VLOOKUP($F52,Data!$A:$D,4,FALSE),"")</f>
@@ -7483,7 +7453,7 @@
         <v>Prof. Charles Hoffman</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="K52" s="6" t="str">
         <f>IFERROR(VLOOKUP($J52,Data!$A:$D,4,FALSE),"")</f>
@@ -7500,10 +7470,10 @@
     </row>
     <row r="53" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>708</v>
+        <v>683</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="C53" s="6" t="str">
         <f>IFERROR(VLOOKUP($B53,Data!$A:$D,4,FALSE),"")</f>
@@ -7518,7 +7488,7 @@
         <v>Prof. Markus Buehler</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="G53" s="6" t="str">
         <f>IFERROR(VLOOKUP($F53,Data!$A:$D,4,FALSE),"")</f>
@@ -7533,7 +7503,7 @@
         <v>Prof. Susan Hagen, Dr. Xu Xu</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="K53" s="6" t="str">
         <f>IFERROR(VLOOKUP($J53,Data!$A:$D,4,FALSE),"")</f>
@@ -7550,10 +7520,10 @@
     </row>
     <row r="54" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>709</v>
+        <v>684</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="C54" s="6" t="str">
         <f>IFERROR(VLOOKUP($B54,Data!$A:$D,4,FALSE),"")</f>
@@ -7568,7 +7538,7 @@
         <v>Prof. Jenny Hoffman</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="G54" s="6" t="str">
         <f>IFERROR(VLOOKUP($F54,Data!$A:$D,4,FALSE),"")</f>
@@ -7583,7 +7553,7 @@
         <v>Prof. Susan Hagen, Dr. Xu Xu</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="K54" s="6" t="str">
         <f>IFERROR(VLOOKUP($J54,Data!$A:$D,4,FALSE),"")</f>
@@ -7600,10 +7570,10 @@
     </row>
     <row r="55" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="C55" s="6" t="str">
         <f>IFERROR(VLOOKUP($B55,Data!$A:$D,4,FALSE),"")</f>
@@ -7618,7 +7588,7 @@
         <v>Prof. Jenny Hoffman</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="G55" s="6" t="str">
         <f>IFERROR(VLOOKUP($F55,Data!$A:$D,4,FALSE),"")</f>
@@ -7633,7 +7603,7 @@
         <v>Prof. Koroush Shirvan</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="K55" s="6" t="str">
         <f>IFERROR(VLOOKUP($J55,Data!$A:$D,4,FALSE),"")</f>
@@ -7650,10 +7620,10 @@
     </row>
     <row r="56" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
-        <v>711</v>
+        <v>693</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="C56" s="6" t="str">
         <f>IFERROR(VLOOKUP($B56,Data!$A:$D,4,FALSE),"")</f>
@@ -7668,7 +7638,7 @@
         <v>Dr. David T. Miyamoto</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="G56" s="6" t="str">
         <f>IFERROR(VLOOKUP($F56,Data!$A:$D,4,FALSE),"")</f>
@@ -7683,7 +7653,7 @@
         <v>Dr. Artur A. Indzhykulian</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="K56" s="6" t="str">
         <f>IFERROR(VLOOKUP($J56,Data!$A:$D,4,FALSE),"")</f>
@@ -7700,7 +7670,7 @@
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B57" s="9"/>
       <c r="C57" s="9"/>
@@ -7717,7 +7687,7 @@
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58" s="11" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="B58" s="9"/>
       <c r="C58" s="9"/>
@@ -7795,10 +7765,10 @@
     </row>
     <row r="61" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
-        <v>712</v>
+        <v>685</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="C61" s="6" t="str">
         <f>IFERROR(VLOOKUP($B61,Data!$A:$D,4,FALSE),"")</f>
@@ -7813,7 +7783,7 @@
         <v>Prof. Fengfeng Bei</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="G61" s="6" t="str">
         <f>IFERROR(VLOOKUP($F61,Data!$A:$D,4,FALSE),"")</f>
@@ -7828,7 +7798,7 @@
         <v>Prof. Maggie Qi, Shu Yang</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="K61" s="6" t="str">
         <f>IFERROR(VLOOKUP($J61,Data!$A:$D,4,FALSE),"")</f>
@@ -7845,10 +7815,10 @@
     </row>
     <row r="62" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
-        <v>713</v>
+        <v>686</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="C62" s="6" t="str">
         <f>IFERROR(VLOOKUP($B62,Data!$A:$D,4,FALSE),"")</f>
@@ -7863,7 +7833,7 @@
         <v>Prof. James Michaelson</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="G62" s="6" t="str">
         <f>IFERROR(VLOOKUP($F62,Data!$A:$D,4,FALSE),"")</f>
@@ -7878,7 +7848,7 @@
         <v>Prof. Maggie Qi, Shu Yang</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="K62" s="6" t="str">
         <f>IFERROR(VLOOKUP($J62,Data!$A:$D,4,FALSE),"")</f>
@@ -7895,10 +7865,10 @@
     </row>
     <row r="63" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>714</v>
+        <v>687</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="C63" s="6" t="str">
         <f>IFERROR(VLOOKUP($B63,Data!$A:$D,4,FALSE),"")</f>
@@ -7913,7 +7883,7 @@
         <v>Prof. James Michaelson</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="G63" s="6" t="str">
         <f>IFERROR(VLOOKUP($F63,Data!$A:$D,4,FALSE),"")</f>
@@ -7943,10 +7913,10 @@
     </row>
     <row r="64" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
-        <v>715</v>
+        <v>688</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="C64" s="6" t="str">
         <f>IFERROR(VLOOKUP($B64,Data!$A:$D,4,FALSE),"")</f>
@@ -7961,7 +7931,7 @@
         <v>Dr. Basak Icli</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="G64" s="6" t="str">
         <f>IFERROR(VLOOKUP($F64,Data!$A:$D,4,FALSE),"")</f>

--- a/RSI_2026_Schedule.xlsx
+++ b/RSI_2026_Schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/evanlim/Documents/rsi-symposium/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0CAC5F9-9860-5141-858E-CF225DE2A465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F32A43CB-F819-6C43-ADD4-BD4725E8E733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -1554,9 +1554,6 @@
     <t>namie</t>
   </si>
   <si>
-    <t>W-Flow: Continuous-variable Quantum State Tomography via Flow-based Generative Modeling</t>
-  </si>
-  <si>
     <t>No-wong</t>
   </si>
   <si>
@@ -2031,9 +2028,6 @@
     <t>A Taxicab Journey to Triangle Centres</t>
   </si>
   <si>
-    <t>Effect of ZAP70 Mutations on CAR T-Cell Effectiveness Targeting GD2 in Brain Tumors and N6 Leukemia Cells</t>
-  </si>
-  <si>
     <t>Enumerating Nilpotent Matrices over Finite Fields</t>
   </si>
   <si>
@@ -2155,6 +2149,12 @@
   </si>
   <si>
     <t>4:30 PM – 4:45 PM</t>
+  </si>
+  <si>
+    <t>Effect of ZAP70 Mutations on CAR T-Cell effectiveness Targeting GD2 in Cancer Cells</t>
+  </si>
+  <si>
+    <t>S-Flow: Harnessing Informed Sampling for Flow Models in Perturbation-Aware Quantum State Tomography</t>
   </si>
 </sst>
 </file>
@@ -3091,7 +3091,7 @@
         <v>108</v>
       </c>
       <c r="B4" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C4" t="s">
         <v>140</v>
@@ -3169,7 +3169,7 @@
         <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C7" t="s">
         <v>157</v>
@@ -3458,7 +3458,7 @@
         <v>222</v>
       </c>
       <c r="C18" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D18" t="s">
         <v>200</v>
@@ -3507,7 +3507,7 @@
         <v>58</v>
       </c>
       <c r="B20" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C20" t="s">
         <v>206</v>
@@ -3533,7 +3533,7 @@
         <v>66</v>
       </c>
       <c r="B21" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C21" t="s">
         <v>236</v>
@@ -3559,7 +3559,7 @@
         <v>44</v>
       </c>
       <c r="B22" t="s">
-        <v>664</v>
+        <v>704</v>
       </c>
       <c r="C22" t="s">
         <v>241</v>
@@ -3637,7 +3637,7 @@
         <v>76</v>
       </c>
       <c r="B25" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C25" t="s">
         <v>256</v>
@@ -3663,7 +3663,7 @@
         <v>69</v>
       </c>
       <c r="B26" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C26" t="s">
         <v>262</v>
@@ -3793,7 +3793,7 @@
         <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C31" t="s">
         <v>288</v>
@@ -3871,7 +3871,7 @@
         <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C34" t="s">
         <v>152</v>
@@ -3897,7 +3897,7 @@
         <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C35" t="s">
         <v>146</v>
@@ -4339,7 +4339,7 @@
         <v>46</v>
       </c>
       <c r="B52" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C52" t="s">
         <v>348</v>
@@ -4495,7 +4495,7 @@
         <v>96</v>
       </c>
       <c r="B58" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C58" t="s">
         <v>134</v>
@@ -4755,7 +4755,7 @@
         <v>39</v>
       </c>
       <c r="B68" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C68" t="s">
         <v>489</v>
@@ -4833,25 +4833,25 @@
         <v>116</v>
       </c>
       <c r="B71" t="s">
-        <v>505</v>
+        <v>705</v>
       </c>
       <c r="C71" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="D71" t="s">
         <v>200</v>
       </c>
       <c r="E71" t="s">
+        <v>505</v>
+      </c>
+      <c r="F71" t="s">
         <v>506</v>
       </c>
-      <c r="F71" t="s">
+      <c r="G71" t="s">
         <v>507</v>
       </c>
-      <c r="G71" t="s">
+      <c r="H71" t="s">
         <v>508</v>
-      </c>
-      <c r="H71" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
@@ -4859,25 +4859,25 @@
         <v>37</v>
       </c>
       <c r="B72" t="s">
+        <v>509</v>
+      </c>
+      <c r="C72" t="s">
         <v>510</v>
-      </c>
-      <c r="C72" t="s">
-        <v>511</v>
       </c>
       <c r="D72" t="s">
         <v>193</v>
       </c>
       <c r="E72" t="s">
+        <v>511</v>
+      </c>
+      <c r="F72" t="s">
         <v>512</v>
       </c>
-      <c r="F72" t="s">
+      <c r="G72" t="s">
         <v>513</v>
       </c>
-      <c r="G72" t="s">
+      <c r="H72" t="s">
         <v>514</v>
-      </c>
-      <c r="H72" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
@@ -4885,25 +4885,25 @@
         <v>41</v>
       </c>
       <c r="B73" t="s">
+        <v>515</v>
+      </c>
+      <c r="C73" t="s">
         <v>516</v>
-      </c>
-      <c r="C73" t="s">
-        <v>517</v>
       </c>
       <c r="D73" t="s">
         <v>186</v>
       </c>
       <c r="E73" t="s">
+        <v>517</v>
+      </c>
+      <c r="F73" t="s">
         <v>518</v>
       </c>
-      <c r="F73" t="s">
+      <c r="G73" t="s">
         <v>519</v>
       </c>
-      <c r="G73" t="s">
+      <c r="H73" t="s">
         <v>520</v>
-      </c>
-      <c r="H73" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
@@ -4911,25 +4911,25 @@
         <v>111</v>
       </c>
       <c r="B74" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C74" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D74" t="s">
         <v>135</v>
       </c>
       <c r="E74" t="s">
+        <v>522</v>
+      </c>
+      <c r="F74" t="s">
         <v>523</v>
       </c>
-      <c r="F74" t="s">
+      <c r="G74" t="s">
         <v>524</v>
       </c>
-      <c r="G74" t="s">
+      <c r="H74" t="s">
         <v>525</v>
-      </c>
-      <c r="H74" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
@@ -4937,25 +4937,25 @@
         <v>45</v>
       </c>
       <c r="B75" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C75" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D75" t="s">
         <v>377</v>
       </c>
       <c r="E75" t="s">
+        <v>527</v>
+      </c>
+      <c r="F75" t="s">
         <v>528</v>
       </c>
-      <c r="F75" t="s">
+      <c r="G75" t="s">
         <v>529</v>
       </c>
-      <c r="G75" t="s">
+      <c r="H75" t="s">
         <v>530</v>
-      </c>
-      <c r="H75" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
@@ -4963,25 +4963,25 @@
         <v>49</v>
       </c>
       <c r="B76" t="s">
+        <v>531</v>
+      </c>
+      <c r="C76" t="s">
         <v>532</v>
-      </c>
-      <c r="C76" t="s">
-        <v>533</v>
       </c>
       <c r="D76" t="s">
         <v>193</v>
       </c>
       <c r="E76" t="s">
+        <v>533</v>
+      </c>
+      <c r="F76" t="s">
         <v>534</v>
       </c>
-      <c r="F76" t="s">
+      <c r="G76" t="s">
         <v>535</v>
       </c>
-      <c r="G76" t="s">
+      <c r="H76" t="s">
         <v>536</v>
-      </c>
-      <c r="H76" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
@@ -4989,7 +4989,7 @@
         <v>65</v>
       </c>
       <c r="B77" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C77" t="s">
         <v>269</v>
@@ -4998,16 +4998,16 @@
         <v>128</v>
       </c>
       <c r="E77" t="s">
+        <v>538</v>
+      </c>
+      <c r="F77" t="s">
         <v>539</v>
       </c>
-      <c r="F77" t="s">
+      <c r="G77" t="s">
         <v>540</v>
       </c>
-      <c r="G77" t="s">
+      <c r="H77" t="s">
         <v>541</v>
-      </c>
-      <c r="H77" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
@@ -5015,25 +5015,25 @@
         <v>119</v>
       </c>
       <c r="B78" t="s">
+        <v>542</v>
+      </c>
+      <c r="C78" t="s">
         <v>543</v>
-      </c>
-      <c r="C78" t="s">
-        <v>544</v>
       </c>
       <c r="D78" t="s">
         <v>135</v>
       </c>
       <c r="E78" t="s">
+        <v>544</v>
+      </c>
+      <c r="F78" t="s">
         <v>545</v>
       </c>
-      <c r="F78" t="s">
+      <c r="G78" t="s">
         <v>546</v>
       </c>
-      <c r="G78" t="s">
+      <c r="H78" t="s">
         <v>547</v>
-      </c>
-      <c r="H78" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
@@ -5041,7 +5041,7 @@
         <v>47</v>
       </c>
       <c r="B79" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C79" t="s">
         <v>241</v>
@@ -5050,16 +5050,16 @@
         <v>135</v>
       </c>
       <c r="E79" t="s">
+        <v>549</v>
+      </c>
+      <c r="F79" t="s">
         <v>550</v>
       </c>
-      <c r="F79" t="s">
+      <c r="G79" t="s">
         <v>551</v>
       </c>
-      <c r="G79" t="s">
+      <c r="H79" t="s">
         <v>552</v>
-      </c>
-      <c r="H79" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
@@ -5067,25 +5067,25 @@
         <v>67</v>
       </c>
       <c r="B80" t="s">
+        <v>553</v>
+      </c>
+      <c r="C80" t="s">
         <v>554</v>
-      </c>
-      <c r="C80" t="s">
-        <v>555</v>
       </c>
       <c r="D80" t="s">
         <v>135</v>
       </c>
       <c r="E80" t="s">
+        <v>555</v>
+      </c>
+      <c r="F80" t="s">
         <v>556</v>
       </c>
-      <c r="F80" t="s">
+      <c r="G80" t="s">
         <v>557</v>
       </c>
-      <c r="G80" t="s">
+      <c r="H80" t="s">
         <v>558</v>
-      </c>
-      <c r="H80" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
@@ -5093,7 +5093,7 @@
         <v>117</v>
       </c>
       <c r="B81" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C81" t="s">
         <v>461</v>
@@ -5102,16 +5102,16 @@
         <v>135</v>
       </c>
       <c r="E81" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F81" t="s">
+        <v>560</v>
+      </c>
+      <c r="G81" t="s">
         <v>561</v>
       </c>
-      <c r="G81" t="s">
+      <c r="H81" t="s">
         <v>562</v>
-      </c>
-      <c r="H81" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
@@ -5119,7 +5119,7 @@
         <v>120</v>
       </c>
       <c r="B82" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C82" t="s">
         <v>376</v>
@@ -5128,16 +5128,16 @@
         <v>377</v>
       </c>
       <c r="E82" t="s">
+        <v>564</v>
+      </c>
+      <c r="F82" t="s">
         <v>565</v>
       </c>
-      <c r="F82" t="s">
+      <c r="G82" t="s">
         <v>566</v>
       </c>
-      <c r="G82" t="s">
+      <c r="H82" t="s">
         <v>567</v>
-      </c>
-      <c r="H82" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
@@ -5145,25 +5145,25 @@
         <v>48</v>
       </c>
       <c r="B83" t="s">
+        <v>568</v>
+      </c>
+      <c r="C83" t="s">
         <v>569</v>
-      </c>
-      <c r="C83" t="s">
-        <v>570</v>
       </c>
       <c r="D83" t="s">
         <v>135</v>
       </c>
       <c r="E83" t="s">
+        <v>570</v>
+      </c>
+      <c r="F83" t="s">
         <v>571</v>
       </c>
-      <c r="F83" t="s">
+      <c r="G83" t="s">
         <v>572</v>
       </c>
-      <c r="G83" t="s">
+      <c r="H83" t="s">
         <v>573</v>
-      </c>
-      <c r="H83" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
@@ -5171,25 +5171,25 @@
         <v>53</v>
       </c>
       <c r="B84" t="s">
+        <v>574</v>
+      </c>
+      <c r="C84" t="s">
         <v>575</v>
-      </c>
-      <c r="C84" t="s">
-        <v>576</v>
       </c>
       <c r="D84" t="s">
         <v>377</v>
       </c>
       <c r="E84" t="s">
+        <v>576</v>
+      </c>
+      <c r="F84" t="s">
         <v>577</v>
       </c>
-      <c r="F84" t="s">
+      <c r="G84" t="s">
         <v>578</v>
       </c>
-      <c r="G84" t="s">
+      <c r="H84" t="s">
         <v>579</v>
-      </c>
-      <c r="H84" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
@@ -5197,25 +5197,25 @@
         <v>28</v>
       </c>
       <c r="B85" t="s">
+        <v>580</v>
+      </c>
+      <c r="C85" t="s">
         <v>581</v>
-      </c>
-      <c r="C85" t="s">
-        <v>582</v>
       </c>
       <c r="D85" t="s">
         <v>257</v>
       </c>
       <c r="E85" t="s">
+        <v>582</v>
+      </c>
+      <c r="F85" t="s">
         <v>583</v>
       </c>
-      <c r="F85" t="s">
+      <c r="G85" t="s">
         <v>584</v>
       </c>
-      <c r="G85" t="s">
+      <c r="H85" t="s">
         <v>585</v>
-      </c>
-      <c r="H85" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
@@ -5223,7 +5223,7 @@
         <v>34</v>
       </c>
       <c r="B86" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C86" t="s">
         <v>467</v>
@@ -5232,16 +5232,16 @@
         <v>193</v>
       </c>
       <c r="E86" t="s">
+        <v>587</v>
+      </c>
+      <c r="F86" t="s">
         <v>588</v>
       </c>
-      <c r="F86" t="s">
+      <c r="G86" t="s">
         <v>589</v>
       </c>
-      <c r="G86" t="s">
+      <c r="H86" t="s">
         <v>590</v>
-      </c>
-      <c r="H86" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
@@ -5249,7 +5249,7 @@
         <v>63</v>
       </c>
       <c r="B87" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C87" t="s">
         <v>315</v>
@@ -5258,16 +5258,16 @@
         <v>135</v>
       </c>
       <c r="E87" t="s">
+        <v>592</v>
+      </c>
+      <c r="F87" t="s">
         <v>593</v>
       </c>
-      <c r="F87" t="s">
+      <c r="G87" t="s">
         <v>594</v>
       </c>
-      <c r="G87" t="s">
+      <c r="H87" t="s">
         <v>595</v>
-      </c>
-      <c r="H87" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
@@ -5275,7 +5275,7 @@
         <v>72</v>
       </c>
       <c r="B88" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C88" t="s">
         <v>206</v>
@@ -5284,16 +5284,16 @@
         <v>213</v>
       </c>
       <c r="E88" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="F88" t="s">
+        <v>596</v>
+      </c>
+      <c r="G88" t="s">
         <v>597</v>
       </c>
-      <c r="G88" t="s">
+      <c r="H88" t="s">
         <v>598</v>
-      </c>
-      <c r="H88" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
@@ -5301,25 +5301,25 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
+        <v>599</v>
+      </c>
+      <c r="C89" t="s">
         <v>600</v>
-      </c>
-      <c r="C89" t="s">
-        <v>601</v>
       </c>
       <c r="D89" t="s">
         <v>128</v>
       </c>
       <c r="E89" t="s">
+        <v>601</v>
+      </c>
+      <c r="F89" t="s">
         <v>602</v>
       </c>
-      <c r="F89" t="s">
+      <c r="G89" t="s">
         <v>603</v>
       </c>
-      <c r="G89" t="s">
+      <c r="H89" t="s">
         <v>604</v>
-      </c>
-      <c r="H89" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
@@ -5327,7 +5327,7 @@
         <v>38</v>
       </c>
       <c r="B90" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C90" t="s">
         <v>473</v>
@@ -5336,16 +5336,16 @@
         <v>200</v>
       </c>
       <c r="E90" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F90" t="s">
         <v>311</v>
       </c>
       <c r="G90" t="s">
+        <v>607</v>
+      </c>
+      <c r="H90" t="s">
         <v>608</v>
-      </c>
-      <c r="H90" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
@@ -5353,25 +5353,25 @@
         <v>97</v>
       </c>
       <c r="B91" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C91" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D91" t="s">
         <v>128</v>
       </c>
       <c r="E91" t="s">
+        <v>610</v>
+      </c>
+      <c r="F91" t="s">
         <v>611</v>
       </c>
-      <c r="F91" t="s">
+      <c r="G91" t="s">
         <v>612</v>
       </c>
-      <c r="G91" t="s">
+      <c r="H91" t="s">
         <v>613</v>
-      </c>
-      <c r="H91" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
@@ -5379,25 +5379,25 @@
         <v>54</v>
       </c>
       <c r="B92" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C92" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D92" t="s">
         <v>193</v>
       </c>
       <c r="E92" t="s">
+        <v>614</v>
+      </c>
+      <c r="F92" t="s">
         <v>615</v>
       </c>
-      <c r="F92" t="s">
+      <c r="G92" t="s">
         <v>616</v>
       </c>
-      <c r="G92" t="s">
+      <c r="H92" t="s">
         <v>617</v>
-      </c>
-      <c r="H92" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
@@ -5405,25 +5405,25 @@
         <v>40</v>
       </c>
       <c r="B93" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C93" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D93" t="s">
         <v>193</v>
       </c>
       <c r="E93" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F93" t="s">
         <v>432</v>
       </c>
       <c r="G93" t="s">
+        <v>620</v>
+      </c>
+      <c r="H93" t="s">
         <v>621</v>
-      </c>
-      <c r="H93" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
@@ -5431,7 +5431,7 @@
         <v>26</v>
       </c>
       <c r="B94" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C94" t="s">
         <v>413</v>
@@ -5440,16 +5440,16 @@
         <v>193</v>
       </c>
       <c r="E94" t="s">
+        <v>623</v>
+      </c>
+      <c r="F94" t="s">
         <v>624</v>
       </c>
-      <c r="F94" t="s">
+      <c r="G94" t="s">
         <v>625</v>
       </c>
-      <c r="G94" t="s">
+      <c r="H94" t="s">
         <v>626</v>
-      </c>
-      <c r="H94" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
@@ -5457,7 +5457,7 @@
         <v>86</v>
       </c>
       <c r="B95" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C95" t="s">
         <v>157</v>
@@ -5466,16 +5466,16 @@
         <v>135</v>
       </c>
       <c r="E95" t="s">
+        <v>627</v>
+      </c>
+      <c r="F95" t="s">
+        <v>588</v>
+      </c>
+      <c r="G95" t="s">
         <v>628</v>
       </c>
-      <c r="F95" t="s">
-        <v>589</v>
-      </c>
-      <c r="G95" t="s">
+      <c r="H95" t="s">
         <v>629</v>
-      </c>
-      <c r="H95" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
@@ -5483,25 +5483,25 @@
         <v>57</v>
       </c>
       <c r="B96" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C96" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D96" t="s">
         <v>193</v>
       </c>
       <c r="E96" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="F96" t="s">
         <v>469</v>
       </c>
       <c r="G96" t="s">
+        <v>631</v>
+      </c>
+      <c r="H96" t="s">
         <v>632</v>
-      </c>
-      <c r="H96" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
@@ -5509,25 +5509,25 @@
         <v>104</v>
       </c>
       <c r="B97" t="s">
+        <v>633</v>
+      </c>
+      <c r="C97" t="s">
         <v>634</v>
-      </c>
-      <c r="C97" t="s">
-        <v>635</v>
       </c>
       <c r="D97" t="s">
         <v>200</v>
       </c>
       <c r="E97" t="s">
+        <v>635</v>
+      </c>
+      <c r="F97" t="s">
         <v>636</v>
       </c>
-      <c r="F97" t="s">
+      <c r="G97" t="s">
         <v>637</v>
       </c>
-      <c r="G97" t="s">
+      <c r="H97" t="s">
         <v>638</v>
-      </c>
-      <c r="H97" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
@@ -5535,7 +5535,7 @@
         <v>75</v>
       </c>
       <c r="B98" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C98" t="s">
         <v>206</v>
@@ -5544,16 +5544,16 @@
         <v>213</v>
       </c>
       <c r="E98" t="s">
+        <v>639</v>
+      </c>
+      <c r="F98" t="s">
         <v>640</v>
       </c>
-      <c r="F98" t="s">
+      <c r="G98" t="s">
         <v>641</v>
       </c>
-      <c r="G98" t="s">
+      <c r="H98" t="s">
         <v>642</v>
-      </c>
-      <c r="H98" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
@@ -5561,25 +5561,25 @@
         <v>109</v>
       </c>
       <c r="B99" t="s">
+        <v>643</v>
+      </c>
+      <c r="C99" t="s">
         <v>644</v>
-      </c>
-      <c r="C99" t="s">
-        <v>645</v>
       </c>
       <c r="D99" t="s">
         <v>377</v>
       </c>
       <c r="E99" t="s">
+        <v>645</v>
+      </c>
+      <c r="F99" t="s">
         <v>646</v>
       </c>
-      <c r="F99" t="s">
+      <c r="G99" t="s">
         <v>647</v>
       </c>
-      <c r="G99" t="s">
+      <c r="H99" t="s">
         <v>648</v>
-      </c>
-      <c r="H99" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
@@ -5587,25 +5587,25 @@
         <v>15</v>
       </c>
       <c r="B100" t="s">
+        <v>649</v>
+      </c>
+      <c r="C100" t="s">
         <v>650</v>
-      </c>
-      <c r="C100" t="s">
-        <v>651</v>
       </c>
       <c r="D100" t="s">
         <v>213</v>
       </c>
       <c r="E100" t="s">
+        <v>651</v>
+      </c>
+      <c r="F100" t="s">
         <v>652</v>
       </c>
-      <c r="F100" t="s">
+      <c r="G100" t="s">
         <v>653</v>
       </c>
-      <c r="G100" t="s">
+      <c r="H100" t="s">
         <v>654</v>
-      </c>
-      <c r="H100" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
@@ -5613,7 +5613,7 @@
         <v>89</v>
       </c>
       <c r="B101" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C101" t="s">
         <v>157</v>
@@ -5622,16 +5622,16 @@
         <v>128</v>
       </c>
       <c r="E101" t="s">
+        <v>656</v>
+      </c>
+      <c r="F101" t="s">
         <v>657</v>
       </c>
-      <c r="F101" t="s">
+      <c r="G101" t="s">
         <v>658</v>
       </c>
-      <c r="G101" t="s">
+      <c r="H101" t="s">
         <v>659</v>
-      </c>
-      <c r="H101" t="s">
-        <v>660</v>
       </c>
     </row>
   </sheetData>
@@ -5790,7 +5790,7 @@
     </row>
     <row r="9" spans="1:13" ht="39" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>12</v>
@@ -5840,7 +5840,7 @@
     </row>
     <row r="10" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>15</v>
@@ -5890,7 +5890,7 @@
     </row>
     <row r="11" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>18</v>
@@ -5940,7 +5940,7 @@
     </row>
     <row r="12" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>21</v>
@@ -5990,7 +5990,7 @@
     </row>
     <row r="13" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>24</v>
@@ -6040,7 +6040,7 @@
     </row>
     <row r="14" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>27</v>
@@ -6185,7 +6185,7 @@
     </row>
     <row r="19" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>32</v>
@@ -6235,7 +6235,7 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>35</v>
@@ -6285,7 +6285,7 @@
     </row>
     <row r="21" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>38</v>
@@ -6335,7 +6335,7 @@
     </row>
     <row r="22" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>41</v>
@@ -6385,7 +6385,7 @@
     </row>
     <row r="23" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>44</v>
@@ -6396,7 +6396,7 @@
       </c>
       <c r="D23" s="6" t="str">
         <f>IFERROR(VLOOKUP($B23,Data!$A:$D,2,FALSE),"")</f>
-        <v>Effect of ZAP70 Mutations on CAR T-Cell Effectiveness Targeting GD2 in Brain Tumors and N6 Leukemia Cells</v>
+        <v>Effect of ZAP70 Mutations on CAR T-Cell effectiveness Targeting GD2 in Cancer Cells</v>
       </c>
       <c r="E23" s="6" t="str">
         <f>IFERROR(VLOOKUP($B23,Data!$A:$D,3,FALSE),"")</f>
@@ -6435,7 +6435,7 @@
     </row>
     <row r="24" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>47</v>
@@ -6580,7 +6580,7 @@
     </row>
     <row r="29" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>52</v>
@@ -6630,7 +6630,7 @@
     </row>
     <row r="30" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>55</v>
@@ -6680,7 +6680,7 @@
     </row>
     <row r="31" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>58</v>
@@ -6730,7 +6730,7 @@
     </row>
     <row r="32" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>61</v>
@@ -6780,7 +6780,7 @@
     </row>
     <row r="33" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>64</v>
@@ -6830,7 +6830,7 @@
     </row>
     <row r="34" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>75</v>
@@ -6975,7 +6975,7 @@
     </row>
     <row r="39" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>72</v>
@@ -7025,7 +7025,7 @@
     </row>
     <row r="40" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>67</v>
@@ -7075,7 +7075,7 @@
     </row>
     <row r="41" spans="1:13" ht="39" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>78</v>
@@ -7125,7 +7125,7 @@
     </row>
     <row r="42" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>81</v>
@@ -7175,7 +7175,7 @@
     </row>
     <row r="43" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>84</v>
@@ -7225,7 +7225,7 @@
     </row>
     <row r="44" spans="1:13" ht="39" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>87</v>
@@ -7370,7 +7370,7 @@
     </row>
     <row r="51" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>92</v>
@@ -7420,7 +7420,7 @@
     </row>
     <row r="52" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>95</v>
@@ -7470,7 +7470,7 @@
     </row>
     <row r="53" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>98</v>
@@ -7520,7 +7520,7 @@
     </row>
     <row r="54" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>101</v>
@@ -7570,7 +7570,7 @@
     </row>
     <row r="55" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>104</v>
@@ -7620,7 +7620,7 @@
     </row>
     <row r="56" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>107</v>
@@ -7765,7 +7765,7 @@
     </row>
     <row r="61" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>111</v>
@@ -7815,7 +7815,7 @@
     </row>
     <row r="62" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>114</v>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="L62" s="6" t="str">
         <f>IFERROR(VLOOKUP($J62,Data!$A:$D,2,FALSE),"")</f>
-        <v>W-Flow: Continuous-variable Quantum State Tomography via Flow-based Generative Modeling</v>
+        <v>S-Flow: Harnessing Informed Sampling for Flow Models in Perturbation-Aware Quantum State Tomography</v>
       </c>
       <c r="M62" s="6" t="str">
         <f>IFERROR(VLOOKUP($J62,Data!$A:$D,3,FALSE),"")</f>
@@ -7865,7 +7865,7 @@
     </row>
     <row r="63" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>117</v>
@@ -7913,7 +7913,7 @@
     </row>
     <row r="64" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>119</v>

--- a/RSI_2026_Schedule.xlsx
+++ b/RSI_2026_Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/evanlim/Documents/rsi-symposium/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F32A43CB-F819-6C43-ADD4-BD4725E8E733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F1B4BB-94C9-BA4E-B583-CE1FED2672F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -438,9 +438,6 @@
     <t>aaru0302</t>
   </si>
   <si>
-    <t>Optimization of a Yeast-Based High-Throughput Screening Platform to Identify PfPDEγ Inhibitor Candidates</t>
-  </si>
-  <si>
     <t>Prof. Charles Hoffman</t>
   </si>
   <si>
@@ -612,9 +609,6 @@
     <t>annika8</t>
   </si>
   <si>
-    <t>On Counting Prime Solutions to Quadratic Forms via the Hardy-Littlewood Circle Method</t>
-  </si>
-  <si>
     <t>Siqi Wu</t>
   </si>
   <si>
@@ -1698,9 +1692,6 @@
     <t>sarmit21</t>
   </si>
   <si>
-    <t>Computational and mathematical modeling of cellular dynamics in hydrogels to optimize large-scale bioprinting</t>
-  </si>
-  <si>
     <t>Prof. Ron Weiss</t>
   </si>
   <si>
@@ -2155,6 +2146,15 @@
   </si>
   <si>
     <t>S-Flow: Harnessing Informed Sampling for Flow Models in Perturbation-Aware Quantum State Tomography</t>
+  </si>
+  <si>
+    <t>Counting Prime Solutions to Quadratic Forms</t>
+  </si>
+  <si>
+    <t>Optimization of a Yeast-Based High-Throughput Screening Platform to Detect Small-Molecule Modulators of PfPDE𝛄  for Antimalarial Drug Discovery</t>
+  </si>
+  <si>
+    <t>Computational and Mathematical Modeling of Cellular Dynamics in Hydrogels to Optimize Large-Scale Bioprinting</t>
   </si>
 </sst>
 </file>
@@ -3065,25 +3065,25 @@
         <v>93</v>
       </c>
       <c r="B3" t="s">
+        <v>704</v>
+      </c>
+      <c r="C3" t="s">
         <v>133</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>134</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>135</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>136</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>137</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>138</v>
-      </c>
-      <c r="H3" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -3091,25 +3091,25 @@
         <v>108</v>
       </c>
       <c r="B4" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E4" t="s">
         <v>140</v>
       </c>
-      <c r="D4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>141</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>142</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>143</v>
-      </c>
-      <c r="H4" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -3117,25 +3117,25 @@
         <v>16</v>
       </c>
       <c r="B5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" t="s">
         <v>145</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E5" t="s">
         <v>146</v>
       </c>
-      <c r="D5" t="s">
-        <v>135</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>147</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>148</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>149</v>
-      </c>
-      <c r="H5" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -3143,25 +3143,25 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" t="s">
         <v>151</v>
-      </c>
-      <c r="C6" t="s">
-        <v>152</v>
       </c>
       <c r="D6" t="s">
         <v>128</v>
       </c>
       <c r="E6" t="s">
+        <v>152</v>
+      </c>
+      <c r="F6" t="s">
         <v>153</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>154</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>155</v>
-      </c>
-      <c r="H6" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -3169,25 +3169,25 @@
         <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E7" t="s">
         <v>157</v>
       </c>
-      <c r="D7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>158</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>159</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>160</v>
-      </c>
-      <c r="H7" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -3195,25 +3195,25 @@
         <v>99</v>
       </c>
       <c r="B8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C8" t="s">
         <v>162</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>134</v>
+      </c>
+      <c r="E8" t="s">
         <v>163</v>
       </c>
-      <c r="D8" t="s">
-        <v>135</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>164</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>165</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>166</v>
-      </c>
-      <c r="H8" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -3221,25 +3221,25 @@
         <v>77</v>
       </c>
       <c r="B9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D9" t="s">
+        <v>134</v>
+      </c>
+      <c r="E9" t="s">
         <v>168</v>
       </c>
-      <c r="C9" t="s">
-        <v>157</v>
-      </c>
-      <c r="D9" t="s">
-        <v>135</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>169</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>170</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>171</v>
-      </c>
-      <c r="H9" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -3247,25 +3247,25 @@
         <v>88</v>
       </c>
       <c r="B10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C10" t="s">
         <v>173</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E10" t="s">
         <v>174</v>
       </c>
-      <c r="D10" t="s">
-        <v>135</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>175</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>176</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>177</v>
-      </c>
-      <c r="H10" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -3273,25 +3273,25 @@
         <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C11" t="s">
         <v>127</v>
       </c>
       <c r="D11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E11" t="s">
+        <v>179</v>
+      </c>
+      <c r="F11" t="s">
         <v>180</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>181</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>182</v>
-      </c>
-      <c r="H11" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -3299,25 +3299,25 @@
         <v>112</v>
       </c>
       <c r="B12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C12" t="s">
         <v>184</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>185</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>186</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>187</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>188</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>189</v>
-      </c>
-      <c r="H12" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -3325,25 +3325,25 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
+        <v>703</v>
+      </c>
+      <c r="C13" t="s">
+        <v>190</v>
+      </c>
+      <c r="D13" t="s">
         <v>191</v>
       </c>
-      <c r="C13" t="s">
+      <c r="E13" t="s">
         <v>192</v>
       </c>
-      <c r="D13" t="s">
+      <c r="F13" t="s">
         <v>193</v>
       </c>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
         <v>194</v>
       </c>
-      <c r="F13" t="s">
+      <c r="H13" t="s">
         <v>195</v>
-      </c>
-      <c r="G13" t="s">
-        <v>196</v>
-      </c>
-      <c r="H13" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -3351,25 +3351,25 @@
         <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D14" t="s">
+        <v>134</v>
+      </c>
+      <c r="E14" t="s">
         <v>199</v>
       </c>
-      <c r="D14" t="s">
-        <v>135</v>
-      </c>
-      <c r="E14" t="s">
-        <v>201</v>
-      </c>
       <c r="F14" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H14" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -3377,25 +3377,25 @@
         <v>52</v>
       </c>
       <c r="B15" t="s">
+        <v>209</v>
+      </c>
+      <c r="C15" t="s">
+        <v>204</v>
+      </c>
+      <c r="D15" t="s">
         <v>211</v>
       </c>
-      <c r="C15" t="s">
+      <c r="E15" t="s">
+        <v>205</v>
+      </c>
+      <c r="F15" t="s">
         <v>206</v>
       </c>
-      <c r="D15" t="s">
+      <c r="G15" t="s">
         <v>213</v>
       </c>
-      <c r="E15" t="s">
-        <v>207</v>
-      </c>
-      <c r="F15" t="s">
-        <v>208</v>
-      </c>
-      <c r="G15" t="s">
-        <v>215</v>
-      </c>
       <c r="H15" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -3403,25 +3403,25 @@
         <v>113</v>
       </c>
       <c r="B16" t="s">
+        <v>196</v>
+      </c>
+      <c r="C16" t="s">
+        <v>210</v>
+      </c>
+      <c r="D16" t="s">
         <v>198</v>
       </c>
-      <c r="C16" t="s">
+      <c r="E16" t="s">
         <v>212</v>
       </c>
-      <c r="D16" t="s">
+      <c r="F16" t="s">
         <v>200</v>
       </c>
-      <c r="E16" t="s">
-        <v>214</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
+        <v>201</v>
+      </c>
+      <c r="H16" t="s">
         <v>202</v>
-      </c>
-      <c r="G16" t="s">
-        <v>203</v>
-      </c>
-      <c r="H16" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -3429,25 +3429,25 @@
         <v>55</v>
       </c>
       <c r="B17" t="s">
+        <v>215</v>
+      </c>
+      <c r="C17" t="s">
+        <v>204</v>
+      </c>
+      <c r="D17" t="s">
+        <v>211</v>
+      </c>
+      <c r="E17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F17" t="s">
         <v>217</v>
       </c>
-      <c r="C17" t="s">
-        <v>206</v>
-      </c>
-      <c r="D17" t="s">
-        <v>213</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="G17" t="s">
         <v>218</v>
       </c>
-      <c r="F17" t="s">
+      <c r="H17" t="s">
         <v>219</v>
-      </c>
-      <c r="G17" t="s">
-        <v>220</v>
-      </c>
-      <c r="H17" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -3455,25 +3455,25 @@
         <v>101</v>
       </c>
       <c r="B18" t="s">
+        <v>220</v>
+      </c>
+      <c r="C18" t="s">
+        <v>631</v>
+      </c>
+      <c r="D18" t="s">
+        <v>198</v>
+      </c>
+      <c r="E18" t="s">
+        <v>221</v>
+      </c>
+      <c r="F18" t="s">
         <v>222</v>
       </c>
-      <c r="C18" t="s">
-        <v>634</v>
-      </c>
-      <c r="D18" t="s">
-        <v>200</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="G18" t="s">
         <v>223</v>
       </c>
-      <c r="F18" t="s">
+      <c r="H18" t="s">
         <v>224</v>
-      </c>
-      <c r="G18" t="s">
-        <v>225</v>
-      </c>
-      <c r="H18" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -3481,25 +3481,25 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C19" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D19" t="s">
         <v>128</v>
       </c>
       <c r="E19" t="s">
+        <v>227</v>
+      </c>
+      <c r="F19" t="s">
+        <v>228</v>
+      </c>
+      <c r="G19" t="s">
         <v>229</v>
       </c>
-      <c r="F19" t="s">
+      <c r="H19" t="s">
         <v>230</v>
-      </c>
-      <c r="G19" t="s">
-        <v>231</v>
-      </c>
-      <c r="H19" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -3507,25 +3507,25 @@
         <v>58</v>
       </c>
       <c r="B20" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="C20" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D20" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E20" t="s">
+        <v>231</v>
+      </c>
+      <c r="F20" t="s">
+        <v>164</v>
+      </c>
+      <c r="G20" t="s">
+        <v>232</v>
+      </c>
+      <c r="H20" t="s">
         <v>233</v>
-      </c>
-      <c r="F20" t="s">
-        <v>165</v>
-      </c>
-      <c r="G20" t="s">
-        <v>234</v>
-      </c>
-      <c r="H20" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -3533,25 +3533,25 @@
         <v>66</v>
       </c>
       <c r="B21" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="C21" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D21" t="s">
         <v>128</v>
       </c>
       <c r="E21" t="s">
+        <v>235</v>
+      </c>
+      <c r="F21" t="s">
+        <v>236</v>
+      </c>
+      <c r="G21" t="s">
         <v>237</v>
       </c>
-      <c r="F21" t="s">
+      <c r="H21" t="s">
         <v>238</v>
-      </c>
-      <c r="G21" t="s">
-        <v>239</v>
-      </c>
-      <c r="H21" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -3559,25 +3559,25 @@
         <v>44</v>
       </c>
       <c r="B22" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="C22" t="s">
+        <v>239</v>
+      </c>
+      <c r="D22" t="s">
+        <v>134</v>
+      </c>
+      <c r="E22" t="s">
+        <v>240</v>
+      </c>
+      <c r="F22" t="s">
         <v>241</v>
       </c>
-      <c r="D22" t="s">
-        <v>135</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="G22" t="s">
         <v>242</v>
       </c>
-      <c r="F22" t="s">
+      <c r="H22" t="s">
         <v>243</v>
-      </c>
-      <c r="G22" t="s">
-        <v>244</v>
-      </c>
-      <c r="H22" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -3585,25 +3585,25 @@
         <v>80</v>
       </c>
       <c r="B23" t="s">
+        <v>244</v>
+      </c>
+      <c r="C23" t="s">
+        <v>156</v>
+      </c>
+      <c r="D23" t="s">
+        <v>134</v>
+      </c>
+      <c r="E23" t="s">
+        <v>245</v>
+      </c>
+      <c r="F23" t="s">
         <v>246</v>
       </c>
-      <c r="C23" t="s">
-        <v>157</v>
-      </c>
-      <c r="D23" t="s">
-        <v>135</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="G23" t="s">
         <v>247</v>
       </c>
-      <c r="F23" t="s">
+      <c r="H23" t="s">
         <v>248</v>
-      </c>
-      <c r="G23" t="s">
-        <v>249</v>
-      </c>
-      <c r="H23" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
@@ -3611,25 +3611,25 @@
         <v>61</v>
       </c>
       <c r="B24" t="s">
+        <v>249</v>
+      </c>
+      <c r="C24" t="s">
+        <v>204</v>
+      </c>
+      <c r="D24" t="s">
+        <v>211</v>
+      </c>
+      <c r="E24" t="s">
+        <v>250</v>
+      </c>
+      <c r="F24" t="s">
         <v>251</v>
       </c>
-      <c r="C24" t="s">
-        <v>206</v>
-      </c>
-      <c r="D24" t="s">
-        <v>213</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="G24" t="s">
         <v>252</v>
       </c>
-      <c r="F24" t="s">
+      <c r="H24" t="s">
         <v>253</v>
-      </c>
-      <c r="G24" t="s">
-        <v>254</v>
-      </c>
-      <c r="H24" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -3637,25 +3637,25 @@
         <v>76</v>
       </c>
       <c r="B25" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="C25" t="s">
+        <v>254</v>
+      </c>
+      <c r="D25" t="s">
+        <v>255</v>
+      </c>
+      <c r="E25" t="s">
         <v>256</v>
       </c>
-      <c r="D25" t="s">
+      <c r="F25" t="s">
         <v>257</v>
       </c>
-      <c r="E25" t="s">
+      <c r="G25" t="s">
         <v>258</v>
       </c>
-      <c r="F25" t="s">
+      <c r="H25" t="s">
         <v>259</v>
-      </c>
-      <c r="G25" t="s">
-        <v>260</v>
-      </c>
-      <c r="H25" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
@@ -3663,25 +3663,25 @@
         <v>69</v>
       </c>
       <c r="B26" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="C26" t="s">
+        <v>260</v>
+      </c>
+      <c r="D26" t="s">
+        <v>261</v>
+      </c>
+      <c r="E26" t="s">
         <v>262</v>
       </c>
-      <c r="D26" t="s">
+      <c r="F26" t="s">
         <v>263</v>
       </c>
-      <c r="E26" t="s">
+      <c r="G26" t="s">
         <v>264</v>
       </c>
-      <c r="F26" t="s">
+      <c r="H26" t="s">
         <v>265</v>
-      </c>
-      <c r="G26" t="s">
-        <v>266</v>
-      </c>
-      <c r="H26" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -3689,25 +3689,25 @@
         <v>56</v>
       </c>
       <c r="B27" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C27" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D27" t="s">
         <v>128</v>
       </c>
       <c r="E27" t="s">
+        <v>268</v>
+      </c>
+      <c r="F27" t="s">
+        <v>269</v>
+      </c>
+      <c r="G27" t="s">
         <v>270</v>
       </c>
-      <c r="F27" t="s">
+      <c r="H27" t="s">
         <v>271</v>
-      </c>
-      <c r="G27" t="s">
-        <v>272</v>
-      </c>
-      <c r="H27" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -3715,25 +3715,25 @@
         <v>95</v>
       </c>
       <c r="B28" t="s">
+        <v>278</v>
+      </c>
+      <c r="C28" t="s">
+        <v>273</v>
+      </c>
+      <c r="D28" t="s">
+        <v>185</v>
+      </c>
+      <c r="E28" t="s">
+        <v>274</v>
+      </c>
+      <c r="F28" t="s">
+        <v>275</v>
+      </c>
+      <c r="G28" t="s">
+        <v>279</v>
+      </c>
+      <c r="H28" t="s">
         <v>280</v>
-      </c>
-      <c r="C28" t="s">
-        <v>275</v>
-      </c>
-      <c r="D28" t="s">
-        <v>186</v>
-      </c>
-      <c r="E28" t="s">
-        <v>276</v>
-      </c>
-      <c r="F28" t="s">
-        <v>277</v>
-      </c>
-      <c r="G28" t="s">
-        <v>281</v>
-      </c>
-      <c r="H28" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -3741,25 +3741,25 @@
         <v>98</v>
       </c>
       <c r="B29" t="s">
+        <v>272</v>
+      </c>
+      <c r="C29" t="s">
+        <v>273</v>
+      </c>
+      <c r="D29" t="s">
+        <v>185</v>
+      </c>
+      <c r="E29" t="s">
         <v>274</v>
       </c>
-      <c r="C29" t="s">
-        <v>275</v>
-      </c>
-      <c r="D29" t="s">
-        <v>186</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
+        <v>200</v>
+      </c>
+      <c r="G29" t="s">
         <v>276</v>
       </c>
-      <c r="F29" t="s">
-        <v>202</v>
-      </c>
-      <c r="G29" t="s">
-        <v>278</v>
-      </c>
       <c r="H29" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -3767,25 +3767,25 @@
         <v>115</v>
       </c>
       <c r="B30" t="s">
+        <v>281</v>
+      </c>
+      <c r="C30" t="s">
+        <v>184</v>
+      </c>
+      <c r="D30" t="s">
+        <v>185</v>
+      </c>
+      <c r="E30" t="s">
+        <v>282</v>
+      </c>
+      <c r="F30" t="s">
         <v>283</v>
       </c>
-      <c r="C30" t="s">
-        <v>185</v>
-      </c>
-      <c r="D30" t="s">
-        <v>186</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="G30" t="s">
         <v>284</v>
       </c>
-      <c r="F30" t="s">
+      <c r="H30" t="s">
         <v>285</v>
-      </c>
-      <c r="G30" t="s">
-        <v>286</v>
-      </c>
-      <c r="H30" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -3793,25 +3793,25 @@
         <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="C31" t="s">
+        <v>286</v>
+      </c>
+      <c r="D31" t="s">
+        <v>198</v>
+      </c>
+      <c r="E31" t="s">
+        <v>287</v>
+      </c>
+      <c r="F31" t="s">
         <v>288</v>
       </c>
-      <c r="D31" t="s">
-        <v>200</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="G31" t="s">
         <v>289</v>
       </c>
-      <c r="F31" t="s">
+      <c r="H31" t="s">
         <v>290</v>
-      </c>
-      <c r="G31" t="s">
-        <v>291</v>
-      </c>
-      <c r="H31" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -3819,25 +3819,25 @@
         <v>92</v>
       </c>
       <c r="B32" t="s">
+        <v>291</v>
+      </c>
+      <c r="C32" t="s">
+        <v>292</v>
+      </c>
+      <c r="D32" t="s">
         <v>293</v>
       </c>
-      <c r="C32" t="s">
+      <c r="E32" t="s">
         <v>294</v>
       </c>
-      <c r="D32" t="s">
+      <c r="F32" t="s">
         <v>295</v>
       </c>
-      <c r="E32" t="s">
+      <c r="G32" t="s">
         <v>296</v>
       </c>
-      <c r="F32" t="s">
+      <c r="H32" t="s">
         <v>297</v>
-      </c>
-      <c r="G32" t="s">
-        <v>298</v>
-      </c>
-      <c r="H32" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -3845,25 +3845,25 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>298</v>
+      </c>
+      <c r="C33" t="s">
+        <v>299</v>
+      </c>
+      <c r="D33" t="s">
+        <v>255</v>
+      </c>
+      <c r="E33" t="s">
         <v>300</v>
       </c>
-      <c r="C33" t="s">
+      <c r="F33" t="s">
         <v>301</v>
       </c>
-      <c r="D33" t="s">
-        <v>257</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="G33" t="s">
         <v>302</v>
       </c>
-      <c r="F33" t="s">
+      <c r="H33" t="s">
         <v>303</v>
-      </c>
-      <c r="G33" t="s">
-        <v>304</v>
-      </c>
-      <c r="H33" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
@@ -3871,25 +3871,25 @@
         <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C34" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D34" t="s">
         <v>128</v>
       </c>
       <c r="E34" t="s">
+        <v>304</v>
+      </c>
+      <c r="F34" t="s">
+        <v>305</v>
+      </c>
+      <c r="G34" t="s">
         <v>306</v>
       </c>
-      <c r="F34" t="s">
+      <c r="H34" t="s">
         <v>307</v>
-      </c>
-      <c r="G34" t="s">
-        <v>308</v>
-      </c>
-      <c r="H34" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -3897,25 +3897,25 @@
         <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="C35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D35" t="s">
         <v>128</v>
       </c>
       <c r="E35" t="s">
+        <v>308</v>
+      </c>
+      <c r="F35" t="s">
+        <v>309</v>
+      </c>
+      <c r="G35" t="s">
         <v>310</v>
       </c>
-      <c r="F35" t="s">
+      <c r="H35" t="s">
         <v>311</v>
-      </c>
-      <c r="G35" t="s">
-        <v>312</v>
-      </c>
-      <c r="H35" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -3923,25 +3923,25 @@
         <v>60</v>
       </c>
       <c r="B36" t="s">
+        <v>312</v>
+      </c>
+      <c r="C36" t="s">
+        <v>313</v>
+      </c>
+      <c r="D36" t="s">
+        <v>134</v>
+      </c>
+      <c r="E36" t="s">
         <v>314</v>
       </c>
-      <c r="C36" t="s">
+      <c r="F36" t="s">
         <v>315</v>
       </c>
-      <c r="D36" t="s">
-        <v>135</v>
-      </c>
-      <c r="E36" t="s">
+      <c r="G36" t="s">
         <v>316</v>
       </c>
-      <c r="F36" t="s">
+      <c r="H36" t="s">
         <v>317</v>
-      </c>
-      <c r="G36" t="s">
-        <v>318</v>
-      </c>
-      <c r="H36" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -3949,25 +3949,25 @@
         <v>17</v>
       </c>
       <c r="B37" t="s">
+        <v>318</v>
+      </c>
+      <c r="C37" t="s">
+        <v>190</v>
+      </c>
+      <c r="D37" t="s">
+        <v>191</v>
+      </c>
+      <c r="E37" t="s">
+        <v>319</v>
+      </c>
+      <c r="F37" t="s">
         <v>320</v>
       </c>
-      <c r="C37" t="s">
-        <v>192</v>
-      </c>
-      <c r="D37" t="s">
-        <v>193</v>
-      </c>
-      <c r="E37" t="s">
+      <c r="G37" t="s">
         <v>321</v>
       </c>
-      <c r="F37" t="s">
+      <c r="H37" t="s">
         <v>322</v>
-      </c>
-      <c r="G37" t="s">
-        <v>323</v>
-      </c>
-      <c r="H37" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
@@ -3975,25 +3975,25 @@
         <v>102</v>
       </c>
       <c r="B38" t="s">
+        <v>323</v>
+      </c>
+      <c r="C38" t="s">
+        <v>162</v>
+      </c>
+      <c r="D38" t="s">
+        <v>134</v>
+      </c>
+      <c r="E38" t="s">
+        <v>324</v>
+      </c>
+      <c r="F38" t="s">
         <v>325</v>
       </c>
-      <c r="C38" t="s">
-        <v>163</v>
-      </c>
-      <c r="D38" t="s">
-        <v>135</v>
-      </c>
-      <c r="E38" t="s">
+      <c r="G38" t="s">
         <v>326</v>
       </c>
-      <c r="F38" t="s">
+      <c r="H38" t="s">
         <v>327</v>
-      </c>
-      <c r="G38" t="s">
-        <v>328</v>
-      </c>
-      <c r="H38" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -4001,25 +4001,25 @@
         <v>107</v>
       </c>
       <c r="B39" t="s">
+        <v>328</v>
+      </c>
+      <c r="C39" t="s">
+        <v>329</v>
+      </c>
+      <c r="D39" t="s">
+        <v>134</v>
+      </c>
+      <c r="E39" t="s">
         <v>330</v>
       </c>
-      <c r="C39" t="s">
+      <c r="F39" t="s">
         <v>331</v>
       </c>
-      <c r="D39" t="s">
-        <v>135</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="G39" t="s">
         <v>332</v>
       </c>
-      <c r="F39" t="s">
+      <c r="H39" t="s">
         <v>333</v>
-      </c>
-      <c r="G39" t="s">
-        <v>334</v>
-      </c>
-      <c r="H39" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -4027,25 +4027,25 @@
         <v>83</v>
       </c>
       <c r="B40" t="s">
+        <v>334</v>
+      </c>
+      <c r="C40" t="s">
+        <v>156</v>
+      </c>
+      <c r="D40" t="s">
+        <v>185</v>
+      </c>
+      <c r="E40" t="s">
+        <v>335</v>
+      </c>
+      <c r="F40" t="s">
         <v>336</v>
       </c>
-      <c r="C40" t="s">
-        <v>157</v>
-      </c>
-      <c r="D40" t="s">
-        <v>186</v>
-      </c>
-      <c r="E40" t="s">
+      <c r="G40" t="s">
         <v>337</v>
       </c>
-      <c r="F40" t="s">
+      <c r="H40" t="s">
         <v>338</v>
-      </c>
-      <c r="G40" t="s">
-        <v>339</v>
-      </c>
-      <c r="H40" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -4053,25 +4053,25 @@
         <v>100</v>
       </c>
       <c r="B41" t="s">
+        <v>339</v>
+      </c>
+      <c r="C41" t="s">
+        <v>340</v>
+      </c>
+      <c r="D41" t="s">
+        <v>134</v>
+      </c>
+      <c r="E41" t="s">
         <v>341</v>
       </c>
-      <c r="C41" t="s">
+      <c r="F41" t="s">
         <v>342</v>
       </c>
-      <c r="D41" t="s">
-        <v>135</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="G41" t="s">
         <v>343</v>
       </c>
-      <c r="F41" t="s">
+      <c r="H41" t="s">
         <v>344</v>
-      </c>
-      <c r="G41" t="s">
-        <v>345</v>
-      </c>
-      <c r="H41" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
@@ -4079,25 +4079,25 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
+        <v>351</v>
+      </c>
+      <c r="C42" t="s">
+        <v>346</v>
+      </c>
+      <c r="D42" t="s">
+        <v>191</v>
+      </c>
+      <c r="E42" t="s">
+        <v>347</v>
+      </c>
+      <c r="F42" t="s">
+        <v>348</v>
+      </c>
+      <c r="G42" t="s">
         <v>353</v>
       </c>
-      <c r="C42" t="s">
-        <v>348</v>
-      </c>
-      <c r="D42" t="s">
-        <v>193</v>
-      </c>
-      <c r="E42" t="s">
-        <v>349</v>
-      </c>
-      <c r="F42" t="s">
-        <v>350</v>
-      </c>
-      <c r="G42" t="s">
-        <v>355</v>
-      </c>
       <c r="H42" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -4105,25 +4105,25 @@
         <v>87</v>
       </c>
       <c r="B43" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C43" t="s">
         <v>127</v>
       </c>
       <c r="D43" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E43" t="s">
+        <v>347</v>
+      </c>
+      <c r="F43" t="s">
+        <v>352</v>
+      </c>
+      <c r="G43" t="s">
         <v>349</v>
       </c>
-      <c r="F43" t="s">
-        <v>354</v>
-      </c>
-      <c r="G43" t="s">
-        <v>351</v>
-      </c>
       <c r="H43" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -4131,25 +4131,25 @@
         <v>85</v>
       </c>
       <c r="B44" t="s">
+        <v>355</v>
+      </c>
+      <c r="C44" t="s">
+        <v>356</v>
+      </c>
+      <c r="D44" t="s">
+        <v>261</v>
+      </c>
+      <c r="E44" t="s">
         <v>357</v>
       </c>
-      <c r="C44" t="s">
+      <c r="F44" t="s">
         <v>358</v>
       </c>
-      <c r="D44" t="s">
-        <v>263</v>
-      </c>
-      <c r="E44" t="s">
+      <c r="G44" t="s">
         <v>359</v>
       </c>
-      <c r="F44" t="s">
+      <c r="H44" t="s">
         <v>360</v>
-      </c>
-      <c r="G44" t="s">
-        <v>361</v>
-      </c>
-      <c r="H44" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -4157,25 +4157,25 @@
         <v>27</v>
       </c>
       <c r="B45" t="s">
+        <v>361</v>
+      </c>
+      <c r="C45" t="s">
+        <v>362</v>
+      </c>
+      <c r="D45" t="s">
+        <v>255</v>
+      </c>
+      <c r="E45" t="s">
         <v>363</v>
       </c>
-      <c r="C45" t="s">
+      <c r="F45" t="s">
         <v>364</v>
       </c>
-      <c r="D45" t="s">
-        <v>257</v>
-      </c>
-      <c r="E45" t="s">
+      <c r="G45" t="s">
         <v>365</v>
       </c>
-      <c r="F45" t="s">
+      <c r="H45" t="s">
         <v>366</v>
-      </c>
-      <c r="G45" t="s">
-        <v>367</v>
-      </c>
-      <c r="H45" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
@@ -4183,25 +4183,25 @@
         <v>103</v>
       </c>
       <c r="B46" t="s">
+        <v>367</v>
+      </c>
+      <c r="C46" t="s">
+        <v>368</v>
+      </c>
+      <c r="D46" t="s">
+        <v>134</v>
+      </c>
+      <c r="E46" t="s">
         <v>369</v>
       </c>
-      <c r="C46" t="s">
+      <c r="F46" t="s">
         <v>370</v>
       </c>
-      <c r="D46" t="s">
-        <v>135</v>
-      </c>
-      <c r="E46" t="s">
+      <c r="G46" t="s">
         <v>371</v>
       </c>
-      <c r="F46" t="s">
+      <c r="H46" t="s">
         <v>372</v>
-      </c>
-      <c r="G46" t="s">
-        <v>373</v>
-      </c>
-      <c r="H46" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
@@ -4209,25 +4209,25 @@
         <v>118</v>
       </c>
       <c r="B47" t="s">
+        <v>373</v>
+      </c>
+      <c r="C47" t="s">
+        <v>374</v>
+      </c>
+      <c r="D47" t="s">
         <v>375</v>
       </c>
-      <c r="C47" t="s">
+      <c r="E47" t="s">
         <v>376</v>
       </c>
-      <c r="D47" t="s">
+      <c r="F47" t="s">
         <v>377</v>
       </c>
-      <c r="E47" t="s">
+      <c r="G47" t="s">
         <v>378</v>
       </c>
-      <c r="F47" t="s">
+      <c r="H47" t="s">
         <v>379</v>
-      </c>
-      <c r="G47" t="s">
-        <v>380</v>
-      </c>
-      <c r="H47" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
@@ -4235,25 +4235,25 @@
         <v>20</v>
       </c>
       <c r="B48" t="s">
+        <v>380</v>
+      </c>
+      <c r="C48" t="s">
+        <v>381</v>
+      </c>
+      <c r="D48" t="s">
+        <v>191</v>
+      </c>
+      <c r="E48" t="s">
         <v>382</v>
       </c>
-      <c r="C48" t="s">
+      <c r="F48" t="s">
         <v>383</v>
       </c>
-      <c r="D48" t="s">
-        <v>193</v>
-      </c>
-      <c r="E48" t="s">
+      <c r="G48" t="s">
         <v>384</v>
       </c>
-      <c r="F48" t="s">
+      <c r="H48" t="s">
         <v>385</v>
-      </c>
-      <c r="G48" t="s">
-        <v>386</v>
-      </c>
-      <c r="H48" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
@@ -4261,25 +4261,25 @@
         <v>82</v>
       </c>
       <c r="B49" t="s">
+        <v>386</v>
+      </c>
+      <c r="C49" t="s">
+        <v>387</v>
+      </c>
+      <c r="D49" t="s">
+        <v>134</v>
+      </c>
+      <c r="E49" t="s">
         <v>388</v>
       </c>
-      <c r="C49" t="s">
+      <c r="F49" t="s">
         <v>389</v>
       </c>
-      <c r="D49" t="s">
-        <v>135</v>
-      </c>
-      <c r="E49" t="s">
+      <c r="G49" t="s">
         <v>390</v>
       </c>
-      <c r="F49" t="s">
+      <c r="H49" t="s">
         <v>391</v>
-      </c>
-      <c r="G49" t="s">
-        <v>392</v>
-      </c>
-      <c r="H49" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
@@ -4287,25 +4287,25 @@
         <v>24</v>
       </c>
       <c r="B50" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C50" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D50" t="s">
         <v>128</v>
       </c>
       <c r="E50" t="s">
+        <v>393</v>
+      </c>
+      <c r="F50" t="s">
+        <v>394</v>
+      </c>
+      <c r="G50" t="s">
         <v>395</v>
       </c>
-      <c r="F50" t="s">
+      <c r="H50" t="s">
         <v>396</v>
-      </c>
-      <c r="G50" t="s">
-        <v>397</v>
-      </c>
-      <c r="H50" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
@@ -4313,25 +4313,25 @@
         <v>59</v>
       </c>
       <c r="B51" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C51" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D51" t="s">
         <v>128</v>
       </c>
       <c r="E51" t="s">
+        <v>398</v>
+      </c>
+      <c r="F51" t="s">
+        <v>399</v>
+      </c>
+      <c r="G51" t="s">
         <v>400</v>
       </c>
-      <c r="F51" t="s">
+      <c r="H51" t="s">
         <v>401</v>
-      </c>
-      <c r="G51" t="s">
-        <v>402</v>
-      </c>
-      <c r="H51" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
@@ -4339,25 +4339,25 @@
         <v>46</v>
       </c>
       <c r="B52" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="C52" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D52" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E52" t="s">
+        <v>402</v>
+      </c>
+      <c r="F52" t="s">
+        <v>403</v>
+      </c>
+      <c r="G52" t="s">
         <v>404</v>
       </c>
-      <c r="F52" t="s">
+      <c r="H52" t="s">
         <v>405</v>
-      </c>
-      <c r="G52" t="s">
-        <v>406</v>
-      </c>
-      <c r="H52" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
@@ -4365,25 +4365,25 @@
         <v>79</v>
       </c>
       <c r="B53" t="s">
+        <v>406</v>
+      </c>
+      <c r="C53" t="s">
+        <v>254</v>
+      </c>
+      <c r="D53" t="s">
+        <v>255</v>
+      </c>
+      <c r="E53" t="s">
+        <v>407</v>
+      </c>
+      <c r="F53" t="s">
+        <v>309</v>
+      </c>
+      <c r="G53" t="s">
         <v>408</v>
       </c>
-      <c r="C53" t="s">
-        <v>256</v>
-      </c>
-      <c r="D53" t="s">
-        <v>257</v>
-      </c>
-      <c r="E53" t="s">
+      <c r="H53" t="s">
         <v>409</v>
-      </c>
-      <c r="F53" t="s">
-        <v>311</v>
-      </c>
-      <c r="G53" t="s">
-        <v>410</v>
-      </c>
-      <c r="H53" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
@@ -4391,25 +4391,25 @@
         <v>23</v>
       </c>
       <c r="B54" t="s">
+        <v>410</v>
+      </c>
+      <c r="C54" t="s">
+        <v>411</v>
+      </c>
+      <c r="D54" t="s">
+        <v>191</v>
+      </c>
+      <c r="E54" t="s">
         <v>412</v>
       </c>
-      <c r="C54" t="s">
+      <c r="F54" t="s">
+        <v>383</v>
+      </c>
+      <c r="G54" t="s">
         <v>413</v>
       </c>
-      <c r="D54" t="s">
-        <v>193</v>
-      </c>
-      <c r="E54" t="s">
+      <c r="H54" t="s">
         <v>414</v>
-      </c>
-      <c r="F54" t="s">
-        <v>385</v>
-      </c>
-      <c r="G54" t="s">
-        <v>415</v>
-      </c>
-      <c r="H54" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
@@ -4417,25 +4417,25 @@
         <v>33</v>
       </c>
       <c r="B55" t="s">
+        <v>415</v>
+      </c>
+      <c r="C55" t="s">
+        <v>416</v>
+      </c>
+      <c r="D55" t="s">
+        <v>198</v>
+      </c>
+      <c r="E55" t="s">
         <v>417</v>
       </c>
-      <c r="C55" t="s">
+      <c r="F55" t="s">
         <v>418</v>
       </c>
-      <c r="D55" t="s">
-        <v>200</v>
-      </c>
-      <c r="E55" t="s">
+      <c r="G55" t="s">
         <v>419</v>
       </c>
-      <c r="F55" t="s">
+      <c r="H55" t="s">
         <v>420</v>
-      </c>
-      <c r="G55" t="s">
-        <v>421</v>
-      </c>
-      <c r="H55" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
@@ -4443,25 +4443,25 @@
         <v>105</v>
       </c>
       <c r="B56" t="s">
+        <v>421</v>
+      </c>
+      <c r="C56" t="s">
+        <v>422</v>
+      </c>
+      <c r="D56" t="s">
+        <v>261</v>
+      </c>
+      <c r="E56" t="s">
         <v>423</v>
       </c>
-      <c r="C56" t="s">
+      <c r="F56" t="s">
         <v>424</v>
       </c>
-      <c r="D56" t="s">
-        <v>263</v>
-      </c>
-      <c r="E56" t="s">
+      <c r="G56" t="s">
         <v>425</v>
       </c>
-      <c r="F56" t="s">
+      <c r="H56" t="s">
         <v>426</v>
-      </c>
-      <c r="G56" t="s">
-        <v>427</v>
-      </c>
-      <c r="H56" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
@@ -4469,25 +4469,25 @@
         <v>106</v>
       </c>
       <c r="B57" t="s">
+        <v>427</v>
+      </c>
+      <c r="C57" t="s">
+        <v>428</v>
+      </c>
+      <c r="D57" t="s">
+        <v>134</v>
+      </c>
+      <c r="E57" t="s">
         <v>429</v>
       </c>
-      <c r="C57" t="s">
+      <c r="F57" t="s">
         <v>430</v>
       </c>
-      <c r="D57" t="s">
-        <v>135</v>
-      </c>
-      <c r="E57" t="s">
+      <c r="G57" t="s">
         <v>431</v>
       </c>
-      <c r="F57" t="s">
+      <c r="H57" t="s">
         <v>432</v>
-      </c>
-      <c r="G57" t="s">
-        <v>433</v>
-      </c>
-      <c r="H57" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -4495,25 +4495,25 @@
         <v>96</v>
       </c>
       <c r="B58" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="C58" t="s">
+        <v>133</v>
+      </c>
+      <c r="D58" t="s">
         <v>134</v>
       </c>
-      <c r="D58" t="s">
-        <v>135</v>
-      </c>
       <c r="E58" t="s">
+        <v>433</v>
+      </c>
+      <c r="F58" t="s">
+        <v>434</v>
+      </c>
+      <c r="G58" t="s">
         <v>435</v>
       </c>
-      <c r="F58" t="s">
+      <c r="H58" t="s">
         <v>436</v>
-      </c>
-      <c r="G58" t="s">
-        <v>437</v>
-      </c>
-      <c r="H58" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
@@ -4521,25 +4521,25 @@
         <v>13</v>
       </c>
       <c r="B59" t="s">
+        <v>437</v>
+      </c>
+      <c r="C59" t="s">
+        <v>145</v>
+      </c>
+      <c r="D59" t="s">
+        <v>134</v>
+      </c>
+      <c r="E59" t="s">
+        <v>438</v>
+      </c>
+      <c r="F59" t="s">
         <v>439</v>
       </c>
-      <c r="C59" t="s">
-        <v>146</v>
-      </c>
-      <c r="D59" t="s">
-        <v>135</v>
-      </c>
-      <c r="E59" t="s">
+      <c r="G59" t="s">
         <v>440</v>
       </c>
-      <c r="F59" t="s">
+      <c r="H59" t="s">
         <v>441</v>
-      </c>
-      <c r="G59" t="s">
-        <v>442</v>
-      </c>
-      <c r="H59" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
@@ -4547,25 +4547,25 @@
         <v>73</v>
       </c>
       <c r="B60" t="s">
+        <v>442</v>
+      </c>
+      <c r="C60" t="s">
+        <v>443</v>
+      </c>
+      <c r="D60" t="s">
+        <v>293</v>
+      </c>
+      <c r="E60" t="s">
         <v>444</v>
       </c>
-      <c r="C60" t="s">
+      <c r="F60" t="s">
         <v>445</v>
       </c>
-      <c r="D60" t="s">
-        <v>295</v>
-      </c>
-      <c r="E60" t="s">
+      <c r="G60" t="s">
         <v>446</v>
       </c>
-      <c r="F60" t="s">
+      <c r="H60" t="s">
         <v>447</v>
-      </c>
-      <c r="G60" t="s">
-        <v>448</v>
-      </c>
-      <c r="H60" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
@@ -4573,25 +4573,25 @@
         <v>64</v>
       </c>
       <c r="B61" t="s">
+        <v>448</v>
+      </c>
+      <c r="C61" t="s">
+        <v>204</v>
+      </c>
+      <c r="D61" t="s">
+        <v>211</v>
+      </c>
+      <c r="E61" t="s">
+        <v>449</v>
+      </c>
+      <c r="F61" t="s">
         <v>450</v>
       </c>
-      <c r="C61" t="s">
-        <v>206</v>
-      </c>
-      <c r="D61" t="s">
-        <v>213</v>
-      </c>
-      <c r="E61" t="s">
+      <c r="G61" t="s">
         <v>451</v>
       </c>
-      <c r="F61" t="s">
+      <c r="H61" t="s">
         <v>452</v>
-      </c>
-      <c r="G61" t="s">
-        <v>453</v>
-      </c>
-      <c r="H61" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
@@ -4599,25 +4599,25 @@
         <v>25</v>
       </c>
       <c r="B62" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C62" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D62" t="s">
         <v>128</v>
       </c>
       <c r="E62" t="s">
+        <v>454</v>
+      </c>
+      <c r="F62" t="s">
+        <v>455</v>
+      </c>
+      <c r="G62" t="s">
         <v>456</v>
       </c>
-      <c r="F62" t="s">
+      <c r="H62" t="s">
         <v>457</v>
-      </c>
-      <c r="G62" t="s">
-        <v>458</v>
-      </c>
-      <c r="H62" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
@@ -4625,25 +4625,25 @@
         <v>114</v>
       </c>
       <c r="B63" t="s">
+        <v>458</v>
+      </c>
+      <c r="C63" t="s">
+        <v>459</v>
+      </c>
+      <c r="D63" t="s">
+        <v>134</v>
+      </c>
+      <c r="E63" t="s">
         <v>460</v>
       </c>
-      <c r="C63" t="s">
+      <c r="F63" t="s">
         <v>461</v>
       </c>
-      <c r="D63" t="s">
-        <v>135</v>
-      </c>
-      <c r="E63" t="s">
+      <c r="G63" t="s">
         <v>462</v>
       </c>
-      <c r="F63" t="s">
+      <c r="H63" t="s">
         <v>463</v>
-      </c>
-      <c r="G63" t="s">
-        <v>464</v>
-      </c>
-      <c r="H63" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
@@ -4651,25 +4651,25 @@
         <v>29</v>
       </c>
       <c r="B64" t="s">
+        <v>464</v>
+      </c>
+      <c r="C64" t="s">
+        <v>465</v>
+      </c>
+      <c r="D64" t="s">
+        <v>191</v>
+      </c>
+      <c r="E64" t="s">
         <v>466</v>
       </c>
-      <c r="C64" t="s">
+      <c r="F64" t="s">
         <v>467</v>
       </c>
-      <c r="D64" t="s">
-        <v>193</v>
-      </c>
-      <c r="E64" t="s">
+      <c r="G64" t="s">
         <v>468</v>
       </c>
-      <c r="F64" t="s">
+      <c r="H64" t="s">
         <v>469</v>
-      </c>
-      <c r="G64" t="s">
-        <v>470</v>
-      </c>
-      <c r="H64" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
@@ -4677,25 +4677,25 @@
         <v>35</v>
       </c>
       <c r="B65" t="s">
+        <v>470</v>
+      </c>
+      <c r="C65" t="s">
+        <v>471</v>
+      </c>
+      <c r="D65" t="s">
+        <v>198</v>
+      </c>
+      <c r="E65" t="s">
         <v>472</v>
       </c>
-      <c r="C65" t="s">
+      <c r="F65" t="s">
         <v>473</v>
       </c>
-      <c r="D65" t="s">
-        <v>200</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="G65" t="s">
         <v>474</v>
       </c>
-      <c r="F65" t="s">
+      <c r="H65" t="s">
         <v>475</v>
-      </c>
-      <c r="G65" t="s">
-        <v>476</v>
-      </c>
-      <c r="H65" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
@@ -4703,25 +4703,25 @@
         <v>36</v>
       </c>
       <c r="B66" t="s">
+        <v>476</v>
+      </c>
+      <c r="C66" t="s">
+        <v>416</v>
+      </c>
+      <c r="D66" t="s">
+        <v>198</v>
+      </c>
+      <c r="E66" t="s">
+        <v>477</v>
+      </c>
+      <c r="F66" t="s">
         <v>478</v>
       </c>
-      <c r="C66" t="s">
-        <v>418</v>
-      </c>
-      <c r="D66" t="s">
-        <v>200</v>
-      </c>
-      <c r="E66" t="s">
+      <c r="G66" t="s">
         <v>479</v>
       </c>
-      <c r="F66" t="s">
+      <c r="H66" t="s">
         <v>480</v>
-      </c>
-      <c r="G66" t="s">
-        <v>481</v>
-      </c>
-      <c r="H66" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
@@ -4729,25 +4729,25 @@
         <v>12</v>
       </c>
       <c r="B67" t="s">
+        <v>481</v>
+      </c>
+      <c r="C67" t="s">
+        <v>482</v>
+      </c>
+      <c r="D67" t="s">
+        <v>375</v>
+      </c>
+      <c r="E67" t="s">
         <v>483</v>
       </c>
-      <c r="C67" t="s">
+      <c r="F67" t="s">
         <v>484</v>
       </c>
-      <c r="D67" t="s">
-        <v>377</v>
-      </c>
-      <c r="E67" t="s">
+      <c r="G67" t="s">
         <v>485</v>
       </c>
-      <c r="F67" t="s">
+      <c r="H67" t="s">
         <v>486</v>
-      </c>
-      <c r="G67" t="s">
-        <v>487</v>
-      </c>
-      <c r="H67" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
@@ -4755,25 +4755,25 @@
         <v>39</v>
       </c>
       <c r="B68" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="C68" t="s">
+        <v>487</v>
+      </c>
+      <c r="D68" t="s">
+        <v>261</v>
+      </c>
+      <c r="E68" t="s">
+        <v>488</v>
+      </c>
+      <c r="F68" t="s">
         <v>489</v>
       </c>
-      <c r="D68" t="s">
-        <v>263</v>
-      </c>
-      <c r="E68" t="s">
+      <c r="G68" t="s">
         <v>490</v>
       </c>
-      <c r="F68" t="s">
+      <c r="H68" t="s">
         <v>491</v>
-      </c>
-      <c r="G68" t="s">
-        <v>492</v>
-      </c>
-      <c r="H68" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
@@ -4781,25 +4781,25 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>492</v>
+      </c>
+      <c r="C69" t="s">
+        <v>493</v>
+      </c>
+      <c r="D69" t="s">
+        <v>375</v>
+      </c>
+      <c r="E69" t="s">
         <v>494</v>
       </c>
-      <c r="C69" t="s">
+      <c r="F69" t="s">
         <v>495</v>
       </c>
-      <c r="D69" t="s">
-        <v>377</v>
-      </c>
-      <c r="E69" t="s">
+      <c r="G69" t="s">
         <v>496</v>
       </c>
-      <c r="F69" t="s">
+      <c r="H69" t="s">
         <v>497</v>
-      </c>
-      <c r="G69" t="s">
-        <v>498</v>
-      </c>
-      <c r="H69" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
@@ -4807,25 +4807,25 @@
         <v>62</v>
       </c>
       <c r="B70" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C70" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D70" t="s">
         <v>128</v>
       </c>
       <c r="E70" t="s">
+        <v>499</v>
+      </c>
+      <c r="F70" t="s">
+        <v>500</v>
+      </c>
+      <c r="G70" t="s">
         <v>501</v>
       </c>
-      <c r="F70" t="s">
+      <c r="H70" t="s">
         <v>502</v>
-      </c>
-      <c r="G70" t="s">
-        <v>503</v>
-      </c>
-      <c r="H70" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
@@ -4833,25 +4833,25 @@
         <v>116</v>
       </c>
       <c r="B71" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="C71" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="D71" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E71" t="s">
+        <v>503</v>
+      </c>
+      <c r="F71" t="s">
+        <v>504</v>
+      </c>
+      <c r="G71" t="s">
         <v>505</v>
       </c>
-      <c r="F71" t="s">
+      <c r="H71" t="s">
         <v>506</v>
-      </c>
-      <c r="G71" t="s">
-        <v>507</v>
-      </c>
-      <c r="H71" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
@@ -4859,25 +4859,25 @@
         <v>37</v>
       </c>
       <c r="B72" t="s">
+        <v>507</v>
+      </c>
+      <c r="C72" t="s">
+        <v>508</v>
+      </c>
+      <c r="D72" t="s">
+        <v>191</v>
+      </c>
+      <c r="E72" t="s">
         <v>509</v>
       </c>
-      <c r="C72" t="s">
+      <c r="F72" t="s">
         <v>510</v>
       </c>
-      <c r="D72" t="s">
-        <v>193</v>
-      </c>
-      <c r="E72" t="s">
+      <c r="G72" t="s">
         <v>511</v>
       </c>
-      <c r="F72" t="s">
+      <c r="H72" t="s">
         <v>512</v>
-      </c>
-      <c r="G72" t="s">
-        <v>513</v>
-      </c>
-      <c r="H72" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
@@ -4885,25 +4885,25 @@
         <v>41</v>
       </c>
       <c r="B73" t="s">
+        <v>513</v>
+      </c>
+      <c r="C73" t="s">
+        <v>514</v>
+      </c>
+      <c r="D73" t="s">
+        <v>185</v>
+      </c>
+      <c r="E73" t="s">
         <v>515</v>
       </c>
-      <c r="C73" t="s">
+      <c r="F73" t="s">
         <v>516</v>
       </c>
-      <c r="D73" t="s">
-        <v>186</v>
-      </c>
-      <c r="E73" t="s">
+      <c r="G73" t="s">
         <v>517</v>
       </c>
-      <c r="F73" t="s">
+      <c r="H73" t="s">
         <v>518</v>
-      </c>
-      <c r="G73" t="s">
-        <v>519</v>
-      </c>
-      <c r="H73" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
@@ -4911,25 +4911,25 @@
         <v>111</v>
       </c>
       <c r="B74" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="C74" t="s">
+        <v>519</v>
+      </c>
+      <c r="D74" t="s">
+        <v>134</v>
+      </c>
+      <c r="E74" t="s">
+        <v>520</v>
+      </c>
+      <c r="F74" t="s">
         <v>521</v>
       </c>
-      <c r="D74" t="s">
-        <v>135</v>
-      </c>
-      <c r="E74" t="s">
+      <c r="G74" t="s">
         <v>522</v>
       </c>
-      <c r="F74" t="s">
+      <c r="H74" t="s">
         <v>523</v>
-      </c>
-      <c r="G74" t="s">
-        <v>524</v>
-      </c>
-      <c r="H74" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
@@ -4937,25 +4937,25 @@
         <v>45</v>
       </c>
       <c r="B75" t="s">
+        <v>524</v>
+      </c>
+      <c r="C75" t="s">
+        <v>658</v>
+      </c>
+      <c r="D75" t="s">
+        <v>375</v>
+      </c>
+      <c r="E75" t="s">
+        <v>525</v>
+      </c>
+      <c r="F75" t="s">
         <v>526</v>
       </c>
-      <c r="C75" t="s">
-        <v>661</v>
-      </c>
-      <c r="D75" t="s">
-        <v>377</v>
-      </c>
-      <c r="E75" t="s">
+      <c r="G75" t="s">
         <v>527</v>
       </c>
-      <c r="F75" t="s">
+      <c r="H75" t="s">
         <v>528</v>
-      </c>
-      <c r="G75" t="s">
-        <v>529</v>
-      </c>
-      <c r="H75" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
@@ -4963,25 +4963,25 @@
         <v>49</v>
       </c>
       <c r="B76" t="s">
+        <v>529</v>
+      </c>
+      <c r="C76" t="s">
+        <v>530</v>
+      </c>
+      <c r="D76" t="s">
+        <v>191</v>
+      </c>
+      <c r="E76" t="s">
         <v>531</v>
       </c>
-      <c r="C76" t="s">
+      <c r="F76" t="s">
         <v>532</v>
       </c>
-      <c r="D76" t="s">
-        <v>193</v>
-      </c>
-      <c r="E76" t="s">
+      <c r="G76" t="s">
         <v>533</v>
       </c>
-      <c r="F76" t="s">
+      <c r="H76" t="s">
         <v>534</v>
-      </c>
-      <c r="G76" t="s">
-        <v>535</v>
-      </c>
-      <c r="H76" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
@@ -4989,25 +4989,25 @@
         <v>65</v>
       </c>
       <c r="B77" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C77" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D77" t="s">
         <v>128</v>
       </c>
       <c r="E77" t="s">
+        <v>536</v>
+      </c>
+      <c r="F77" t="s">
+        <v>537</v>
+      </c>
+      <c r="G77" t="s">
         <v>538</v>
       </c>
-      <c r="F77" t="s">
+      <c r="H77" t="s">
         <v>539</v>
-      </c>
-      <c r="G77" t="s">
-        <v>540</v>
-      </c>
-      <c r="H77" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
@@ -5015,25 +5015,25 @@
         <v>119</v>
       </c>
       <c r="B78" t="s">
+        <v>540</v>
+      </c>
+      <c r="C78" t="s">
+        <v>541</v>
+      </c>
+      <c r="D78" t="s">
+        <v>134</v>
+      </c>
+      <c r="E78" t="s">
         <v>542</v>
       </c>
-      <c r="C78" t="s">
+      <c r="F78" t="s">
         <v>543</v>
       </c>
-      <c r="D78" t="s">
-        <v>135</v>
-      </c>
-      <c r="E78" t="s">
+      <c r="G78" t="s">
         <v>544</v>
       </c>
-      <c r="F78" t="s">
+      <c r="H78" t="s">
         <v>545</v>
-      </c>
-      <c r="G78" t="s">
-        <v>546</v>
-      </c>
-      <c r="H78" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
@@ -5041,25 +5041,25 @@
         <v>47</v>
       </c>
       <c r="B79" t="s">
+        <v>546</v>
+      </c>
+      <c r="C79" t="s">
+        <v>239</v>
+      </c>
+      <c r="D79" t="s">
+        <v>134</v>
+      </c>
+      <c r="E79" t="s">
+        <v>547</v>
+      </c>
+      <c r="F79" t="s">
         <v>548</v>
       </c>
-      <c r="C79" t="s">
-        <v>241</v>
-      </c>
-      <c r="D79" t="s">
-        <v>135</v>
-      </c>
-      <c r="E79" t="s">
+      <c r="G79" t="s">
         <v>549</v>
       </c>
-      <c r="F79" t="s">
+      <c r="H79" t="s">
         <v>550</v>
-      </c>
-      <c r="G79" t="s">
-        <v>551</v>
-      </c>
-      <c r="H79" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
@@ -5067,25 +5067,25 @@
         <v>67</v>
       </c>
       <c r="B80" t="s">
+        <v>705</v>
+      </c>
+      <c r="C80" t="s">
+        <v>551</v>
+      </c>
+      <c r="D80" t="s">
+        <v>134</v>
+      </c>
+      <c r="E80" t="s">
+        <v>552</v>
+      </c>
+      <c r="F80" t="s">
         <v>553</v>
       </c>
-      <c r="C80" t="s">
+      <c r="G80" t="s">
         <v>554</v>
       </c>
-      <c r="D80" t="s">
-        <v>135</v>
-      </c>
-      <c r="E80" t="s">
+      <c r="H80" t="s">
         <v>555</v>
-      </c>
-      <c r="F80" t="s">
-        <v>556</v>
-      </c>
-      <c r="G80" t="s">
-        <v>557</v>
-      </c>
-      <c r="H80" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
@@ -5093,25 +5093,25 @@
         <v>117</v>
       </c>
       <c r="B81" t="s">
+        <v>556</v>
+      </c>
+      <c r="C81" t="s">
+        <v>459</v>
+      </c>
+      <c r="D81" t="s">
+        <v>134</v>
+      </c>
+      <c r="E81" t="s">
+        <v>552</v>
+      </c>
+      <c r="F81" t="s">
+        <v>557</v>
+      </c>
+      <c r="G81" t="s">
+        <v>558</v>
+      </c>
+      <c r="H81" t="s">
         <v>559</v>
-      </c>
-      <c r="C81" t="s">
-        <v>461</v>
-      </c>
-      <c r="D81" t="s">
-        <v>135</v>
-      </c>
-      <c r="E81" t="s">
-        <v>555</v>
-      </c>
-      <c r="F81" t="s">
-        <v>560</v>
-      </c>
-      <c r="G81" t="s">
-        <v>561</v>
-      </c>
-      <c r="H81" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
@@ -5119,25 +5119,25 @@
         <v>120</v>
       </c>
       <c r="B82" t="s">
+        <v>560</v>
+      </c>
+      <c r="C82" t="s">
+        <v>374</v>
+      </c>
+      <c r="D82" t="s">
+        <v>375</v>
+      </c>
+      <c r="E82" t="s">
+        <v>561</v>
+      </c>
+      <c r="F82" t="s">
+        <v>562</v>
+      </c>
+      <c r="G82" t="s">
         <v>563</v>
       </c>
-      <c r="C82" t="s">
-        <v>376</v>
-      </c>
-      <c r="D82" t="s">
-        <v>377</v>
-      </c>
-      <c r="E82" t="s">
+      <c r="H82" t="s">
         <v>564</v>
-      </c>
-      <c r="F82" t="s">
-        <v>565</v>
-      </c>
-      <c r="G82" t="s">
-        <v>566</v>
-      </c>
-      <c r="H82" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
@@ -5145,25 +5145,25 @@
         <v>48</v>
       </c>
       <c r="B83" t="s">
+        <v>565</v>
+      </c>
+      <c r="C83" t="s">
+        <v>566</v>
+      </c>
+      <c r="D83" t="s">
+        <v>134</v>
+      </c>
+      <c r="E83" t="s">
+        <v>567</v>
+      </c>
+      <c r="F83" t="s">
         <v>568</v>
       </c>
-      <c r="C83" t="s">
+      <c r="G83" t="s">
         <v>569</v>
       </c>
-      <c r="D83" t="s">
-        <v>135</v>
-      </c>
-      <c r="E83" t="s">
+      <c r="H83" t="s">
         <v>570</v>
-      </c>
-      <c r="F83" t="s">
-        <v>571</v>
-      </c>
-      <c r="G83" t="s">
-        <v>572</v>
-      </c>
-      <c r="H83" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
@@ -5171,25 +5171,25 @@
         <v>53</v>
       </c>
       <c r="B84" t="s">
+        <v>571</v>
+      </c>
+      <c r="C84" t="s">
+        <v>572</v>
+      </c>
+      <c r="D84" t="s">
+        <v>375</v>
+      </c>
+      <c r="E84" t="s">
+        <v>573</v>
+      </c>
+      <c r="F84" t="s">
         <v>574</v>
       </c>
-      <c r="C84" t="s">
+      <c r="G84" t="s">
         <v>575</v>
       </c>
-      <c r="D84" t="s">
-        <v>377</v>
-      </c>
-      <c r="E84" t="s">
+      <c r="H84" t="s">
         <v>576</v>
-      </c>
-      <c r="F84" t="s">
-        <v>577</v>
-      </c>
-      <c r="G84" t="s">
-        <v>578</v>
-      </c>
-      <c r="H84" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
@@ -5197,25 +5197,25 @@
         <v>28</v>
       </c>
       <c r="B85" t="s">
+        <v>577</v>
+      </c>
+      <c r="C85" t="s">
+        <v>578</v>
+      </c>
+      <c r="D85" t="s">
+        <v>255</v>
+      </c>
+      <c r="E85" t="s">
+        <v>579</v>
+      </c>
+      <c r="F85" t="s">
         <v>580</v>
       </c>
-      <c r="C85" t="s">
+      <c r="G85" t="s">
         <v>581</v>
       </c>
-      <c r="D85" t="s">
-        <v>257</v>
-      </c>
-      <c r="E85" t="s">
+      <c r="H85" t="s">
         <v>582</v>
-      </c>
-      <c r="F85" t="s">
-        <v>583</v>
-      </c>
-      <c r="G85" t="s">
-        <v>584</v>
-      </c>
-      <c r="H85" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
@@ -5223,25 +5223,25 @@
         <v>34</v>
       </c>
       <c r="B86" t="s">
+        <v>583</v>
+      </c>
+      <c r="C86" t="s">
+        <v>465</v>
+      </c>
+      <c r="D86" t="s">
+        <v>191</v>
+      </c>
+      <c r="E86" t="s">
+        <v>584</v>
+      </c>
+      <c r="F86" t="s">
+        <v>585</v>
+      </c>
+      <c r="G86" t="s">
         <v>586</v>
       </c>
-      <c r="C86" t="s">
-        <v>467</v>
-      </c>
-      <c r="D86" t="s">
-        <v>193</v>
-      </c>
-      <c r="E86" t="s">
+      <c r="H86" t="s">
         <v>587</v>
-      </c>
-      <c r="F86" t="s">
-        <v>588</v>
-      </c>
-      <c r="G86" t="s">
-        <v>589</v>
-      </c>
-      <c r="H86" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
@@ -5249,25 +5249,25 @@
         <v>63</v>
       </c>
       <c r="B87" t="s">
+        <v>588</v>
+      </c>
+      <c r="C87" t="s">
+        <v>313</v>
+      </c>
+      <c r="D87" t="s">
+        <v>134</v>
+      </c>
+      <c r="E87" t="s">
+        <v>589</v>
+      </c>
+      <c r="F87" t="s">
+        <v>590</v>
+      </c>
+      <c r="G87" t="s">
         <v>591</v>
       </c>
-      <c r="C87" t="s">
-        <v>315</v>
-      </c>
-      <c r="D87" t="s">
-        <v>135</v>
-      </c>
-      <c r="E87" t="s">
+      <c r="H87" t="s">
         <v>592</v>
-      </c>
-      <c r="F87" t="s">
-        <v>593</v>
-      </c>
-      <c r="G87" t="s">
-        <v>594</v>
-      </c>
-      <c r="H87" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
@@ -5275,25 +5275,25 @@
         <v>72</v>
       </c>
       <c r="B88" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="C88" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D88" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E88" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="F88" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="G88" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="H88" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
@@ -5301,25 +5301,25 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="C89" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="D89" t="s">
         <v>128</v>
       </c>
       <c r="E89" t="s">
+        <v>598</v>
+      </c>
+      <c r="F89" t="s">
+        <v>599</v>
+      </c>
+      <c r="G89" t="s">
+        <v>600</v>
+      </c>
+      <c r="H89" t="s">
         <v>601</v>
-      </c>
-      <c r="F89" t="s">
-        <v>602</v>
-      </c>
-      <c r="G89" t="s">
-        <v>603</v>
-      </c>
-      <c r="H89" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
@@ -5327,25 +5327,25 @@
         <v>38</v>
       </c>
       <c r="B90" t="s">
+        <v>602</v>
+      </c>
+      <c r="C90" t="s">
+        <v>471</v>
+      </c>
+      <c r="D90" t="s">
+        <v>198</v>
+      </c>
+      <c r="E90" t="s">
+        <v>603</v>
+      </c>
+      <c r="F90" t="s">
+        <v>309</v>
+      </c>
+      <c r="G90" t="s">
+        <v>604</v>
+      </c>
+      <c r="H90" t="s">
         <v>605</v>
-      </c>
-      <c r="C90" t="s">
-        <v>473</v>
-      </c>
-      <c r="D90" t="s">
-        <v>200</v>
-      </c>
-      <c r="E90" t="s">
-        <v>606</v>
-      </c>
-      <c r="F90" t="s">
-        <v>311</v>
-      </c>
-      <c r="G90" t="s">
-        <v>607</v>
-      </c>
-      <c r="H90" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
@@ -5353,25 +5353,25 @@
         <v>97</v>
       </c>
       <c r="B91" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C91" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="D91" t="s">
         <v>128</v>
       </c>
       <c r="E91" t="s">
+        <v>607</v>
+      </c>
+      <c r="F91" t="s">
+        <v>608</v>
+      </c>
+      <c r="G91" t="s">
+        <v>609</v>
+      </c>
+      <c r="H91" t="s">
         <v>610</v>
-      </c>
-      <c r="F91" t="s">
-        <v>611</v>
-      </c>
-      <c r="G91" t="s">
-        <v>612</v>
-      </c>
-      <c r="H91" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
@@ -5379,25 +5379,25 @@
         <v>54</v>
       </c>
       <c r="B92" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="C92" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D92" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E92" t="s">
+        <v>611</v>
+      </c>
+      <c r="F92" t="s">
+        <v>612</v>
+      </c>
+      <c r="G92" t="s">
+        <v>613</v>
+      </c>
+      <c r="H92" t="s">
         <v>614</v>
-      </c>
-      <c r="F92" t="s">
-        <v>615</v>
-      </c>
-      <c r="G92" t="s">
-        <v>616</v>
-      </c>
-      <c r="H92" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
@@ -5405,25 +5405,25 @@
         <v>40</v>
       </c>
       <c r="B93" t="s">
+        <v>615</v>
+      </c>
+      <c r="C93" t="s">
+        <v>508</v>
+      </c>
+      <c r="D93" t="s">
+        <v>191</v>
+      </c>
+      <c r="E93" t="s">
+        <v>616</v>
+      </c>
+      <c r="F93" t="s">
+        <v>430</v>
+      </c>
+      <c r="G93" t="s">
+        <v>617</v>
+      </c>
+      <c r="H93" t="s">
         <v>618</v>
-      </c>
-      <c r="C93" t="s">
-        <v>510</v>
-      </c>
-      <c r="D93" t="s">
-        <v>193</v>
-      </c>
-      <c r="E93" t="s">
-        <v>619</v>
-      </c>
-      <c r="F93" t="s">
-        <v>432</v>
-      </c>
-      <c r="G93" t="s">
-        <v>620</v>
-      </c>
-      <c r="H93" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
@@ -5431,25 +5431,25 @@
         <v>26</v>
       </c>
       <c r="B94" t="s">
+        <v>619</v>
+      </c>
+      <c r="C94" t="s">
+        <v>411</v>
+      </c>
+      <c r="D94" t="s">
+        <v>191</v>
+      </c>
+      <c r="E94" t="s">
+        <v>620</v>
+      </c>
+      <c r="F94" t="s">
+        <v>621</v>
+      </c>
+      <c r="G94" t="s">
         <v>622</v>
       </c>
-      <c r="C94" t="s">
-        <v>413</v>
-      </c>
-      <c r="D94" t="s">
-        <v>193</v>
-      </c>
-      <c r="E94" t="s">
+      <c r="H94" t="s">
         <v>623</v>
-      </c>
-      <c r="F94" t="s">
-        <v>624</v>
-      </c>
-      <c r="G94" t="s">
-        <v>625</v>
-      </c>
-      <c r="H94" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
@@ -5457,25 +5457,25 @@
         <v>86</v>
       </c>
       <c r="B95" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="C95" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D95" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E95" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="F95" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="G95" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="H95" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
@@ -5483,25 +5483,25 @@
         <v>57</v>
       </c>
       <c r="B96" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="C96" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D96" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E96" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="F96" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="G96" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="H96" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
@@ -5509,25 +5509,25 @@
         <v>104</v>
       </c>
       <c r="B97" t="s">
+        <v>630</v>
+      </c>
+      <c r="C97" t="s">
+        <v>631</v>
+      </c>
+      <c r="D97" t="s">
+        <v>198</v>
+      </c>
+      <c r="E97" t="s">
+        <v>632</v>
+      </c>
+      <c r="F97" t="s">
         <v>633</v>
       </c>
-      <c r="C97" t="s">
+      <c r="G97" t="s">
         <v>634</v>
       </c>
-      <c r="D97" t="s">
-        <v>200</v>
-      </c>
-      <c r="E97" t="s">
+      <c r="H97" t="s">
         <v>635</v>
-      </c>
-      <c r="F97" t="s">
-        <v>636</v>
-      </c>
-      <c r="G97" t="s">
-        <v>637</v>
-      </c>
-      <c r="H97" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
@@ -5535,25 +5535,25 @@
         <v>75</v>
       </c>
       <c r="B98" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="C98" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D98" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E98" t="s">
+        <v>636</v>
+      </c>
+      <c r="F98" t="s">
+        <v>637</v>
+      </c>
+      <c r="G98" t="s">
+        <v>638</v>
+      </c>
+      <c r="H98" t="s">
         <v>639</v>
-      </c>
-      <c r="F98" t="s">
-        <v>640</v>
-      </c>
-      <c r="G98" t="s">
-        <v>641</v>
-      </c>
-      <c r="H98" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
@@ -5561,25 +5561,25 @@
         <v>109</v>
       </c>
       <c r="B99" t="s">
+        <v>640</v>
+      </c>
+      <c r="C99" t="s">
+        <v>641</v>
+      </c>
+      <c r="D99" t="s">
+        <v>375</v>
+      </c>
+      <c r="E99" t="s">
+        <v>642</v>
+      </c>
+      <c r="F99" t="s">
         <v>643</v>
       </c>
-      <c r="C99" t="s">
+      <c r="G99" t="s">
         <v>644</v>
       </c>
-      <c r="D99" t="s">
-        <v>377</v>
-      </c>
-      <c r="E99" t="s">
+      <c r="H99" t="s">
         <v>645</v>
-      </c>
-      <c r="F99" t="s">
-        <v>646</v>
-      </c>
-      <c r="G99" t="s">
-        <v>647</v>
-      </c>
-      <c r="H99" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
@@ -5587,25 +5587,25 @@
         <v>15</v>
       </c>
       <c r="B100" t="s">
+        <v>646</v>
+      </c>
+      <c r="C100" t="s">
+        <v>647</v>
+      </c>
+      <c r="D100" t="s">
+        <v>211</v>
+      </c>
+      <c r="E100" t="s">
+        <v>648</v>
+      </c>
+      <c r="F100" t="s">
         <v>649</v>
       </c>
-      <c r="C100" t="s">
+      <c r="G100" t="s">
         <v>650</v>
       </c>
-      <c r="D100" t="s">
-        <v>213</v>
-      </c>
-      <c r="E100" t="s">
+      <c r="H100" t="s">
         <v>651</v>
-      </c>
-      <c r="F100" t="s">
-        <v>652</v>
-      </c>
-      <c r="G100" t="s">
-        <v>653</v>
-      </c>
-      <c r="H100" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
@@ -5613,25 +5613,25 @@
         <v>89</v>
       </c>
       <c r="B101" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="C101" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D101" t="s">
         <v>128</v>
       </c>
       <c r="E101" t="s">
+        <v>653</v>
+      </c>
+      <c r="F101" t="s">
+        <v>654</v>
+      </c>
+      <c r="G101" t="s">
+        <v>655</v>
+      </c>
+      <c r="H101" t="s">
         <v>656</v>
-      </c>
-      <c r="F101" t="s">
-        <v>657</v>
-      </c>
-      <c r="G101" t="s">
-        <v>658</v>
-      </c>
-      <c r="H101" t="s">
-        <v>659</v>
       </c>
     </row>
   </sheetData>
@@ -5790,7 +5790,7 @@
     </row>
     <row r="9" spans="1:13" ht="39" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>12</v>
@@ -5831,7 +5831,7 @@
       </c>
       <c r="L9" s="6" t="str">
         <f>IFERROR(VLOOKUP($J9,Data!$A:$D,2,FALSE),"")</f>
-        <v>On Counting Prime Solutions to Quadratic Forms via the Hardy-Littlewood Circle Method</v>
+        <v>Counting Prime Solutions to Quadratic Forms</v>
       </c>
       <c r="M9" s="6" t="str">
         <f>IFERROR(VLOOKUP($J9,Data!$A:$D,3,FALSE),"")</f>
@@ -5840,7 +5840,7 @@
     </row>
     <row r="10" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>15</v>
@@ -5890,7 +5890,7 @@
     </row>
     <row r="11" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>18</v>
@@ -5940,7 +5940,7 @@
     </row>
     <row r="12" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>21</v>
@@ -5990,7 +5990,7 @@
     </row>
     <row r="13" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>24</v>
@@ -6040,7 +6040,7 @@
     </row>
     <row r="14" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>27</v>
@@ -6185,7 +6185,7 @@
     </row>
     <row r="19" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>32</v>
@@ -6235,7 +6235,7 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>35</v>
@@ -6285,7 +6285,7 @@
     </row>
     <row r="21" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>38</v>
@@ -6335,7 +6335,7 @@
     </row>
     <row r="22" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>41</v>
@@ -6385,7 +6385,7 @@
     </row>
     <row r="23" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>44</v>
@@ -6435,7 +6435,7 @@
     </row>
     <row r="24" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>47</v>
@@ -6580,7 +6580,7 @@
     </row>
     <row r="29" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>52</v>
@@ -6630,7 +6630,7 @@
     </row>
     <row r="30" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>55</v>
@@ -6680,7 +6680,7 @@
     </row>
     <row r="31" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>58</v>
@@ -6730,7 +6730,7 @@
     </row>
     <row r="32" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>61</v>
@@ -6780,7 +6780,7 @@
     </row>
     <row r="33" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>64</v>
@@ -6830,7 +6830,7 @@
     </row>
     <row r="34" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>75</v>
@@ -6975,7 +6975,7 @@
     </row>
     <row r="39" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>72</v>
@@ -7025,7 +7025,7 @@
     </row>
     <row r="40" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>67</v>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="D40" s="6" t="str">
         <f>IFERROR(VLOOKUP($B40,Data!$A:$D,2,FALSE),"")</f>
-        <v>Computational and mathematical modeling of cellular dynamics in hydrogels to optimize large-scale bioprinting</v>
+        <v>Computational and Mathematical Modeling of Cellular Dynamics in Hydrogels to Optimize Large-Scale Bioprinting</v>
       </c>
       <c r="E40" s="6" t="str">
         <f>IFERROR(VLOOKUP($B40,Data!$A:$D,3,FALSE),"")</f>
@@ -7075,7 +7075,7 @@
     </row>
     <row r="41" spans="1:13" ht="39" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>78</v>
@@ -7125,7 +7125,7 @@
     </row>
     <row r="42" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>81</v>
@@ -7175,7 +7175,7 @@
     </row>
     <row r="43" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>84</v>
@@ -7225,7 +7225,7 @@
     </row>
     <row r="44" spans="1:13" ht="39" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>87</v>
@@ -7370,7 +7370,7 @@
     </row>
     <row r="51" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>92</v>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="H51" s="6" t="str">
         <f>IFERROR(VLOOKUP($F51,Data!$A:$D,2,FALSE),"")</f>
-        <v>Optimization of a Yeast-Based High-Throughput Screening Platform to Identify PfPDEγ Inhibitor Candidates</v>
+        <v>Optimization of a Yeast-Based High-Throughput Screening Platform to Detect Small-Molecule Modulators of PfPDE𝛄  for Antimalarial Drug Discovery</v>
       </c>
       <c r="I51" s="6" t="str">
         <f>IFERROR(VLOOKUP($F51,Data!$A:$D,3,FALSE),"")</f>
@@ -7420,7 +7420,7 @@
     </row>
     <row r="52" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>95</v>
@@ -7470,7 +7470,7 @@
     </row>
     <row r="53" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>98</v>
@@ -7520,7 +7520,7 @@
     </row>
     <row r="54" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>101</v>
@@ -7570,7 +7570,7 @@
     </row>
     <row r="55" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>104</v>
@@ -7620,7 +7620,7 @@
     </row>
     <row r="56" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>107</v>
@@ -7765,7 +7765,7 @@
     </row>
     <row r="61" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>111</v>
@@ -7815,7 +7815,7 @@
     </row>
     <row r="62" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>114</v>
@@ -7865,7 +7865,7 @@
     </row>
     <row r="63" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>117</v>
@@ -7913,7 +7913,7 @@
     </row>
     <row r="64" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>119</v>

--- a/RSI_2026_Schedule.xlsx
+++ b/RSI_2026_Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/evanlim/Documents/rsi-symposium/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F1B4BB-94C9-BA4E-B583-CE1FED2672F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C7DC23-471A-984A-842A-11702BF690D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2142,9 +2142,6 @@
     <t>4:30 PM – 4:45 PM</t>
   </si>
   <si>
-    <t>Effect of ZAP70 Mutations on CAR T-Cell effectiveness Targeting GD2 in Cancer Cells</t>
-  </si>
-  <si>
     <t>S-Flow: Harnessing Informed Sampling for Flow Models in Perturbation-Aware Quantum State Tomography</t>
   </si>
   <si>
@@ -2155,6 +2152,9 @@
   </si>
   <si>
     <t>Computational and Mathematical Modeling of Cellular Dynamics in Hydrogels to Optimize Large-Scale Bioprinting</t>
+  </si>
+  <si>
+    <t>Effect of ZAP70 Mutations on CAR T-Cell Effectiveness Targeting GD2 in Cancer Cells</t>
   </si>
 </sst>
 </file>
@@ -3065,7 +3065,7 @@
         <v>93</v>
       </c>
       <c r="B3" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C3" t="s">
         <v>133</v>
@@ -3325,7 +3325,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C13" t="s">
         <v>190</v>
@@ -3559,7 +3559,7 @@
         <v>44</v>
       </c>
       <c r="B22" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="C22" t="s">
         <v>239</v>
@@ -4833,7 +4833,7 @@
         <v>116</v>
       </c>
       <c r="B71" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C71" t="s">
         <v>665</v>
@@ -5067,7 +5067,7 @@
         <v>67</v>
       </c>
       <c r="B80" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C80" t="s">
         <v>551</v>
@@ -6396,7 +6396,7 @@
       </c>
       <c r="D23" s="6" t="str">
         <f>IFERROR(VLOOKUP($B23,Data!$A:$D,2,FALSE),"")</f>
-        <v>Effect of ZAP70 Mutations on CAR T-Cell effectiveness Targeting GD2 in Cancer Cells</v>
+        <v>Effect of ZAP70 Mutations on CAR T-Cell Effectiveness Targeting GD2 in Cancer Cells</v>
       </c>
       <c r="E23" s="6" t="str">
         <f>IFERROR(VLOOKUP($B23,Data!$A:$D,3,FALSE),"")</f>
